--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -766,39 +766,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128721501</v>
+        <v>128722554</v>
       </c>
       <c r="B3" t="n">
-        <v>88662</v>
+        <v>86927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715178</v>
+        <v>715247</v>
       </c>
       <c r="R3" t="n">
-        <v>6367628</v>
+        <v>6368027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,28 +852,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128721652</v>
+        <v>128722539</v>
       </c>
       <c r="B4" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715207</v>
+        <v>715181</v>
       </c>
       <c r="R4" t="n">
-        <v>6367759</v>
+        <v>6367653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,22 +956,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128721539</v>
+        <v>128722600</v>
       </c>
       <c r="B5" t="n">
-        <v>75115</v>
+        <v>86890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +979,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715289</v>
+        <v>715327</v>
       </c>
       <c r="R5" t="n">
-        <v>6368047</v>
+        <v>6367976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,22 +1053,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128722539</v>
+        <v>128722536</v>
       </c>
       <c r="B6" t="n">
-        <v>86729</v>
+        <v>91239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1076,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1100,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715181</v>
+        <v>715340</v>
       </c>
       <c r="R6" t="n">
-        <v>6367653</v>
+        <v>6367945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1144,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1161,10 +1163,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128722536</v>
+        <v>128721652</v>
       </c>
       <c r="B7" t="n">
-        <v>91239</v>
+        <v>86890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1174,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1198,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715340</v>
+        <v>715207</v>
       </c>
       <c r="R7" t="n">
-        <v>6367945</v>
+        <v>6367759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,51 +1242,50 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128722554</v>
+        <v>128721501</v>
       </c>
       <c r="B8" t="n">
-        <v>86927</v>
+        <v>88662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1294,10 +1295,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715247</v>
+        <v>715178</v>
       </c>
       <c r="R8" t="n">
-        <v>6368027</v>
+        <v>6367628</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,29 +1339,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128722600</v>
+        <v>128721539</v>
       </c>
       <c r="B9" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715327</v>
+        <v>715289</v>
       </c>
       <c r="R9" t="n">
-        <v>6367976</v>
+        <v>6368047</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,12 +1442,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B14" t="n">
-        <v>105627</v>
+        <v>86914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R14" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B15" t="n">
-        <v>86914</v>
+        <v>105629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R15" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,19 +2030,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128721558</v>
+        <v>128721560</v>
       </c>
       <c r="B16" t="n">
         <v>86949</v>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715424</v>
+        <v>715503</v>
       </c>
       <c r="R16" t="n">
-        <v>6367651</v>
+        <v>6367589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,14 +2132,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721560</v>
+        <v>128721559</v>
       </c>
       <c r="B17" t="n">
         <v>86949</v>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715503</v>
+        <v>715505</v>
       </c>
       <c r="R17" t="n">
-        <v>6367589</v>
+        <v>6367598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,32 +2236,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721499</v>
+        <v>128722540</v>
       </c>
       <c r="B18" t="n">
-        <v>86972</v>
+        <v>86729</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715394</v>
+        <v>715194</v>
       </c>
       <c r="R18" t="n">
-        <v>6368208</v>
+        <v>6367837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2315,28 +2315,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721643</v>
+        <v>128721499</v>
       </c>
       <c r="B19" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715270</v>
+        <v>715394</v>
       </c>
       <c r="R19" t="n">
-        <v>6367607</v>
+        <v>6368208</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2418,19 +2419,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128721559</v>
+        <v>128721643</v>
       </c>
       <c r="B20" t="n">
         <v>86949</v>
@@ -2465,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715505</v>
+        <v>715270</v>
       </c>
       <c r="R20" t="n">
-        <v>6367598</v>
+        <v>6367607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2490,7 +2491,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2515,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2617,37 +2618,41 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721554</v>
+        <v>128721558</v>
       </c>
       <c r="B22" t="n">
-        <v>86999</v>
+        <v>86949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>249249</v>
+        <v>449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grynspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius olidoamethysteus s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2655,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715194</v>
+        <v>715424</v>
       </c>
       <c r="R22" t="n">
-        <v>6367904</v>
+        <v>6367651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2685,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2710,17 +2715,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128722534</v>
+        <v>128722582</v>
       </c>
       <c r="B23" t="n">
-        <v>98566</v>
+        <v>92790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,34 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715228</v>
+        <v>715492</v>
       </c>
       <c r="R23" t="n">
-        <v>6367909</v>
+        <v>6367899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2796,6 +2804,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2814,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128722582</v>
+        <v>128722534</v>
       </c>
       <c r="B24" t="n">
-        <v>92790</v>
+        <v>98566</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,37 +2834,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>715492</v>
+        <v>715228</v>
       </c>
       <c r="R24" t="n">
-        <v>6367899</v>
+        <v>6367909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2896,7 +2902,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2915,32 +2920,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128722540</v>
+        <v>128721505</v>
       </c>
       <c r="B25" t="n">
-        <v>86729</v>
+        <v>86775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715194</v>
+        <v>715150</v>
       </c>
       <c r="R25" t="n">
-        <v>6367837</v>
+        <v>6367765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2994,51 +2999,50 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128721543</v>
+        <v>128722567</v>
       </c>
       <c r="B26" t="n">
-        <v>75115</v>
+        <v>86972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715500</v>
+        <v>715339</v>
       </c>
       <c r="R26" t="n">
-        <v>6367588</v>
+        <v>6367894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,7 +3077,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3086,56 +3090,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128721505</v>
+        <v>128722602</v>
       </c>
       <c r="B27" t="n">
-        <v>86775</v>
+        <v>86890</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715150</v>
+        <v>715200</v>
       </c>
       <c r="R27" t="n">
-        <v>6367765</v>
+        <v>6367935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3195,44 +3205,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128722567</v>
+        <v>128721543</v>
       </c>
       <c r="B28" t="n">
-        <v>86972</v>
+        <v>75115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715339</v>
+        <v>715500</v>
       </c>
       <c r="R28" t="n">
-        <v>6367894</v>
+        <v>6367588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3267,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3280,62 +3290,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128722602</v>
+        <v>128721628</v>
       </c>
       <c r="B29" t="n">
-        <v>86890</v>
+        <v>86972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715200</v>
+        <v>715222</v>
       </c>
       <c r="R29" t="n">
-        <v>6367935</v>
+        <v>6367915</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3389,18 +3393,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3504,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128721628</v>
+        <v>128721540</v>
       </c>
       <c r="B31" t="n">
-        <v>86972</v>
+        <v>75115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715222</v>
+        <v>715278</v>
       </c>
       <c r="R31" t="n">
-        <v>6367915</v>
+        <v>6368028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3583,64 +3588,66 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128721540</v>
+        <v>128722518</v>
       </c>
       <c r="B32" t="n">
-        <v>75115</v>
+        <v>86682</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>249278</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715278</v>
+        <v>715536</v>
       </c>
       <c r="R32" t="n">
-        <v>6368028</v>
+        <v>6367906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3681,66 +3688,64 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722518</v>
+        <v>128722608</v>
       </c>
       <c r="B33" t="n">
-        <v>86682</v>
+        <v>86890</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715536</v>
+        <v>715211</v>
       </c>
       <c r="R33" t="n">
-        <v>6367906</v>
+        <v>6367929</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,7 +3786,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3800,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721511</v>
+        <v>128722564</v>
       </c>
       <c r="B34" t="n">
-        <v>91239</v>
+        <v>86914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>3599</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715180</v>
+        <v>715387</v>
       </c>
       <c r="R34" t="n">
-        <v>6367626</v>
+        <v>6367908</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,22 +3889,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128721513</v>
+        <v>128721511</v>
       </c>
       <c r="B35" t="n">
-        <v>86729</v>
+        <v>91239</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3908,21 +3912,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715408</v>
+        <v>715180</v>
       </c>
       <c r="R35" t="n">
-        <v>6368189</v>
+        <v>6367626</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,55 +3991,52 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128722517</v>
+        <v>128721513</v>
       </c>
       <c r="B36" t="n">
-        <v>86682</v>
+        <v>86729</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>249278</v>
+        <v>3762</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715318</v>
+        <v>715408</v>
       </c>
       <c r="R36" t="n">
-        <v>6367974</v>
+        <v>6368189</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4076,51 +4077,50 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722556</v>
+        <v>128722542</v>
       </c>
       <c r="B37" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715180</v>
+        <v>715218</v>
       </c>
       <c r="R37" t="n">
-        <v>6368021</v>
+        <v>6367844</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4174,7 +4174,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4290,10 +4289,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722564</v>
+        <v>128722566</v>
       </c>
       <c r="B39" t="n">
-        <v>86914</v>
+        <v>91001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,21 +4300,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715387</v>
+        <v>715288</v>
       </c>
       <c r="R39" t="n">
-        <v>6367908</v>
+        <v>6367866</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,45 +4386,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722566</v>
+        <v>128722517</v>
       </c>
       <c r="B40" t="n">
-        <v>91001</v>
+        <v>86682</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5747</v>
+        <v>249278</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715288</v>
+        <v>715318</v>
       </c>
       <c r="R40" t="n">
-        <v>6367866</v>
+        <v>6367974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,6 +4468,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4484,32 +4487,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722608</v>
+        <v>128722556</v>
       </c>
       <c r="B41" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4519,10 +4522,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715211</v>
+        <v>715180</v>
       </c>
       <c r="R41" t="n">
-        <v>6367929</v>
+        <v>6368021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4563,6 +4566,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4581,32 +4585,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128722542</v>
+        <v>128721517</v>
       </c>
       <c r="B42" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715218</v>
+        <v>715323</v>
       </c>
       <c r="R42" t="n">
-        <v>6367844</v>
+        <v>6368092</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4660,50 +4664,51 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721577</v>
+        <v>128721631</v>
       </c>
       <c r="B43" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4718,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715221</v>
+        <v>715172</v>
       </c>
       <c r="R43" t="n">
-        <v>6367967</v>
+        <v>6367927</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4757,18 +4762,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4866,39 +4872,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721557</v>
+        <v>128722543</v>
       </c>
       <c r="B45" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4908,10 +4914,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715213</v>
+        <v>715253</v>
       </c>
       <c r="R45" t="n">
-        <v>6367921</v>
+        <v>6367647</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4958,19 +4964,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721653</v>
+        <v>128721577</v>
       </c>
       <c r="B46" t="n">
         <v>86890</v>
@@ -5005,10 +5011,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715476</v>
+        <v>715221</v>
       </c>
       <c r="R46" t="n">
-        <v>6367609</v>
+        <v>6367967</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5030,7 +5036,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5055,44 +5061,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721517</v>
+        <v>128721653</v>
       </c>
       <c r="B47" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5102,10 +5108,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715323</v>
+        <v>715476</v>
       </c>
       <c r="R47" t="n">
-        <v>6368092</v>
+        <v>6367609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5127,7 +5133,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5146,51 +5152,50 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128721631</v>
+        <v>128722606</v>
       </c>
       <c r="B48" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5205,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715172</v>
+        <v>715323</v>
       </c>
       <c r="R48" t="n">
-        <v>6367927</v>
+        <v>6367903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5244,51 +5249,50 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128722543</v>
+        <v>128721557</v>
       </c>
       <c r="B49" t="n">
-        <v>86729</v>
+        <v>86949</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5298,10 +5302,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715253</v>
+        <v>715213</v>
       </c>
       <c r="R49" t="n">
-        <v>6367647</v>
+        <v>6367921</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5348,22 +5352,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722606</v>
+        <v>128722544</v>
       </c>
       <c r="B50" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5371,21 +5375,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5395,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715323</v>
+        <v>715251</v>
       </c>
       <c r="R50" t="n">
-        <v>6367903</v>
+        <v>6367635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5457,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128722575</v>
+        <v>128721582</v>
       </c>
       <c r="B51" t="n">
-        <v>105640</v>
+        <v>86890</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5468,21 +5472,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5492,10 +5496,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715498</v>
+        <v>715178</v>
       </c>
       <c r="R51" t="n">
-        <v>6367908</v>
+        <v>6367640</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5542,12 +5546,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5651,10 +5655,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128722544</v>
+        <v>128721568</v>
       </c>
       <c r="B53" t="n">
-        <v>86729</v>
+        <v>86753</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5662,21 +5666,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5686,10 +5690,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715251</v>
+        <v>715200</v>
       </c>
       <c r="R53" t="n">
-        <v>6367635</v>
+        <v>6367963</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5736,22 +5740,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721568</v>
+        <v>128721563</v>
       </c>
       <c r="B54" t="n">
-        <v>86753</v>
+        <v>92790</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5759,34 +5763,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715200</v>
+        <v>715232</v>
       </c>
       <c r="R54" t="n">
-        <v>6367963</v>
+        <v>6367928</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5827,6 +5834,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5838,17 +5846,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128721582</v>
+        <v>128722575</v>
       </c>
       <c r="B55" t="n">
-        <v>86890</v>
+        <v>105642</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5856,21 +5864,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3674</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5880,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715178</v>
+        <v>715498</v>
       </c>
       <c r="R55" t="n">
-        <v>6367640</v>
+        <v>6367908</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5930,22 +5938,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128721563</v>
+        <v>128722604</v>
       </c>
       <c r="B56" t="n">
-        <v>92790</v>
+        <v>86890</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5953,37 +5961,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715232</v>
+        <v>715309</v>
       </c>
       <c r="R56" t="n">
-        <v>6367928</v>
+        <v>6367880</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6024,51 +6029,50 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128721496</v>
+        <v>128721580</v>
       </c>
       <c r="B57" t="n">
-        <v>86870</v>
+        <v>86890</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>473</v>
+        <v>3674</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6078,10 +6082,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715344</v>
+        <v>715147</v>
       </c>
       <c r="R57" t="n">
-        <v>6368190</v>
+        <v>6367801</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6122,7 +6126,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6134,39 +6137,39 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128721580</v>
+        <v>128722553</v>
       </c>
       <c r="B58" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6176,10 +6179,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715147</v>
+        <v>715261</v>
       </c>
       <c r="R58" t="n">
-        <v>6367801</v>
+        <v>6368006</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6220,18 +6223,19 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6241,7 +6245,7 @@
         <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>105627</v>
+        <v>105629</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6328,55 +6332,52 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128722530</v>
+        <v>128721496</v>
       </c>
       <c r="B60" t="n">
-        <v>86961</v>
+        <v>86870</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248939</v>
+        <v>473</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715197</v>
+        <v>715344</v>
       </c>
       <c r="R60" t="n">
-        <v>6367895</v>
+        <v>6368190</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6424,19 +6425,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128722553</v>
+        <v>128722557</v>
       </c>
       <c r="B61" t="n">
         <v>86927</v>
@@ -6471,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715261</v>
+        <v>715218</v>
       </c>
       <c r="R61" t="n">
-        <v>6368006</v>
+        <v>6367940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6534,32 +6535,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128722604</v>
+        <v>128721644</v>
       </c>
       <c r="B62" t="n">
-        <v>86890</v>
+        <v>86949</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6569,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715309</v>
+        <v>715497</v>
       </c>
       <c r="R62" t="n">
-        <v>6367880</v>
+        <v>6367603</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6594,7 +6595,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -6619,12 +6620,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6729,32 +6730,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128722557</v>
+        <v>128721567</v>
       </c>
       <c r="B64" t="n">
-        <v>86927</v>
+        <v>96187</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6764,10 +6765,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715218</v>
+        <v>715422</v>
       </c>
       <c r="R64" t="n">
-        <v>6367940</v>
+        <v>6367626</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6789,7 +6790,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6808,19 +6809,18 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -6917,39 +6917,39 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721644</v>
+        <v>128721635</v>
       </c>
       <c r="B66" t="n">
-        <v>86949</v>
+        <v>86903</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>449</v>
+        <v>1988</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715497</v>
+        <v>715194</v>
       </c>
       <c r="R66" t="n">
-        <v>6367603</v>
+        <v>6367686</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -7021,10 +7021,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721567</v>
+        <v>128722601</v>
       </c>
       <c r="B67" t="n">
-        <v>96187</v>
+        <v>86890</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715422</v>
+        <v>715264</v>
       </c>
       <c r="R67" t="n">
-        <v>6367626</v>
+        <v>6367986</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -7106,22 +7106,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721514</v>
+        <v>128721579</v>
       </c>
       <c r="B68" t="n">
-        <v>86729</v>
+        <v>86890</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715141</v>
+        <v>715191</v>
       </c>
       <c r="R68" t="n">
-        <v>6367822</v>
+        <v>6367888</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7215,10 +7215,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721579</v>
+        <v>128721514</v>
       </c>
       <c r="B69" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715191</v>
+        <v>715141</v>
       </c>
       <c r="R69" t="n">
-        <v>6367888</v>
+        <v>6367822</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7305,39 +7305,39 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721629</v>
+        <v>128721651</v>
       </c>
       <c r="B70" t="n">
-        <v>57686</v>
+        <v>86890</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715504</v>
+        <v>715215</v>
       </c>
       <c r="R70" t="n">
-        <v>6367595</v>
+        <v>6367933</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -7409,10 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721522</v>
+        <v>128721629</v>
       </c>
       <c r="B71" t="n">
-        <v>86927</v>
+        <v>57686</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715221</v>
+        <v>715504</v>
       </c>
       <c r="R71" t="n">
-        <v>6367902</v>
+        <v>6367595</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7488,51 +7488,50 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128721651</v>
+        <v>128721522</v>
       </c>
       <c r="B72" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7542,10 +7541,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715215</v>
+        <v>715221</v>
       </c>
       <c r="R72" t="n">
-        <v>6367933</v>
+        <v>6367902</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7586,50 +7585,51 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721635</v>
+        <v>128722550</v>
       </c>
       <c r="B73" t="n">
-        <v>86903</v>
+        <v>86927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715194</v>
+        <v>715321</v>
       </c>
       <c r="R73" t="n">
-        <v>6367686</v>
+        <v>6367984</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7683,50 +7683,51 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128721523</v>
+        <v>128722596</v>
       </c>
       <c r="B74" t="n">
-        <v>86927</v>
+        <v>86880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7736,10 +7737,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715146</v>
+        <v>715196</v>
       </c>
       <c r="R74" t="n">
-        <v>6367798</v>
+        <v>6367906</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7787,44 +7788,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128722601</v>
+        <v>128721523</v>
       </c>
       <c r="B75" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7834,10 +7835,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715264</v>
+        <v>715146</v>
       </c>
       <c r="R75" t="n">
-        <v>6367986</v>
+        <v>6367798</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7878,28 +7879,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128722550</v>
+        <v>128722516</v>
       </c>
       <c r="B76" t="n">
-        <v>86927</v>
+        <v>86682</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7907,34 +7909,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715321</v>
+        <v>715492</v>
       </c>
       <c r="R76" t="n">
-        <v>6367984</v>
+        <v>6367910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7994,10 +7999,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128722596</v>
+        <v>128722521</v>
       </c>
       <c r="B77" t="n">
-        <v>86880</v>
+        <v>86972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8005,21 +8010,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003235</v>
+        <v>3767</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8029,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715196</v>
+        <v>715207</v>
       </c>
       <c r="R77" t="n">
-        <v>6367906</v>
+        <v>6367905</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,48 +8097,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128722516</v>
+        <v>128721642</v>
       </c>
       <c r="B78" t="n">
-        <v>86682</v>
+        <v>86949</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>249278</v>
+        <v>449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715492</v>
+        <v>715204</v>
       </c>
       <c r="R78" t="n">
-        <v>6367910</v>
+        <v>6367900</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8174,51 +8176,50 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721642</v>
+        <v>128721503</v>
       </c>
       <c r="B79" t="n">
-        <v>86949</v>
+        <v>110704</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8228,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715204</v>
+        <v>715170</v>
       </c>
       <c r="R79" t="n">
-        <v>6367900</v>
+        <v>6367852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8278,44 +8279,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128721503</v>
+        <v>128721521</v>
       </c>
       <c r="B80" t="n">
-        <v>110701</v>
+        <v>86927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8325,10 +8326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715170</v>
+        <v>715183</v>
       </c>
       <c r="R80" t="n">
-        <v>6367852</v>
+        <v>6368007</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8369,6 +8370,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8380,14 +8382,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128721521</v>
+        <v>128722549</v>
       </c>
       <c r="B81" t="n">
         <v>86927</v>
@@ -8422,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715183</v>
+        <v>715448</v>
       </c>
       <c r="R81" t="n">
-        <v>6368007</v>
+        <v>6367902</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8473,22 +8475,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128722521</v>
+        <v>128721502</v>
       </c>
       <c r="B82" t="n">
-        <v>86972</v>
+        <v>90986</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8496,21 +8498,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3767</v>
+        <v>256335</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8520,10 +8522,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715207</v>
+        <v>715210</v>
       </c>
       <c r="R82" t="n">
-        <v>6367905</v>
+        <v>6367925</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8571,44 +8573,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722607</v>
+        <v>128722560</v>
       </c>
       <c r="B83" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8618,10 +8620,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715545</v>
+        <v>715549</v>
       </c>
       <c r="R83" t="n">
-        <v>6367864</v>
+        <v>6367883</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8662,6 +8664,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8680,32 +8683,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722589</v>
+        <v>128722547</v>
       </c>
       <c r="B84" t="n">
-        <v>86775</v>
+        <v>86927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8718,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715223</v>
+        <v>715525</v>
       </c>
       <c r="R84" t="n">
-        <v>6367944</v>
+        <v>6367901</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8759,6 +8762,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8777,32 +8781,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722547</v>
+        <v>128722589</v>
       </c>
       <c r="B85" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8812,10 +8816,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715525</v>
+        <v>715223</v>
       </c>
       <c r="R85" t="n">
-        <v>6367901</v>
+        <v>6367944</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8856,7 +8860,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -8875,32 +8878,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722565</v>
+        <v>128722607</v>
       </c>
       <c r="B86" t="n">
-        <v>91001</v>
+        <v>86890</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8910,10 +8913,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715311</v>
+        <v>715545</v>
       </c>
       <c r="R86" t="n">
-        <v>6367855</v>
+        <v>6367864</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8972,32 +8975,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128722549</v>
+        <v>128721575</v>
       </c>
       <c r="B87" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9007,10 +9010,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715448</v>
+        <v>715333</v>
       </c>
       <c r="R87" t="n">
-        <v>6367902</v>
+        <v>6368090</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9051,51 +9054,50 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722560</v>
+        <v>128721581</v>
       </c>
       <c r="B88" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9105,10 +9107,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715549</v>
+        <v>715150</v>
       </c>
       <c r="R88" t="n">
-        <v>6367883</v>
+        <v>6367790</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9149,19 +9151,18 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9265,10 +9266,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128721575</v>
+        <v>128721552</v>
       </c>
       <c r="B90" t="n">
-        <v>86890</v>
+        <v>105642</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9276,21 +9277,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3674</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9300,10 +9301,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715333</v>
+        <v>715197</v>
       </c>
       <c r="R90" t="n">
-        <v>6368090</v>
+        <v>6367683</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9355,39 +9356,39 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128721581</v>
+        <v>128722565</v>
       </c>
       <c r="B91" t="n">
-        <v>86890</v>
+        <v>91001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9397,10 +9398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715150</v>
+        <v>715311</v>
       </c>
       <c r="R91" t="n">
-        <v>6367790</v>
+        <v>6367855</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9447,44 +9448,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128721552</v>
+        <v>128722558</v>
       </c>
       <c r="B92" t="n">
-        <v>105640</v>
+        <v>86927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9494,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715197</v>
+        <v>715177</v>
       </c>
       <c r="R92" t="n">
-        <v>6367683</v>
+        <v>6367636</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9538,50 +9539,51 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128721502</v>
+        <v>128721647</v>
       </c>
       <c r="B93" t="n">
-        <v>90986</v>
+        <v>86682</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>256335</v>
+        <v>249278</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9591,10 +9593,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715210</v>
+        <v>715216</v>
       </c>
       <c r="R93" t="n">
-        <v>6367925</v>
+        <v>6367898</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9629,6 +9631,11 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -9642,44 +9649,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128721647</v>
+        <v>128722603</v>
       </c>
       <c r="B94" t="n">
-        <v>86682</v>
+        <v>86890</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9689,10 +9696,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715216</v>
+        <v>715233</v>
       </c>
       <c r="R94" t="n">
-        <v>6367898</v>
+        <v>6367868</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9727,30 +9734,24 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9854,45 +9855,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128722603</v>
+        <v>128721508</v>
       </c>
       <c r="B96" t="n">
-        <v>86890</v>
+        <v>57686</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715233</v>
+        <v>715206</v>
       </c>
       <c r="R96" t="n">
-        <v>6367868</v>
+        <v>6367909</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9939,44 +9948,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128722558</v>
+        <v>128722597</v>
       </c>
       <c r="B97" t="n">
-        <v>86927</v>
+        <v>86880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9986,10 +9995,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715177</v>
+        <v>715216</v>
       </c>
       <c r="R97" t="n">
-        <v>6367636</v>
+        <v>6367914</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10049,10 +10058,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721542</v>
+        <v>128721649</v>
       </c>
       <c r="B98" t="n">
-        <v>75115</v>
+        <v>86890</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10060,21 +10069,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10093,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715519</v>
+        <v>715314</v>
       </c>
       <c r="R98" t="n">
-        <v>6367602</v>
+        <v>6368077</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10109,7 +10118,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -10134,12 +10143,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10236,17 +10245,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721649</v>
+        <v>128721542</v>
       </c>
       <c r="B100" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10254,21 +10263,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10278,10 +10287,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715314</v>
+        <v>715519</v>
       </c>
       <c r="R100" t="n">
-        <v>6368077</v>
+        <v>6367602</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10303,7 +10312,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -10328,65 +10337,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128721508</v>
+        <v>128722587</v>
       </c>
       <c r="B101" t="n">
-        <v>57686</v>
+        <v>86950</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715206</v>
+        <v>715464</v>
       </c>
       <c r="R101" t="n">
-        <v>6367909</v>
+        <v>6367911</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10433,44 +10434,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722597</v>
+        <v>128721519</v>
       </c>
       <c r="B102" t="n">
-        <v>86880</v>
+        <v>86927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10480,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715216</v>
+        <v>715287</v>
       </c>
       <c r="R102" t="n">
-        <v>6367914</v>
+        <v>6368083</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10531,44 +10532,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128721583</v>
+        <v>128722546</v>
       </c>
       <c r="B103" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10578,10 +10579,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715492</v>
+        <v>715298</v>
       </c>
       <c r="R103" t="n">
-        <v>6367606</v>
+        <v>6367872</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10603,7 +10604,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10622,50 +10623,51 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128721519</v>
+        <v>128722598</v>
       </c>
       <c r="B104" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10677,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715287</v>
+        <v>715487</v>
       </c>
       <c r="R104" t="n">
-        <v>6368083</v>
+        <v>6367923</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10719,51 +10721,50 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722587</v>
+        <v>128722579</v>
       </c>
       <c r="B105" t="n">
-        <v>86950</v>
+        <v>86949</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>248947</v>
+        <v>449</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10773,10 +10774,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715464</v>
+        <v>715205</v>
       </c>
       <c r="R105" t="n">
-        <v>6367911</v>
+        <v>6367943</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10835,32 +10836,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128722579</v>
+        <v>128721583</v>
       </c>
       <c r="B106" t="n">
-        <v>86949</v>
+        <v>86890</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10870,10 +10871,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715205</v>
+        <v>715492</v>
       </c>
       <c r="R106" t="n">
-        <v>6367943</v>
+        <v>6367606</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10895,7 +10896,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -10920,44 +10921,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722546</v>
+        <v>128722522</v>
       </c>
       <c r="B107" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10967,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715298</v>
+        <v>715314</v>
       </c>
       <c r="R107" t="n">
-        <v>6367872</v>
+        <v>6367886</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11011,7 +11012,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11030,32 +11030,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128722598</v>
+        <v>128722585</v>
       </c>
       <c r="B108" t="n">
-        <v>86775</v>
+        <v>86729</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11065,10 +11065,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715487</v>
+        <v>715309</v>
       </c>
       <c r="R108" t="n">
-        <v>6367923</v>
+        <v>6367883</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11127,32 +11127,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128721520</v>
+        <v>128722599</v>
       </c>
       <c r="B109" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11162,10 +11162,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715280</v>
+        <v>715214</v>
       </c>
       <c r="R109" t="n">
-        <v>6368028</v>
+        <v>6367950</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11200,6 +11200,11 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -11213,44 +11218,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128721572</v>
+        <v>128722545</v>
       </c>
       <c r="B110" t="n">
-        <v>86880</v>
+        <v>86729</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003235</v>
+        <v>3762</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11260,10 +11265,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715132</v>
+        <v>715261</v>
       </c>
       <c r="R110" t="n">
-        <v>6367819</v>
+        <v>6367632</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11310,44 +11315,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128722585</v>
+        <v>128721572</v>
       </c>
       <c r="B111" t="n">
-        <v>86729</v>
+        <v>86880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3762</v>
+        <v>6003235</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11357,10 +11362,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715309</v>
+        <v>715132</v>
       </c>
       <c r="R111" t="n">
-        <v>6367883</v>
+        <v>6367819</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11407,44 +11412,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128722522</v>
+        <v>128721520</v>
       </c>
       <c r="B112" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11454,10 +11459,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715314</v>
+        <v>715280</v>
       </c>
       <c r="R112" t="n">
-        <v>6367886</v>
+        <v>6368028</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11498,50 +11503,51 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128722545</v>
+        <v>128721500</v>
       </c>
       <c r="B113" t="n">
-        <v>86729</v>
+        <v>86972</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11551,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715261</v>
+        <v>715318</v>
       </c>
       <c r="R113" t="n">
-        <v>6367632</v>
+        <v>6368090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11601,44 +11607,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128722599</v>
+        <v>128722523</v>
       </c>
       <c r="B114" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11648,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715214</v>
+        <v>715327</v>
       </c>
       <c r="R114" t="n">
-        <v>6367950</v>
+        <v>6367899</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11686,18 +11692,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -11716,32 +11716,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128721524</v>
+        <v>128721650</v>
       </c>
       <c r="B115" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11751,10 +11751,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715222</v>
+        <v>715161</v>
       </c>
       <c r="R115" t="n">
-        <v>6367894</v>
+        <v>6368017</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11795,29 +11795,28 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128721650</v>
+        <v>128722535</v>
       </c>
       <c r="B116" t="n">
-        <v>86890</v>
+        <v>86753</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11825,21 +11824,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11849,10 +11848,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715161</v>
+        <v>715500</v>
       </c>
       <c r="R116" t="n">
-        <v>6368017</v>
+        <v>6367907</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11899,44 +11898,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128721500</v>
+        <v>128722541</v>
       </c>
       <c r="B117" t="n">
-        <v>86972</v>
+        <v>86729</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11946,10 +11945,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715318</v>
+        <v>715501</v>
       </c>
       <c r="R117" t="n">
-        <v>6368090</v>
+        <v>6367911</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11996,22 +11995,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128721537</v>
+        <v>128722586</v>
       </c>
       <c r="B118" t="n">
-        <v>75115</v>
+        <v>86729</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12019,21 +12018,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12043,10 +12042,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715344</v>
+        <v>715507</v>
       </c>
       <c r="R118" t="n">
-        <v>6368190</v>
+        <v>6367904</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12093,22 +12092,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128722535</v>
+        <v>128721537</v>
       </c>
       <c r="B119" t="n">
-        <v>86753</v>
+        <v>75115</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12116,21 +12115,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12140,10 +12139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715500</v>
+        <v>715344</v>
       </c>
       <c r="R119" t="n">
-        <v>6367907</v>
+        <v>6368190</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12190,22 +12189,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722523</v>
+        <v>128722562</v>
       </c>
       <c r="B120" t="n">
-        <v>86729</v>
+        <v>98622</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12213,21 +12212,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3762</v>
+        <v>219874</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12237,10 +12236,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715327</v>
+        <v>715452</v>
       </c>
       <c r="R120" t="n">
-        <v>6367899</v>
+        <v>6367610</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12262,7 +12261,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12299,32 +12298,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128722541</v>
+        <v>128722548</v>
       </c>
       <c r="B121" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12334,10 +12333,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715501</v>
+        <v>715513</v>
       </c>
       <c r="R121" t="n">
-        <v>6367911</v>
+        <v>6367892</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12378,6 +12377,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12396,32 +12396,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128722562</v>
+        <v>128721524</v>
       </c>
       <c r="B122" t="n">
-        <v>98622</v>
+        <v>86927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12431,10 +12431,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715452</v>
+        <v>715222</v>
       </c>
       <c r="R122" t="n">
-        <v>6367610</v>
+        <v>6367894</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -12475,28 +12475,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128722586</v>
+        <v>128722605</v>
       </c>
       <c r="B123" t="n">
-        <v>86729</v>
+        <v>86890</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12504,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12528,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715507</v>
+        <v>715315</v>
       </c>
       <c r="R123" t="n">
-        <v>6367904</v>
+        <v>6367838</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12590,32 +12591,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128722548</v>
+        <v>128721538</v>
       </c>
       <c r="B124" t="n">
-        <v>86927</v>
+        <v>75115</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12625,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715513</v>
+        <v>715352</v>
       </c>
       <c r="R124" t="n">
-        <v>6367892</v>
+        <v>6368147</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12669,51 +12670,50 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721525</v>
+        <v>128721526</v>
       </c>
       <c r="B125" t="n">
-        <v>86927</v>
+        <v>58059</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003295</v>
+        <v>103015</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715141</v>
+        <v>715155</v>
       </c>
       <c r="R125" t="n">
-        <v>6367814</v>
+        <v>6367801</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12767,7 +12767,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12779,39 +12778,39 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128721526</v>
+        <v>128722590</v>
       </c>
       <c r="B126" t="n">
-        <v>58059</v>
+        <v>86950</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>248947</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12821,10 +12820,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715155</v>
+        <v>715473</v>
       </c>
       <c r="R126" t="n">
-        <v>6367801</v>
+        <v>6367917</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12871,44 +12870,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128721538</v>
+        <v>128721525</v>
       </c>
       <c r="B127" t="n">
-        <v>75115</v>
+        <v>86927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12918,10 +12917,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715352</v>
+        <v>715141</v>
       </c>
       <c r="R127" t="n">
-        <v>6368147</v>
+        <v>6367814</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12962,6 +12961,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -12973,39 +12973,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722605</v>
+        <v>128722559</v>
       </c>
       <c r="B128" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715315</v>
+        <v>715256</v>
       </c>
       <c r="R128" t="n">
-        <v>6367838</v>
+        <v>6367627</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13059,6 +13059,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13077,7 +13078,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128722561</v>
+        <v>128722551</v>
       </c>
       <c r="B129" t="n">
         <v>86927</v>
@@ -13112,10 +13113,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715545</v>
+        <v>715313</v>
       </c>
       <c r="R129" t="n">
-        <v>6367898</v>
+        <v>6368003</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13175,7 +13176,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722551</v>
+        <v>128722561</v>
       </c>
       <c r="B130" t="n">
         <v>86927</v>
@@ -13210,10 +13211,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715313</v>
+        <v>715545</v>
       </c>
       <c r="R130" t="n">
-        <v>6368003</v>
+        <v>6367898</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13273,45 +13274,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128722590</v>
+        <v>128722530</v>
       </c>
       <c r="B131" t="n">
-        <v>86950</v>
+        <v>86961</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>248947</v>
+        <v>248939</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Tallpraktspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius terpsichores</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Melot</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>715473</v>
+        <v>715197</v>
       </c>
       <c r="R131" t="n">
-        <v>6367917</v>
+        <v>6367895</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13352,6 +13356,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13370,32 +13375,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128722559</v>
+        <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>86927</v>
+        <v>110704</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6003295</v>
+        <v>219711</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13405,10 +13410,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>715256</v>
+        <v>715450</v>
       </c>
       <c r="R132" t="n">
-        <v>6367627</v>
+        <v>6367880</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13438,18 +13443,27 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128721516</v>
+        <v>128722539</v>
       </c>
       <c r="B2" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715344</v>
+        <v>715181</v>
       </c>
       <c r="R2" t="n">
-        <v>6368182</v>
+        <v>6367653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,51 +754,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128722554</v>
+        <v>128722600</v>
       </c>
       <c r="B3" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715247</v>
+        <v>715327</v>
       </c>
       <c r="R3" t="n">
-        <v>6368027</v>
+        <v>6367976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -871,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722539</v>
+        <v>128722536</v>
       </c>
       <c r="B4" t="n">
-        <v>86729</v>
+        <v>91239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -882,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -906,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715181</v>
+        <v>715340</v>
       </c>
       <c r="R4" t="n">
-        <v>6367653</v>
+        <v>6367945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -968,7 +967,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128722600</v>
+        <v>128721652</v>
       </c>
       <c r="B5" t="n">
         <v>86890</v>
@@ -1003,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715327</v>
+        <v>715207</v>
       </c>
       <c r="R5" t="n">
-        <v>6367976</v>
+        <v>6367759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,22 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128722536</v>
+        <v>128721501</v>
       </c>
       <c r="B6" t="n">
-        <v>91239</v>
+        <v>88662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1076,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>4379</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1100,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715340</v>
+        <v>715178</v>
       </c>
       <c r="R6" t="n">
-        <v>6367945</v>
+        <v>6367628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,29 +1143,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721652</v>
+        <v>128721539</v>
       </c>
       <c r="B7" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1174,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1198,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715207</v>
+        <v>715289</v>
       </c>
       <c r="R7" t="n">
-        <v>6367759</v>
+        <v>6368047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,44 +1246,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128721501</v>
+        <v>128721516</v>
       </c>
       <c r="B8" t="n">
-        <v>88662</v>
+        <v>86927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1295,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715178</v>
+        <v>715344</v>
       </c>
       <c r="R8" t="n">
-        <v>6367628</v>
+        <v>6368182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1337,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1350,39 +1349,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128721539</v>
+        <v>128722554</v>
       </c>
       <c r="B9" t="n">
-        <v>75115</v>
+        <v>86927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715289</v>
+        <v>715247</v>
       </c>
       <c r="R9" t="n">
-        <v>6368047</v>
+        <v>6368027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,63 +1435,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128722578</v>
+        <v>128722583</v>
       </c>
       <c r="B10" t="n">
-        <v>86949</v>
+        <v>92790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715461</v>
+        <v>715227</v>
       </c>
       <c r="R10" t="n">
-        <v>6367905</v>
+        <v>6367937</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1533,6 +1536,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1747,48 +1751,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722583</v>
+        <v>128722578</v>
       </c>
       <c r="B13" t="n">
-        <v>92790</v>
+        <v>86949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715227</v>
+        <v>715461</v>
       </c>
       <c r="R13" t="n">
-        <v>6367937</v>
+        <v>6367905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1829,7 +1830,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B14" t="n">
-        <v>86914</v>
+        <v>105638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R14" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B15" t="n">
-        <v>105629</v>
+        <v>86914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R15" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,44 +2030,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128721560</v>
+        <v>128722540</v>
       </c>
       <c r="B16" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715503</v>
+        <v>715194</v>
       </c>
       <c r="R16" t="n">
-        <v>6367589</v>
+        <v>6367837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2121,28 +2121,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721559</v>
+        <v>128721499</v>
       </c>
       <c r="B17" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715505</v>
+        <v>715394</v>
       </c>
       <c r="R17" t="n">
-        <v>6367598</v>
+        <v>6368208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2199,7 +2200,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2236,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128722540</v>
+        <v>128721578</v>
       </c>
       <c r="B18" t="n">
-        <v>86729</v>
+        <v>86890</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715194</v>
+        <v>715215</v>
       </c>
       <c r="R18" t="n">
-        <v>6367837</v>
+        <v>6367918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2315,64 +2316,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721499</v>
+        <v>128722582</v>
       </c>
       <c r="B19" t="n">
-        <v>86972</v>
+        <v>92790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715394</v>
+        <v>715492</v>
       </c>
       <c r="R19" t="n">
-        <v>6368208</v>
+        <v>6367899</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2413,50 +2416,51 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128721643</v>
+        <v>128722534</v>
       </c>
       <c r="B20" t="n">
-        <v>86949</v>
+        <v>98569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715270</v>
+        <v>715228</v>
       </c>
       <c r="R20" t="n">
-        <v>6367607</v>
+        <v>6367909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2516,44 +2520,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721578</v>
+        <v>128721560</v>
       </c>
       <c r="B21" t="n">
-        <v>86890</v>
+        <v>86949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715215</v>
+        <v>715503</v>
       </c>
       <c r="R21" t="n">
-        <v>6367918</v>
+        <v>6367589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2588,7 +2592,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2618,14 +2622,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721558</v>
+        <v>128721559</v>
       </c>
       <c r="B22" t="n">
         <v>86949</v>
@@ -2660,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715424</v>
+        <v>715505</v>
       </c>
       <c r="R22" t="n">
-        <v>6367651</v>
+        <v>6367598</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2715,55 +2719,52 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128722582</v>
+        <v>128721643</v>
       </c>
       <c r="B23" t="n">
-        <v>92790</v>
+        <v>86949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715492</v>
+        <v>715270</v>
       </c>
       <c r="R23" t="n">
-        <v>6367899</v>
+        <v>6367607</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2804,51 +2805,50 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128722534</v>
+        <v>128721558</v>
       </c>
       <c r="B24" t="n">
-        <v>98566</v>
+        <v>86949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>715228</v>
+        <v>715424</v>
       </c>
       <c r="R24" t="n">
-        <v>6367909</v>
+        <v>6367651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2908,22 +2908,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128721505</v>
+        <v>128722567</v>
       </c>
       <c r="B25" t="n">
-        <v>86775</v>
+        <v>86972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715150</v>
+        <v>715339</v>
       </c>
       <c r="R25" t="n">
-        <v>6367765</v>
+        <v>6367894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2993,56 +2993,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128722567</v>
+        <v>128722602</v>
       </c>
       <c r="B26" t="n">
-        <v>86972</v>
+        <v>86890</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715339</v>
+        <v>715200</v>
       </c>
       <c r="R26" t="n">
-        <v>6367894</v>
+        <v>6367935</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3090,18 +3096,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128722602</v>
+        <v>128721543</v>
       </c>
       <c r="B27" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715200</v>
+        <v>715500</v>
       </c>
       <c r="R27" t="n">
-        <v>6367935</v>
+        <v>6367588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3205,44 +3205,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128721543</v>
+        <v>128721505</v>
       </c>
       <c r="B28" t="n">
-        <v>75115</v>
+        <v>86775</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>424</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715500</v>
+        <v>715150</v>
       </c>
       <c r="R28" t="n">
-        <v>6367588</v>
+        <v>6367765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3307,39 +3307,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128721628</v>
+        <v>128722532</v>
       </c>
       <c r="B29" t="n">
-        <v>86972</v>
+        <v>92401</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715222</v>
+        <v>715460</v>
       </c>
       <c r="R29" t="n">
-        <v>6367915</v>
+        <v>6367601</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3393,29 +3393,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128722532</v>
+        <v>128721540</v>
       </c>
       <c r="B30" t="n">
-        <v>92401</v>
+        <v>75115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3422,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715460</v>
+        <v>715278</v>
       </c>
       <c r="R30" t="n">
-        <v>6367601</v>
+        <v>6368028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3472,7 +3471,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3497,44 +3496,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128721540</v>
+        <v>128721628</v>
       </c>
       <c r="B31" t="n">
-        <v>75115</v>
+        <v>86972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715278</v>
+        <v>715222</v>
       </c>
       <c r="R31" t="n">
-        <v>6368028</v>
+        <v>6367915</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3588,18 +3587,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3707,32 +3707,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722608</v>
+        <v>128722577</v>
       </c>
       <c r="B33" t="n">
-        <v>86890</v>
+        <v>86949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715211</v>
+        <v>715502</v>
       </c>
       <c r="R33" t="n">
-        <v>6367929</v>
+        <v>6367602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3804,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722564</v>
+        <v>128722608</v>
       </c>
       <c r="B34" t="n">
-        <v>86914</v>
+        <v>86890</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3599</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715387</v>
+        <v>715211</v>
       </c>
       <c r="R34" t="n">
-        <v>6367908</v>
+        <v>6367929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128721511</v>
+        <v>128722564</v>
       </c>
       <c r="B35" t="n">
-        <v>91239</v>
+        <v>86914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>3599</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715180</v>
+        <v>715387</v>
       </c>
       <c r="R35" t="n">
-        <v>6367626</v>
+        <v>6367908</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3986,22 +3986,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721513</v>
+        <v>128721511</v>
       </c>
       <c r="B36" t="n">
-        <v>86729</v>
+        <v>91239</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715408</v>
+        <v>715180</v>
       </c>
       <c r="R36" t="n">
-        <v>6368189</v>
+        <v>6367626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4088,14 +4088,14 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722542</v>
+        <v>128721513</v>
       </c>
       <c r="B37" t="n">
         <v>86729</v>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715218</v>
+        <v>715408</v>
       </c>
       <c r="R37" t="n">
-        <v>6367844</v>
+        <v>6368189</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,44 +4180,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128722577</v>
+        <v>128722542</v>
       </c>
       <c r="B38" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715502</v>
+        <v>715218</v>
       </c>
       <c r="R38" t="n">
-        <v>6367602</v>
+        <v>6367844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4585,32 +4585,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721517</v>
+        <v>128721557</v>
       </c>
       <c r="B42" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715323</v>
+        <v>715213</v>
       </c>
       <c r="R42" t="n">
-        <v>6368092</v>
+        <v>6367921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4664,7 +4664,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4676,39 +4675,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721631</v>
+        <v>128721497</v>
       </c>
       <c r="B43" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4718,10 +4717,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715172</v>
+        <v>715243</v>
       </c>
       <c r="R43" t="n">
-        <v>6367927</v>
+        <v>6367615</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,44 +4768,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721497</v>
+        <v>128722543</v>
       </c>
       <c r="B44" t="n">
-        <v>86972</v>
+        <v>86729</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715243</v>
+        <v>715253</v>
       </c>
       <c r="R44" t="n">
-        <v>6367615</v>
+        <v>6367647</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4860,29 +4859,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128722543</v>
+        <v>128721577</v>
       </c>
       <c r="B45" t="n">
-        <v>86729</v>
+        <v>86890</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4890,21 +4888,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4914,10 +4912,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715253</v>
+        <v>715221</v>
       </c>
       <c r="R45" t="n">
-        <v>6367647</v>
+        <v>6367967</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,19 +4962,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721577</v>
+        <v>128721653</v>
       </c>
       <c r="B46" t="n">
         <v>86890</v>
@@ -5011,10 +5009,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715221</v>
+        <v>715476</v>
       </c>
       <c r="R46" t="n">
-        <v>6367967</v>
+        <v>6367609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5036,7 +5034,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5061,19 +5059,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721653</v>
+        <v>128722606</v>
       </c>
       <c r="B47" t="n">
         <v>86890</v>
@@ -5108,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715476</v>
+        <v>715323</v>
       </c>
       <c r="R47" t="n">
-        <v>6367609</v>
+        <v>6367903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5133,7 +5131,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5158,44 +5156,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128722606</v>
+        <v>128721631</v>
       </c>
       <c r="B48" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5205,10 +5203,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715323</v>
+        <v>715172</v>
       </c>
       <c r="R48" t="n">
-        <v>6367903</v>
+        <v>6367927</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5249,50 +5247,51 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128721557</v>
+        <v>128721517</v>
       </c>
       <c r="B49" t="n">
-        <v>86949</v>
+        <v>86927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5302,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715213</v>
+        <v>715323</v>
       </c>
       <c r="R49" t="n">
-        <v>6367921</v>
+        <v>6368092</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,6 +5345,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5357,39 +5357,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722544</v>
+        <v>128722580</v>
       </c>
       <c r="B50" t="n">
-        <v>86729</v>
+        <v>86949</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715251</v>
+        <v>715209</v>
       </c>
       <c r="R50" t="n">
-        <v>6367635</v>
+        <v>6367900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128721582</v>
+        <v>128722544</v>
       </c>
       <c r="B51" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715178</v>
+        <v>715251</v>
       </c>
       <c r="R51" t="n">
-        <v>6367640</v>
+        <v>6367635</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,44 +5546,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128722580</v>
+        <v>128721582</v>
       </c>
       <c r="B52" t="n">
-        <v>86949</v>
+        <v>86890</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715209</v>
+        <v>715178</v>
       </c>
       <c r="R52" t="n">
-        <v>6367900</v>
+        <v>6367640</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,12 +5643,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
         <v>128722575</v>
       </c>
       <c r="B55" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6137,17 +6137,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128722553</v>
+        <v>128721496</v>
       </c>
       <c r="B58" t="n">
-        <v>86927</v>
+        <v>86870</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6155,21 +6155,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>473</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715261</v>
+        <v>715344</v>
       </c>
       <c r="R58" t="n">
-        <v>6368006</v>
+        <v>6368190</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,12 +6230,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6245,7 +6245,7 @@
         <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>105629</v>
+        <v>105638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128721496</v>
+        <v>128722553</v>
       </c>
       <c r="B60" t="n">
-        <v>86870</v>
+        <v>86927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6350,21 +6350,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715344</v>
+        <v>715261</v>
       </c>
       <c r="R60" t="n">
-        <v>6368190</v>
+        <v>6368006</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6425,44 +6425,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128722557</v>
+        <v>128722520</v>
       </c>
       <c r="B61" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715218</v>
+        <v>715450</v>
       </c>
       <c r="R61" t="n">
-        <v>6367940</v>
+        <v>6367880</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6535,32 +6535,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128721644</v>
+        <v>128721567</v>
       </c>
       <c r="B62" t="n">
-        <v>86949</v>
+        <v>96187</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>449</v>
+        <v>2180</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715497</v>
+        <v>715422</v>
       </c>
       <c r="R62" t="n">
-        <v>6367603</v>
+        <v>6367626</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6620,44 +6620,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128722520</v>
+        <v>128721507</v>
       </c>
       <c r="B63" t="n">
-        <v>86972</v>
+        <v>57686</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3767</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715450</v>
+        <v>715452</v>
       </c>
       <c r="R63" t="n">
-        <v>6367880</v>
+        <v>6367607</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -6711,51 +6711,50 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721567</v>
+        <v>128722557</v>
       </c>
       <c r="B64" t="n">
-        <v>96187</v>
+        <v>86927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6765,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715422</v>
+        <v>715218</v>
       </c>
       <c r="R64" t="n">
-        <v>6367626</v>
+        <v>6367940</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6790,7 +6789,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6809,50 +6808,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128721507</v>
+        <v>128721644</v>
       </c>
       <c r="B65" t="n">
-        <v>57686</v>
+        <v>86949</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715452</v>
+        <v>715497</v>
       </c>
       <c r="R65" t="n">
-        <v>6367607</v>
+        <v>6367603</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6912,22 +6912,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721635</v>
+        <v>128722601</v>
       </c>
       <c r="B66" t="n">
-        <v>86903</v>
+        <v>86890</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715194</v>
+        <v>715264</v>
       </c>
       <c r="R66" t="n">
-        <v>6367686</v>
+        <v>6367986</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7009,19 +7009,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128722601</v>
+        <v>128721579</v>
       </c>
       <c r="B67" t="n">
         <v>86890</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715264</v>
+        <v>715191</v>
       </c>
       <c r="R67" t="n">
-        <v>6367986</v>
+        <v>6367888</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7106,22 +7106,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721579</v>
+        <v>128721514</v>
       </c>
       <c r="B68" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715191</v>
+        <v>715141</v>
       </c>
       <c r="R68" t="n">
-        <v>6367888</v>
+        <v>6367822</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7215,10 +7215,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721514</v>
+        <v>128721651</v>
       </c>
       <c r="B69" t="n">
-        <v>86729</v>
+        <v>86890</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715141</v>
+        <v>715215</v>
       </c>
       <c r="R69" t="n">
-        <v>6367822</v>
+        <v>6367933</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7300,22 +7300,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721651</v>
+        <v>128721635</v>
       </c>
       <c r="B70" t="n">
-        <v>86890</v>
+        <v>86903</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,21 +7323,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715215</v>
+        <v>715194</v>
       </c>
       <c r="R70" t="n">
-        <v>6367933</v>
+        <v>6367686</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -7999,10 +7999,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128722521</v>
+        <v>128721642</v>
       </c>
       <c r="B77" t="n">
-        <v>86972</v>
+        <v>86949</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715207</v>
+        <v>715204</v>
       </c>
       <c r="R77" t="n">
-        <v>6367905</v>
+        <v>6367900</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8078,29 +8078,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128721642</v>
+        <v>128722521</v>
       </c>
       <c r="B78" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8108,21 +8107,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8132,10 +8131,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715204</v>
+        <v>715207</v>
       </c>
       <c r="R78" t="n">
-        <v>6367900</v>
+        <v>6367905</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8176,50 +8175,51 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721503</v>
+        <v>128721521</v>
       </c>
       <c r="B79" t="n">
-        <v>110704</v>
+        <v>86927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715170</v>
+        <v>715183</v>
       </c>
       <c r="R79" t="n">
-        <v>6367852</v>
+        <v>6368007</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8273,6 +8273,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8284,39 +8285,39 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128721521</v>
+        <v>128721503</v>
       </c>
       <c r="B80" t="n">
-        <v>86927</v>
+        <v>110713</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>219711</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8326,10 +8327,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715183</v>
+        <v>715170</v>
       </c>
       <c r="R80" t="n">
-        <v>6368007</v>
+        <v>6367852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8370,7 +8371,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8382,39 +8382,39 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722549</v>
+        <v>128722589</v>
       </c>
       <c r="B81" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715448</v>
+        <v>715223</v>
       </c>
       <c r="R81" t="n">
-        <v>6367902</v>
+        <v>6367944</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8468,7 +8468,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8487,10 +8486,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128721502</v>
+        <v>128722581</v>
       </c>
       <c r="B82" t="n">
-        <v>90986</v>
+        <v>86949</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8498,21 +8497,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>256335</v>
+        <v>449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8566,51 +8565,50 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722560</v>
+        <v>128722607</v>
       </c>
       <c r="B83" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8620,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715549</v>
+        <v>715545</v>
       </c>
       <c r="R83" t="n">
-        <v>6367883</v>
+        <v>6367864</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8664,7 +8662,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8683,32 +8680,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722547</v>
+        <v>128721575</v>
       </c>
       <c r="B84" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8718,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715525</v>
+        <v>715333</v>
       </c>
       <c r="R84" t="n">
-        <v>6367901</v>
+        <v>6368090</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8762,51 +8759,50 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722589</v>
+        <v>128721581</v>
       </c>
       <c r="B85" t="n">
-        <v>86775</v>
+        <v>86890</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8816,10 +8812,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715223</v>
+        <v>715150</v>
       </c>
       <c r="R85" t="n">
-        <v>6367944</v>
+        <v>6367790</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8866,44 +8862,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722607</v>
+        <v>128722549</v>
       </c>
       <c r="B86" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8913,10 +8909,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715545</v>
+        <v>715448</v>
       </c>
       <c r="R86" t="n">
-        <v>6367864</v>
+        <v>6367902</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8957,6 +8953,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -8975,32 +8972,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128721575</v>
+        <v>128721502</v>
       </c>
       <c r="B87" t="n">
-        <v>86890</v>
+        <v>90986</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3674</v>
+        <v>256335</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9010,10 +9007,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715333</v>
+        <v>715210</v>
       </c>
       <c r="R87" t="n">
-        <v>6368090</v>
+        <v>6367925</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9054,6 +9051,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9065,39 +9063,39 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128721581</v>
+        <v>128722560</v>
       </c>
       <c r="B88" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9107,10 +9105,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715150</v>
+        <v>715549</v>
       </c>
       <c r="R88" t="n">
-        <v>6367790</v>
+        <v>6367883</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9151,50 +9149,51 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722581</v>
+        <v>128722547</v>
       </c>
       <c r="B89" t="n">
-        <v>86949</v>
+        <v>86927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9204,10 +9203,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715210</v>
+        <v>715525</v>
       </c>
       <c r="R89" t="n">
-        <v>6367925</v>
+        <v>6367901</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9248,6 +9247,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9266,32 +9266,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128721552</v>
+        <v>128722565</v>
       </c>
       <c r="B90" t="n">
-        <v>105642</v>
+        <v>91001</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>5747</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715197</v>
+        <v>715311</v>
       </c>
       <c r="R90" t="n">
-        <v>6367683</v>
+        <v>6367855</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9351,44 +9351,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128722565</v>
+        <v>128721552</v>
       </c>
       <c r="B91" t="n">
-        <v>91001</v>
+        <v>105651</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5747</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715311</v>
+        <v>715197</v>
       </c>
       <c r="R91" t="n">
-        <v>6367855</v>
+        <v>6367683</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9448,44 +9448,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128722558</v>
+        <v>128722519</v>
       </c>
       <c r="B92" t="n">
-        <v>86927</v>
+        <v>90941</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>720</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715177</v>
+        <v>715292</v>
       </c>
       <c r="R92" t="n">
-        <v>6367636</v>
+        <v>6367865</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9539,7 +9539,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9558,32 +9557,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128721647</v>
+        <v>128722603</v>
       </c>
       <c r="B93" t="n">
-        <v>86682</v>
+        <v>86890</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9593,10 +9592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715216</v>
+        <v>715233</v>
       </c>
       <c r="R93" t="n">
-        <v>6367898</v>
+        <v>6367868</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9631,62 +9630,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722603</v>
+        <v>128722558</v>
       </c>
       <c r="B94" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9696,10 +9689,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715233</v>
+        <v>715177</v>
       </c>
       <c r="R94" t="n">
-        <v>6367868</v>
+        <v>6367636</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9740,6 +9733,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9758,32 +9752,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722519</v>
+        <v>128721647</v>
       </c>
       <c r="B95" t="n">
-        <v>90941</v>
+        <v>86682</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>720</v>
+        <v>249278</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9787,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715292</v>
+        <v>715216</v>
       </c>
       <c r="R95" t="n">
-        <v>6367865</v>
+        <v>6367898</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9831,77 +9825,75 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721508</v>
+        <v>128721541</v>
       </c>
       <c r="B96" t="n">
-        <v>57686</v>
+        <v>75115</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715206</v>
+        <v>715250</v>
       </c>
       <c r="R96" t="n">
-        <v>6367909</v>
+        <v>6367931</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9953,39 +9945,39 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128722597</v>
+        <v>128721542</v>
       </c>
       <c r="B97" t="n">
-        <v>86880</v>
+        <v>75115</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003235</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9995,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715216</v>
+        <v>715519</v>
       </c>
       <c r="R97" t="n">
-        <v>6367914</v>
+        <v>6367602</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10020,7 +10012,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10039,51 +10031,50 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721649</v>
+        <v>128722597</v>
       </c>
       <c r="B98" t="n">
-        <v>86890</v>
+        <v>86880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>6003235</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10093,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715314</v>
+        <v>715216</v>
       </c>
       <c r="R98" t="n">
-        <v>6368077</v>
+        <v>6367914</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10137,28 +10128,29 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721541</v>
+        <v>128721649</v>
       </c>
       <c r="B99" t="n">
-        <v>75115</v>
+        <v>86890</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10166,21 +10158,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10190,10 +10182,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715250</v>
+        <v>715314</v>
       </c>
       <c r="R99" t="n">
-        <v>6367931</v>
+        <v>6368077</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10240,57 +10232,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721542</v>
+        <v>128721508</v>
       </c>
       <c r="B100" t="n">
-        <v>75115</v>
+        <v>57686</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715519</v>
+        <v>715206</v>
       </c>
       <c r="R100" t="n">
-        <v>6367602</v>
+        <v>6367909</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -10349,32 +10349,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128722587</v>
+        <v>128722598</v>
       </c>
       <c r="B101" t="n">
-        <v>86950</v>
+        <v>86775</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715464</v>
+        <v>715487</v>
       </c>
       <c r="R101" t="n">
-        <v>6367911</v>
+        <v>6367923</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10446,32 +10446,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128721519</v>
+        <v>128722579</v>
       </c>
       <c r="B102" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715287</v>
+        <v>715205</v>
       </c>
       <c r="R102" t="n">
-        <v>6368083</v>
+        <v>6367943</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10525,51 +10525,50 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128722546</v>
+        <v>128721583</v>
       </c>
       <c r="B103" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10579,10 +10578,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715298</v>
+        <v>715492</v>
       </c>
       <c r="R103" t="n">
-        <v>6367872</v>
+        <v>6367606</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10604,7 +10603,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10623,51 +10622,50 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722598</v>
+        <v>128722587</v>
       </c>
       <c r="B104" t="n">
-        <v>86775</v>
+        <v>86950</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10677,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715487</v>
+        <v>715464</v>
       </c>
       <c r="R104" t="n">
-        <v>6367923</v>
+        <v>6367911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10739,32 +10737,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722579</v>
+        <v>128721519</v>
       </c>
       <c r="B105" t="n">
-        <v>86949</v>
+        <v>86927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10774,10 +10772,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715205</v>
+        <v>715287</v>
       </c>
       <c r="R105" t="n">
-        <v>6367943</v>
+        <v>6368083</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10818,50 +10816,51 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128721583</v>
+        <v>128722546</v>
       </c>
       <c r="B106" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10871,10 +10870,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715492</v>
+        <v>715298</v>
       </c>
       <c r="R106" t="n">
-        <v>6367606</v>
+        <v>6367872</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10896,7 +10895,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -10915,50 +10914,51 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722522</v>
+        <v>128722599</v>
       </c>
       <c r="B107" t="n">
-        <v>86729</v>
+        <v>86949</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715314</v>
+        <v>715214</v>
       </c>
       <c r="R107" t="n">
-        <v>6367886</v>
+        <v>6367950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11006,12 +11006,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11030,7 +11036,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128722585</v>
+        <v>128722522</v>
       </c>
       <c r="B108" t="n">
         <v>86729</v>
@@ -11065,10 +11071,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715309</v>
+        <v>715314</v>
       </c>
       <c r="R108" t="n">
-        <v>6367883</v>
+        <v>6367886</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11127,32 +11133,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128722599</v>
+        <v>128722585</v>
       </c>
       <c r="B109" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11162,10 +11168,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715214</v>
+        <v>715309</v>
       </c>
       <c r="R109" t="n">
-        <v>6367950</v>
+        <v>6367883</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11200,18 +11206,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11417,7 +11417,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11515,39 +11515,39 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128721500</v>
+        <v>128722548</v>
       </c>
       <c r="B113" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715318</v>
+        <v>715513</v>
       </c>
       <c r="R113" t="n">
-        <v>6368090</v>
+        <v>6367892</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11601,50 +11601,51 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128722523</v>
+        <v>128721524</v>
       </c>
       <c r="B114" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11655,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715327</v>
+        <v>715222</v>
       </c>
       <c r="R114" t="n">
-        <v>6367899</v>
+        <v>6367894</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11698,50 +11699,51 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128721650</v>
+        <v>128721500</v>
       </c>
       <c r="B115" t="n">
-        <v>86890</v>
+        <v>86972</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11751,10 +11753,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715161</v>
+        <v>715318</v>
       </c>
       <c r="R115" t="n">
-        <v>6368017</v>
+        <v>6368090</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11801,22 +11803,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128722535</v>
+        <v>128722523</v>
       </c>
       <c r="B116" t="n">
-        <v>86753</v>
+        <v>86729</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11824,21 +11826,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11848,10 +11850,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715500</v>
+        <v>715327</v>
       </c>
       <c r="R116" t="n">
-        <v>6367907</v>
+        <v>6367899</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11910,10 +11912,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722541</v>
+        <v>128721650</v>
       </c>
       <c r="B117" t="n">
-        <v>86729</v>
+        <v>86890</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11921,21 +11923,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11945,10 +11947,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715501</v>
+        <v>715161</v>
       </c>
       <c r="R117" t="n">
-        <v>6367911</v>
+        <v>6368017</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11995,22 +11997,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722586</v>
+        <v>128722535</v>
       </c>
       <c r="B118" t="n">
-        <v>86729</v>
+        <v>86753</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12018,21 +12020,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12042,10 +12044,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715507</v>
+        <v>715500</v>
       </c>
       <c r="R118" t="n">
-        <v>6367904</v>
+        <v>6367907</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12104,10 +12106,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128721537</v>
+        <v>128722541</v>
       </c>
       <c r="B119" t="n">
-        <v>75115</v>
+        <v>86729</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12115,21 +12117,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12139,10 +12141,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715344</v>
+        <v>715501</v>
       </c>
       <c r="R119" t="n">
-        <v>6368190</v>
+        <v>6367911</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12189,22 +12191,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722562</v>
+        <v>128722586</v>
       </c>
       <c r="B120" t="n">
-        <v>98622</v>
+        <v>86729</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12212,21 +12214,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219874</v>
+        <v>3762</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12236,10 +12238,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715452</v>
+        <v>715507</v>
       </c>
       <c r="R120" t="n">
-        <v>6367610</v>
+        <v>6367904</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12261,7 +12263,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12298,32 +12300,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128722548</v>
+        <v>128721537</v>
       </c>
       <c r="B121" t="n">
-        <v>86927</v>
+        <v>75115</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12333,10 +12335,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715513</v>
+        <v>715344</v>
       </c>
       <c r="R121" t="n">
-        <v>6367892</v>
+        <v>6368190</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12377,51 +12379,50 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128721524</v>
+        <v>128722562</v>
       </c>
       <c r="B122" t="n">
-        <v>86927</v>
+        <v>98625</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12431,10 +12432,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715222</v>
+        <v>715452</v>
       </c>
       <c r="R122" t="n">
-        <v>6367894</v>
+        <v>6367610</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12456,7 +12457,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -12475,29 +12476,28 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128722605</v>
+        <v>128721538</v>
       </c>
       <c r="B123" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715315</v>
+        <v>715352</v>
       </c>
       <c r="R123" t="n">
-        <v>6367838</v>
+        <v>6368147</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12579,22 +12579,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128721538</v>
+        <v>128722605</v>
       </c>
       <c r="B124" t="n">
-        <v>75115</v>
+        <v>86890</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715352</v>
+        <v>715315</v>
       </c>
       <c r="R124" t="n">
-        <v>6368147</v>
+        <v>6367838</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,12 +12676,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13378,7 +13378,7 @@
         <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -1454,48 +1454,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128722583</v>
+        <v>128722552</v>
       </c>
       <c r="B10" t="n">
-        <v>92790</v>
+        <v>86927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715227</v>
+        <v>715271</v>
       </c>
       <c r="R10" t="n">
-        <v>6367937</v>
+        <v>6367998</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1555,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722552</v>
+        <v>128722595</v>
       </c>
       <c r="B11" t="n">
-        <v>86927</v>
+        <v>86880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1590,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715271</v>
+        <v>715468</v>
       </c>
       <c r="R11" t="n">
-        <v>6367998</v>
+        <v>6367935</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722595</v>
+        <v>128722578</v>
       </c>
       <c r="B12" t="n">
-        <v>86880</v>
+        <v>86949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003235</v>
+        <v>449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715468</v>
+        <v>715461</v>
       </c>
       <c r="R12" t="n">
-        <v>6367935</v>
+        <v>6367905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1732,7 +1729,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1751,45 +1747,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722578</v>
+        <v>128722583</v>
       </c>
       <c r="B13" t="n">
-        <v>86949</v>
+        <v>92790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715461</v>
+        <v>715227</v>
       </c>
       <c r="R13" t="n">
-        <v>6367905</v>
+        <v>6367937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,6 +1829,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B14" t="n">
-        <v>105638</v>
+        <v>86914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R14" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B15" t="n">
-        <v>86914</v>
+        <v>105638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R15" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,12 +2030,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3707,45 +3707,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722577</v>
+        <v>128722517</v>
       </c>
       <c r="B33" t="n">
-        <v>86949</v>
+        <v>86682</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>449</v>
+        <v>249278</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715502</v>
+        <v>715318</v>
       </c>
       <c r="R33" t="n">
-        <v>6367602</v>
+        <v>6367974</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3767,7 +3770,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3786,6 +3789,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3804,32 +3808,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722608</v>
+        <v>128722556</v>
       </c>
       <c r="B34" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3843,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715211</v>
+        <v>715180</v>
       </c>
       <c r="R34" t="n">
-        <v>6367929</v>
+        <v>6368021</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3883,6 +3887,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3901,10 +3906,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722564</v>
+        <v>128722577</v>
       </c>
       <c r="B35" t="n">
-        <v>86914</v>
+        <v>86949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3912,21 +3917,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3941,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715387</v>
+        <v>715502</v>
       </c>
       <c r="R35" t="n">
-        <v>6367908</v>
+        <v>6367602</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3961,7 +3966,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3998,10 +4003,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721511</v>
+        <v>128722608</v>
       </c>
       <c r="B36" t="n">
-        <v>91239</v>
+        <v>86890</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4009,21 +4014,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4038,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715180</v>
+        <v>715211</v>
       </c>
       <c r="R36" t="n">
-        <v>6367626</v>
+        <v>6367929</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,44 +4088,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721513</v>
+        <v>128722564</v>
       </c>
       <c r="B37" t="n">
-        <v>86729</v>
+        <v>86914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3762</v>
+        <v>3599</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715408</v>
+        <v>715387</v>
       </c>
       <c r="R37" t="n">
-        <v>6368189</v>
+        <v>6367908</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,22 +4185,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128722542</v>
+        <v>128721511</v>
       </c>
       <c r="B38" t="n">
-        <v>86729</v>
+        <v>91239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4203,21 +4208,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4227,10 +4232,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715218</v>
+        <v>715180</v>
       </c>
       <c r="R38" t="n">
-        <v>6367844</v>
+        <v>6367626</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4277,44 +4282,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722566</v>
+        <v>128721513</v>
       </c>
       <c r="B39" t="n">
-        <v>91001</v>
+        <v>86729</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5747</v>
+        <v>3762</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715288</v>
+        <v>715408</v>
       </c>
       <c r="R39" t="n">
-        <v>6367866</v>
+        <v>6368189</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,60 +4379,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722517</v>
+        <v>128722542</v>
       </c>
       <c r="B40" t="n">
-        <v>86682</v>
+        <v>86729</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>249278</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715318</v>
+        <v>715218</v>
       </c>
       <c r="R40" t="n">
-        <v>6367974</v>
+        <v>6367844</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,7 +4470,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4487,32 +4488,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722556</v>
+        <v>128722566</v>
       </c>
       <c r="B41" t="n">
-        <v>86927</v>
+        <v>91001</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4522,10 +4523,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715180</v>
+        <v>715288</v>
       </c>
       <c r="R41" t="n">
-        <v>6368021</v>
+        <v>6367866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6144,32 +6144,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128721496</v>
+        <v>128721547</v>
       </c>
       <c r="B58" t="n">
-        <v>86870</v>
+        <v>105638</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>473</v>
+        <v>224098</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715344</v>
+        <v>715154</v>
       </c>
       <c r="R58" t="n">
-        <v>6368190</v>
+        <v>6367783</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6223,7 +6223,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6242,32 +6241,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128721547</v>
+        <v>128721496</v>
       </c>
       <c r="B59" t="n">
-        <v>105638</v>
+        <v>86870</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>224098</v>
+        <v>473</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6277,10 +6276,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715154</v>
+        <v>715344</v>
       </c>
       <c r="R59" t="n">
-        <v>6367783</v>
+        <v>6368190</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6321,6 +6320,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6924,32 +6924,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128722601</v>
+        <v>128721522</v>
       </c>
       <c r="B66" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715264</v>
+        <v>715221</v>
       </c>
       <c r="R66" t="n">
-        <v>6367986</v>
+        <v>6367902</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7003,50 +7003,51 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721579</v>
+        <v>128722550</v>
       </c>
       <c r="B67" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7057,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715191</v>
+        <v>715321</v>
       </c>
       <c r="R67" t="n">
-        <v>6367888</v>
+        <v>6367984</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7100,50 +7101,51 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721514</v>
+        <v>128722596</v>
       </c>
       <c r="B68" t="n">
-        <v>86729</v>
+        <v>86880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3762</v>
+        <v>6003235</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7155,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715141</v>
+        <v>715196</v>
       </c>
       <c r="R68" t="n">
-        <v>6367822</v>
+        <v>6367906</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7197,50 +7199,51 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721651</v>
+        <v>128721523</v>
       </c>
       <c r="B69" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715215</v>
+        <v>715146</v>
       </c>
       <c r="R69" t="n">
-        <v>6367933</v>
+        <v>6367798</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7294,63 +7297,67 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721635</v>
+        <v>128722516</v>
       </c>
       <c r="B70" t="n">
-        <v>86903</v>
+        <v>86682</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715194</v>
+        <v>715492</v>
       </c>
       <c r="R70" t="n">
-        <v>6367686</v>
+        <v>6367910</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7391,50 +7398,51 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721629</v>
+        <v>128722601</v>
       </c>
       <c r="B71" t="n">
-        <v>57686</v>
+        <v>86890</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7452,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715504</v>
+        <v>715264</v>
       </c>
       <c r="R71" t="n">
-        <v>6367595</v>
+        <v>6367986</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7469,7 +7477,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7494,44 +7502,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128721522</v>
+        <v>128721635</v>
       </c>
       <c r="B72" t="n">
-        <v>86927</v>
+        <v>86903</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7541,10 +7549,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715221</v>
+        <v>715194</v>
       </c>
       <c r="R72" t="n">
-        <v>6367902</v>
+        <v>6367686</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7585,51 +7593,50 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128722550</v>
+        <v>128721579</v>
       </c>
       <c r="B73" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7639,10 +7646,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715321</v>
+        <v>715191</v>
       </c>
       <c r="R73" t="n">
-        <v>6367984</v>
+        <v>6367888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7683,51 +7690,50 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128722596</v>
+        <v>128721514</v>
       </c>
       <c r="B74" t="n">
-        <v>86880</v>
+        <v>86729</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003235</v>
+        <v>3762</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7737,10 +7743,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715196</v>
+        <v>715141</v>
       </c>
       <c r="R74" t="n">
-        <v>6367906</v>
+        <v>6367822</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7781,51 +7787,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128721523</v>
+        <v>128721651</v>
       </c>
       <c r="B75" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7835,10 +7840,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715146</v>
+        <v>715215</v>
       </c>
       <c r="R75" t="n">
-        <v>6367798</v>
+        <v>6367933</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7879,29 +7884,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128722516</v>
+        <v>128721629</v>
       </c>
       <c r="B76" t="n">
-        <v>86682</v>
+        <v>57686</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,37 +7913,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>249278</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715492</v>
+        <v>715504</v>
       </c>
       <c r="R76" t="n">
-        <v>6367910</v>
+        <v>6367595</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7961,7 +7962,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -7980,29 +7981,28 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128721642</v>
+        <v>128722521</v>
       </c>
       <c r="B77" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715204</v>
+        <v>715207</v>
       </c>
       <c r="R77" t="n">
-        <v>6367900</v>
+        <v>6367905</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8078,28 +8078,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128722521</v>
+        <v>128721642</v>
       </c>
       <c r="B78" t="n">
-        <v>86972</v>
+        <v>86949</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8107,21 +8108,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8131,10 +8132,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715207</v>
+        <v>715204</v>
       </c>
       <c r="R78" t="n">
-        <v>6367905</v>
+        <v>6367900</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8175,51 +8176,50 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721521</v>
+        <v>128721503</v>
       </c>
       <c r="B79" t="n">
-        <v>86927</v>
+        <v>110713</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>219711</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715183</v>
+        <v>715170</v>
       </c>
       <c r="R79" t="n">
-        <v>6368007</v>
+        <v>6367852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8273,7 +8273,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8292,32 +8291,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128721503</v>
+        <v>128721521</v>
       </c>
       <c r="B80" t="n">
-        <v>110713</v>
+        <v>86927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8327,10 +8326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715170</v>
+        <v>715183</v>
       </c>
       <c r="R80" t="n">
-        <v>6367852</v>
+        <v>6368007</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8371,6 +8370,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722589</v>
+        <v>128722607</v>
       </c>
       <c r="B81" t="n">
-        <v>86775</v>
+        <v>86890</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715223</v>
+        <v>715545</v>
       </c>
       <c r="R81" t="n">
-        <v>6367944</v>
+        <v>6367864</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8486,32 +8486,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128722581</v>
+        <v>128721575</v>
       </c>
       <c r="B82" t="n">
-        <v>86949</v>
+        <v>86890</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715210</v>
+        <v>715333</v>
       </c>
       <c r="R82" t="n">
-        <v>6367925</v>
+        <v>6368090</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8571,19 +8571,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722607</v>
+        <v>128721581</v>
       </c>
       <c r="B83" t="n">
         <v>86890</v>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715545</v>
+        <v>715150</v>
       </c>
       <c r="R83" t="n">
-        <v>6367864</v>
+        <v>6367790</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8668,44 +8668,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128721575</v>
+        <v>128722589</v>
       </c>
       <c r="B84" t="n">
-        <v>86890</v>
+        <v>86775</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715333</v>
+        <v>715223</v>
       </c>
       <c r="R84" t="n">
-        <v>6368090</v>
+        <v>6367944</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8765,44 +8765,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128721581</v>
+        <v>128722581</v>
       </c>
       <c r="B85" t="n">
-        <v>86890</v>
+        <v>86949</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715150</v>
+        <v>715210</v>
       </c>
       <c r="R85" t="n">
-        <v>6367790</v>
+        <v>6367925</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8862,44 +8862,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722549</v>
+        <v>128722565</v>
       </c>
       <c r="B86" t="n">
-        <v>86927</v>
+        <v>91001</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715448</v>
+        <v>715311</v>
       </c>
       <c r="R86" t="n">
-        <v>6367902</v>
+        <v>6367855</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8953,7 +8953,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -8972,32 +8971,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128721502</v>
+        <v>128721552</v>
       </c>
       <c r="B87" t="n">
-        <v>90986</v>
+        <v>105651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>256335</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9007,10 +9006,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715210</v>
+        <v>715197</v>
       </c>
       <c r="R87" t="n">
-        <v>6367925</v>
+        <v>6367683</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9051,7 +9050,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9070,7 +9068,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722560</v>
+        <v>128722549</v>
       </c>
       <c r="B88" t="n">
         <v>86927</v>
@@ -9105,10 +9103,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715549</v>
+        <v>715448</v>
       </c>
       <c r="R88" t="n">
-        <v>6367883</v>
+        <v>6367902</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9168,32 +9166,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722547</v>
+        <v>128721502</v>
       </c>
       <c r="B89" t="n">
-        <v>86927</v>
+        <v>90986</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>256335</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9203,10 +9201,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715525</v>
+        <v>715210</v>
       </c>
       <c r="R89" t="n">
-        <v>6367901</v>
+        <v>6367925</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9254,44 +9252,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128722565</v>
+        <v>128722560</v>
       </c>
       <c r="B90" t="n">
-        <v>91001</v>
+        <v>86927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9301,10 +9299,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715311</v>
+        <v>715549</v>
       </c>
       <c r="R90" t="n">
-        <v>6367855</v>
+        <v>6367883</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9345,6 +9343,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9363,32 +9362,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128721552</v>
+        <v>128722547</v>
       </c>
       <c r="B91" t="n">
-        <v>105651</v>
+        <v>86927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>6003295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9397,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715197</v>
+        <v>715525</v>
       </c>
       <c r="R91" t="n">
-        <v>6367683</v>
+        <v>6367901</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9442,18 +9441,19 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10933,10 +10933,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722599</v>
+        <v>128721572</v>
       </c>
       <c r="B107" t="n">
-        <v>86949</v>
+        <v>86880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10944,21 +10944,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>449</v>
+        <v>6003235</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715214</v>
+        <v>715132</v>
       </c>
       <c r="R107" t="n">
-        <v>6367950</v>
+        <v>6367819</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11006,62 +11006,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128722522</v>
+        <v>128721520</v>
       </c>
       <c r="B108" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11071,10 +11065,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715314</v>
+        <v>715280</v>
       </c>
       <c r="R108" t="n">
-        <v>6367886</v>
+        <v>6368028</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11115,50 +11109,51 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128722585</v>
+        <v>128722599</v>
       </c>
       <c r="B109" t="n">
-        <v>86729</v>
+        <v>86949</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11168,10 +11163,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715309</v>
+        <v>715214</v>
       </c>
       <c r="R109" t="n">
-        <v>6367883</v>
+        <v>6367950</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11206,12 +11201,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11230,7 +11231,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128722545</v>
+        <v>128722522</v>
       </c>
       <c r="B110" t="n">
         <v>86729</v>
@@ -11265,10 +11266,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715261</v>
+        <v>715314</v>
       </c>
       <c r="R110" t="n">
-        <v>6367632</v>
+        <v>6367886</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11327,32 +11328,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128721572</v>
+        <v>128722585</v>
       </c>
       <c r="B111" t="n">
-        <v>86880</v>
+        <v>86729</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003235</v>
+        <v>3762</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11362,10 +11363,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715132</v>
+        <v>715309</v>
       </c>
       <c r="R111" t="n">
-        <v>6367819</v>
+        <v>6367883</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11412,44 +11413,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128721520</v>
+        <v>128722545</v>
       </c>
       <c r="B112" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11459,10 +11460,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715280</v>
+        <v>715261</v>
       </c>
       <c r="R112" t="n">
-        <v>6368028</v>
+        <v>6367632</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11503,51 +11504,50 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128722548</v>
+        <v>128721500</v>
       </c>
       <c r="B113" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715513</v>
+        <v>715318</v>
       </c>
       <c r="R113" t="n">
-        <v>6367892</v>
+        <v>6368090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11601,51 +11601,50 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128721524</v>
+        <v>128722523</v>
       </c>
       <c r="B114" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11655,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715222</v>
+        <v>715327</v>
       </c>
       <c r="R114" t="n">
-        <v>6367894</v>
+        <v>6367899</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11699,51 +11698,50 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128721500</v>
+        <v>128721650</v>
       </c>
       <c r="B115" t="n">
-        <v>86972</v>
+        <v>86890</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11753,10 +11751,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715318</v>
+        <v>715161</v>
       </c>
       <c r="R115" t="n">
-        <v>6368090</v>
+        <v>6368017</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11803,22 +11801,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128722523</v>
+        <v>128722535</v>
       </c>
       <c r="B116" t="n">
-        <v>86729</v>
+        <v>86753</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11826,21 +11824,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11850,10 +11848,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715327</v>
+        <v>715500</v>
       </c>
       <c r="R116" t="n">
-        <v>6367899</v>
+        <v>6367907</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11912,10 +11910,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128721650</v>
+        <v>128722541</v>
       </c>
       <c r="B117" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11923,21 +11921,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11947,10 +11945,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715161</v>
+        <v>715501</v>
       </c>
       <c r="R117" t="n">
-        <v>6368017</v>
+        <v>6367911</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11997,22 +11995,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722535</v>
+        <v>128722586</v>
       </c>
       <c r="B118" t="n">
-        <v>86753</v>
+        <v>86729</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12020,21 +12018,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12044,10 +12042,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715500</v>
+        <v>715507</v>
       </c>
       <c r="R118" t="n">
-        <v>6367907</v>
+        <v>6367904</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12106,10 +12104,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128722541</v>
+        <v>128721537</v>
       </c>
       <c r="B119" t="n">
-        <v>86729</v>
+        <v>75115</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12117,21 +12115,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12141,10 +12139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715501</v>
+        <v>715344</v>
       </c>
       <c r="R119" t="n">
-        <v>6367911</v>
+        <v>6368190</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12191,22 +12189,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722586</v>
+        <v>128722562</v>
       </c>
       <c r="B120" t="n">
-        <v>86729</v>
+        <v>98625</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12214,21 +12212,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3762</v>
+        <v>219874</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12238,10 +12236,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715507</v>
+        <v>715452</v>
       </c>
       <c r="R120" t="n">
-        <v>6367904</v>
+        <v>6367610</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12263,7 +12261,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12300,32 +12298,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128721537</v>
+        <v>128722548</v>
       </c>
       <c r="B121" t="n">
-        <v>75115</v>
+        <v>86927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12335,10 +12333,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715344</v>
+        <v>715513</v>
       </c>
       <c r="R121" t="n">
-        <v>6368190</v>
+        <v>6367892</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12379,50 +12377,51 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128722562</v>
+        <v>128721524</v>
       </c>
       <c r="B122" t="n">
-        <v>98625</v>
+        <v>86927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12432,10 +12431,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715452</v>
+        <v>715222</v>
       </c>
       <c r="R122" t="n">
-        <v>6367610</v>
+        <v>6367894</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12457,7 +12456,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -12476,28 +12475,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128721538</v>
+        <v>128722605</v>
       </c>
       <c r="B123" t="n">
-        <v>75115</v>
+        <v>86890</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715352</v>
+        <v>715315</v>
       </c>
       <c r="R123" t="n">
-        <v>6368147</v>
+        <v>6367838</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12579,22 +12579,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128722605</v>
+        <v>128721538</v>
       </c>
       <c r="B124" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715315</v>
+        <v>715352</v>
       </c>
       <c r="R124" t="n">
-        <v>6367838</v>
+        <v>6368147</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,12 +12676,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128722539</v>
+        <v>128721539</v>
       </c>
       <c r="B2" t="n">
-        <v>86729</v>
+        <v>75115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715181</v>
+        <v>715289</v>
       </c>
       <c r="R2" t="n">
-        <v>6367653</v>
+        <v>6368047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128722600</v>
+        <v>128722539</v>
       </c>
       <c r="B3" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715327</v>
+        <v>715181</v>
       </c>
       <c r="R3" t="n">
-        <v>6367976</v>
+        <v>6367653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722536</v>
+        <v>128722600</v>
       </c>
       <c r="B4" t="n">
-        <v>91239</v>
+        <v>86890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715340</v>
+        <v>715327</v>
       </c>
       <c r="R4" t="n">
-        <v>6367945</v>
+        <v>6367976</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -967,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128721652</v>
+        <v>128722536</v>
       </c>
       <c r="B5" t="n">
-        <v>86890</v>
+        <v>91240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715207</v>
+        <v>715340</v>
       </c>
       <c r="R5" t="n">
-        <v>6367759</v>
+        <v>6367945</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,28 +1045,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128721501</v>
+        <v>128721652</v>
       </c>
       <c r="B6" t="n">
-        <v>88662</v>
+        <v>86890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4379</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715178</v>
+        <v>715207</v>
       </c>
       <c r="R6" t="n">
-        <v>6367628</v>
+        <v>6367759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,44 +1149,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721539</v>
+        <v>128721516</v>
       </c>
       <c r="B7" t="n">
-        <v>75115</v>
+        <v>86927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715289</v>
+        <v>715344</v>
       </c>
       <c r="R7" t="n">
-        <v>6368047</v>
+        <v>6368182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,6 +1240,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,7 +1259,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128721516</v>
+        <v>128722554</v>
       </c>
       <c r="B8" t="n">
         <v>86927</v>
@@ -1293,10 +1294,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715344</v>
+        <v>715247</v>
       </c>
       <c r="R8" t="n">
-        <v>6368182</v>
+        <v>6368027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,44 +1345,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128722554</v>
+        <v>128721501</v>
       </c>
       <c r="B9" t="n">
-        <v>86927</v>
+        <v>88662</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715247</v>
+        <v>715178</v>
       </c>
       <c r="R9" t="n">
-        <v>6368027</v>
+        <v>6367628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,19 +1436,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1650,45 +1650,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722578</v>
+        <v>128722583</v>
       </c>
       <c r="B12" t="n">
-        <v>86949</v>
+        <v>92791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715461</v>
+        <v>715227</v>
       </c>
       <c r="R12" t="n">
-        <v>6367905</v>
+        <v>6367937</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1729,6 +1732,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1747,48 +1751,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722583</v>
+        <v>128722578</v>
       </c>
       <c r="B13" t="n">
-        <v>92790</v>
+        <v>86949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715227</v>
+        <v>715461</v>
       </c>
       <c r="R13" t="n">
-        <v>6367937</v>
+        <v>6367905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1829,7 +1830,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>128721548</v>
       </c>
       <c r="B15" t="n">
-        <v>105638</v>
+        <v>105641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128722540</v>
+        <v>128721560</v>
       </c>
       <c r="B16" t="n">
-        <v>86729</v>
+        <v>86949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715194</v>
+        <v>715503</v>
       </c>
       <c r="R16" t="n">
-        <v>6367837</v>
+        <v>6367589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2121,29 +2121,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721499</v>
+        <v>128721559</v>
       </c>
       <c r="B17" t="n">
-        <v>86972</v>
+        <v>86949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715394</v>
+        <v>715505</v>
       </c>
       <c r="R17" t="n">
-        <v>6368208</v>
+        <v>6367598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,7 +2199,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2237,32 +2236,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721578</v>
+        <v>128721643</v>
       </c>
       <c r="B18" t="n">
-        <v>86890</v>
+        <v>86949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715215</v>
+        <v>715270</v>
       </c>
       <c r="R18" t="n">
-        <v>6367918</v>
+        <v>6367607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2322,60 +2321,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128722582</v>
+        <v>128721558</v>
       </c>
       <c r="B19" t="n">
-        <v>92790</v>
+        <v>86949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715492</v>
+        <v>715424</v>
       </c>
       <c r="R19" t="n">
-        <v>6367899</v>
+        <v>6367651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2397,7 +2393,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2416,29 +2412,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128722534</v>
+        <v>128722582</v>
       </c>
       <c r="B20" t="n">
-        <v>98569</v>
+        <v>92791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2446,34 +2441,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715228</v>
+        <v>715492</v>
       </c>
       <c r="R20" t="n">
-        <v>6367909</v>
+        <v>6367899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2514,6 +2512,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2532,32 +2531,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721560</v>
+        <v>128722540</v>
       </c>
       <c r="B21" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715503</v>
+        <v>715194</v>
       </c>
       <c r="R21" t="n">
-        <v>6367589</v>
+        <v>6367837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2592,7 +2591,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2611,28 +2610,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721559</v>
+        <v>128721499</v>
       </c>
       <c r="B22" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715505</v>
+        <v>715394</v>
       </c>
       <c r="R22" t="n">
-        <v>6367598</v>
+        <v>6368208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128721643</v>
+        <v>128721578</v>
       </c>
       <c r="B23" t="n">
-        <v>86949</v>
+        <v>86890</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715270</v>
+        <v>715215</v>
       </c>
       <c r="R23" t="n">
-        <v>6367607</v>
+        <v>6367918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2811,44 +2811,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128721558</v>
+        <v>128722534</v>
       </c>
       <c r="B24" t="n">
-        <v>86949</v>
+        <v>98570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>449</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>715424</v>
+        <v>715228</v>
       </c>
       <c r="R24" t="n">
-        <v>6367651</v>
+        <v>6367909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2908,44 +2908,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128722567</v>
+        <v>128721543</v>
       </c>
       <c r="B25" t="n">
-        <v>86972</v>
+        <v>75115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715339</v>
+        <v>715500</v>
       </c>
       <c r="R25" t="n">
-        <v>6367894</v>
+        <v>6367588</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -2993,62 +2993,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128722602</v>
+        <v>128721505</v>
       </c>
       <c r="B26" t="n">
-        <v>86890</v>
+        <v>86775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715200</v>
+        <v>715150</v>
       </c>
       <c r="R26" t="n">
-        <v>6367935</v>
+        <v>6367765</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3108,44 +3102,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128721543</v>
+        <v>128722567</v>
       </c>
       <c r="B27" t="n">
-        <v>75115</v>
+        <v>86972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715500</v>
+        <v>715339</v>
       </c>
       <c r="R27" t="n">
-        <v>6367588</v>
+        <v>6367894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3180,7 +3174,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3193,56 +3187,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128721505</v>
+        <v>128722602</v>
       </c>
       <c r="B28" t="n">
-        <v>86775</v>
+        <v>86890</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715150</v>
+        <v>715200</v>
       </c>
       <c r="R28" t="n">
-        <v>6367765</v>
+        <v>6367935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3302,22 +3302,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128722532</v>
+        <v>128721540</v>
       </c>
       <c r="B29" t="n">
-        <v>92401</v>
+        <v>75115</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715460</v>
+        <v>715278</v>
       </c>
       <c r="R29" t="n">
-        <v>6367601</v>
+        <v>6368028</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3399,44 +3399,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128721540</v>
+        <v>128721628</v>
       </c>
       <c r="B30" t="n">
-        <v>75115</v>
+        <v>86972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715278</v>
+        <v>715222</v>
       </c>
       <c r="R30" t="n">
-        <v>6368028</v>
+        <v>6367915</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3490,50 +3490,51 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128721628</v>
+        <v>128722532</v>
       </c>
       <c r="B31" t="n">
-        <v>86972</v>
+        <v>92402</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715222</v>
+        <v>715460</v>
       </c>
       <c r="R31" t="n">
-        <v>6367915</v>
+        <v>6367601</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3568,7 +3569,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3587,19 +3588,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3707,48 +3707,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722517</v>
+        <v>128722577</v>
       </c>
       <c r="B33" t="n">
-        <v>86682</v>
+        <v>86949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>249278</v>
+        <v>449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715318</v>
+        <v>715502</v>
       </c>
       <c r="R33" t="n">
-        <v>6367974</v>
+        <v>6367602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3770,7 +3767,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3789,7 +3786,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3808,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722556</v>
+        <v>128722608</v>
       </c>
       <c r="B34" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3843,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715180</v>
+        <v>715211</v>
       </c>
       <c r="R34" t="n">
-        <v>6368021</v>
+        <v>6367929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3887,7 +3883,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3906,10 +3901,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722577</v>
+        <v>128722564</v>
       </c>
       <c r="B35" t="n">
-        <v>86949</v>
+        <v>86914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3917,21 +3912,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3941,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715502</v>
+        <v>715387</v>
       </c>
       <c r="R35" t="n">
-        <v>6367602</v>
+        <v>6367908</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3966,7 +3961,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4003,10 +3998,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128722608</v>
+        <v>128721511</v>
       </c>
       <c r="B36" t="n">
-        <v>86890</v>
+        <v>91240</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4014,21 +4009,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4038,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715211</v>
+        <v>715180</v>
       </c>
       <c r="R36" t="n">
-        <v>6367929</v>
+        <v>6367626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4088,44 +4083,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722564</v>
+        <v>128721513</v>
       </c>
       <c r="B37" t="n">
-        <v>86914</v>
+        <v>86729</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3599</v>
+        <v>3762</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4135,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715387</v>
+        <v>715408</v>
       </c>
       <c r="R37" t="n">
-        <v>6367908</v>
+        <v>6368189</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4185,22 +4180,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721511</v>
+        <v>128722542</v>
       </c>
       <c r="B38" t="n">
-        <v>91239</v>
+        <v>86729</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4208,21 +4203,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4232,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715180</v>
+        <v>715218</v>
       </c>
       <c r="R38" t="n">
-        <v>6367626</v>
+        <v>6367844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4282,44 +4277,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721513</v>
+        <v>128722556</v>
       </c>
       <c r="B39" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715408</v>
+        <v>715180</v>
       </c>
       <c r="R39" t="n">
-        <v>6368189</v>
+        <v>6368021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4373,50 +4368,51 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722542</v>
+        <v>128722566</v>
       </c>
       <c r="B40" t="n">
-        <v>86729</v>
+        <v>91002</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3762</v>
+        <v>5747</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4426,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715218</v>
+        <v>715288</v>
       </c>
       <c r="R40" t="n">
-        <v>6367844</v>
+        <v>6367866</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4488,45 +4484,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722566</v>
+        <v>128722517</v>
       </c>
       <c r="B41" t="n">
-        <v>91001</v>
+        <v>86682</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5747</v>
+        <v>249278</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715288</v>
+        <v>715318</v>
       </c>
       <c r="R41" t="n">
-        <v>6367866</v>
+        <v>6367974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128721631</v>
+        <v>128721517</v>
       </c>
       <c r="B48" t="n">
         <v>86927</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715172</v>
+        <v>715323</v>
       </c>
       <c r="R48" t="n">
-        <v>6367927</v>
+        <v>6368092</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,19 +5254,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128721517</v>
+        <v>128721631</v>
       </c>
       <c r="B49" t="n">
         <v>86927</v>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715323</v>
+        <v>715172</v>
       </c>
       <c r="R49" t="n">
-        <v>6368092</v>
+        <v>6367927</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5352,44 +5352,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722580</v>
+        <v>128722544</v>
       </c>
       <c r="B50" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715209</v>
+        <v>715251</v>
       </c>
       <c r="R50" t="n">
-        <v>6367900</v>
+        <v>6367635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128722544</v>
+        <v>128721582</v>
       </c>
       <c r="B51" t="n">
-        <v>86729</v>
+        <v>86890</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715251</v>
+        <v>715178</v>
       </c>
       <c r="R51" t="n">
-        <v>6367635</v>
+        <v>6367640</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,22 +5546,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721582</v>
+        <v>128721568</v>
       </c>
       <c r="B52" t="n">
-        <v>86890</v>
+        <v>86753</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715178</v>
+        <v>715200</v>
       </c>
       <c r="R52" t="n">
-        <v>6367640</v>
+        <v>6367963</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128721568</v>
+        <v>128722580</v>
       </c>
       <c r="B53" t="n">
-        <v>86753</v>
+        <v>86949</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715200</v>
+        <v>715209</v>
       </c>
       <c r="R53" t="n">
-        <v>6367963</v>
+        <v>6367900</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,12 +5740,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
         <v>128721563</v>
       </c>
       <c r="B54" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>128722575</v>
       </c>
       <c r="B55" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128722604</v>
+        <v>128721496</v>
       </c>
       <c r="B56" t="n">
-        <v>86890</v>
+        <v>86870</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3674</v>
+        <v>473</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715309</v>
+        <v>715344</v>
       </c>
       <c r="R56" t="n">
-        <v>6367880</v>
+        <v>6368190</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6029,25 +6029,26 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128721580</v>
+        <v>128722604</v>
       </c>
       <c r="B57" t="n">
         <v>86890</v>
@@ -6082,10 +6083,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715147</v>
+        <v>715309</v>
       </c>
       <c r="R57" t="n">
-        <v>6367801</v>
+        <v>6367880</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6132,22 +6133,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128721547</v>
+        <v>128721580</v>
       </c>
       <c r="B58" t="n">
-        <v>105638</v>
+        <v>86890</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6155,21 +6156,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>224098</v>
+        <v>3674</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6179,10 +6180,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715154</v>
+        <v>715147</v>
       </c>
       <c r="R58" t="n">
-        <v>6367783</v>
+        <v>6367801</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6241,32 +6242,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128721496</v>
+        <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>86870</v>
+        <v>105641</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>473</v>
+        <v>224098</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6276,10 +6277,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715344</v>
+        <v>715154</v>
       </c>
       <c r="R59" t="n">
-        <v>6368190</v>
+        <v>6367783</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6320,7 +6321,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128722520</v>
+        <v>128721644</v>
       </c>
       <c r="B61" t="n">
-        <v>86972</v>
+        <v>86949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6448,21 +6448,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715450</v>
+        <v>715497</v>
       </c>
       <c r="R61" t="n">
-        <v>6367880</v>
+        <v>6367603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,51 +6516,50 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128721567</v>
+        <v>128722520</v>
       </c>
       <c r="B62" t="n">
-        <v>96187</v>
+        <v>86972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715422</v>
+        <v>715450</v>
       </c>
       <c r="R62" t="n">
-        <v>6367626</v>
+        <v>6367880</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6595,7 +6594,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -6614,50 +6613,51 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128721507</v>
+        <v>128721567</v>
       </c>
       <c r="B63" t="n">
-        <v>57686</v>
+        <v>96188</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715452</v>
+        <v>715422</v>
       </c>
       <c r="R63" t="n">
-        <v>6367607</v>
+        <v>6367626</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128722557</v>
+        <v>128721507</v>
       </c>
       <c r="B64" t="n">
-        <v>86927</v>
+        <v>57686</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,21 +6740,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715218</v>
+        <v>715452</v>
       </c>
       <c r="R64" t="n">
-        <v>6367940</v>
+        <v>6367607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6808,51 +6808,50 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128721644</v>
+        <v>128722557</v>
       </c>
       <c r="B65" t="n">
-        <v>86949</v>
+        <v>86927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6862,10 +6861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715497</v>
+        <v>715218</v>
       </c>
       <c r="R65" t="n">
-        <v>6367603</v>
+        <v>6367940</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6887,7 +6886,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -6906,50 +6905,51 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721522</v>
+        <v>128721635</v>
       </c>
       <c r="B66" t="n">
-        <v>86927</v>
+        <v>86903</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715221</v>
+        <v>715194</v>
       </c>
       <c r="R66" t="n">
-        <v>6367902</v>
+        <v>6367686</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7003,51 +7003,50 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128722550</v>
+        <v>128722601</v>
       </c>
       <c r="B67" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7057,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715321</v>
+        <v>715264</v>
       </c>
       <c r="R67" t="n">
-        <v>6367984</v>
+        <v>6367986</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7101,7 +7100,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7120,32 +7118,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128722596</v>
+        <v>128721579</v>
       </c>
       <c r="B68" t="n">
-        <v>86880</v>
+        <v>86890</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003235</v>
+        <v>3674</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7155,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715196</v>
+        <v>715191</v>
       </c>
       <c r="R68" t="n">
-        <v>6367906</v>
+        <v>6367888</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7199,51 +7197,50 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721523</v>
+        <v>128721514</v>
       </c>
       <c r="B69" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7253,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715146</v>
+        <v>715141</v>
       </c>
       <c r="R69" t="n">
-        <v>6367798</v>
+        <v>6367822</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7297,7 +7294,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7316,48 +7312,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128722516</v>
+        <v>128721651</v>
       </c>
       <c r="B70" t="n">
-        <v>86682</v>
+        <v>86890</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715492</v>
+        <v>715215</v>
       </c>
       <c r="R70" t="n">
-        <v>6367910</v>
+        <v>6367933</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7398,51 +7391,50 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128722601</v>
+        <v>128721629</v>
       </c>
       <c r="B71" t="n">
-        <v>86890</v>
+        <v>57686</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7452,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715264</v>
+        <v>715504</v>
       </c>
       <c r="R71" t="n">
-        <v>6367986</v>
+        <v>6367595</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7477,7 +7469,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7502,44 +7494,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128721635</v>
+        <v>128721523</v>
       </c>
       <c r="B72" t="n">
-        <v>86903</v>
+        <v>86927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7549,10 +7541,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715194</v>
+        <v>715146</v>
       </c>
       <c r="R72" t="n">
-        <v>6367686</v>
+        <v>6367798</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7593,50 +7585,51 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721579</v>
+        <v>128722596</v>
       </c>
       <c r="B73" t="n">
-        <v>86890</v>
+        <v>86880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3674</v>
+        <v>6003235</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7646,10 +7639,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715191</v>
+        <v>715196</v>
       </c>
       <c r="R73" t="n">
-        <v>6367888</v>
+        <v>6367906</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,50 +7683,51 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128721514</v>
+        <v>128722550</v>
       </c>
       <c r="B74" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7743,10 +7737,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715141</v>
+        <v>715321</v>
       </c>
       <c r="R74" t="n">
-        <v>6367822</v>
+        <v>6367984</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7787,50 +7781,51 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128721651</v>
+        <v>128721522</v>
       </c>
       <c r="B75" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7840,10 +7835,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715215</v>
+        <v>715221</v>
       </c>
       <c r="R75" t="n">
-        <v>6367933</v>
+        <v>6367902</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7884,28 +7879,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128721629</v>
+        <v>128722516</v>
       </c>
       <c r="B76" t="n">
-        <v>57686</v>
+        <v>86682</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7913,34 +7909,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>249278</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715504</v>
+        <v>715492</v>
       </c>
       <c r="R76" t="n">
-        <v>6367595</v>
+        <v>6367910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7962,7 +7961,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -7981,28 +7980,29 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128722521</v>
+        <v>128721642</v>
       </c>
       <c r="B77" t="n">
-        <v>86972</v>
+        <v>86949</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715207</v>
+        <v>715204</v>
       </c>
       <c r="R77" t="n">
-        <v>6367905</v>
+        <v>6367900</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8078,29 +8078,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128721642</v>
+        <v>128722521</v>
       </c>
       <c r="B78" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8108,21 +8107,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8132,10 +8131,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715204</v>
+        <v>715207</v>
       </c>
       <c r="R78" t="n">
-        <v>6367900</v>
+        <v>6367905</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8176,18 +8175,19 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
         <v>128721503</v>
       </c>
       <c r="B79" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722607</v>
+        <v>128722565</v>
       </c>
       <c r="B81" t="n">
-        <v>86890</v>
+        <v>91002</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715545</v>
+        <v>715311</v>
       </c>
       <c r="R81" t="n">
-        <v>6367864</v>
+        <v>6367855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8486,32 +8486,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128721575</v>
+        <v>128721502</v>
       </c>
       <c r="B82" t="n">
-        <v>86890</v>
+        <v>90987</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3674</v>
+        <v>256335</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715333</v>
+        <v>715210</v>
       </c>
       <c r="R82" t="n">
-        <v>6368090</v>
+        <v>6367925</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8565,6 +8565,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8583,32 +8584,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128721581</v>
+        <v>128722589</v>
       </c>
       <c r="B83" t="n">
-        <v>86890</v>
+        <v>86775</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8618,10 +8619,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715150</v>
+        <v>715223</v>
       </c>
       <c r="R83" t="n">
-        <v>6367790</v>
+        <v>6367944</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8668,22 +8669,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722589</v>
+        <v>128722581</v>
       </c>
       <c r="B84" t="n">
-        <v>86775</v>
+        <v>86949</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8691,21 +8692,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8716,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715223</v>
+        <v>715210</v>
       </c>
       <c r="R84" t="n">
-        <v>6367944</v>
+        <v>6367925</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8777,32 +8778,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722581</v>
+        <v>128722607</v>
       </c>
       <c r="B85" t="n">
-        <v>86949</v>
+        <v>86890</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8812,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715210</v>
+        <v>715545</v>
       </c>
       <c r="R85" t="n">
-        <v>6367925</v>
+        <v>6367864</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8874,32 +8875,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722565</v>
+        <v>128721575</v>
       </c>
       <c r="B86" t="n">
-        <v>91001</v>
+        <v>86890</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8909,10 +8910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715311</v>
+        <v>715333</v>
       </c>
       <c r="R86" t="n">
-        <v>6367855</v>
+        <v>6368090</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8959,22 +8960,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128721552</v>
+        <v>128721581</v>
       </c>
       <c r="B87" t="n">
-        <v>105651</v>
+        <v>86890</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8982,21 +8983,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221144</v>
+        <v>3674</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9006,10 +9007,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715197</v>
+        <v>715150</v>
       </c>
       <c r="R87" t="n">
-        <v>6367683</v>
+        <v>6367790</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9068,32 +9069,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722549</v>
+        <v>128721552</v>
       </c>
       <c r="B88" t="n">
-        <v>86927</v>
+        <v>105654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6003295</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9103,10 +9104,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715448</v>
+        <v>715197</v>
       </c>
       <c r="R88" t="n">
-        <v>6367902</v>
+        <v>6367683</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9147,51 +9148,50 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128721502</v>
+        <v>128722547</v>
       </c>
       <c r="B89" t="n">
-        <v>90986</v>
+        <v>86927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>256335</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715210</v>
+        <v>715525</v>
       </c>
       <c r="R89" t="n">
-        <v>6367925</v>
+        <v>6367901</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9252,12 +9252,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128722547</v>
+        <v>128722549</v>
       </c>
       <c r="B91" t="n">
         <v>86927</v>
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715525</v>
+        <v>715448</v>
       </c>
       <c r="R91" t="n">
-        <v>6367901</v>
+        <v>6367902</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9460,32 +9460,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128722519</v>
+        <v>128721647</v>
       </c>
       <c r="B92" t="n">
-        <v>90941</v>
+        <v>86682</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>720</v>
+        <v>249278</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715292</v>
+        <v>715216</v>
       </c>
       <c r="R92" t="n">
-        <v>6367865</v>
+        <v>6367898</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,56 +9533,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722603</v>
+        <v>128722558</v>
       </c>
       <c r="B93" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9592,10 +9598,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715233</v>
+        <v>715177</v>
       </c>
       <c r="R93" t="n">
-        <v>6367868</v>
+        <v>6367636</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9636,6 +9642,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9654,32 +9661,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722558</v>
+        <v>128722519</v>
       </c>
       <c r="B94" t="n">
-        <v>86927</v>
+        <v>90942</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6003295</v>
+        <v>720</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9689,10 +9696,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715177</v>
+        <v>715292</v>
       </c>
       <c r="R94" t="n">
-        <v>6367636</v>
+        <v>6367865</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9733,7 +9740,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9752,32 +9758,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128721647</v>
+        <v>128722603</v>
       </c>
       <c r="B95" t="n">
-        <v>86682</v>
+        <v>86890</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9787,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715216</v>
+        <v>715233</v>
       </c>
       <c r="R95" t="n">
-        <v>6367898</v>
+        <v>6367868</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9825,75 +9831,77 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721541</v>
+        <v>128721508</v>
       </c>
       <c r="B96" t="n">
-        <v>75115</v>
+        <v>57686</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715250</v>
+        <v>715206</v>
       </c>
       <c r="R96" t="n">
-        <v>6367931</v>
+        <v>6367909</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9952,32 +9960,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721542</v>
+        <v>128722597</v>
       </c>
       <c r="B97" t="n">
-        <v>75115</v>
+        <v>86880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6426</v>
+        <v>6003235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9995,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715519</v>
+        <v>715216</v>
       </c>
       <c r="R97" t="n">
-        <v>6367602</v>
+        <v>6367914</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10012,7 +10020,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10031,50 +10039,51 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128722597</v>
+        <v>128721541</v>
       </c>
       <c r="B98" t="n">
-        <v>86880</v>
+        <v>75115</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6003235</v>
+        <v>6426</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10093,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715216</v>
+        <v>715250</v>
       </c>
       <c r="R98" t="n">
-        <v>6367914</v>
+        <v>6367931</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10128,29 +10137,28 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721649</v>
+        <v>128721542</v>
       </c>
       <c r="B99" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10158,21 +10166,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10182,10 +10190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715314</v>
+        <v>715519</v>
       </c>
       <c r="R99" t="n">
-        <v>6368077</v>
+        <v>6367602</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10207,7 +10215,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -10232,65 +10240,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721508</v>
+        <v>128721649</v>
       </c>
       <c r="B100" t="n">
-        <v>57686</v>
+        <v>86890</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715206</v>
+        <v>715314</v>
       </c>
       <c r="R100" t="n">
-        <v>6367909</v>
+        <v>6368077</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10337,12 +10337,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10933,10 +10933,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128721572</v>
+        <v>128722599</v>
       </c>
       <c r="B107" t="n">
-        <v>86880</v>
+        <v>86949</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10944,21 +10944,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003235</v>
+        <v>449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715132</v>
+        <v>715214</v>
       </c>
       <c r="R107" t="n">
-        <v>6367819</v>
+        <v>6367950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11006,56 +11006,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128721520</v>
+        <v>128722522</v>
       </c>
       <c r="B108" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11065,10 +11071,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715280</v>
+        <v>715314</v>
       </c>
       <c r="R108" t="n">
-        <v>6368028</v>
+        <v>6367886</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11109,51 +11115,50 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128722599</v>
+        <v>128722585</v>
       </c>
       <c r="B109" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11163,10 +11168,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715214</v>
+        <v>715309</v>
       </c>
       <c r="R109" t="n">
-        <v>6367950</v>
+        <v>6367883</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11201,18 +11206,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11231,7 +11230,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128722522</v>
+        <v>128722545</v>
       </c>
       <c r="B110" t="n">
         <v>86729</v>
@@ -11266,10 +11265,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715314</v>
+        <v>715261</v>
       </c>
       <c r="R110" t="n">
-        <v>6367886</v>
+        <v>6367632</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11328,32 +11327,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128722585</v>
+        <v>128721520</v>
       </c>
       <c r="B111" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11363,10 +11362,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715309</v>
+        <v>715280</v>
       </c>
       <c r="R111" t="n">
-        <v>6367883</v>
+        <v>6368028</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11407,50 +11406,51 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128722545</v>
+        <v>128721572</v>
       </c>
       <c r="B112" t="n">
-        <v>86729</v>
+        <v>86880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3762</v>
+        <v>6003235</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11460,10 +11460,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715261</v>
+        <v>715132</v>
       </c>
       <c r="R112" t="n">
-        <v>6367632</v>
+        <v>6367819</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11510,44 +11510,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128721500</v>
+        <v>128721537</v>
       </c>
       <c r="B113" t="n">
-        <v>86972</v>
+        <v>75115</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715318</v>
+        <v>715344</v>
       </c>
       <c r="R113" t="n">
-        <v>6368090</v>
+        <v>6368190</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11619,32 +11619,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128722523</v>
+        <v>128721500</v>
       </c>
       <c r="B114" t="n">
-        <v>86729</v>
+        <v>86972</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715327</v>
+        <v>715318</v>
       </c>
       <c r="R114" t="n">
-        <v>6367899</v>
+        <v>6368090</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11704,22 +11704,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128721650</v>
+        <v>128722523</v>
       </c>
       <c r="B115" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11727,21 +11727,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11751,10 +11751,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715161</v>
+        <v>715327</v>
       </c>
       <c r="R115" t="n">
-        <v>6368017</v>
+        <v>6367899</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11801,22 +11801,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128722535</v>
+        <v>128721650</v>
       </c>
       <c r="B116" t="n">
-        <v>86753</v>
+        <v>86890</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11824,21 +11824,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11848,10 +11848,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715500</v>
+        <v>715161</v>
       </c>
       <c r="R116" t="n">
-        <v>6367907</v>
+        <v>6368017</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11898,22 +11898,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722541</v>
+        <v>128722535</v>
       </c>
       <c r="B117" t="n">
-        <v>86729</v>
+        <v>86753</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11921,21 +11921,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715501</v>
+        <v>715500</v>
       </c>
       <c r="R117" t="n">
-        <v>6367911</v>
+        <v>6367907</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12007,7 +12007,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722586</v>
+        <v>128722541</v>
       </c>
       <c r="B118" t="n">
         <v>86729</v>
@@ -12042,10 +12042,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715507</v>
+        <v>715501</v>
       </c>
       <c r="R118" t="n">
-        <v>6367904</v>
+        <v>6367911</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12104,10 +12104,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128721537</v>
+        <v>128722586</v>
       </c>
       <c r="B119" t="n">
-        <v>75115</v>
+        <v>86729</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12115,21 +12115,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12139,10 +12139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715344</v>
+        <v>715507</v>
       </c>
       <c r="R119" t="n">
-        <v>6368190</v>
+        <v>6367904</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12189,12 +12189,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12204,7 +12204,7 @@
         <v>128722562</v>
       </c>
       <c r="B120" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12494,10 +12494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128722605</v>
+        <v>128721538</v>
       </c>
       <c r="B123" t="n">
-        <v>86890</v>
+        <v>75115</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715315</v>
+        <v>715352</v>
       </c>
       <c r="R123" t="n">
-        <v>6367838</v>
+        <v>6368147</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12579,22 +12579,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128721538</v>
+        <v>128722605</v>
       </c>
       <c r="B124" t="n">
-        <v>75115</v>
+        <v>86890</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715352</v>
+        <v>715315</v>
       </c>
       <c r="R124" t="n">
-        <v>6368147</v>
+        <v>6367838</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,44 +12676,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721526</v>
+        <v>128722590</v>
       </c>
       <c r="B125" t="n">
-        <v>58059</v>
+        <v>86950</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103015</v>
+        <v>248947</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715155</v>
+        <v>715473</v>
       </c>
       <c r="R125" t="n">
-        <v>6367801</v>
+        <v>6367917</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12773,44 +12773,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128722590</v>
+        <v>128721526</v>
       </c>
       <c r="B126" t="n">
-        <v>86950</v>
+        <v>58059</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>248947</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12820,10 +12820,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715473</v>
+        <v>715155</v>
       </c>
       <c r="R126" t="n">
-        <v>6367917</v>
+        <v>6367801</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12870,12 +12870,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -12980,7 +12980,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722559</v>
+        <v>128722561</v>
       </c>
       <c r="B128" t="n">
         <v>86927</v>
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715256</v>
+        <v>715545</v>
       </c>
       <c r="R128" t="n">
-        <v>6367627</v>
+        <v>6367898</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13176,7 +13176,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722561</v>
+        <v>128722559</v>
       </c>
       <c r="B130" t="n">
         <v>86927</v>
@@ -13211,10 +13211,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715545</v>
+        <v>715256</v>
       </c>
       <c r="R130" t="n">
-        <v>6367898</v>
+        <v>6367627</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13378,7 +13378,7 @@
         <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128721539</v>
+        <v>128722536</v>
       </c>
       <c r="B2" t="n">
-        <v>75115</v>
+        <v>91267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715289</v>
+        <v>715340</v>
       </c>
       <c r="R2" t="n">
-        <v>6368047</v>
+        <v>6367945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,28 +754,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128722539</v>
+        <v>128721501</v>
       </c>
       <c r="B3" t="n">
-        <v>86729</v>
+        <v>88689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>4379</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715181</v>
+        <v>715178</v>
       </c>
       <c r="R3" t="n">
-        <v>6367653</v>
+        <v>6367628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722600</v>
+        <v>128722539</v>
       </c>
       <c r="B4" t="n">
-        <v>86890</v>
+        <v>86756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715327</v>
+        <v>715181</v>
       </c>
       <c r="R4" t="n">
-        <v>6367976</v>
+        <v>6367653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128722536</v>
+        <v>128722600</v>
       </c>
       <c r="B5" t="n">
-        <v>91240</v>
+        <v>86917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715340</v>
+        <v>715327</v>
       </c>
       <c r="R5" t="n">
-        <v>6367945</v>
+        <v>6367976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,7 +1046,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>128721652</v>
       </c>
       <c r="B6" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721516</v>
+        <v>128721539</v>
       </c>
       <c r="B7" t="n">
-        <v>86927</v>
+        <v>75142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715344</v>
+        <v>715289</v>
       </c>
       <c r="R7" t="n">
-        <v>6368182</v>
+        <v>6368047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1252,17 +1251,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128722554</v>
+        <v>128721516</v>
       </c>
       <c r="B8" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715247</v>
+        <v>715344</v>
       </c>
       <c r="R8" t="n">
-        <v>6368027</v>
+        <v>6368182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,44 +1344,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128721501</v>
+        <v>128722554</v>
       </c>
       <c r="B9" t="n">
-        <v>88662</v>
+        <v>86954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715178</v>
+        <v>715247</v>
       </c>
       <c r="R9" t="n">
-        <v>6367628</v>
+        <v>6368027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,63 +1435,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128722552</v>
+        <v>128722583</v>
       </c>
       <c r="B10" t="n">
-        <v>86927</v>
+        <v>92818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715271</v>
+        <v>715227</v>
       </c>
       <c r="R10" t="n">
-        <v>6367998</v>
+        <v>6367937</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1555,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722595</v>
+        <v>128722552</v>
       </c>
       <c r="B11" t="n">
-        <v>86880</v>
+        <v>86954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1590,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715468</v>
+        <v>715271</v>
       </c>
       <c r="R11" t="n">
-        <v>6367935</v>
+        <v>6367998</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,48 +1653,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722583</v>
+        <v>128722595</v>
       </c>
       <c r="B12" t="n">
-        <v>92791</v>
+        <v>86907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6003235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715227</v>
+        <v>715468</v>
       </c>
       <c r="R12" t="n">
-        <v>6367937</v>
+        <v>6367935</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>128722578</v>
       </c>
       <c r="B13" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128722563</v>
       </c>
       <c r="B14" t="n">
-        <v>86914</v>
+        <v>86941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128721548</v>
       </c>
       <c r="B15" t="n">
-        <v>105641</v>
+        <v>105669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,17 +2035,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128721560</v>
+        <v>128721643</v>
       </c>
       <c r="B16" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715503</v>
+        <v>715270</v>
       </c>
       <c r="R16" t="n">
-        <v>6367589</v>
+        <v>6367607</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2127,22 +2127,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721559</v>
+        <v>128721560</v>
       </c>
       <c r="B17" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715505</v>
+        <v>715503</v>
       </c>
       <c r="R17" t="n">
-        <v>6367598</v>
+        <v>6367589</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,17 +2229,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721643</v>
+        <v>128721559</v>
       </c>
       <c r="B18" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715270</v>
+        <v>715505</v>
       </c>
       <c r="R18" t="n">
-        <v>6367607</v>
+        <v>6367598</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2321,12 +2321,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2336,7 +2336,7 @@
         <v>128721558</v>
       </c>
       <c r="B19" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
         <v>128722582</v>
       </c>
       <c r="B20" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>128722540</v>
       </c>
       <c r="B21" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>128721499</v>
       </c>
       <c r="B22" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
         <v>128721578</v>
       </c>
       <c r="B23" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
         <v>128722534</v>
       </c>
       <c r="B24" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128721543</v>
+        <v>128722602</v>
       </c>
       <c r="B25" t="n">
-        <v>75115</v>
+        <v>86917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715500</v>
+        <v>715200</v>
       </c>
       <c r="R25" t="n">
-        <v>6367588</v>
+        <v>6367935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3005,12 +3005,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
         <v>128721505</v>
       </c>
       <c r="B26" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
         <v>128722567</v>
       </c>
       <c r="B27" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128722602</v>
+        <v>128721543</v>
       </c>
       <c r="B28" t="n">
-        <v>86890</v>
+        <v>75142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715200</v>
+        <v>715500</v>
       </c>
       <c r="R28" t="n">
-        <v>6367935</v>
+        <v>6367588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3302,12 +3302,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
         <v>128721540</v>
       </c>
       <c r="B29" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,52 +3404,55 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128721628</v>
+        <v>128722518</v>
       </c>
       <c r="B30" t="n">
-        <v>86972</v>
+        <v>86709</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715222</v>
+        <v>715536</v>
       </c>
       <c r="R30" t="n">
-        <v>6367915</v>
+        <v>6367906</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3497,12 +3500,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3512,7 +3515,7 @@
         <v>128722532</v>
       </c>
       <c r="B31" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,48 +3609,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128722518</v>
+        <v>128721628</v>
       </c>
       <c r="B32" t="n">
-        <v>86682</v>
+        <v>86999</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715536</v>
+        <v>715222</v>
       </c>
       <c r="R32" t="n">
-        <v>6367906</v>
+        <v>6367915</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3695,44 +3695,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722577</v>
+        <v>128721511</v>
       </c>
       <c r="B33" t="n">
-        <v>86949</v>
+        <v>91267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>449</v>
+        <v>3215</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715502</v>
+        <v>715180</v>
       </c>
       <c r="R33" t="n">
-        <v>6367602</v>
+        <v>6367626</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3792,44 +3792,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722608</v>
+        <v>128722564</v>
       </c>
       <c r="B34" t="n">
-        <v>86890</v>
+        <v>86941</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>3599</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715211</v>
+        <v>715387</v>
       </c>
       <c r="R34" t="n">
-        <v>6367929</v>
+        <v>6367908</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722564</v>
+        <v>128722577</v>
       </c>
       <c r="B35" t="n">
-        <v>86914</v>
+        <v>86976</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715387</v>
+        <v>715502</v>
       </c>
       <c r="R35" t="n">
-        <v>6367908</v>
+        <v>6367602</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3998,32 +3998,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721511</v>
+        <v>128722566</v>
       </c>
       <c r="B36" t="n">
-        <v>91240</v>
+        <v>91029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>5747</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715180</v>
+        <v>715288</v>
       </c>
       <c r="R36" t="n">
-        <v>6367626</v>
+        <v>6367866</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,22 +4083,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721513</v>
+        <v>128722608</v>
       </c>
       <c r="B37" t="n">
-        <v>86729</v>
+        <v>86917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4106,21 +4106,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715408</v>
+        <v>715211</v>
       </c>
       <c r="R37" t="n">
-        <v>6368189</v>
+        <v>6367929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,22 +4180,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128722542</v>
+        <v>128721513</v>
       </c>
       <c r="B38" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715218</v>
+        <v>715408</v>
       </c>
       <c r="R38" t="n">
-        <v>6367844</v>
+        <v>6368189</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4277,44 +4277,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722556</v>
+        <v>128722542</v>
       </c>
       <c r="B39" t="n">
-        <v>86927</v>
+        <v>86756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715180</v>
+        <v>715218</v>
       </c>
       <c r="R39" t="n">
-        <v>6368021</v>
+        <v>6367844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4368,7 +4368,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4387,45 +4386,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722566</v>
+        <v>128722517</v>
       </c>
       <c r="B40" t="n">
-        <v>91002</v>
+        <v>86709</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5747</v>
+        <v>249278</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715288</v>
+        <v>715318</v>
       </c>
       <c r="R40" t="n">
-        <v>6367866</v>
+        <v>6367974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,6 +4468,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4484,10 +4487,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722517</v>
+        <v>128722556</v>
       </c>
       <c r="B41" t="n">
-        <v>86682</v>
+        <v>86954</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,37 +4498,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715318</v>
+        <v>715180</v>
       </c>
       <c r="R41" t="n">
-        <v>6367974</v>
+        <v>6368021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>128721557</v>
       </c>
       <c r="B42" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4685,7 +4685,7 @@
         <v>128721497</v>
       </c>
       <c r="B43" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
         <v>128722543</v>
       </c>
       <c r="B44" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>128721577</v>
       </c>
       <c r="B45" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
         <v>128721653</v>
       </c>
       <c r="B46" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>128722606</v>
       </c>
       <c r="B47" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128721517</v>
+        <v>128721631</v>
       </c>
       <c r="B48" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715323</v>
+        <v>715172</v>
       </c>
       <c r="R48" t="n">
-        <v>6368092</v>
+        <v>6367927</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,22 +5254,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128721631</v>
+        <v>128721517</v>
       </c>
       <c r="B49" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715172</v>
+        <v>715323</v>
       </c>
       <c r="R49" t="n">
-        <v>6367927</v>
+        <v>6368092</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5352,44 +5352,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722544</v>
+        <v>128722580</v>
       </c>
       <c r="B50" t="n">
-        <v>86729</v>
+        <v>86976</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715251</v>
+        <v>715209</v>
       </c>
       <c r="R50" t="n">
-        <v>6367635</v>
+        <v>6367900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128721582</v>
+        <v>128721563</v>
       </c>
       <c r="B51" t="n">
-        <v>86890</v>
+        <v>92818</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,34 +5472,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715178</v>
+        <v>715232</v>
       </c>
       <c r="R51" t="n">
-        <v>6367640</v>
+        <v>6367928</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5540,6 +5543,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5551,17 +5555,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721568</v>
+        <v>128722544</v>
       </c>
       <c r="B52" t="n">
-        <v>86753</v>
+        <v>86756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,21 +5573,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5593,10 +5597,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715200</v>
+        <v>715251</v>
       </c>
       <c r="R52" t="n">
-        <v>6367963</v>
+        <v>6367635</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,44 +5647,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128722580</v>
+        <v>128721582</v>
       </c>
       <c r="B53" t="n">
-        <v>86949</v>
+        <v>86917</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5690,10 +5694,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715209</v>
+        <v>715178</v>
       </c>
       <c r="R53" t="n">
-        <v>6367900</v>
+        <v>6367640</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,22 +5744,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721563</v>
+        <v>128721568</v>
       </c>
       <c r="B54" t="n">
-        <v>92791</v>
+        <v>86780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5763,37 +5767,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715232</v>
+        <v>715200</v>
       </c>
       <c r="R54" t="n">
-        <v>6367928</v>
+        <v>6367963</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5834,7 +5835,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
         <v>128722575</v>
       </c>
       <c r="B55" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>128721496</v>
       </c>
       <c r="B56" t="n">
-        <v>86870</v>
+        <v>86897</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6041,17 +6041,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128722604</v>
+        <v>128721580</v>
       </c>
       <c r="B57" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715309</v>
+        <v>715147</v>
       </c>
       <c r="R57" t="n">
-        <v>6367880</v>
+        <v>6367801</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,22 +6133,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128721580</v>
+        <v>128722604</v>
       </c>
       <c r="B58" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715147</v>
+        <v>715309</v>
       </c>
       <c r="R58" t="n">
-        <v>6367801</v>
+        <v>6367880</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,12 +6230,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6245,7 +6245,7 @@
         <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>105641</v>
+        <v>105669</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6342,7 +6342,7 @@
         <v>128722553</v>
       </c>
       <c r="B60" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6437,32 +6437,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128721644</v>
+        <v>128721567</v>
       </c>
       <c r="B61" t="n">
-        <v>86949</v>
+        <v>96215</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>449</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715497</v>
+        <v>715422</v>
       </c>
       <c r="R61" t="n">
-        <v>6367603</v>
+        <v>6367626</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6522,22 +6522,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128722520</v>
+        <v>128721644</v>
       </c>
       <c r="B62" t="n">
-        <v>86972</v>
+        <v>86976</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6545,21 +6545,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715450</v>
+        <v>715497</v>
       </c>
       <c r="R62" t="n">
-        <v>6367880</v>
+        <v>6367603</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -6613,51 +6613,50 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128721567</v>
+        <v>128721507</v>
       </c>
       <c r="B63" t="n">
-        <v>96188</v>
+        <v>57713</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6666,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715422</v>
+        <v>715452</v>
       </c>
       <c r="R63" t="n">
-        <v>6367626</v>
+        <v>6367607</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6722,17 +6721,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721507</v>
+        <v>128722557</v>
       </c>
       <c r="B64" t="n">
-        <v>57686</v>
+        <v>86954</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,21 +6739,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6764,10 +6763,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715452</v>
+        <v>715218</v>
       </c>
       <c r="R64" t="n">
-        <v>6367607</v>
+        <v>6367940</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6789,7 +6788,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6808,50 +6807,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128722557</v>
+        <v>128722520</v>
       </c>
       <c r="B65" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715218</v>
+        <v>715450</v>
       </c>
       <c r="R65" t="n">
-        <v>6367940</v>
+        <v>6367880</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721635</v>
+        <v>128721651</v>
       </c>
       <c r="B66" t="n">
-        <v>86903</v>
+        <v>86917</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715194</v>
+        <v>715215</v>
       </c>
       <c r="R66" t="n">
-        <v>6367686</v>
+        <v>6367933</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7021,10 +7021,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128722601</v>
+        <v>128721635</v>
       </c>
       <c r="B67" t="n">
-        <v>86890</v>
+        <v>86930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715264</v>
+        <v>715194</v>
       </c>
       <c r="R67" t="n">
-        <v>6367986</v>
+        <v>6367686</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7106,22 +7106,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721579</v>
+        <v>128722601</v>
       </c>
       <c r="B68" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715191</v>
+        <v>715264</v>
       </c>
       <c r="R68" t="n">
-        <v>6367888</v>
+        <v>6367986</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7203,22 +7203,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721514</v>
+        <v>128721579</v>
       </c>
       <c r="B69" t="n">
-        <v>86729</v>
+        <v>86917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715141</v>
+        <v>715191</v>
       </c>
       <c r="R69" t="n">
-        <v>6367822</v>
+        <v>6367888</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7305,17 +7305,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721651</v>
+        <v>128721514</v>
       </c>
       <c r="B70" t="n">
-        <v>86890</v>
+        <v>86756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,21 +7323,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715215</v>
+        <v>715141</v>
       </c>
       <c r="R70" t="n">
-        <v>6367933</v>
+        <v>6367822</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7397,12 +7397,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7412,7 +7412,7 @@
         <v>128721629</v>
       </c>
       <c r="B71" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128721523</v>
+        <v>128722516</v>
       </c>
       <c r="B72" t="n">
-        <v>86927</v>
+        <v>86709</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715146</v>
+        <v>715492</v>
       </c>
       <c r="R72" t="n">
-        <v>6367798</v>
+        <v>6367910</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7592,44 +7595,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128722596</v>
+        <v>128721522</v>
       </c>
       <c r="B73" t="n">
-        <v>86880</v>
+        <v>86954</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7639,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715196</v>
+        <v>715221</v>
       </c>
       <c r="R73" t="n">
-        <v>6367906</v>
+        <v>6367902</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,12 +7693,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7705,7 +7708,7 @@
         <v>128722550</v>
       </c>
       <c r="B74" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7800,32 +7803,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128721522</v>
+        <v>128722596</v>
       </c>
       <c r="B75" t="n">
-        <v>86927</v>
+        <v>86907</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7835,10 +7838,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715221</v>
+        <v>715196</v>
       </c>
       <c r="R75" t="n">
-        <v>6367902</v>
+        <v>6367906</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7886,22 +7889,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128722516</v>
+        <v>128721523</v>
       </c>
       <c r="B76" t="n">
-        <v>86682</v>
+        <v>86954</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,37 +7912,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715492</v>
+        <v>715146</v>
       </c>
       <c r="R76" t="n">
-        <v>6367910</v>
+        <v>6367798</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7987,12 +7987,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8002,7 +8002,7 @@
         <v>128721642</v>
       </c>
       <c r="B77" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>128722521</v>
       </c>
       <c r="B78" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8194,32 +8194,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721503</v>
+        <v>128721521</v>
       </c>
       <c r="B79" t="n">
-        <v>110718</v>
+        <v>86954</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715170</v>
+        <v>715183</v>
       </c>
       <c r="R79" t="n">
-        <v>6367852</v>
+        <v>6368007</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8273,6 +8273,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8284,39 +8285,39 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128721521</v>
+        <v>128721503</v>
       </c>
       <c r="B80" t="n">
-        <v>86927</v>
+        <v>110746</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>219711</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8326,10 +8327,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715183</v>
+        <v>715170</v>
       </c>
       <c r="R80" t="n">
-        <v>6368007</v>
+        <v>6367852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8370,7 +8371,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8382,17 +8382,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722565</v>
+        <v>128722581</v>
       </c>
       <c r="B81" t="n">
-        <v>91002</v>
+        <v>86976</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8400,21 +8400,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5747</v>
+        <v>449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715311</v>
+        <v>715210</v>
       </c>
       <c r="R81" t="n">
-        <v>6367855</v>
+        <v>6367925</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8486,32 +8486,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128721502</v>
+        <v>128721575</v>
       </c>
       <c r="B82" t="n">
-        <v>90987</v>
+        <v>86917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>256335</v>
+        <v>3674</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715210</v>
+        <v>715333</v>
       </c>
       <c r="R82" t="n">
-        <v>6367925</v>
+        <v>6368090</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8565,7 +8565,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8577,39 +8576,39 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722589</v>
+        <v>128721581</v>
       </c>
       <c r="B83" t="n">
-        <v>86775</v>
+        <v>86917</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8619,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715223</v>
+        <v>715150</v>
       </c>
       <c r="R83" t="n">
-        <v>6367944</v>
+        <v>6367790</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8669,44 +8668,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722581</v>
+        <v>128722607</v>
       </c>
       <c r="B84" t="n">
-        <v>86949</v>
+        <v>86917</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8716,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715210</v>
+        <v>715545</v>
       </c>
       <c r="R84" t="n">
-        <v>6367925</v>
+        <v>6367864</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8778,32 +8777,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722607</v>
+        <v>128722589</v>
       </c>
       <c r="B85" t="n">
-        <v>86890</v>
+        <v>86802</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8813,10 +8812,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715545</v>
+        <v>715223</v>
       </c>
       <c r="R85" t="n">
-        <v>6367864</v>
+        <v>6367944</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8875,32 +8874,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128721575</v>
+        <v>128722565</v>
       </c>
       <c r="B86" t="n">
-        <v>86890</v>
+        <v>91029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8910,10 +8909,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715333</v>
+        <v>715311</v>
       </c>
       <c r="R86" t="n">
-        <v>6368090</v>
+        <v>6367855</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8960,44 +8959,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128721581</v>
+        <v>128721502</v>
       </c>
       <c r="B87" t="n">
-        <v>86890</v>
+        <v>91014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3674</v>
+        <v>256335</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9007,10 +9006,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715150</v>
+        <v>715210</v>
       </c>
       <c r="R87" t="n">
-        <v>6367790</v>
+        <v>6367925</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9051,6 +9050,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9062,39 +9062,39 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128721552</v>
+        <v>128722549</v>
       </c>
       <c r="B88" t="n">
-        <v>105654</v>
+        <v>86954</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>6003295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715197</v>
+        <v>715448</v>
       </c>
       <c r="R88" t="n">
-        <v>6367683</v>
+        <v>6367902</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9148,28 +9148,29 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722547</v>
+        <v>128722560</v>
       </c>
       <c r="B89" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9201,10 +9202,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715525</v>
+        <v>715549</v>
       </c>
       <c r="R89" t="n">
-        <v>6367901</v>
+        <v>6367883</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9264,10 +9265,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128722560</v>
+        <v>128722547</v>
       </c>
       <c r="B90" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9299,10 +9300,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715549</v>
+        <v>715525</v>
       </c>
       <c r="R90" t="n">
-        <v>6367883</v>
+        <v>6367901</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9362,32 +9363,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128722549</v>
+        <v>128721552</v>
       </c>
       <c r="B91" t="n">
-        <v>86927</v>
+        <v>105682</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9397,10 +9398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715448</v>
+        <v>715197</v>
       </c>
       <c r="R91" t="n">
-        <v>6367902</v>
+        <v>6367683</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9441,51 +9442,50 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128721647</v>
+        <v>128722519</v>
       </c>
       <c r="B92" t="n">
-        <v>86682</v>
+        <v>90969</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>249278</v>
+        <v>720</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715216</v>
+        <v>715292</v>
       </c>
       <c r="R92" t="n">
-        <v>6367898</v>
+        <v>6367865</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,62 +9533,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722558</v>
+        <v>128722603</v>
       </c>
       <c r="B93" t="n">
-        <v>86927</v>
+        <v>86917</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9598,10 +9592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715177</v>
+        <v>715233</v>
       </c>
       <c r="R93" t="n">
-        <v>6367636</v>
+        <v>6367868</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9642,7 +9636,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9661,32 +9654,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722519</v>
+        <v>128721647</v>
       </c>
       <c r="B94" t="n">
-        <v>90942</v>
+        <v>86709</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>720</v>
+        <v>249278</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9696,10 +9689,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715292</v>
+        <v>715216</v>
       </c>
       <c r="R94" t="n">
-        <v>6367865</v>
+        <v>6367898</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9734,56 +9727,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722603</v>
+        <v>128722558</v>
       </c>
       <c r="B95" t="n">
-        <v>86890</v>
+        <v>86954</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9792,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715233</v>
+        <v>715177</v>
       </c>
       <c r="R95" t="n">
-        <v>6367868</v>
+        <v>6367636</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9837,6 +9836,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9855,53 +9855,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721508</v>
+        <v>128722597</v>
       </c>
       <c r="B96" t="n">
-        <v>57686</v>
+        <v>86907</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6003235</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715206</v>
+        <v>715216</v>
       </c>
       <c r="R96" t="n">
-        <v>6367909</v>
+        <v>6367914</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9942,50 +9934,51 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128722597</v>
+        <v>128721649</v>
       </c>
       <c r="B97" t="n">
-        <v>86880</v>
+        <v>86917</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003235</v>
+        <v>3674</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9995,10 +9988,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715216</v>
+        <v>715314</v>
       </c>
       <c r="R97" t="n">
-        <v>6367914</v>
+        <v>6368077</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10039,19 +10032,18 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10061,7 +10053,7 @@
         <v>128721541</v>
       </c>
       <c r="B98" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10148,7 +10140,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10158,7 +10150,7 @@
         <v>128721542</v>
       </c>
       <c r="B99" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10245,52 +10237,60 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721649</v>
+        <v>128721508</v>
       </c>
       <c r="B100" t="n">
-        <v>86890</v>
+        <v>57713</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715314</v>
+        <v>715206</v>
       </c>
       <c r="R100" t="n">
-        <v>6368077</v>
+        <v>6367909</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10337,44 +10337,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128722598</v>
+        <v>128721583</v>
       </c>
       <c r="B101" t="n">
-        <v>86775</v>
+        <v>86917</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715487</v>
+        <v>715492</v>
       </c>
       <c r="R101" t="n">
-        <v>6367923</v>
+        <v>6367606</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -10434,22 +10434,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722579</v>
+        <v>128722598</v>
       </c>
       <c r="B102" t="n">
-        <v>86949</v>
+        <v>86802</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10457,21 +10457,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715205</v>
+        <v>715487</v>
       </c>
       <c r="R102" t="n">
-        <v>6367943</v>
+        <v>6367923</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10543,32 +10543,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128721583</v>
+        <v>128722579</v>
       </c>
       <c r="B103" t="n">
-        <v>86890</v>
+        <v>86976</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715492</v>
+        <v>715205</v>
       </c>
       <c r="R103" t="n">
-        <v>6367606</v>
+        <v>6367943</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10628,44 +10628,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722587</v>
+        <v>128721519</v>
       </c>
       <c r="B104" t="n">
-        <v>86950</v>
+        <v>86954</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715464</v>
+        <v>715287</v>
       </c>
       <c r="R104" t="n">
-        <v>6367911</v>
+        <v>6368083</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10719,28 +10719,29 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128721519</v>
+        <v>128722546</v>
       </c>
       <c r="B105" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10772,10 +10773,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715287</v>
+        <v>715298</v>
       </c>
       <c r="R105" t="n">
-        <v>6368083</v>
+        <v>6367872</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10823,44 +10824,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128722546</v>
+        <v>128722587</v>
       </c>
       <c r="B106" t="n">
-        <v>86927</v>
+        <v>86977</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10870,10 +10871,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715298</v>
+        <v>715464</v>
       </c>
       <c r="R106" t="n">
-        <v>6367872</v>
+        <v>6367911</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10914,7 +10915,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>128722599</v>
       </c>
       <c r="B107" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>128722522</v>
       </c>
       <c r="B108" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>128722585</v>
       </c>
       <c r="B109" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>128722545</v>
       </c>
       <c r="B110" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11327,32 +11327,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128721520</v>
+        <v>128721572</v>
       </c>
       <c r="B111" t="n">
-        <v>86927</v>
+        <v>86907</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715280</v>
+        <v>715132</v>
       </c>
       <c r="R111" t="n">
-        <v>6368028</v>
+        <v>6367819</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11406,7 +11406,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11418,39 +11417,39 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128721572</v>
+        <v>128721520</v>
       </c>
       <c r="B112" t="n">
-        <v>86880</v>
+        <v>86954</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11460,10 +11459,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715132</v>
+        <v>715280</v>
       </c>
       <c r="R112" t="n">
-        <v>6367819</v>
+        <v>6368028</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11504,6 +11503,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11515,17 +11515,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128721537</v>
+        <v>128722562</v>
       </c>
       <c r="B113" t="n">
-        <v>75115</v>
+        <v>98653</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11533,21 +11533,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6426</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715344</v>
+        <v>715452</v>
       </c>
       <c r="R113" t="n">
-        <v>6368190</v>
+        <v>6367610</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -11607,44 +11607,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128721500</v>
+        <v>128722548</v>
       </c>
       <c r="B114" t="n">
-        <v>86972</v>
+        <v>86954</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715318</v>
+        <v>715513</v>
       </c>
       <c r="R114" t="n">
-        <v>6368090</v>
+        <v>6367892</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11698,50 +11698,51 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128722523</v>
+        <v>128721524</v>
       </c>
       <c r="B115" t="n">
-        <v>86729</v>
+        <v>86954</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11751,10 +11752,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715327</v>
+        <v>715222</v>
       </c>
       <c r="R115" t="n">
-        <v>6367899</v>
+        <v>6367894</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11795,50 +11796,51 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128721650</v>
+        <v>128721500</v>
       </c>
       <c r="B116" t="n">
-        <v>86890</v>
+        <v>86999</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11848,10 +11850,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715161</v>
+        <v>715318</v>
       </c>
       <c r="R116" t="n">
-        <v>6368017</v>
+        <v>6368090</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11898,22 +11900,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722535</v>
+        <v>128722523</v>
       </c>
       <c r="B117" t="n">
-        <v>86753</v>
+        <v>86756</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11921,21 +11923,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11945,10 +11947,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715500</v>
+        <v>715327</v>
       </c>
       <c r="R117" t="n">
-        <v>6367907</v>
+        <v>6367899</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12007,10 +12009,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722541</v>
+        <v>128721650</v>
       </c>
       <c r="B118" t="n">
-        <v>86729</v>
+        <v>86917</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12018,21 +12020,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12042,10 +12044,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715501</v>
+        <v>715161</v>
       </c>
       <c r="R118" t="n">
-        <v>6367911</v>
+        <v>6368017</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12092,22 +12094,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128722586</v>
+        <v>128722535</v>
       </c>
       <c r="B119" t="n">
-        <v>86729</v>
+        <v>86780</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12115,21 +12117,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12139,10 +12141,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715507</v>
+        <v>715500</v>
       </c>
       <c r="R119" t="n">
-        <v>6367904</v>
+        <v>6367907</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12201,10 +12203,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722562</v>
+        <v>128722541</v>
       </c>
       <c r="B120" t="n">
-        <v>98626</v>
+        <v>86756</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12212,21 +12214,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219874</v>
+        <v>3762</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12236,10 +12238,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715452</v>
+        <v>715501</v>
       </c>
       <c r="R120" t="n">
-        <v>6367610</v>
+        <v>6367911</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12261,7 +12263,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12298,32 +12300,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128722548</v>
+        <v>128722586</v>
       </c>
       <c r="B121" t="n">
-        <v>86927</v>
+        <v>86756</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12333,10 +12335,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715513</v>
+        <v>715507</v>
       </c>
       <c r="R121" t="n">
-        <v>6367892</v>
+        <v>6367904</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12377,7 +12379,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12396,32 +12397,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128721524</v>
+        <v>128721537</v>
       </c>
       <c r="B122" t="n">
-        <v>86927</v>
+        <v>75142</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12431,10 +12432,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715222</v>
+        <v>715344</v>
       </c>
       <c r="R122" t="n">
-        <v>6367894</v>
+        <v>6368190</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12475,7 +12476,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12497,7 +12497,7 @@
         <v>128721538</v>
       </c>
       <c r="B123" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -12594,7 +12594,7 @@
         <v>128722605</v>
       </c>
       <c r="B124" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12688,32 +12688,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128722590</v>
+        <v>128721526</v>
       </c>
       <c r="B125" t="n">
-        <v>86950</v>
+        <v>58086</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>248947</v>
+        <v>103015</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715473</v>
+        <v>715155</v>
       </c>
       <c r="R125" t="n">
-        <v>6367917</v>
+        <v>6367801</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12773,44 +12773,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128721526</v>
+        <v>128722590</v>
       </c>
       <c r="B126" t="n">
-        <v>58059</v>
+        <v>86977</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>248947</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12820,10 +12820,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715155</v>
+        <v>715473</v>
       </c>
       <c r="R126" t="n">
-        <v>6367801</v>
+        <v>6367917</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12870,12 +12870,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -12885,7 +12885,7 @@
         <v>128721525</v>
       </c>
       <c r="B127" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12973,17 +12973,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722561</v>
+        <v>128722559</v>
       </c>
       <c r="B128" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715545</v>
+        <v>715256</v>
       </c>
       <c r="R128" t="n">
-        <v>6367898</v>
+        <v>6367627</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13081,7 +13081,7 @@
         <v>128722551</v>
       </c>
       <c r="B129" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13176,10 +13176,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722559</v>
+        <v>128722561</v>
       </c>
       <c r="B130" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13211,10 +13211,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715256</v>
+        <v>715545</v>
       </c>
       <c r="R130" t="n">
-        <v>6367627</v>
+        <v>6367898</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13277,7 +13277,7 @@
         <v>128722530</v>
       </c>
       <c r="B131" t="n">
-        <v>86961</v>
+        <v>86988</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B14" t="n">
-        <v>86941</v>
+        <v>105669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R14" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B15" t="n">
-        <v>105669</v>
+        <v>86941</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R15" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,57 +2030,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128721643</v>
+        <v>128722582</v>
       </c>
       <c r="B16" t="n">
-        <v>86976</v>
+        <v>92818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715270</v>
+        <v>715492</v>
       </c>
       <c r="R16" t="n">
-        <v>6367607</v>
+        <v>6367899</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2121,50 +2124,51 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721560</v>
+        <v>128722540</v>
       </c>
       <c r="B17" t="n">
-        <v>86976</v>
+        <v>86756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715503</v>
+        <v>715194</v>
       </c>
       <c r="R17" t="n">
-        <v>6367589</v>
+        <v>6367837</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2199,7 +2203,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2218,28 +2222,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721559</v>
+        <v>128721499</v>
       </c>
       <c r="B18" t="n">
-        <v>86976</v>
+        <v>86999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715505</v>
+        <v>715394</v>
       </c>
       <c r="R18" t="n">
-        <v>6367598</v>
+        <v>6368208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2296,7 +2301,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2326,39 +2331,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721558</v>
+        <v>128721578</v>
       </c>
       <c r="B19" t="n">
-        <v>86976</v>
+        <v>86917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715424</v>
+        <v>715215</v>
       </c>
       <c r="R19" t="n">
-        <v>6367651</v>
+        <v>6367918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2393,7 +2398,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2423,55 +2428,52 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128722582</v>
+        <v>128721560</v>
       </c>
       <c r="B20" t="n">
-        <v>92818</v>
+        <v>86976</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715492</v>
+        <v>715503</v>
       </c>
       <c r="R20" t="n">
-        <v>6367899</v>
+        <v>6367589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2493,7 +2495,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2512,51 +2514,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128722540</v>
+        <v>128721559</v>
       </c>
       <c r="B21" t="n">
-        <v>86756</v>
+        <v>86976</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715194</v>
+        <v>715505</v>
       </c>
       <c r="R21" t="n">
-        <v>6367837</v>
+        <v>6367598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2591,7 +2592,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2610,29 +2611,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721499</v>
+        <v>128721643</v>
       </c>
       <c r="B22" t="n">
-        <v>86999</v>
+        <v>86976</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715394</v>
+        <v>715270</v>
       </c>
       <c r="R22" t="n">
-        <v>6368208</v>
+        <v>6367607</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2714,44 +2714,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128721578</v>
+        <v>128721558</v>
       </c>
       <c r="B23" t="n">
-        <v>86917</v>
+        <v>86976</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715215</v>
+        <v>715424</v>
       </c>
       <c r="R23" t="n">
-        <v>6367918</v>
+        <v>6367651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128722602</v>
+        <v>128721505</v>
       </c>
       <c r="B25" t="n">
-        <v>86917</v>
+        <v>86802</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715200</v>
+        <v>715150</v>
       </c>
       <c r="R25" t="n">
-        <v>6367935</v>
+        <v>6367765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,44 +3005,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128721505</v>
+        <v>128721543</v>
       </c>
       <c r="B26" t="n">
-        <v>86802</v>
+        <v>75142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>424</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715150</v>
+        <v>715500</v>
       </c>
       <c r="R26" t="n">
-        <v>6367765</v>
+        <v>6367588</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128721543</v>
+        <v>128722602</v>
       </c>
       <c r="B28" t="n">
-        <v>75142</v>
+        <v>86917</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715500</v>
+        <v>715200</v>
       </c>
       <c r="R28" t="n">
-        <v>6367588</v>
+        <v>6367935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3302,44 +3302,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128721540</v>
+        <v>128721628</v>
       </c>
       <c r="B29" t="n">
-        <v>75142</v>
+        <v>86999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715278</v>
+        <v>715222</v>
       </c>
       <c r="R29" t="n">
-        <v>6368028</v>
+        <v>6367915</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3393,66 +3393,64 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128722518</v>
+        <v>128721540</v>
       </c>
       <c r="B30" t="n">
-        <v>86709</v>
+        <v>75142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>249278</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715536</v>
+        <v>715278</v>
       </c>
       <c r="R30" t="n">
-        <v>6367906</v>
+        <v>6368028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,19 +3491,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3609,45 +3606,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128721628</v>
+        <v>128722518</v>
       </c>
       <c r="B32" t="n">
-        <v>86999</v>
+        <v>86709</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715222</v>
+        <v>715536</v>
       </c>
       <c r="R32" t="n">
-        <v>6367915</v>
+        <v>6367906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3695,22 +3695,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721511</v>
+        <v>128722608</v>
       </c>
       <c r="B33" t="n">
-        <v>91267</v>
+        <v>86917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3718,21 +3718,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715180</v>
+        <v>715211</v>
       </c>
       <c r="R33" t="n">
-        <v>6367626</v>
+        <v>6367929</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3792,12 +3792,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722577</v>
+        <v>128721513</v>
       </c>
       <c r="B35" t="n">
-        <v>86976</v>
+        <v>86756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715502</v>
+        <v>715408</v>
       </c>
       <c r="R35" t="n">
-        <v>6367602</v>
+        <v>6368189</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3986,44 +3986,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128722566</v>
+        <v>128722542</v>
       </c>
       <c r="B36" t="n">
-        <v>91029</v>
+        <v>86756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5747</v>
+        <v>3762</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715288</v>
+        <v>715218</v>
       </c>
       <c r="R36" t="n">
-        <v>6367866</v>
+        <v>6367844</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,45 +4095,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722608</v>
+        <v>128722517</v>
       </c>
       <c r="B37" t="n">
-        <v>86917</v>
+        <v>86709</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715211</v>
+        <v>715318</v>
       </c>
       <c r="R37" t="n">
-        <v>6367929</v>
+        <v>6367974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4174,6 +4177,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4192,32 +4196,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721513</v>
+        <v>128722556</v>
       </c>
       <c r="B38" t="n">
-        <v>86756</v>
+        <v>86954</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4227,10 +4231,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715408</v>
+        <v>715180</v>
       </c>
       <c r="R38" t="n">
-        <v>6368189</v>
+        <v>6368021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4271,28 +4275,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722542</v>
+        <v>128721511</v>
       </c>
       <c r="B39" t="n">
-        <v>86756</v>
+        <v>91267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4300,21 +4305,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715218</v>
+        <v>715180</v>
       </c>
       <c r="R39" t="n">
-        <v>6367844</v>
+        <v>6367626</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,60 +4379,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722517</v>
+        <v>128722577</v>
       </c>
       <c r="B40" t="n">
-        <v>86709</v>
+        <v>86976</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>249278</v>
+        <v>449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715318</v>
+        <v>715502</v>
       </c>
       <c r="R40" t="n">
-        <v>6367974</v>
+        <v>6367602</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4449,7 +4451,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4468,7 +4470,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4487,32 +4488,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722556</v>
+        <v>128722566</v>
       </c>
       <c r="B41" t="n">
-        <v>86954</v>
+        <v>91029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4522,10 +4523,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715180</v>
+        <v>715288</v>
       </c>
       <c r="R41" t="n">
-        <v>6368021</v>
+        <v>6367866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4585,10 +4585,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721557</v>
+        <v>128721497</v>
       </c>
       <c r="B42" t="n">
-        <v>86976</v>
+        <v>86999</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4596,21 +4596,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715213</v>
+        <v>715243</v>
       </c>
       <c r="R42" t="n">
-        <v>6367921</v>
+        <v>6367615</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4664,6 +4664,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4675,39 +4676,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721497</v>
+        <v>128722543</v>
       </c>
       <c r="B43" t="n">
-        <v>86999</v>
+        <v>86756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4717,10 +4718,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715243</v>
+        <v>715253</v>
       </c>
       <c r="R43" t="n">
-        <v>6367615</v>
+        <v>6367647</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4761,29 +4762,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128722543</v>
+        <v>128721577</v>
       </c>
       <c r="B44" t="n">
-        <v>86756</v>
+        <v>86917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715253</v>
+        <v>715221</v>
       </c>
       <c r="R44" t="n">
-        <v>6367647</v>
+        <v>6367967</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4865,19 +4865,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721577</v>
+        <v>128721653</v>
       </c>
       <c r="B45" t="n">
         <v>86917</v>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715221</v>
+        <v>715476</v>
       </c>
       <c r="R45" t="n">
-        <v>6367967</v>
+        <v>6367609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4962,19 +4962,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721653</v>
+        <v>128722606</v>
       </c>
       <c r="B46" t="n">
         <v>86917</v>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715476</v>
+        <v>715323</v>
       </c>
       <c r="R46" t="n">
-        <v>6367609</v>
+        <v>6367903</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5059,44 +5059,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128722606</v>
+        <v>128721557</v>
       </c>
       <c r="B47" t="n">
-        <v>86917</v>
+        <v>86976</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715323</v>
+        <v>715213</v>
       </c>
       <c r="R47" t="n">
-        <v>6367903</v>
+        <v>6367921</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,12 +5156,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5357,39 +5357,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722580</v>
+        <v>128722544</v>
       </c>
       <c r="B50" t="n">
-        <v>86976</v>
+        <v>86756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715209</v>
+        <v>715251</v>
       </c>
       <c r="R50" t="n">
-        <v>6367900</v>
+        <v>6367635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128721563</v>
+        <v>128721582</v>
       </c>
       <c r="B51" t="n">
-        <v>92818</v>
+        <v>86917</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,37 +5472,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715232</v>
+        <v>715178</v>
       </c>
       <c r="R51" t="n">
-        <v>6367928</v>
+        <v>6367640</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5543,7 +5540,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5555,17 +5551,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128722544</v>
+        <v>128721568</v>
       </c>
       <c r="B52" t="n">
-        <v>86756</v>
+        <v>86780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5573,21 +5569,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5597,10 +5593,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715251</v>
+        <v>715200</v>
       </c>
       <c r="R52" t="n">
-        <v>6367635</v>
+        <v>6367963</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5647,44 +5643,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128721582</v>
+        <v>128722580</v>
       </c>
       <c r="B53" t="n">
-        <v>86917</v>
+        <v>86976</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5694,10 +5690,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715178</v>
+        <v>715209</v>
       </c>
       <c r="R53" t="n">
-        <v>6367640</v>
+        <v>6367900</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,22 +5740,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721568</v>
+        <v>128722575</v>
       </c>
       <c r="B54" t="n">
-        <v>86780</v>
+        <v>105682</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5763,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3712</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5787,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715200</v>
+        <v>715498</v>
       </c>
       <c r="R54" t="n">
-        <v>6367963</v>
+        <v>6367908</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5841,22 +5837,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128722575</v>
+        <v>128721563</v>
       </c>
       <c r="B55" t="n">
-        <v>105682</v>
+        <v>92818</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5864,34 +5860,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715498</v>
+        <v>715232</v>
       </c>
       <c r="R55" t="n">
-        <v>6367908</v>
+        <v>6367928</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5932,50 +5931,51 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128721496</v>
+        <v>128722604</v>
       </c>
       <c r="B56" t="n">
-        <v>86897</v>
+        <v>86917</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>473</v>
+        <v>3674</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715344</v>
+        <v>715309</v>
       </c>
       <c r="R56" t="n">
-        <v>6368190</v>
+        <v>6367880</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6029,19 +6029,18 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6138,17 +6137,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128722604</v>
+        <v>128721547</v>
       </c>
       <c r="B58" t="n">
-        <v>86917</v>
+        <v>105669</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6156,21 +6155,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3674</v>
+        <v>224098</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6180,10 +6179,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715309</v>
+        <v>715154</v>
       </c>
       <c r="R58" t="n">
-        <v>6367880</v>
+        <v>6367783</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,44 +6229,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128721547</v>
+        <v>128722553</v>
       </c>
       <c r="B59" t="n">
-        <v>105669</v>
+        <v>86954</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6277,10 +6276,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715154</v>
+        <v>715261</v>
       </c>
       <c r="R59" t="n">
-        <v>6367783</v>
+        <v>6368006</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6321,28 +6320,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128722553</v>
+        <v>128721496</v>
       </c>
       <c r="B60" t="n">
-        <v>86954</v>
+        <v>86897</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6350,21 +6350,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>473</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715261</v>
+        <v>715344</v>
       </c>
       <c r="R60" t="n">
-        <v>6368006</v>
+        <v>6368190</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6425,44 +6425,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128721567</v>
+        <v>128722520</v>
       </c>
       <c r="B61" t="n">
-        <v>96215</v>
+        <v>86999</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715422</v>
+        <v>715450</v>
       </c>
       <c r="R61" t="n">
-        <v>6367626</v>
+        <v>6367880</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,18 +6516,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6631,10 +6632,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128721507</v>
+        <v>128722557</v>
       </c>
       <c r="B63" t="n">
-        <v>57713</v>
+        <v>86954</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6642,21 +6643,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6666,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715452</v>
+        <v>715218</v>
       </c>
       <c r="R63" t="n">
-        <v>6367607</v>
+        <v>6367940</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6691,7 +6692,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -6710,50 +6711,51 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128722557</v>
+        <v>128721567</v>
       </c>
       <c r="B64" t="n">
-        <v>86954</v>
+        <v>96215</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6763,10 +6765,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715218</v>
+        <v>715422</v>
       </c>
       <c r="R64" t="n">
-        <v>6367940</v>
+        <v>6367626</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6788,7 +6790,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6807,51 +6809,50 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128722520</v>
+        <v>128721507</v>
       </c>
       <c r="B65" t="n">
-        <v>86999</v>
+        <v>57713</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3767</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6861,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715450</v>
+        <v>715452</v>
       </c>
       <c r="R65" t="n">
-        <v>6367880</v>
+        <v>6367607</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6886,7 +6887,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -6905,51 +6906,50 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721651</v>
+        <v>128721629</v>
       </c>
       <c r="B66" t="n">
-        <v>86917</v>
+        <v>57713</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715215</v>
+        <v>715504</v>
       </c>
       <c r="R66" t="n">
-        <v>6367933</v>
+        <v>6367595</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -7021,32 +7021,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721635</v>
+        <v>128721522</v>
       </c>
       <c r="B67" t="n">
-        <v>86930</v>
+        <v>86954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715194</v>
+        <v>715221</v>
       </c>
       <c r="R67" t="n">
-        <v>6367686</v>
+        <v>6367902</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7100,50 +7100,51 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128722601</v>
+        <v>128722550</v>
       </c>
       <c r="B68" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7154,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715264</v>
+        <v>715321</v>
       </c>
       <c r="R68" t="n">
-        <v>6367986</v>
+        <v>6367984</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7197,6 +7198,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7215,32 +7217,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721579</v>
+        <v>128722596</v>
       </c>
       <c r="B69" t="n">
-        <v>86917</v>
+        <v>86907</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3674</v>
+        <v>6003235</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7252,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715191</v>
+        <v>715196</v>
       </c>
       <c r="R69" t="n">
-        <v>6367888</v>
+        <v>6367906</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7294,50 +7296,51 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721514</v>
+        <v>128721523</v>
       </c>
       <c r="B70" t="n">
-        <v>86756</v>
+        <v>86954</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7350,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715141</v>
+        <v>715146</v>
       </c>
       <c r="R70" t="n">
-        <v>6367822</v>
+        <v>6367798</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7391,6 +7394,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7402,39 +7406,39 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721629</v>
+        <v>128721635</v>
       </c>
       <c r="B71" t="n">
-        <v>57713</v>
+        <v>86930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1988</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7448,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715504</v>
+        <v>715194</v>
       </c>
       <c r="R71" t="n">
-        <v>6367595</v>
+        <v>6367686</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7469,7 +7473,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7506,48 +7510,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128722516</v>
+        <v>128722601</v>
       </c>
       <c r="B72" t="n">
-        <v>86709</v>
+        <v>86917</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715492</v>
+        <v>715264</v>
       </c>
       <c r="R72" t="n">
-        <v>6367910</v>
+        <v>6367986</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7588,7 +7589,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7607,32 +7607,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721522</v>
+        <v>128721579</v>
       </c>
       <c r="B73" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715221</v>
+        <v>715191</v>
       </c>
       <c r="R73" t="n">
-        <v>6367902</v>
+        <v>6367888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7686,7 +7686,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7698,39 +7697,39 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128722550</v>
+        <v>128721514</v>
       </c>
       <c r="B74" t="n">
-        <v>86954</v>
+        <v>86756</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7740,10 +7739,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715321</v>
+        <v>715141</v>
       </c>
       <c r="R74" t="n">
-        <v>6367984</v>
+        <v>6367822</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7784,51 +7783,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128722596</v>
+        <v>128721651</v>
       </c>
       <c r="B75" t="n">
-        <v>86907</v>
+        <v>86917</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003235</v>
+        <v>3674</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7838,10 +7836,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715196</v>
+        <v>715215</v>
       </c>
       <c r="R75" t="n">
-        <v>6367906</v>
+        <v>6367933</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7882,29 +7880,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128721523</v>
+        <v>128722516</v>
       </c>
       <c r="B76" t="n">
-        <v>86954</v>
+        <v>86709</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7912,34 +7909,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715146</v>
+        <v>715492</v>
       </c>
       <c r="R76" t="n">
-        <v>6367798</v>
+        <v>6367910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7987,22 +7987,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128721642</v>
+        <v>128722521</v>
       </c>
       <c r="B77" t="n">
-        <v>86976</v>
+        <v>86999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715204</v>
+        <v>715207</v>
       </c>
       <c r="R77" t="n">
-        <v>6367900</v>
+        <v>6367905</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8078,28 +8078,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128722521</v>
+        <v>128721642</v>
       </c>
       <c r="B78" t="n">
-        <v>86999</v>
+        <v>86976</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8107,21 +8108,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8131,10 +8132,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715207</v>
+        <v>715204</v>
       </c>
       <c r="R78" t="n">
-        <v>6367905</v>
+        <v>6367900</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8175,51 +8176,50 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721521</v>
+        <v>128721503</v>
       </c>
       <c r="B79" t="n">
-        <v>86954</v>
+        <v>110746</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>219711</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715183</v>
+        <v>715170</v>
       </c>
       <c r="R79" t="n">
-        <v>6368007</v>
+        <v>6367852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8273,7 +8273,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8285,39 +8284,39 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128721503</v>
+        <v>128721521</v>
       </c>
       <c r="B80" t="n">
-        <v>110746</v>
+        <v>86954</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8327,10 +8326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715170</v>
+        <v>715183</v>
       </c>
       <c r="R80" t="n">
-        <v>6367852</v>
+        <v>6368007</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8371,6 +8370,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8382,39 +8382,39 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722581</v>
+        <v>128722607</v>
       </c>
       <c r="B81" t="n">
-        <v>86976</v>
+        <v>86917</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715210</v>
+        <v>715545</v>
       </c>
       <c r="R81" t="n">
-        <v>6367925</v>
+        <v>6367864</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8673,39 +8673,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722607</v>
+        <v>128722589</v>
       </c>
       <c r="B84" t="n">
-        <v>86917</v>
+        <v>86802</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715545</v>
+        <v>715223</v>
       </c>
       <c r="R84" t="n">
-        <v>6367864</v>
+        <v>6367944</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8777,10 +8777,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722589</v>
+        <v>128722581</v>
       </c>
       <c r="B85" t="n">
-        <v>86802</v>
+        <v>86976</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8788,21 +8788,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715223</v>
+        <v>715210</v>
       </c>
       <c r="R85" t="n">
-        <v>6367944</v>
+        <v>6367925</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8971,32 +8971,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128721502</v>
+        <v>128722549</v>
       </c>
       <c r="B87" t="n">
-        <v>91014</v>
+        <v>86954</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>256335</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715210</v>
+        <v>715448</v>
       </c>
       <c r="R87" t="n">
-        <v>6367925</v>
+        <v>6367902</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9057,19 +9057,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722549</v>
+        <v>128722560</v>
       </c>
       <c r="B88" t="n">
         <v>86954</v>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715448</v>
+        <v>715549</v>
       </c>
       <c r="R88" t="n">
-        <v>6367902</v>
+        <v>6367883</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9167,7 +9167,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722560</v>
+        <v>128722547</v>
       </c>
       <c r="B89" t="n">
         <v>86954</v>
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715549</v>
+        <v>715525</v>
       </c>
       <c r="R89" t="n">
-        <v>6367883</v>
+        <v>6367901</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9265,32 +9265,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128722547</v>
+        <v>128721552</v>
       </c>
       <c r="B90" t="n">
-        <v>86954</v>
+        <v>105682</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6003295</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715525</v>
+        <v>715197</v>
       </c>
       <c r="R90" t="n">
-        <v>6367901</v>
+        <v>6367683</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9344,51 +9344,50 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128721552</v>
+        <v>128721502</v>
       </c>
       <c r="B91" t="n">
-        <v>105682</v>
+        <v>91014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>256335</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9397,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715197</v>
+        <v>715210</v>
       </c>
       <c r="R91" t="n">
-        <v>6367683</v>
+        <v>6367925</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9442,6 +9441,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9557,32 +9557,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722603</v>
+        <v>128721647</v>
       </c>
       <c r="B93" t="n">
-        <v>86917</v>
+        <v>86709</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715233</v>
+        <v>715216</v>
       </c>
       <c r="R93" t="n">
-        <v>6367868</v>
+        <v>6367898</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,34 +9630,40 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128721647</v>
+        <v>128722558</v>
       </c>
       <c r="B94" t="n">
-        <v>86709</v>
+        <v>86954</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9665,21 +9671,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9689,10 +9695,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715216</v>
+        <v>715177</v>
       </c>
       <c r="R94" t="n">
-        <v>6367898</v>
+        <v>6367636</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9727,11 +9733,6 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -9745,44 +9746,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722558</v>
+        <v>128722603</v>
       </c>
       <c r="B95" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9792,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715177</v>
+        <v>715233</v>
       </c>
       <c r="R95" t="n">
-        <v>6367636</v>
+        <v>6367868</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9836,7 +9837,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9855,32 +9855,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128722597</v>
+        <v>128721541</v>
       </c>
       <c r="B96" t="n">
-        <v>86907</v>
+        <v>75142</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003235</v>
+        <v>6426</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715216</v>
+        <v>715250</v>
       </c>
       <c r="R96" t="n">
-        <v>6367914</v>
+        <v>6367931</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9934,29 +9934,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721649</v>
+        <v>128721542</v>
       </c>
       <c r="B97" t="n">
-        <v>86917</v>
+        <v>75142</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9964,21 +9963,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9988,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715314</v>
+        <v>715519</v>
       </c>
       <c r="R97" t="n">
-        <v>6368077</v>
+        <v>6367602</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10013,7 +10012,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10038,22 +10037,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721541</v>
+        <v>128721649</v>
       </c>
       <c r="B98" t="n">
-        <v>75142</v>
+        <v>86917</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10061,21 +10060,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10085,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715250</v>
+        <v>715314</v>
       </c>
       <c r="R98" t="n">
-        <v>6367931</v>
+        <v>6368077</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10135,57 +10134,65 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721542</v>
+        <v>128721508</v>
       </c>
       <c r="B99" t="n">
-        <v>75142</v>
+        <v>57713</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715519</v>
+        <v>715206</v>
       </c>
       <c r="R99" t="n">
-        <v>6367602</v>
+        <v>6367909</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10207,7 +10214,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -10237,60 +10244,52 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721508</v>
+        <v>128722597</v>
       </c>
       <c r="B100" t="n">
-        <v>57713</v>
+        <v>86907</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6003235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715206</v>
+        <v>715216</v>
       </c>
       <c r="R100" t="n">
-        <v>6367909</v>
+        <v>6367914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10331,18 +10330,19 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10439,39 +10439,39 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722598</v>
+        <v>128722587</v>
       </c>
       <c r="B102" t="n">
-        <v>86802</v>
+        <v>86977</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715487</v>
+        <v>715464</v>
       </c>
       <c r="R102" t="n">
-        <v>6367923</v>
+        <v>6367911</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10543,10 +10543,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128722579</v>
+        <v>128722598</v>
       </c>
       <c r="B103" t="n">
-        <v>86976</v>
+        <v>86802</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10554,21 +10554,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715205</v>
+        <v>715487</v>
       </c>
       <c r="R103" t="n">
-        <v>6367943</v>
+        <v>6367923</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10640,32 +10640,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128721519</v>
+        <v>128722579</v>
       </c>
       <c r="B104" t="n">
-        <v>86954</v>
+        <v>86976</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715287</v>
+        <v>715205</v>
       </c>
       <c r="R104" t="n">
-        <v>6368083</v>
+        <v>6367943</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10719,26 +10719,25 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722546</v>
+        <v>128721519</v>
       </c>
       <c r="B105" t="n">
         <v>86954</v>
@@ -10773,10 +10772,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715298</v>
+        <v>715287</v>
       </c>
       <c r="R105" t="n">
-        <v>6367872</v>
+        <v>6368083</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10824,44 +10823,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128722587</v>
+        <v>128722546</v>
       </c>
       <c r="B106" t="n">
-        <v>86977</v>
+        <v>86954</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10871,10 +10870,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715464</v>
+        <v>715298</v>
       </c>
       <c r="R106" t="n">
-        <v>6367911</v>
+        <v>6367872</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10915,6 +10914,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10933,32 +10933,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722599</v>
+        <v>128722522</v>
       </c>
       <c r="B107" t="n">
-        <v>86976</v>
+        <v>86756</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715214</v>
+        <v>715314</v>
       </c>
       <c r="R107" t="n">
-        <v>6367950</v>
+        <v>6367886</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11006,18 +11006,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11036,7 +11030,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128722522</v>
+        <v>128722585</v>
       </c>
       <c r="B108" t="n">
         <v>86756</v>
@@ -11071,10 +11065,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715314</v>
+        <v>715309</v>
       </c>
       <c r="R108" t="n">
-        <v>6367886</v>
+        <v>6367883</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11133,7 +11127,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128722585</v>
+        <v>128722545</v>
       </c>
       <c r="B109" t="n">
         <v>86756</v>
@@ -11168,10 +11162,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715309</v>
+        <v>715261</v>
       </c>
       <c r="R109" t="n">
-        <v>6367883</v>
+        <v>6367632</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11230,32 +11224,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128722545</v>
+        <v>128722599</v>
       </c>
       <c r="B110" t="n">
-        <v>86756</v>
+        <v>86976</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11265,10 +11259,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715261</v>
+        <v>715214</v>
       </c>
       <c r="R110" t="n">
-        <v>6367632</v>
+        <v>6367950</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11303,12 +11297,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11417,7 +11417,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -11905,7 +11905,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12487,17 +12487,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128721538</v>
+        <v>128722605</v>
       </c>
       <c r="B123" t="n">
-        <v>75142</v>
+        <v>86917</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715352</v>
+        <v>715315</v>
       </c>
       <c r="R123" t="n">
-        <v>6368147</v>
+        <v>6367838</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12579,22 +12579,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128722605</v>
+        <v>128721538</v>
       </c>
       <c r="B124" t="n">
-        <v>86917</v>
+        <v>75142</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715315</v>
+        <v>715352</v>
       </c>
       <c r="R124" t="n">
-        <v>6367838</v>
+        <v>6368147</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,12 +12676,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128722536</v>
+        <v>128722600</v>
       </c>
       <c r="B2" t="n">
-        <v>91267</v>
+        <v>86921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715340</v>
+        <v>715327</v>
       </c>
       <c r="R2" t="n">
-        <v>6367945</v>
+        <v>6367976</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -773,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128721501</v>
+        <v>128722536</v>
       </c>
       <c r="B3" t="n">
-        <v>88689</v>
+        <v>91272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4379</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715178</v>
+        <v>715340</v>
       </c>
       <c r="R3" t="n">
-        <v>6367628</v>
+        <v>6367945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,28 +851,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722539</v>
+        <v>128721652</v>
       </c>
       <c r="B4" t="n">
-        <v>86756</v>
+        <v>86921</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715181</v>
+        <v>715207</v>
       </c>
       <c r="R4" t="n">
-        <v>6367653</v>
+        <v>6367759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,22 +955,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128722600</v>
+        <v>128721501</v>
       </c>
       <c r="B5" t="n">
-        <v>86917</v>
+        <v>88693</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>4379</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715327</v>
+        <v>715178</v>
       </c>
       <c r="R5" t="n">
-        <v>6367976</v>
+        <v>6367628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,22 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128721652</v>
+        <v>128722539</v>
       </c>
       <c r="B6" t="n">
-        <v>86917</v>
+        <v>86760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715207</v>
+        <v>715181</v>
       </c>
       <c r="R6" t="n">
-        <v>6367759</v>
+        <v>6367653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,12 +1149,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1164,7 +1164,7 @@
         <v>128721539</v>
       </c>
       <c r="B7" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128721516</v>
       </c>
       <c r="B8" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128722554</v>
       </c>
       <c r="B9" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>128722583</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,32 +1555,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722552</v>
+        <v>128722578</v>
       </c>
       <c r="B11" t="n">
-        <v>86954</v>
+        <v>86980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715271</v>
+        <v>715461</v>
       </c>
       <c r="R11" t="n">
-        <v>6367998</v>
+        <v>6367905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,7 +1634,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1653,32 +1652,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722595</v>
+        <v>128722552</v>
       </c>
       <c r="B12" t="n">
-        <v>86907</v>
+        <v>86958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1687,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715468</v>
+        <v>715271</v>
       </c>
       <c r="R12" t="n">
-        <v>6367935</v>
+        <v>6367998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722578</v>
+        <v>128722595</v>
       </c>
       <c r="B13" t="n">
-        <v>86976</v>
+        <v>86911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>449</v>
+        <v>6003235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715461</v>
+        <v>715468</v>
       </c>
       <c r="R13" t="n">
-        <v>6367905</v>
+        <v>6367935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,6 +1829,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>128721548</v>
       </c>
       <c r="B14" t="n">
-        <v>105669</v>
+        <v>105675</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128722563</v>
       </c>
       <c r="B15" t="n">
-        <v>86941</v>
+        <v>86945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128722582</v>
+        <v>128722540</v>
       </c>
       <c r="B16" t="n">
-        <v>92818</v>
+        <v>86760</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,37 +2053,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715492</v>
+        <v>715194</v>
       </c>
       <c r="R16" t="n">
-        <v>6367899</v>
+        <v>6367837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128722540</v>
+        <v>128721499</v>
       </c>
       <c r="B17" t="n">
-        <v>86756</v>
+        <v>87003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715194</v>
+        <v>715394</v>
       </c>
       <c r="R17" t="n">
-        <v>6367837</v>
+        <v>6368208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2222,64 +2219,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721499</v>
+        <v>128722582</v>
       </c>
       <c r="B18" t="n">
-        <v>86999</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715394</v>
+        <v>715492</v>
       </c>
       <c r="R18" t="n">
-        <v>6368208</v>
+        <v>6367899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2320,50 +2319,51 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721578</v>
+        <v>128721560</v>
       </c>
       <c r="B19" t="n">
-        <v>86917</v>
+        <v>86980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715215</v>
+        <v>715503</v>
       </c>
       <c r="R19" t="n">
-        <v>6367918</v>
+        <v>6367589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128721560</v>
+        <v>128721559</v>
       </c>
       <c r="B20" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715503</v>
+        <v>715505</v>
       </c>
       <c r="R20" t="n">
-        <v>6367589</v>
+        <v>6367598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721559</v>
+        <v>128721643</v>
       </c>
       <c r="B21" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715505</v>
+        <v>715270</v>
       </c>
       <c r="R21" t="n">
-        <v>6367598</v>
+        <v>6367607</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2617,22 +2617,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721643</v>
+        <v>128721558</v>
       </c>
       <c r="B22" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715270</v>
+        <v>715424</v>
       </c>
       <c r="R22" t="n">
-        <v>6367607</v>
+        <v>6367651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2714,44 +2714,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128721558</v>
+        <v>128721578</v>
       </c>
       <c r="B23" t="n">
-        <v>86976</v>
+        <v>86921</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715424</v>
+        <v>715215</v>
       </c>
       <c r="R23" t="n">
-        <v>6367651</v>
+        <v>6367918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2826,7 +2826,7 @@
         <v>128722534</v>
       </c>
       <c r="B24" t="n">
-        <v>98597</v>
+        <v>98603</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128721505</v>
+        <v>128722567</v>
       </c>
       <c r="B25" t="n">
-        <v>86802</v>
+        <v>87003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715150</v>
+        <v>715339</v>
       </c>
       <c r="R25" t="n">
-        <v>6367765</v>
+        <v>6367894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2993,24 +2993,30 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3020,7 +3026,7 @@
         <v>128721543</v>
       </c>
       <c r="B26" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128722567</v>
+        <v>128721505</v>
       </c>
       <c r="B27" t="n">
-        <v>86999</v>
+        <v>86806</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715339</v>
+        <v>715150</v>
       </c>
       <c r="R27" t="n">
-        <v>6367894</v>
+        <v>6367765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3187,30 +3193,24 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
         <v>128722602</v>
       </c>
       <c r="B28" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3314,32 +3314,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128721628</v>
+        <v>128722532</v>
       </c>
       <c r="B29" t="n">
-        <v>86999</v>
+        <v>92434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715222</v>
+        <v>715460</v>
       </c>
       <c r="R29" t="n">
-        <v>6367915</v>
+        <v>6367601</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3393,51 +3393,50 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128721540</v>
+        <v>128721628</v>
       </c>
       <c r="B30" t="n">
-        <v>75142</v>
+        <v>87003</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715278</v>
+        <v>715222</v>
       </c>
       <c r="R30" t="n">
-        <v>6368028</v>
+        <v>6367915</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3491,63 +3490,67 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128722532</v>
+        <v>128722518</v>
       </c>
       <c r="B31" t="n">
-        <v>92429</v>
+        <v>86713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>249278</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715460</v>
+        <v>715536</v>
       </c>
       <c r="R31" t="n">
-        <v>6367601</v>
+        <v>6367906</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3569,7 +3572,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3588,6 +3591,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3606,48 +3610,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128722518</v>
+        <v>128721540</v>
       </c>
       <c r="B32" t="n">
-        <v>86709</v>
+        <v>75143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>249278</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715536</v>
+        <v>715278</v>
       </c>
       <c r="R32" t="n">
-        <v>6367906</v>
+        <v>6368028</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3688,51 +3689,50 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722608</v>
+        <v>128722566</v>
       </c>
       <c r="B33" t="n">
-        <v>86917</v>
+        <v>91034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715211</v>
+        <v>715288</v>
       </c>
       <c r="R33" t="n">
-        <v>6367929</v>
+        <v>6367866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722564</v>
+        <v>128722577</v>
       </c>
       <c r="B34" t="n">
-        <v>86941</v>
+        <v>86980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3815,21 +3815,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715387</v>
+        <v>715502</v>
       </c>
       <c r="R34" t="n">
-        <v>6367908</v>
+        <v>6367602</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128721513</v>
+        <v>128722608</v>
       </c>
       <c r="B35" t="n">
-        <v>86756</v>
+        <v>86921</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715408</v>
+        <v>715211</v>
       </c>
       <c r="R35" t="n">
-        <v>6368189</v>
+        <v>6367929</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3986,44 +3986,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128722542</v>
+        <v>128722564</v>
       </c>
       <c r="B36" t="n">
-        <v>86756</v>
+        <v>86945</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3762</v>
+        <v>3599</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715218</v>
+        <v>715387</v>
       </c>
       <c r="R36" t="n">
-        <v>6367844</v>
+        <v>6367908</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,48 +4095,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722517</v>
+        <v>128721511</v>
       </c>
       <c r="B37" t="n">
-        <v>86709</v>
+        <v>91272</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>249278</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715318</v>
+        <v>715180</v>
       </c>
       <c r="R37" t="n">
-        <v>6367974</v>
+        <v>6367626</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4177,51 +4174,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128722556</v>
+        <v>128721513</v>
       </c>
       <c r="B38" t="n">
-        <v>86954</v>
+        <v>86760</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4231,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715180</v>
+        <v>715408</v>
       </c>
       <c r="R38" t="n">
-        <v>6368021</v>
+        <v>6368189</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4275,29 +4271,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721511</v>
+        <v>128722542</v>
       </c>
       <c r="B39" t="n">
-        <v>91267</v>
+        <v>86760</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4305,21 +4300,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715180</v>
+        <v>715218</v>
       </c>
       <c r="R39" t="n">
-        <v>6367626</v>
+        <v>6367844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,57 +4374,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722577</v>
+        <v>128722517</v>
       </c>
       <c r="B40" t="n">
-        <v>86976</v>
+        <v>86713</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>449</v>
+        <v>249278</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715502</v>
+        <v>715318</v>
       </c>
       <c r="R40" t="n">
-        <v>6367602</v>
+        <v>6367974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4451,7 +4449,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4470,6 +4468,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4488,32 +4487,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722566</v>
+        <v>128722556</v>
       </c>
       <c r="B41" t="n">
-        <v>91029</v>
+        <v>86958</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4523,10 +4522,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715288</v>
+        <v>715180</v>
       </c>
       <c r="R41" t="n">
-        <v>6367866</v>
+        <v>6368021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>128721497</v>
       </c>
       <c r="B42" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>128722543</v>
       </c>
       <c r="B43" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,32 +4780,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721577</v>
+        <v>128721557</v>
       </c>
       <c r="B44" t="n">
-        <v>86917</v>
+        <v>86980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715221</v>
+        <v>715213</v>
       </c>
       <c r="R44" t="n">
-        <v>6367967</v>
+        <v>6367921</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721653</v>
+        <v>128721577</v>
       </c>
       <c r="B45" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715476</v>
+        <v>715221</v>
       </c>
       <c r="R45" t="n">
-        <v>6367609</v>
+        <v>6367967</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4962,22 +4962,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128722606</v>
+        <v>128721653</v>
       </c>
       <c r="B46" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715323</v>
+        <v>715476</v>
       </c>
       <c r="R46" t="n">
-        <v>6367903</v>
+        <v>6367609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5059,44 +5059,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721557</v>
+        <v>128722606</v>
       </c>
       <c r="B47" t="n">
-        <v>86976</v>
+        <v>86921</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715213</v>
+        <v>715323</v>
       </c>
       <c r="R47" t="n">
-        <v>6367921</v>
+        <v>6367903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,12 +5156,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5171,7 +5171,7 @@
         <v>128721631</v>
       </c>
       <c r="B48" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>128721517</v>
       </c>
       <c r="B49" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>128722544</v>
       </c>
       <c r="B50" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128721582</v>
+        <v>128721568</v>
       </c>
       <c r="B51" t="n">
-        <v>86917</v>
+        <v>86784</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715178</v>
+        <v>715200</v>
       </c>
       <c r="R51" t="n">
-        <v>6367640</v>
+        <v>6367963</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721568</v>
+        <v>128721563</v>
       </c>
       <c r="B52" t="n">
-        <v>86780</v>
+        <v>92823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,34 +5569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715200</v>
+        <v>715232</v>
       </c>
       <c r="R52" t="n">
-        <v>6367963</v>
+        <v>6367928</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5637,6 +5640,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5658,7 +5662,7 @@
         <v>128722580</v>
       </c>
       <c r="B53" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5752,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128722575</v>
+        <v>128721582</v>
       </c>
       <c r="B54" t="n">
-        <v>105682</v>
+        <v>86921</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5763,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>3674</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5787,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715498</v>
+        <v>715178</v>
       </c>
       <c r="R54" t="n">
-        <v>6367908</v>
+        <v>6367640</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,22 +5841,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128721563</v>
+        <v>128722575</v>
       </c>
       <c r="B55" t="n">
-        <v>92818</v>
+        <v>105688</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5860,37 +5864,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715232</v>
+        <v>715498</v>
       </c>
       <c r="R55" t="n">
-        <v>6367928</v>
+        <v>6367908</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,19 +5932,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
         <v>128722604</v>
       </c>
       <c r="B56" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>128721580</v>
       </c>
       <c r="B57" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>128721547</v>
       </c>
       <c r="B58" t="n">
-        <v>105669</v>
+        <v>105675</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>128722553</v>
       </c>
       <c r="B59" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>128721496</v>
       </c>
       <c r="B60" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128722520</v>
       </c>
       <c r="B61" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6535,32 +6535,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128721644</v>
+        <v>128721567</v>
       </c>
       <c r="B62" t="n">
-        <v>86976</v>
+        <v>96221</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>449</v>
+        <v>2180</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715497</v>
+        <v>715422</v>
       </c>
       <c r="R62" t="n">
-        <v>6367603</v>
+        <v>6367626</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6620,12 +6620,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
         <v>128722557</v>
       </c>
       <c r="B63" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6730,32 +6730,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721567</v>
+        <v>128721507</v>
       </c>
       <c r="B64" t="n">
-        <v>96215</v>
+        <v>57713</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715422</v>
+        <v>715452</v>
       </c>
       <c r="R64" t="n">
-        <v>6367626</v>
+        <v>6367607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6827,32 +6827,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128721507</v>
+        <v>128721644</v>
       </c>
       <c r="B65" t="n">
-        <v>57713</v>
+        <v>86980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715452</v>
+        <v>715497</v>
       </c>
       <c r="R65" t="n">
-        <v>6367607</v>
+        <v>6367603</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6912,44 +6912,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721629</v>
+        <v>128721514</v>
       </c>
       <c r="B66" t="n">
-        <v>57713</v>
+        <v>86760</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715504</v>
+        <v>715141</v>
       </c>
       <c r="R66" t="n">
-        <v>6367595</v>
+        <v>6367822</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -7009,22 +7009,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721522</v>
+        <v>128721629</v>
       </c>
       <c r="B67" t="n">
-        <v>86954</v>
+        <v>57713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715221</v>
+        <v>715504</v>
       </c>
       <c r="R67" t="n">
-        <v>6367902</v>
+        <v>6367595</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -7100,51 +7100,50 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128722550</v>
+        <v>128721635</v>
       </c>
       <c r="B68" t="n">
-        <v>86954</v>
+        <v>86934</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7154,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715321</v>
+        <v>715194</v>
       </c>
       <c r="R68" t="n">
-        <v>6367984</v>
+        <v>6367686</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7198,51 +7197,50 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128722596</v>
+        <v>128722601</v>
       </c>
       <c r="B69" t="n">
-        <v>86907</v>
+        <v>86921</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003235</v>
+        <v>3674</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7252,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715196</v>
+        <v>715264</v>
       </c>
       <c r="R69" t="n">
-        <v>6367906</v>
+        <v>6367986</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7296,7 +7294,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7315,32 +7312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721523</v>
+        <v>128721579</v>
       </c>
       <c r="B70" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7350,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715146</v>
+        <v>715191</v>
       </c>
       <c r="R70" t="n">
-        <v>6367798</v>
+        <v>6367888</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7394,7 +7391,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7413,10 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721635</v>
+        <v>128721651</v>
       </c>
       <c r="B71" t="n">
-        <v>86930</v>
+        <v>86921</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7424,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7448,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715194</v>
+        <v>715215</v>
       </c>
       <c r="R71" t="n">
-        <v>6367686</v>
+        <v>6367933</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7510,45 +7506,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128722601</v>
+        <v>128722516</v>
       </c>
       <c r="B72" t="n">
-        <v>86917</v>
+        <v>86713</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715264</v>
+        <v>715492</v>
       </c>
       <c r="R72" t="n">
-        <v>6367986</v>
+        <v>6367910</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7589,6 +7588,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7607,32 +7607,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721579</v>
+        <v>128721522</v>
       </c>
       <c r="B73" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715191</v>
+        <v>715221</v>
       </c>
       <c r="R73" t="n">
-        <v>6367888</v>
+        <v>6367902</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7686,6 +7686,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7704,32 +7705,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128721514</v>
+        <v>128722550</v>
       </c>
       <c r="B74" t="n">
-        <v>86756</v>
+        <v>86958</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7739,10 +7740,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715141</v>
+        <v>715321</v>
       </c>
       <c r="R74" t="n">
-        <v>6367822</v>
+        <v>6367984</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7783,50 +7784,51 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128721651</v>
+        <v>128722596</v>
       </c>
       <c r="B75" t="n">
-        <v>86917</v>
+        <v>86911</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3674</v>
+        <v>6003235</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7836,10 +7838,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715215</v>
+        <v>715196</v>
       </c>
       <c r="R75" t="n">
-        <v>6367933</v>
+        <v>6367906</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7880,28 +7882,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128722516</v>
+        <v>128721523</v>
       </c>
       <c r="B76" t="n">
-        <v>86709</v>
+        <v>86958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,37 +7912,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715492</v>
+        <v>715146</v>
       </c>
       <c r="R76" t="n">
-        <v>6367910</v>
+        <v>6367798</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7987,12 +7987,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8002,7 +8002,7 @@
         <v>128722521</v>
       </c>
       <c r="B77" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>128721642</v>
       </c>
       <c r="B78" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>128721503</v>
       </c>
       <c r="B79" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>128721521</v>
       </c>
       <c r="B80" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>128722607</v>
       </c>
       <c r="B81" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>128721575</v>
       </c>
       <c r="B82" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>128721581</v>
       </c>
       <c r="B83" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8680,10 +8680,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722589</v>
+        <v>128721502</v>
       </c>
       <c r="B84" t="n">
-        <v>86802</v>
+        <v>91019</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8691,21 +8691,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>424</v>
+        <v>256335</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715223</v>
+        <v>715210</v>
       </c>
       <c r="R84" t="n">
-        <v>6367944</v>
+        <v>6367925</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8759,50 +8759,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722581</v>
+        <v>128722549</v>
       </c>
       <c r="B85" t="n">
-        <v>86976</v>
+        <v>86958</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8812,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715210</v>
+        <v>715448</v>
       </c>
       <c r="R85" t="n">
-        <v>6367925</v>
+        <v>6367902</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8856,6 +8857,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -8874,32 +8876,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722565</v>
+        <v>128722560</v>
       </c>
       <c r="B86" t="n">
-        <v>91029</v>
+        <v>86958</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8909,10 +8911,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715311</v>
+        <v>715549</v>
       </c>
       <c r="R86" t="n">
-        <v>6367855</v>
+        <v>6367883</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8953,6 +8955,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -8971,10 +8974,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128722549</v>
+        <v>128722547</v>
       </c>
       <c r="B87" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9006,10 +9009,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715448</v>
+        <v>715525</v>
       </c>
       <c r="R87" t="n">
-        <v>6367902</v>
+        <v>6367901</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9069,32 +9072,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722560</v>
+        <v>128721552</v>
       </c>
       <c r="B88" t="n">
-        <v>86954</v>
+        <v>105688</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6003295</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9104,10 +9107,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715549</v>
+        <v>715197</v>
       </c>
       <c r="R88" t="n">
-        <v>6367883</v>
+        <v>6367683</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9148,51 +9151,50 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722547</v>
+        <v>128722565</v>
       </c>
       <c r="B89" t="n">
-        <v>86954</v>
+        <v>91034</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9202,10 +9204,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715525</v>
+        <v>715311</v>
       </c>
       <c r="R89" t="n">
-        <v>6367901</v>
+        <v>6367855</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9246,7 +9248,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9265,32 +9266,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128721552</v>
+        <v>128722589</v>
       </c>
       <c r="B90" t="n">
-        <v>105682</v>
+        <v>86806</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9300,10 +9301,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715197</v>
+        <v>715223</v>
       </c>
       <c r="R90" t="n">
-        <v>6367683</v>
+        <v>6367944</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9350,22 +9351,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128721502</v>
+        <v>128722581</v>
       </c>
       <c r="B91" t="n">
-        <v>91014</v>
+        <v>86980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9373,21 +9374,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>256335</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9441,19 +9442,18 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
         <v>128722519</v>
       </c>
       <c r="B92" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9557,10 +9557,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128721647</v>
+        <v>128722558</v>
       </c>
       <c r="B93" t="n">
-        <v>86709</v>
+        <v>86958</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9568,21 +9568,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715216</v>
+        <v>715177</v>
       </c>
       <c r="R93" t="n">
-        <v>6367898</v>
+        <v>6367636</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,11 +9630,6 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -9648,22 +9643,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722558</v>
+        <v>128721647</v>
       </c>
       <c r="B94" t="n">
-        <v>86954</v>
+        <v>86713</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9671,21 +9666,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9695,10 +9690,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715177</v>
+        <v>715216</v>
       </c>
       <c r="R94" t="n">
-        <v>6367636</v>
+        <v>6367898</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9733,6 +9728,11 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -9746,12 +9746,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9761,7 +9761,7 @@
         <v>128722603</v>
       </c>
       <c r="B95" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721541</v>
+        <v>128721649</v>
       </c>
       <c r="B96" t="n">
-        <v>75142</v>
+        <v>86921</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9866,21 +9866,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715250</v>
+        <v>715314</v>
       </c>
       <c r="R96" t="n">
-        <v>6367931</v>
+        <v>6368077</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9940,44 +9940,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721542</v>
+        <v>128722597</v>
       </c>
       <c r="B97" t="n">
-        <v>75142</v>
+        <v>86911</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6426</v>
+        <v>6003235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715519</v>
+        <v>715216</v>
       </c>
       <c r="R97" t="n">
-        <v>6367602</v>
+        <v>6367914</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10031,28 +10031,29 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721649</v>
+        <v>128721541</v>
       </c>
       <c r="B98" t="n">
-        <v>86917</v>
+        <v>75143</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10060,21 +10061,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715314</v>
+        <v>715250</v>
       </c>
       <c r="R98" t="n">
-        <v>6368077</v>
+        <v>6367931</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10134,65 +10135,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721508</v>
+        <v>128721542</v>
       </c>
       <c r="B99" t="n">
-        <v>57713</v>
+        <v>75143</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715206</v>
+        <v>715519</v>
       </c>
       <c r="R99" t="n">
-        <v>6367909</v>
+        <v>6367602</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10214,7 +10207,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -10251,45 +10244,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128722597</v>
+        <v>128721508</v>
       </c>
       <c r="B100" t="n">
-        <v>86907</v>
+        <v>57713</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003235</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715216</v>
+        <v>715206</v>
       </c>
       <c r="R100" t="n">
-        <v>6367914</v>
+        <v>6367909</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10330,51 +10331,50 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128721583</v>
+        <v>128722598</v>
       </c>
       <c r="B101" t="n">
-        <v>86917</v>
+        <v>86806</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715492</v>
+        <v>715487</v>
       </c>
       <c r="R101" t="n">
-        <v>6367606</v>
+        <v>6367923</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -10434,44 +10434,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722587</v>
+        <v>128722579</v>
       </c>
       <c r="B102" t="n">
-        <v>86977</v>
+        <v>86980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>248947</v>
+        <v>449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715464</v>
+        <v>715205</v>
       </c>
       <c r="R102" t="n">
-        <v>6367911</v>
+        <v>6367943</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10543,32 +10543,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128722598</v>
+        <v>128721583</v>
       </c>
       <c r="B103" t="n">
-        <v>86802</v>
+        <v>86921</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715487</v>
+        <v>715492</v>
       </c>
       <c r="R103" t="n">
-        <v>6367923</v>
+        <v>6367606</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10628,44 +10628,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722579</v>
+        <v>128722587</v>
       </c>
       <c r="B104" t="n">
-        <v>86976</v>
+        <v>86981</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>449</v>
+        <v>248947</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715205</v>
+        <v>715464</v>
       </c>
       <c r="R104" t="n">
-        <v>6367943</v>
+        <v>6367911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
         <v>128721519</v>
       </c>
       <c r="B105" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>128722546</v>
       </c>
       <c r="B106" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>128722522</v>
       </c>
       <c r="B107" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>128722585</v>
       </c>
       <c r="B108" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>128722545</v>
       </c>
       <c r="B109" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>128722599</v>
       </c>
       <c r="B110" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>128721572</v>
       </c>
       <c r="B111" t="n">
-        <v>86907</v>
+        <v>86911</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>128721520</v>
       </c>
       <c r="B112" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11522,32 +11522,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128722562</v>
+        <v>128721500</v>
       </c>
       <c r="B113" t="n">
-        <v>98653</v>
+        <v>87003</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715452</v>
+        <v>715318</v>
       </c>
       <c r="R113" t="n">
-        <v>6367610</v>
+        <v>6368090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -11607,44 +11607,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128722548</v>
+        <v>128722523</v>
       </c>
       <c r="B114" t="n">
-        <v>86954</v>
+        <v>86760</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715513</v>
+        <v>715327</v>
       </c>
       <c r="R114" t="n">
-        <v>6367892</v>
+        <v>6367899</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11698,7 +11698,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -11717,32 +11716,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128721524</v>
+        <v>128722535</v>
       </c>
       <c r="B115" t="n">
-        <v>86954</v>
+        <v>86784</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11752,10 +11751,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715222</v>
+        <v>715500</v>
       </c>
       <c r="R115" t="n">
-        <v>6367894</v>
+        <v>6367907</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11796,51 +11795,50 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128721500</v>
+        <v>128722541</v>
       </c>
       <c r="B116" t="n">
-        <v>86999</v>
+        <v>86760</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11850,10 +11848,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715318</v>
+        <v>715501</v>
       </c>
       <c r="R116" t="n">
-        <v>6368090</v>
+        <v>6367911</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11900,22 +11898,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722523</v>
+        <v>128722586</v>
       </c>
       <c r="B117" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11947,10 +11945,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715327</v>
+        <v>715507</v>
       </c>
       <c r="R117" t="n">
-        <v>6367899</v>
+        <v>6367904</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12009,10 +12007,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128721650</v>
+        <v>128721537</v>
       </c>
       <c r="B118" t="n">
-        <v>86917</v>
+        <v>75143</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12020,21 +12018,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12044,10 +12042,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715161</v>
+        <v>715344</v>
       </c>
       <c r="R118" t="n">
-        <v>6368017</v>
+        <v>6368190</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12094,22 +12092,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128722535</v>
+        <v>128721650</v>
       </c>
       <c r="B119" t="n">
-        <v>86780</v>
+        <v>86921</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12117,21 +12115,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12141,10 +12139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715500</v>
+        <v>715161</v>
       </c>
       <c r="R119" t="n">
-        <v>6367907</v>
+        <v>6368017</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12191,22 +12189,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722541</v>
+        <v>128722562</v>
       </c>
       <c r="B120" t="n">
-        <v>86756</v>
+        <v>98659</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12214,21 +12212,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3762</v>
+        <v>219874</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12238,10 +12236,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715501</v>
+        <v>715452</v>
       </c>
       <c r="R120" t="n">
-        <v>6367911</v>
+        <v>6367610</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12263,7 +12261,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12300,32 +12298,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128722586</v>
+        <v>128722548</v>
       </c>
       <c r="B121" t="n">
-        <v>86756</v>
+        <v>86958</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12335,10 +12333,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715507</v>
+        <v>715513</v>
       </c>
       <c r="R121" t="n">
-        <v>6367904</v>
+        <v>6367892</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12379,6 +12377,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12397,32 +12396,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128721537</v>
+        <v>128721524</v>
       </c>
       <c r="B122" t="n">
-        <v>75142</v>
+        <v>86958</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12432,10 +12431,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715344</v>
+        <v>715222</v>
       </c>
       <c r="R122" t="n">
-        <v>6368190</v>
+        <v>6367894</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12476,6 +12475,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12494,10 +12494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128722605</v>
+        <v>128721538</v>
       </c>
       <c r="B123" t="n">
-        <v>86917</v>
+        <v>75143</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715315</v>
+        <v>715352</v>
       </c>
       <c r="R123" t="n">
-        <v>6367838</v>
+        <v>6368147</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12579,22 +12579,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128721538</v>
+        <v>128722605</v>
       </c>
       <c r="B124" t="n">
-        <v>75142</v>
+        <v>86921</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715352</v>
+        <v>715315</v>
       </c>
       <c r="R124" t="n">
-        <v>6368147</v>
+        <v>6367838</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,12 +12676,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -12788,7 +12788,7 @@
         <v>128722590</v>
       </c>
       <c r="B126" t="n">
-        <v>86977</v>
+        <v>86981</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>128721525</v>
       </c>
       <c r="B127" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>128722559</v>
       </c>
       <c r="B128" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>128722551</v>
       </c>
       <c r="B129" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>128722561</v>
       </c>
       <c r="B130" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>128722530</v>
       </c>
       <c r="B131" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128722600</v>
+        <v>128722536</v>
       </c>
       <c r="B2" t="n">
-        <v>86921</v>
+        <v>91277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715327</v>
+        <v>715340</v>
       </c>
       <c r="R2" t="n">
-        <v>6367976</v>
+        <v>6367945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128722536</v>
+        <v>128722539</v>
       </c>
       <c r="B3" t="n">
-        <v>91272</v>
+        <v>86760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715340</v>
+        <v>715181</v>
       </c>
       <c r="R3" t="n">
-        <v>6367945</v>
+        <v>6367653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +852,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128721652</v>
+        <v>128722600</v>
       </c>
       <c r="B4" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715207</v>
+        <v>715327</v>
       </c>
       <c r="R4" t="n">
-        <v>6367759</v>
+        <v>6367976</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,22 +955,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128721501</v>
+        <v>128721652</v>
       </c>
       <c r="B5" t="n">
-        <v>88693</v>
+        <v>86922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4379</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715178</v>
+        <v>715207</v>
       </c>
       <c r="R5" t="n">
-        <v>6367628</v>
+        <v>6367759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,22 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128722539</v>
+        <v>128721539</v>
       </c>
       <c r="B6" t="n">
-        <v>86760</v>
+        <v>75143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715181</v>
+        <v>715289</v>
       </c>
       <c r="R6" t="n">
-        <v>6367653</v>
+        <v>6368047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,44 +1149,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721539</v>
+        <v>128721516</v>
       </c>
       <c r="B7" t="n">
-        <v>75143</v>
+        <v>86959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715289</v>
+        <v>715344</v>
       </c>
       <c r="R7" t="n">
-        <v>6368047</v>
+        <v>6368182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,6 +1240,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1259,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128721516</v>
+        <v>128722554</v>
       </c>
       <c r="B8" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,10 +1294,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715344</v>
+        <v>715247</v>
       </c>
       <c r="R8" t="n">
-        <v>6368182</v>
+        <v>6368027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,44 +1345,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128722554</v>
+        <v>128721501</v>
       </c>
       <c r="B9" t="n">
-        <v>86958</v>
+        <v>88694</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715247</v>
+        <v>715178</v>
       </c>
       <c r="R9" t="n">
-        <v>6368027</v>
+        <v>6367628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,67 +1436,63 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128722583</v>
+        <v>128722578</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>86981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715227</v>
+        <v>715461</v>
       </c>
       <c r="R10" t="n">
-        <v>6367937</v>
+        <v>6367905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,7 +1533,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1555,45 +1551,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722578</v>
+        <v>128722583</v>
       </c>
       <c r="B11" t="n">
-        <v>86980</v>
+        <v>92830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715461</v>
+        <v>715227</v>
       </c>
       <c r="R11" t="n">
-        <v>6367905</v>
+        <v>6367937</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1633,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>128722552</v>
       </c>
       <c r="B12" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128722595</v>
       </c>
       <c r="B13" t="n">
-        <v>86911</v>
+        <v>86912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B14" t="n">
-        <v>105675</v>
+        <v>86946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R14" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B15" t="n">
-        <v>86945</v>
+        <v>105682</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R15" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,44 +2030,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128722540</v>
+        <v>128721560</v>
       </c>
       <c r="B16" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715194</v>
+        <v>715503</v>
       </c>
       <c r="R16" t="n">
-        <v>6367837</v>
+        <v>6367589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2121,29 +2121,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721499</v>
+        <v>128721559</v>
       </c>
       <c r="B17" t="n">
-        <v>87003</v>
+        <v>86981</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715394</v>
+        <v>715505</v>
       </c>
       <c r="R17" t="n">
-        <v>6368208</v>
+        <v>6367598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,7 +2199,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2237,48 +2236,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128722582</v>
+        <v>128721643</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>86981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715492</v>
+        <v>715270</v>
       </c>
       <c r="R18" t="n">
-        <v>6367899</v>
+        <v>6367607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2319,29 +2315,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721560</v>
+        <v>128721558</v>
       </c>
       <c r="B19" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2373,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715503</v>
+        <v>715424</v>
       </c>
       <c r="R19" t="n">
-        <v>6367589</v>
+        <v>6367651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,45 +2430,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128721559</v>
+        <v>128722582</v>
       </c>
       <c r="B20" t="n">
-        <v>86980</v>
+        <v>92830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715505</v>
+        <v>715492</v>
       </c>
       <c r="R20" t="n">
-        <v>6367598</v>
+        <v>6367899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2495,7 +2493,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2514,50 +2512,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721643</v>
+        <v>128722540</v>
       </c>
       <c r="B21" t="n">
-        <v>86980</v>
+        <v>86760</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715270</v>
+        <v>715194</v>
       </c>
       <c r="R21" t="n">
-        <v>6367607</v>
+        <v>6367837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2611,50 +2610,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721558</v>
+        <v>128721578</v>
       </c>
       <c r="B22" t="n">
-        <v>86980</v>
+        <v>86922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715424</v>
+        <v>715215</v>
       </c>
       <c r="R22" t="n">
-        <v>6367651</v>
+        <v>6367918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128721578</v>
+        <v>128721499</v>
       </c>
       <c r="B23" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715215</v>
+        <v>715394</v>
       </c>
       <c r="R23" t="n">
-        <v>6367918</v>
+        <v>6368208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
         <v>128722534</v>
       </c>
       <c r="B24" t="n">
-        <v>98603</v>
+        <v>98610</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128722567</v>
+        <v>128722602</v>
       </c>
       <c r="B25" t="n">
-        <v>87003</v>
+        <v>86922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715339</v>
+        <v>715200</v>
       </c>
       <c r="R25" t="n">
-        <v>6367894</v>
+        <v>6367935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2993,18 +2993,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3023,32 +3017,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128721543</v>
+        <v>128722567</v>
       </c>
       <c r="B26" t="n">
-        <v>75143</v>
+        <v>87004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715500</v>
+        <v>715339</v>
       </c>
       <c r="R26" t="n">
-        <v>6367588</v>
+        <v>6367894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3083,7 +3077,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3096,24 +3090,30 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128722602</v>
+        <v>128721543</v>
       </c>
       <c r="B28" t="n">
-        <v>86921</v>
+        <v>75143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715200</v>
+        <v>715500</v>
       </c>
       <c r="R28" t="n">
-        <v>6367935</v>
+        <v>6367588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3302,44 +3302,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128722532</v>
+        <v>128721628</v>
       </c>
       <c r="B29" t="n">
-        <v>92434</v>
+        <v>87004</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715460</v>
+        <v>715222</v>
       </c>
       <c r="R29" t="n">
-        <v>6367601</v>
+        <v>6367915</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3393,50 +3393,51 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128721628</v>
+        <v>128722532</v>
       </c>
       <c r="B30" t="n">
-        <v>87003</v>
+        <v>92439</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715222</v>
+        <v>715460</v>
       </c>
       <c r="R30" t="n">
-        <v>6367915</v>
+        <v>6367601</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3471,7 +3472,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3490,67 +3491,63 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128722518</v>
+        <v>128721540</v>
       </c>
       <c r="B31" t="n">
-        <v>86713</v>
+        <v>75143</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>249278</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715536</v>
+        <v>715278</v>
       </c>
       <c r="R31" t="n">
-        <v>6367906</v>
+        <v>6368028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3591,64 +3588,66 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128721540</v>
+        <v>128722518</v>
       </c>
       <c r="B32" t="n">
-        <v>75143</v>
+        <v>86713</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>249278</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715278</v>
+        <v>715536</v>
       </c>
       <c r="R32" t="n">
-        <v>6368028</v>
+        <v>6367906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3689,50 +3688,51 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722566</v>
+        <v>128722556</v>
       </c>
       <c r="B33" t="n">
-        <v>91034</v>
+        <v>86959</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715288</v>
+        <v>715180</v>
       </c>
       <c r="R33" t="n">
-        <v>6367866</v>
+        <v>6368021</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3786,6 +3786,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>128722577</v>
       </c>
       <c r="B34" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3901,32 +3902,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722608</v>
+        <v>128722564</v>
       </c>
       <c r="B35" t="n">
-        <v>86921</v>
+        <v>86946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>3599</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3937,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715211</v>
+        <v>715387</v>
       </c>
       <c r="R35" t="n">
-        <v>6367929</v>
+        <v>6367908</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3998,32 +3999,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128722564</v>
+        <v>128721511</v>
       </c>
       <c r="B36" t="n">
-        <v>86945</v>
+        <v>91277</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3599</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4034,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715387</v>
+        <v>715180</v>
       </c>
       <c r="R36" t="n">
-        <v>6367908</v>
+        <v>6367626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,22 +4084,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721511</v>
+        <v>128722608</v>
       </c>
       <c r="B37" t="n">
-        <v>91272</v>
+        <v>86922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4106,21 +4107,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4130,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715180</v>
+        <v>715211</v>
       </c>
       <c r="R37" t="n">
-        <v>6367626</v>
+        <v>6367929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,12 +4181,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4386,48 +4387,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722517</v>
+        <v>128722566</v>
       </c>
       <c r="B40" t="n">
-        <v>86713</v>
+        <v>91039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>249278</v>
+        <v>5747</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715318</v>
+        <v>715288</v>
       </c>
       <c r="R40" t="n">
-        <v>6367974</v>
+        <v>6367866</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,7 +4466,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4487,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722556</v>
+        <v>128722517</v>
       </c>
       <c r="B41" t="n">
-        <v>86958</v>
+        <v>86713</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,34 +4495,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715180</v>
+        <v>715318</v>
       </c>
       <c r="R41" t="n">
-        <v>6368021</v>
+        <v>6367974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4585,10 +4585,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721497</v>
+        <v>128721557</v>
       </c>
       <c r="B42" t="n">
-        <v>87003</v>
+        <v>86981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4596,21 +4596,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715243</v>
+        <v>715213</v>
       </c>
       <c r="R42" t="n">
-        <v>6367615</v>
+        <v>6367921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4664,7 +4664,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4780,32 +4779,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721557</v>
+        <v>128721577</v>
       </c>
       <c r="B44" t="n">
-        <v>86980</v>
+        <v>86922</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4815,10 +4814,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715213</v>
+        <v>715221</v>
       </c>
       <c r="R44" t="n">
-        <v>6367921</v>
+        <v>6367967</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4877,10 +4876,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721577</v>
+        <v>128721653</v>
       </c>
       <c r="B45" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4912,10 +4911,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715221</v>
+        <v>715476</v>
       </c>
       <c r="R45" t="n">
-        <v>6367967</v>
+        <v>6367609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4937,7 +4936,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4962,22 +4961,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721653</v>
+        <v>128722606</v>
       </c>
       <c r="B46" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5009,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715476</v>
+        <v>715323</v>
       </c>
       <c r="R46" t="n">
-        <v>6367609</v>
+        <v>6367903</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5034,7 +5033,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5059,44 +5058,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128722606</v>
+        <v>128721497</v>
       </c>
       <c r="B47" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5106,10 +5105,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715323</v>
+        <v>715243</v>
       </c>
       <c r="R47" t="n">
-        <v>6367903</v>
+        <v>6367615</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5150,28 +5149,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128721631</v>
+        <v>128721517</v>
       </c>
       <c r="B48" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715172</v>
+        <v>715323</v>
       </c>
       <c r="R48" t="n">
-        <v>6367927</v>
+        <v>6368092</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,22 +5254,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128721517</v>
+        <v>128721631</v>
       </c>
       <c r="B49" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715323</v>
+        <v>715172</v>
       </c>
       <c r="R49" t="n">
-        <v>6368092</v>
+        <v>6367927</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5352,44 +5352,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722544</v>
+        <v>128722580</v>
       </c>
       <c r="B50" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715251</v>
+        <v>715209</v>
       </c>
       <c r="R50" t="n">
-        <v>6367635</v>
+        <v>6367900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128721568</v>
+        <v>128722544</v>
       </c>
       <c r="B51" t="n">
-        <v>86784</v>
+        <v>86760</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715200</v>
+        <v>715251</v>
       </c>
       <c r="R51" t="n">
-        <v>6367963</v>
+        <v>6367635</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,22 +5546,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721563</v>
+        <v>128721582</v>
       </c>
       <c r="B52" t="n">
-        <v>92823</v>
+        <v>86922</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,37 +5569,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715232</v>
+        <v>715178</v>
       </c>
       <c r="R52" t="n">
-        <v>6367928</v>
+        <v>6367640</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5640,7 +5637,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5659,32 +5655,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128722580</v>
+        <v>128721568</v>
       </c>
       <c r="B53" t="n">
-        <v>86980</v>
+        <v>86784</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5694,10 +5690,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715209</v>
+        <v>715200</v>
       </c>
       <c r="R53" t="n">
-        <v>6367900</v>
+        <v>6367963</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,22 +5740,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721582</v>
+        <v>128721563</v>
       </c>
       <c r="B54" t="n">
-        <v>86921</v>
+        <v>92830</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,34 +5763,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715178</v>
+        <v>715232</v>
       </c>
       <c r="R54" t="n">
-        <v>6367640</v>
+        <v>6367928</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5835,6 +5834,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>128722575</v>
       </c>
       <c r="B55" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128722604</v>
+        <v>128721496</v>
       </c>
       <c r="B56" t="n">
-        <v>86921</v>
+        <v>86902</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3674</v>
+        <v>473</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715309</v>
+        <v>715344</v>
       </c>
       <c r="R56" t="n">
-        <v>6367880</v>
+        <v>6368190</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6029,28 +6029,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128721580</v>
+        <v>128722604</v>
       </c>
       <c r="B57" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6082,10 +6083,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715147</v>
+        <v>715309</v>
       </c>
       <c r="R57" t="n">
-        <v>6367801</v>
+        <v>6367880</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6132,22 +6133,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128721547</v>
+        <v>128721580</v>
       </c>
       <c r="B58" t="n">
-        <v>105675</v>
+        <v>86922</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6155,21 +6156,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>224098</v>
+        <v>3674</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6179,10 +6180,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715154</v>
+        <v>715147</v>
       </c>
       <c r="R58" t="n">
-        <v>6367783</v>
+        <v>6367801</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6241,32 +6242,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128722553</v>
+        <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>86958</v>
+        <v>105682</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6276,10 +6277,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715261</v>
+        <v>715154</v>
       </c>
       <c r="R59" t="n">
-        <v>6368006</v>
+        <v>6367783</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6320,29 +6321,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128721496</v>
+        <v>128722553</v>
       </c>
       <c r="B60" t="n">
-        <v>86901</v>
+        <v>86959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6350,21 +6350,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715344</v>
+        <v>715261</v>
       </c>
       <c r="R60" t="n">
-        <v>6368190</v>
+        <v>6368006</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6425,22 +6425,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128722520</v>
+        <v>128721644</v>
       </c>
       <c r="B61" t="n">
-        <v>87003</v>
+        <v>86981</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6448,21 +6448,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715450</v>
+        <v>715497</v>
       </c>
       <c r="R61" t="n">
-        <v>6367880</v>
+        <v>6367603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,51 +6516,50 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128721567</v>
+        <v>128722520</v>
       </c>
       <c r="B62" t="n">
-        <v>96221</v>
+        <v>87004</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715422</v>
+        <v>715450</v>
       </c>
       <c r="R62" t="n">
-        <v>6367626</v>
+        <v>6367880</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6595,7 +6594,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -6614,28 +6613,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128722557</v>
+        <v>128721507</v>
       </c>
       <c r="B63" t="n">
-        <v>86958</v>
+        <v>57713</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6643,21 +6643,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715218</v>
+        <v>715452</v>
       </c>
       <c r="R63" t="n">
-        <v>6367940</v>
+        <v>6367607</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -6711,29 +6711,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721507</v>
+        <v>128722557</v>
       </c>
       <c r="B64" t="n">
-        <v>57713</v>
+        <v>86959</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6741,21 +6740,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6765,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715452</v>
+        <v>715218</v>
       </c>
       <c r="R64" t="n">
-        <v>6367607</v>
+        <v>6367940</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6790,7 +6789,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6809,50 +6808,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128721644</v>
+        <v>128721567</v>
       </c>
       <c r="B65" t="n">
-        <v>86980</v>
+        <v>96228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715497</v>
+        <v>715422</v>
       </c>
       <c r="R65" t="n">
-        <v>6367603</v>
+        <v>6367626</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6912,22 +6912,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721514</v>
+        <v>128721635</v>
       </c>
       <c r="B66" t="n">
-        <v>86760</v>
+        <v>86935</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715141</v>
+        <v>715194</v>
       </c>
       <c r="R66" t="n">
-        <v>6367822</v>
+        <v>6367686</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7009,44 +7009,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721629</v>
+        <v>128722601</v>
       </c>
       <c r="B67" t="n">
-        <v>57713</v>
+        <v>86922</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715504</v>
+        <v>715264</v>
       </c>
       <c r="R67" t="n">
-        <v>6367595</v>
+        <v>6367986</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -7106,22 +7106,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721635</v>
+        <v>128721579</v>
       </c>
       <c r="B68" t="n">
-        <v>86934</v>
+        <v>86922</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715194</v>
+        <v>715191</v>
       </c>
       <c r="R68" t="n">
-        <v>6367686</v>
+        <v>6367888</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7203,22 +7203,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128722601</v>
+        <v>128721514</v>
       </c>
       <c r="B69" t="n">
-        <v>86921</v>
+        <v>86760</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715264</v>
+        <v>715141</v>
       </c>
       <c r="R69" t="n">
-        <v>6367986</v>
+        <v>6367822</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7300,22 +7300,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721579</v>
+        <v>128721651</v>
       </c>
       <c r="B70" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715191</v>
+        <v>715215</v>
       </c>
       <c r="R70" t="n">
-        <v>6367888</v>
+        <v>6367933</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7397,44 +7397,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721651</v>
+        <v>128721629</v>
       </c>
       <c r="B71" t="n">
-        <v>86921</v>
+        <v>57713</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715215</v>
+        <v>715504</v>
       </c>
       <c r="R71" t="n">
-        <v>6367933</v>
+        <v>6367595</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7607,10 +7607,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721522</v>
+        <v>128721523</v>
       </c>
       <c r="B73" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715221</v>
+        <v>715146</v>
       </c>
       <c r="R73" t="n">
-        <v>6367902</v>
+        <v>6367798</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7705,32 +7705,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128722550</v>
+        <v>128722596</v>
       </c>
       <c r="B74" t="n">
-        <v>86958</v>
+        <v>86912</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715321</v>
+        <v>715196</v>
       </c>
       <c r="R74" t="n">
-        <v>6367984</v>
+        <v>6367906</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128722596</v>
+        <v>128722550</v>
       </c>
       <c r="B75" t="n">
-        <v>86911</v>
+        <v>86959</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715196</v>
+        <v>715321</v>
       </c>
       <c r="R75" t="n">
-        <v>6367906</v>
+        <v>6367984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128721523</v>
+        <v>128721522</v>
       </c>
       <c r="B76" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715146</v>
+        <v>715221</v>
       </c>
       <c r="R76" t="n">
-        <v>6367798</v>
+        <v>6367902</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7999,32 +7999,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128722521</v>
+        <v>128721503</v>
       </c>
       <c r="B77" t="n">
-        <v>87003</v>
+        <v>110759</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3767</v>
+        <v>219711</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715207</v>
+        <v>715170</v>
       </c>
       <c r="R77" t="n">
-        <v>6367905</v>
+        <v>6367852</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8078,51 +8078,50 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128721642</v>
+        <v>128721521</v>
       </c>
       <c r="B78" t="n">
-        <v>86980</v>
+        <v>86959</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8132,10 +8131,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715204</v>
+        <v>715183</v>
       </c>
       <c r="R78" t="n">
-        <v>6367900</v>
+        <v>6368007</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8176,50 +8175,51 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721503</v>
+        <v>128722521</v>
       </c>
       <c r="B79" t="n">
-        <v>110752</v>
+        <v>87004</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>3767</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715170</v>
+        <v>715207</v>
       </c>
       <c r="R79" t="n">
-        <v>6367852</v>
+        <v>6367905</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8273,50 +8273,51 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128721521</v>
+        <v>128721642</v>
       </c>
       <c r="B80" t="n">
-        <v>86958</v>
+        <v>86981</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8326,10 +8327,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715183</v>
+        <v>715204</v>
       </c>
       <c r="R80" t="n">
-        <v>6368007</v>
+        <v>6367900</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8370,29 +8371,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722607</v>
+        <v>128721552</v>
       </c>
       <c r="B81" t="n">
-        <v>86921</v>
+        <v>105695</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8400,21 +8400,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3674</v>
+        <v>221144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715545</v>
+        <v>715197</v>
       </c>
       <c r="R81" t="n">
-        <v>6367864</v>
+        <v>6367683</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8474,44 +8474,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128721575</v>
+        <v>128721502</v>
       </c>
       <c r="B82" t="n">
-        <v>86921</v>
+        <v>91024</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3674</v>
+        <v>256335</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715333</v>
+        <v>715210</v>
       </c>
       <c r="R82" t="n">
-        <v>6368090</v>
+        <v>6367925</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8565,6 +8565,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8583,32 +8584,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128721581</v>
+        <v>128722547</v>
       </c>
       <c r="B83" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8618,10 +8619,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715150</v>
+        <v>715525</v>
       </c>
       <c r="R83" t="n">
-        <v>6367790</v>
+        <v>6367901</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8662,50 +8663,51 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128721502</v>
+        <v>128722560</v>
       </c>
       <c r="B84" t="n">
-        <v>91019</v>
+        <v>86959</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>256335</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8717,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715210</v>
+        <v>715549</v>
       </c>
       <c r="R84" t="n">
-        <v>6367925</v>
+        <v>6367883</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8766,12 +8768,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8781,7 +8783,7 @@
         <v>128722549</v>
       </c>
       <c r="B85" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8876,32 +8878,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722560</v>
+        <v>128722589</v>
       </c>
       <c r="B86" t="n">
-        <v>86958</v>
+        <v>86806</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8911,10 +8913,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715549</v>
+        <v>715223</v>
       </c>
       <c r="R86" t="n">
-        <v>6367883</v>
+        <v>6367944</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8955,7 +8957,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -8974,32 +8975,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128722547</v>
+        <v>128722581</v>
       </c>
       <c r="B87" t="n">
-        <v>86958</v>
+        <v>86981</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9009,10 +9010,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715525</v>
+        <v>715210</v>
       </c>
       <c r="R87" t="n">
-        <v>6367901</v>
+        <v>6367925</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9053,7 +9054,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9072,10 +9072,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128721552</v>
+        <v>128722607</v>
       </c>
       <c r="B88" t="n">
-        <v>105688</v>
+        <v>86922</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9083,21 +9083,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>3674</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9107,10 +9107,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715197</v>
+        <v>715545</v>
       </c>
       <c r="R88" t="n">
-        <v>6367683</v>
+        <v>6367864</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9157,44 +9157,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722565</v>
+        <v>128721575</v>
       </c>
       <c r="B89" t="n">
-        <v>91034</v>
+        <v>86922</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715311</v>
+        <v>715333</v>
       </c>
       <c r="R89" t="n">
-        <v>6367855</v>
+        <v>6368090</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9254,44 +9254,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128722589</v>
+        <v>128721581</v>
       </c>
       <c r="B90" t="n">
-        <v>86806</v>
+        <v>86922</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715223</v>
+        <v>715150</v>
       </c>
       <c r="R90" t="n">
-        <v>6367944</v>
+        <v>6367790</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9351,22 +9351,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128722581</v>
+        <v>128722565</v>
       </c>
       <c r="B91" t="n">
-        <v>86980</v>
+        <v>91039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9374,21 +9374,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>5747</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715210</v>
+        <v>715311</v>
       </c>
       <c r="R91" t="n">
-        <v>6367925</v>
+        <v>6367855</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9460,32 +9460,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128722519</v>
+        <v>128721647</v>
       </c>
       <c r="B92" t="n">
-        <v>90974</v>
+        <v>86713</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>720</v>
+        <v>249278</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715292</v>
+        <v>715216</v>
       </c>
       <c r="R92" t="n">
-        <v>6367865</v>
+        <v>6367898</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,56 +9533,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722558</v>
+        <v>128722519</v>
       </c>
       <c r="B93" t="n">
-        <v>86958</v>
+        <v>90979</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>720</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9592,10 +9598,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715177</v>
+        <v>715292</v>
       </c>
       <c r="R93" t="n">
-        <v>6367636</v>
+        <v>6367865</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9636,7 +9642,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9655,32 +9660,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128721647</v>
+        <v>128722603</v>
       </c>
       <c r="B94" t="n">
-        <v>86713</v>
+        <v>86922</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9690,10 +9695,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715216</v>
+        <v>715233</v>
       </c>
       <c r="R94" t="n">
-        <v>6367898</v>
+        <v>6367868</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9728,62 +9733,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722603</v>
+        <v>128722558</v>
       </c>
       <c r="B95" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9792,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715233</v>
+        <v>715177</v>
       </c>
       <c r="R95" t="n">
-        <v>6367868</v>
+        <v>6367636</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9837,6 +9836,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>128721649</v>
       </c>
       <c r="B96" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9952,32 +9952,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128722597</v>
+        <v>128721541</v>
       </c>
       <c r="B97" t="n">
-        <v>86911</v>
+        <v>75143</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003235</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715216</v>
+        <v>715250</v>
       </c>
       <c r="R97" t="n">
-        <v>6367914</v>
+        <v>6367931</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10031,26 +10031,25 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721541</v>
+        <v>128721542</v>
       </c>
       <c r="B98" t="n">
         <v>75143</v>
@@ -10085,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715250</v>
+        <v>715519</v>
       </c>
       <c r="R98" t="n">
-        <v>6367931</v>
+        <v>6367602</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10110,7 +10109,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -10147,32 +10146,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721542</v>
+        <v>128722597</v>
       </c>
       <c r="B99" t="n">
-        <v>75143</v>
+        <v>86912</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6426</v>
+        <v>6003235</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10182,10 +10181,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715519</v>
+        <v>715216</v>
       </c>
       <c r="R99" t="n">
-        <v>6367602</v>
+        <v>6367914</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10207,7 +10206,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -10226,18 +10225,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10349,32 +10349,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128722598</v>
+        <v>128722587</v>
       </c>
       <c r="B101" t="n">
-        <v>86806</v>
+        <v>86982</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715487</v>
+        <v>715464</v>
       </c>
       <c r="R101" t="n">
-        <v>6367923</v>
+        <v>6367911</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10446,32 +10446,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722579</v>
+        <v>128721519</v>
       </c>
       <c r="B102" t="n">
-        <v>86980</v>
+        <v>86959</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715205</v>
+        <v>715287</v>
       </c>
       <c r="R102" t="n">
-        <v>6367943</v>
+        <v>6368083</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10525,50 +10525,51 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128721583</v>
+        <v>128722546</v>
       </c>
       <c r="B103" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10578,10 +10579,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715492</v>
+        <v>715298</v>
       </c>
       <c r="R103" t="n">
-        <v>6367606</v>
+        <v>6367872</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10603,7 +10604,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10622,50 +10623,51 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722587</v>
+        <v>128722598</v>
       </c>
       <c r="B104" t="n">
-        <v>86981</v>
+        <v>86806</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10677,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715464</v>
+        <v>715487</v>
       </c>
       <c r="R104" t="n">
-        <v>6367911</v>
+        <v>6367923</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10737,32 +10739,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128721519</v>
+        <v>128722579</v>
       </c>
       <c r="B105" t="n">
-        <v>86958</v>
+        <v>86981</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10772,10 +10774,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715287</v>
+        <v>715205</v>
       </c>
       <c r="R105" t="n">
-        <v>6368083</v>
+        <v>6367943</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10816,51 +10818,50 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128722546</v>
+        <v>128721583</v>
       </c>
       <c r="B106" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10870,10 +10871,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715298</v>
+        <v>715492</v>
       </c>
       <c r="R106" t="n">
-        <v>6367872</v>
+        <v>6367606</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10895,7 +10896,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -10914,26 +10915,25 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722522</v>
+        <v>128722585</v>
       </c>
       <c r="B107" t="n">
         <v>86760</v>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715314</v>
+        <v>715309</v>
       </c>
       <c r="R107" t="n">
-        <v>6367886</v>
+        <v>6367883</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11030,7 +11030,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128722585</v>
+        <v>128722522</v>
       </c>
       <c r="B108" t="n">
         <v>86760</v>
@@ -11065,10 +11065,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715309</v>
+        <v>715314</v>
       </c>
       <c r="R108" t="n">
-        <v>6367883</v>
+        <v>6367886</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11227,7 +11227,7 @@
         <v>128722599</v>
       </c>
       <c r="B110" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11327,32 +11327,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128721572</v>
+        <v>128721520</v>
       </c>
       <c r="B111" t="n">
-        <v>86911</v>
+        <v>86959</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715132</v>
+        <v>715280</v>
       </c>
       <c r="R111" t="n">
-        <v>6367819</v>
+        <v>6368028</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11406,6 +11406,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11424,32 +11425,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128721520</v>
+        <v>128721572</v>
       </c>
       <c r="B112" t="n">
-        <v>86958</v>
+        <v>86912</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11459,10 +11460,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715280</v>
+        <v>715132</v>
       </c>
       <c r="R112" t="n">
-        <v>6368028</v>
+        <v>6367819</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11503,7 +11504,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11522,32 +11522,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128721500</v>
+        <v>128722548</v>
       </c>
       <c r="B113" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715318</v>
+        <v>715513</v>
       </c>
       <c r="R113" t="n">
-        <v>6368090</v>
+        <v>6367892</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11601,50 +11601,51 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128722523</v>
+        <v>128721524</v>
       </c>
       <c r="B114" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11655,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715327</v>
+        <v>715222</v>
       </c>
       <c r="R114" t="n">
-        <v>6367899</v>
+        <v>6367894</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11698,28 +11699,29 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128722535</v>
+        <v>128722523</v>
       </c>
       <c r="B115" t="n">
-        <v>86784</v>
+        <v>86760</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11727,21 +11729,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11751,10 +11753,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715500</v>
+        <v>715327</v>
       </c>
       <c r="R115" t="n">
-        <v>6367907</v>
+        <v>6367899</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11813,10 +11815,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128722541</v>
+        <v>128721650</v>
       </c>
       <c r="B116" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11824,21 +11826,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11848,10 +11850,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715501</v>
+        <v>715161</v>
       </c>
       <c r="R116" t="n">
-        <v>6367911</v>
+        <v>6368017</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11898,22 +11900,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722586</v>
+        <v>128722535</v>
       </c>
       <c r="B117" t="n">
-        <v>86760</v>
+        <v>86784</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11921,21 +11923,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11945,10 +11947,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715507</v>
+        <v>715500</v>
       </c>
       <c r="R117" t="n">
-        <v>6367904</v>
+        <v>6367907</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12007,10 +12009,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128721537</v>
+        <v>128722586</v>
       </c>
       <c r="B118" t="n">
-        <v>75143</v>
+        <v>86760</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12018,21 +12020,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12042,10 +12044,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715344</v>
+        <v>715507</v>
       </c>
       <c r="R118" t="n">
-        <v>6368190</v>
+        <v>6367904</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12092,44 +12094,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128721650</v>
+        <v>128721500</v>
       </c>
       <c r="B119" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12139,10 +12141,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715161</v>
+        <v>715318</v>
       </c>
       <c r="R119" t="n">
-        <v>6368017</v>
+        <v>6368090</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12189,22 +12191,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722562</v>
+        <v>128722541</v>
       </c>
       <c r="B120" t="n">
-        <v>98659</v>
+        <v>86760</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12212,21 +12214,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219874</v>
+        <v>3762</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12236,10 +12238,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715452</v>
+        <v>715501</v>
       </c>
       <c r="R120" t="n">
-        <v>6367610</v>
+        <v>6367911</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12261,7 +12263,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12298,32 +12300,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128722548</v>
+        <v>128721537</v>
       </c>
       <c r="B121" t="n">
-        <v>86958</v>
+        <v>75143</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12333,10 +12335,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715513</v>
+        <v>715344</v>
       </c>
       <c r="R121" t="n">
-        <v>6367892</v>
+        <v>6368190</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12377,51 +12379,50 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128721524</v>
+        <v>128722562</v>
       </c>
       <c r="B122" t="n">
-        <v>86958</v>
+        <v>98666</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12431,10 +12432,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715222</v>
+        <v>715452</v>
       </c>
       <c r="R122" t="n">
-        <v>6367894</v>
+        <v>6367610</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12456,7 +12457,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -12475,19 +12476,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12594,7 +12594,7 @@
         <v>128722605</v>
       </c>
       <c r="B124" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12688,32 +12688,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721526</v>
+        <v>128721525</v>
       </c>
       <c r="B125" t="n">
-        <v>58086</v>
+        <v>86959</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103015</v>
+        <v>6003295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715155</v>
+        <v>715141</v>
       </c>
       <c r="R125" t="n">
-        <v>6367801</v>
+        <v>6367814</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12767,6 +12767,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12785,32 +12786,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128722590</v>
+        <v>128722561</v>
       </c>
       <c r="B126" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12820,10 +12821,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715473</v>
+        <v>715545</v>
       </c>
       <c r="R126" t="n">
-        <v>6367917</v>
+        <v>6367898</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12864,6 +12865,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -12882,10 +12884,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128721525</v>
+        <v>128722551</v>
       </c>
       <c r="B127" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12917,10 +12919,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715141</v>
+        <v>715313</v>
       </c>
       <c r="R127" t="n">
-        <v>6367814</v>
+        <v>6368003</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12968,12 +12970,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -12983,7 +12985,7 @@
         <v>128722559</v>
       </c>
       <c r="B128" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13078,32 +13080,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128722551</v>
+        <v>128721526</v>
       </c>
       <c r="B129" t="n">
-        <v>86958</v>
+        <v>58086</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003295</v>
+        <v>103015</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13113,10 +13115,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715313</v>
+        <v>715155</v>
       </c>
       <c r="R129" t="n">
-        <v>6368003</v>
+        <v>6367801</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13157,51 +13159,50 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722561</v>
+        <v>128722590</v>
       </c>
       <c r="B130" t="n">
-        <v>86958</v>
+        <v>86982</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13211,10 +13212,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715545</v>
+        <v>715473</v>
       </c>
       <c r="R130" t="n">
-        <v>6367898</v>
+        <v>6367917</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13255,7 +13256,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>128722530</v>
       </c>
       <c r="B131" t="n">
-        <v>86992</v>
+        <v>86993</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722600</v>
+        <v>128721539</v>
       </c>
       <c r="B4" t="n">
-        <v>86922</v>
+        <v>75143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715327</v>
+        <v>715289</v>
       </c>
       <c r="R4" t="n">
-        <v>6367976</v>
+        <v>6368047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,22 +955,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128721652</v>
+        <v>128721501</v>
       </c>
       <c r="B5" t="n">
-        <v>86922</v>
+        <v>88694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>4379</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715207</v>
+        <v>715178</v>
       </c>
       <c r="R5" t="n">
-        <v>6367759</v>
+        <v>6367628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,22 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128721539</v>
+        <v>128721652</v>
       </c>
       <c r="B6" t="n">
-        <v>75143</v>
+        <v>86922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715289</v>
+        <v>715207</v>
       </c>
       <c r="R6" t="n">
-        <v>6368047</v>
+        <v>6367759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,44 +1149,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721516</v>
+        <v>128722600</v>
       </c>
       <c r="B7" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715344</v>
+        <v>715327</v>
       </c>
       <c r="R7" t="n">
-        <v>6368182</v>
+        <v>6367976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,26 +1240,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128722554</v>
+        <v>128721516</v>
       </c>
       <c r="B8" t="n">
         <v>86959</v>
@@ -1294,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715247</v>
+        <v>715344</v>
       </c>
       <c r="R8" t="n">
-        <v>6368027</v>
+        <v>6368182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,44 +1344,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128721501</v>
+        <v>128722554</v>
       </c>
       <c r="B9" t="n">
-        <v>88694</v>
+        <v>86959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715178</v>
+        <v>715247</v>
       </c>
       <c r="R9" t="n">
-        <v>6367628</v>
+        <v>6368027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,50 +1435,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128722578</v>
+        <v>128722552</v>
       </c>
       <c r="B10" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715461</v>
+        <v>715271</v>
       </c>
       <c r="R10" t="n">
-        <v>6367905</v>
+        <v>6367998</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1533,6 +1533,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1551,48 +1552,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722583</v>
+        <v>128722595</v>
       </c>
       <c r="B11" t="n">
-        <v>92830</v>
+        <v>86912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6003235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715227</v>
+        <v>715468</v>
       </c>
       <c r="R11" t="n">
-        <v>6367937</v>
+        <v>6367935</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722552</v>
+        <v>128722578</v>
       </c>
       <c r="B12" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1687,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715271</v>
+        <v>715461</v>
       </c>
       <c r="R12" t="n">
-        <v>6367998</v>
+        <v>6367905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,7 +1729,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1750,45 +1747,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722595</v>
+        <v>128722583</v>
       </c>
       <c r="B13" t="n">
-        <v>86912</v>
+        <v>92830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003235</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715468</v>
+        <v>715227</v>
       </c>
       <c r="R13" t="n">
-        <v>6367935</v>
+        <v>6367937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128722540</v>
+        <v>128721578</v>
       </c>
       <c r="B21" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715194</v>
+        <v>715215</v>
       </c>
       <c r="R21" t="n">
-        <v>6367837</v>
+        <v>6367918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2610,29 +2610,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721578</v>
+        <v>128722540</v>
       </c>
       <c r="B22" t="n">
-        <v>86922</v>
+        <v>86760</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2639,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715215</v>
+        <v>715194</v>
       </c>
       <c r="R22" t="n">
-        <v>6367918</v>
+        <v>6367837</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2708,18 +2707,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128722602</v>
+        <v>128721505</v>
       </c>
       <c r="B25" t="n">
-        <v>86922</v>
+        <v>86806</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715200</v>
+        <v>715150</v>
       </c>
       <c r="R25" t="n">
-        <v>6367935</v>
+        <v>6367765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,12 +3005,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3120,32 +3120,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128721505</v>
+        <v>128721543</v>
       </c>
       <c r="B27" t="n">
-        <v>86806</v>
+        <v>75143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>424</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715150</v>
+        <v>715500</v>
       </c>
       <c r="R27" t="n">
-        <v>6367765</v>
+        <v>6367588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128721543</v>
+        <v>128722602</v>
       </c>
       <c r="B28" t="n">
-        <v>75143</v>
+        <v>86922</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715500</v>
+        <v>715200</v>
       </c>
       <c r="R28" t="n">
-        <v>6367588</v>
+        <v>6367935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3302,12 +3302,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3707,32 +3707,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722556</v>
+        <v>128722577</v>
       </c>
       <c r="B33" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715180</v>
+        <v>715502</v>
       </c>
       <c r="R33" t="n">
-        <v>6368021</v>
+        <v>6367602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3786,7 +3786,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3805,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722577</v>
+        <v>128721513</v>
       </c>
       <c r="B34" t="n">
-        <v>86981</v>
+        <v>86760</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3840,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715502</v>
+        <v>715408</v>
       </c>
       <c r="R34" t="n">
-        <v>6367602</v>
+        <v>6368189</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3865,7 +3864,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3890,44 +3889,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722564</v>
+        <v>128722542</v>
       </c>
       <c r="B35" t="n">
-        <v>86946</v>
+        <v>86760</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3599</v>
+        <v>3762</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3937,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715387</v>
+        <v>715218</v>
       </c>
       <c r="R35" t="n">
-        <v>6367908</v>
+        <v>6367844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3999,32 +3998,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721511</v>
+        <v>128722556</v>
       </c>
       <c r="B36" t="n">
-        <v>91277</v>
+        <v>86959</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4037,7 +4036,7 @@
         <v>715180</v>
       </c>
       <c r="R36" t="n">
-        <v>6367626</v>
+        <v>6368021</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4078,63 +4077,67 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722608</v>
+        <v>128722517</v>
       </c>
       <c r="B37" t="n">
-        <v>86922</v>
+        <v>86713</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715211</v>
+        <v>715318</v>
       </c>
       <c r="R37" t="n">
-        <v>6367929</v>
+        <v>6367974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4175,6 +4178,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4193,10 +4197,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721513</v>
+        <v>128721511</v>
       </c>
       <c r="B38" t="n">
-        <v>86760</v>
+        <v>91277</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4208,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4232,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715408</v>
+        <v>715180</v>
       </c>
       <c r="R38" t="n">
-        <v>6368189</v>
+        <v>6367626</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,32 +4294,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722542</v>
+        <v>128722566</v>
       </c>
       <c r="B39" t="n">
-        <v>86760</v>
+        <v>91039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3762</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4329,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715218</v>
+        <v>715288</v>
       </c>
       <c r="R39" t="n">
-        <v>6367844</v>
+        <v>6367866</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,32 +4391,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722566</v>
+        <v>128722608</v>
       </c>
       <c r="B40" t="n">
-        <v>91039</v>
+        <v>86922</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4426,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715288</v>
+        <v>715211</v>
       </c>
       <c r="R40" t="n">
-        <v>6367866</v>
+        <v>6367929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,48 +4488,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722517</v>
+        <v>128722564</v>
       </c>
       <c r="B41" t="n">
-        <v>86713</v>
+        <v>86946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249278</v>
+        <v>3599</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715318</v>
+        <v>715387</v>
       </c>
       <c r="R41" t="n">
-        <v>6367974</v>
+        <v>6367908</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721557</v>
+        <v>128722606</v>
       </c>
       <c r="B42" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715213</v>
+        <v>715323</v>
       </c>
       <c r="R42" t="n">
-        <v>6367921</v>
+        <v>6367903</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4670,22 +4670,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128722543</v>
+        <v>128721577</v>
       </c>
       <c r="B43" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4693,21 +4693,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715253</v>
+        <v>715221</v>
       </c>
       <c r="R43" t="n">
-        <v>6367647</v>
+        <v>6367967</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4767,19 +4767,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721577</v>
+        <v>128721653</v>
       </c>
       <c r="B44" t="n">
         <v>86922</v>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715221</v>
+        <v>715476</v>
       </c>
       <c r="R44" t="n">
-        <v>6367967</v>
+        <v>6367609</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -4864,44 +4864,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721653</v>
+        <v>128721557</v>
       </c>
       <c r="B45" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715476</v>
+        <v>715213</v>
       </c>
       <c r="R45" t="n">
-        <v>6367609</v>
+        <v>6367921</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4961,44 +4961,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128722606</v>
+        <v>128721497</v>
       </c>
       <c r="B46" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715323</v>
+        <v>715243</v>
       </c>
       <c r="R46" t="n">
-        <v>6367903</v>
+        <v>6367615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5052,50 +5052,51 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721497</v>
+        <v>128722543</v>
       </c>
       <c r="B47" t="n">
-        <v>87004</v>
+        <v>86760</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5105,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715243</v>
+        <v>715253</v>
       </c>
       <c r="R47" t="n">
-        <v>6367615</v>
+        <v>6367647</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5149,19 +5150,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721582</v>
+        <v>128721563</v>
       </c>
       <c r="B52" t="n">
-        <v>86922</v>
+        <v>92830</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,34 +5569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715178</v>
+        <v>715232</v>
       </c>
       <c r="R52" t="n">
-        <v>6367640</v>
+        <v>6367928</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5637,6 +5640,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5752,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721563</v>
+        <v>128721582</v>
       </c>
       <c r="B54" t="n">
-        <v>92830</v>
+        <v>86922</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5763,37 +5767,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715232</v>
+        <v>715178</v>
       </c>
       <c r="R54" t="n">
-        <v>6367928</v>
+        <v>6367640</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5834,7 +5835,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128721496</v>
+        <v>128721547</v>
       </c>
       <c r="B56" t="n">
-        <v>86902</v>
+        <v>105682</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>473</v>
+        <v>224098</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715344</v>
+        <v>715154</v>
       </c>
       <c r="R56" t="n">
-        <v>6368190</v>
+        <v>6367783</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6029,7 +6029,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6048,32 +6047,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128722604</v>
+        <v>128721496</v>
       </c>
       <c r="B57" t="n">
-        <v>86922</v>
+        <v>86902</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3674</v>
+        <v>473</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6083,10 +6082,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715309</v>
+        <v>715344</v>
       </c>
       <c r="R57" t="n">
-        <v>6367880</v>
+        <v>6368190</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6127,18 +6126,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128721547</v>
+        <v>128722604</v>
       </c>
       <c r="B59" t="n">
-        <v>105682</v>
+        <v>86922</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6253,21 +6253,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>224098</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715154</v>
+        <v>715309</v>
       </c>
       <c r="R59" t="n">
-        <v>6367783</v>
+        <v>6367880</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6327,12 +6327,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6437,32 +6437,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128721644</v>
+        <v>128721507</v>
       </c>
       <c r="B61" t="n">
-        <v>86981</v>
+        <v>57713</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715497</v>
+        <v>715452</v>
       </c>
       <c r="R61" t="n">
-        <v>6367603</v>
+        <v>6367607</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6522,44 +6522,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128722520</v>
+        <v>128722557</v>
       </c>
       <c r="B62" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715450</v>
+        <v>715218</v>
       </c>
       <c r="R62" t="n">
-        <v>6367880</v>
+        <v>6367940</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6632,32 +6632,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128721507</v>
+        <v>128721644</v>
       </c>
       <c r="B63" t="n">
-        <v>57713</v>
+        <v>86981</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715452</v>
+        <v>715497</v>
       </c>
       <c r="R63" t="n">
-        <v>6367607</v>
+        <v>6367603</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6717,44 +6717,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128722557</v>
+        <v>128721567</v>
       </c>
       <c r="B64" t="n">
-        <v>86959</v>
+        <v>96228</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715218</v>
+        <v>715422</v>
       </c>
       <c r="R64" t="n">
-        <v>6367940</v>
+        <v>6367626</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6808,51 +6808,50 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128721567</v>
+        <v>128722520</v>
       </c>
       <c r="B65" t="n">
-        <v>96228</v>
+        <v>87004</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6862,10 +6861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715422</v>
+        <v>715450</v>
       </c>
       <c r="R65" t="n">
-        <v>6367626</v>
+        <v>6367880</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6887,7 +6886,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -6906,28 +6905,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721635</v>
+        <v>128721514</v>
       </c>
       <c r="B66" t="n">
-        <v>86935</v>
+        <v>86760</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1988</v>
+        <v>3762</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715194</v>
+        <v>715141</v>
       </c>
       <c r="R66" t="n">
-        <v>6367686</v>
+        <v>6367822</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7009,44 +7009,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128722601</v>
+        <v>128721629</v>
       </c>
       <c r="B67" t="n">
-        <v>86922</v>
+        <v>57713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715264</v>
+        <v>715504</v>
       </c>
       <c r="R67" t="n">
-        <v>6367986</v>
+        <v>6367595</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -7106,22 +7106,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721579</v>
+        <v>128721635</v>
       </c>
       <c r="B68" t="n">
-        <v>86922</v>
+        <v>86935</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715191</v>
+        <v>715194</v>
       </c>
       <c r="R68" t="n">
-        <v>6367888</v>
+        <v>6367686</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7203,22 +7203,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721514</v>
+        <v>128721651</v>
       </c>
       <c r="B69" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715141</v>
+        <v>715215</v>
       </c>
       <c r="R69" t="n">
-        <v>6367822</v>
+        <v>6367933</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7300,19 +7300,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721651</v>
+        <v>128721579</v>
       </c>
       <c r="B70" t="n">
         <v>86922</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715215</v>
+        <v>715191</v>
       </c>
       <c r="R70" t="n">
-        <v>6367933</v>
+        <v>6367888</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7397,44 +7397,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721629</v>
+        <v>128722601</v>
       </c>
       <c r="B71" t="n">
-        <v>57713</v>
+        <v>86922</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715504</v>
+        <v>715264</v>
       </c>
       <c r="R71" t="n">
-        <v>6367595</v>
+        <v>6367986</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7494,12 +7494,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8194,10 +8194,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128722521</v>
+        <v>128721642</v>
       </c>
       <c r="B79" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8205,21 +8205,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715207</v>
+        <v>715204</v>
       </c>
       <c r="R79" t="n">
-        <v>6367905</v>
+        <v>6367900</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8273,29 +8273,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128721642</v>
+        <v>128722521</v>
       </c>
       <c r="B80" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8303,21 +8302,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8327,10 +8326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715204</v>
+        <v>715207</v>
       </c>
       <c r="R80" t="n">
-        <v>6367900</v>
+        <v>6367905</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8371,50 +8370,51 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128721552</v>
+        <v>128722589</v>
       </c>
       <c r="B81" t="n">
-        <v>105695</v>
+        <v>86806</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>424</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715197</v>
+        <v>715223</v>
       </c>
       <c r="R81" t="n">
-        <v>6367683</v>
+        <v>6367944</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8474,22 +8474,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128721502</v>
+        <v>128722581</v>
       </c>
       <c r="B82" t="n">
-        <v>91024</v>
+        <v>86981</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8497,21 +8497,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>256335</v>
+        <v>449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8565,51 +8565,50 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722547</v>
+        <v>128721552</v>
       </c>
       <c r="B83" t="n">
-        <v>86959</v>
+        <v>105695</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>221144</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8619,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715525</v>
+        <v>715197</v>
       </c>
       <c r="R83" t="n">
-        <v>6367901</v>
+        <v>6367683</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8663,51 +8662,50 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722560</v>
+        <v>128721502</v>
       </c>
       <c r="B84" t="n">
-        <v>86959</v>
+        <v>91024</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>256335</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8717,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715549</v>
+        <v>715210</v>
       </c>
       <c r="R84" t="n">
-        <v>6367883</v>
+        <v>6367925</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8768,19 +8766,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722549</v>
+        <v>128722547</v>
       </c>
       <c r="B85" t="n">
         <v>86959</v>
@@ -8815,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715448</v>
+        <v>715525</v>
       </c>
       <c r="R85" t="n">
-        <v>6367902</v>
+        <v>6367901</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8878,32 +8876,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722589</v>
+        <v>128722560</v>
       </c>
       <c r="B86" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8913,10 +8911,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715223</v>
+        <v>715549</v>
       </c>
       <c r="R86" t="n">
-        <v>6367944</v>
+        <v>6367883</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8957,6 +8955,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -8975,32 +8974,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128722581</v>
+        <v>128722549</v>
       </c>
       <c r="B87" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9010,10 +9009,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715210</v>
+        <v>715448</v>
       </c>
       <c r="R87" t="n">
-        <v>6367925</v>
+        <v>6367902</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9054,6 +9053,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9072,32 +9072,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722607</v>
+        <v>128722565</v>
       </c>
       <c r="B88" t="n">
-        <v>86922</v>
+        <v>91039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9107,10 +9107,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715545</v>
+        <v>715311</v>
       </c>
       <c r="R88" t="n">
-        <v>6367864</v>
+        <v>6367855</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128721575</v>
+        <v>128721581</v>
       </c>
       <c r="B89" t="n">
         <v>86922</v>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715333</v>
+        <v>715150</v>
       </c>
       <c r="R89" t="n">
-        <v>6368090</v>
+        <v>6367790</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128721581</v>
+        <v>128722607</v>
       </c>
       <c r="B90" t="n">
         <v>86922</v>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715150</v>
+        <v>715545</v>
       </c>
       <c r="R90" t="n">
-        <v>6367790</v>
+        <v>6367864</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9351,44 +9351,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128722565</v>
+        <v>128721575</v>
       </c>
       <c r="B91" t="n">
-        <v>91039</v>
+        <v>86922</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715311</v>
+        <v>715333</v>
       </c>
       <c r="R91" t="n">
-        <v>6367855</v>
+        <v>6368090</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9448,44 +9448,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128721647</v>
+        <v>128722519</v>
       </c>
       <c r="B92" t="n">
-        <v>86713</v>
+        <v>90979</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>249278</v>
+        <v>720</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715216</v>
+        <v>715292</v>
       </c>
       <c r="R92" t="n">
-        <v>6367898</v>
+        <v>6367865</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,62 +9533,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722519</v>
+        <v>128722603</v>
       </c>
       <c r="B93" t="n">
-        <v>90979</v>
+        <v>86922</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>720</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9598,10 +9592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715292</v>
+        <v>715233</v>
       </c>
       <c r="R93" t="n">
-        <v>6367865</v>
+        <v>6367868</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9660,32 +9654,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722603</v>
+        <v>128721647</v>
       </c>
       <c r="B94" t="n">
-        <v>86922</v>
+        <v>86713</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9695,10 +9689,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715233</v>
+        <v>715216</v>
       </c>
       <c r="R94" t="n">
-        <v>6367868</v>
+        <v>6367898</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9733,24 +9727,30 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721649</v>
+        <v>128721541</v>
       </c>
       <c r="B96" t="n">
-        <v>86922</v>
+        <v>75143</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9866,21 +9866,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715314</v>
+        <v>715250</v>
       </c>
       <c r="R96" t="n">
-        <v>6368077</v>
+        <v>6367931</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9940,19 +9940,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721541</v>
+        <v>128721542</v>
       </c>
       <c r="B97" t="n">
         <v>75143</v>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715250</v>
+        <v>715519</v>
       </c>
       <c r="R97" t="n">
-        <v>6367931</v>
+        <v>6367602</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10049,10 +10049,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721542</v>
+        <v>128721649</v>
       </c>
       <c r="B98" t="n">
-        <v>75143</v>
+        <v>86922</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10060,21 +10060,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715519</v>
+        <v>715314</v>
       </c>
       <c r="R98" t="n">
-        <v>6367602</v>
+        <v>6368077</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -10134,57 +10134,65 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128722597</v>
+        <v>128721508</v>
       </c>
       <c r="B99" t="n">
-        <v>86912</v>
+        <v>57713</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6003235</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715216</v>
+        <v>715206</v>
       </c>
       <c r="R99" t="n">
-        <v>6367914</v>
+        <v>6367909</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10225,72 +10233,63 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721508</v>
+        <v>128722597</v>
       </c>
       <c r="B100" t="n">
-        <v>57713</v>
+        <v>86912</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6003235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715206</v>
+        <v>715216</v>
       </c>
       <c r="R100" t="n">
-        <v>6367909</v>
+        <v>6367914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10331,50 +10330,51 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128722587</v>
+        <v>128722598</v>
       </c>
       <c r="B101" t="n">
-        <v>86982</v>
+        <v>86806</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715464</v>
+        <v>715487</v>
       </c>
       <c r="R101" t="n">
-        <v>6367911</v>
+        <v>6367923</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10446,32 +10446,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128721519</v>
+        <v>128722579</v>
       </c>
       <c r="B102" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715287</v>
+        <v>715205</v>
       </c>
       <c r="R102" t="n">
-        <v>6368083</v>
+        <v>6367943</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10525,51 +10525,50 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128722546</v>
+        <v>128721583</v>
       </c>
       <c r="B103" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10579,10 +10578,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715298</v>
+        <v>715492</v>
       </c>
       <c r="R103" t="n">
-        <v>6367872</v>
+        <v>6367606</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10604,7 +10603,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10623,51 +10622,50 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722598</v>
+        <v>128721519</v>
       </c>
       <c r="B104" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10677,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715487</v>
+        <v>715287</v>
       </c>
       <c r="R104" t="n">
-        <v>6367923</v>
+        <v>6368083</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10721,50 +10719,51 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722579</v>
+        <v>128722546</v>
       </c>
       <c r="B105" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10774,10 +10773,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715205</v>
+        <v>715298</v>
       </c>
       <c r="R105" t="n">
-        <v>6367943</v>
+        <v>6367872</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10818,6 +10817,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10836,32 +10836,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128721583</v>
+        <v>128722587</v>
       </c>
       <c r="B106" t="n">
-        <v>86922</v>
+        <v>86982</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715492</v>
+        <v>715464</v>
       </c>
       <c r="R106" t="n">
-        <v>6367606</v>
+        <v>6367911</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -10921,44 +10921,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722585</v>
+        <v>128722599</v>
       </c>
       <c r="B107" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715309</v>
+        <v>715214</v>
       </c>
       <c r="R107" t="n">
-        <v>6367883</v>
+        <v>6367950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11006,12 +11006,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11127,7 +11133,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128722545</v>
+        <v>128722585</v>
       </c>
       <c r="B109" t="n">
         <v>86760</v>
@@ -11162,10 +11168,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715261</v>
+        <v>715309</v>
       </c>
       <c r="R109" t="n">
-        <v>6367632</v>
+        <v>6367883</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,32 +11230,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128722599</v>
+        <v>128722545</v>
       </c>
       <c r="B110" t="n">
-        <v>86981</v>
+        <v>86760</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11259,10 +11265,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715214</v>
+        <v>715261</v>
       </c>
       <c r="R110" t="n">
-        <v>6367950</v>
+        <v>6367632</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11297,18 +11303,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11522,32 +11522,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128722548</v>
+        <v>128722562</v>
       </c>
       <c r="B113" t="n">
-        <v>86959</v>
+        <v>98666</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715513</v>
+        <v>715452</v>
       </c>
       <c r="R113" t="n">
-        <v>6367892</v>
+        <v>6367610</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -11601,7 +11601,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -11620,7 +11619,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128721524</v>
+        <v>128722548</v>
       </c>
       <c r="B114" t="n">
         <v>86959</v>
@@ -11655,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715222</v>
+        <v>715513</v>
       </c>
       <c r="R114" t="n">
-        <v>6367894</v>
+        <v>6367892</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11706,44 +11705,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128722523</v>
+        <v>128721524</v>
       </c>
       <c r="B115" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11753,10 +11752,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715327</v>
+        <v>715222</v>
       </c>
       <c r="R115" t="n">
-        <v>6367899</v>
+        <v>6367894</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11797,50 +11796,51 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128721650</v>
+        <v>128721500</v>
       </c>
       <c r="B116" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11850,10 +11850,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715161</v>
+        <v>715318</v>
       </c>
       <c r="R116" t="n">
-        <v>6368017</v>
+        <v>6368090</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11900,22 +11900,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722535</v>
+        <v>128722523</v>
       </c>
       <c r="B117" t="n">
-        <v>86784</v>
+        <v>86760</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11923,21 +11923,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715500</v>
+        <v>715327</v>
       </c>
       <c r="R117" t="n">
-        <v>6367907</v>
+        <v>6367899</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12009,7 +12009,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722586</v>
+        <v>128722541</v>
       </c>
       <c r="B118" t="n">
         <v>86760</v>
@@ -12044,10 +12044,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715507</v>
+        <v>715501</v>
       </c>
       <c r="R118" t="n">
-        <v>6367904</v>
+        <v>6367911</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12106,32 +12106,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128721500</v>
+        <v>128722586</v>
       </c>
       <c r="B119" t="n">
-        <v>87004</v>
+        <v>86760</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12141,10 +12141,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715318</v>
+        <v>715507</v>
       </c>
       <c r="R119" t="n">
-        <v>6368090</v>
+        <v>6367904</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12191,22 +12191,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722541</v>
+        <v>128721650</v>
       </c>
       <c r="B120" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12214,21 +12214,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715501</v>
+        <v>715161</v>
       </c>
       <c r="R120" t="n">
-        <v>6367911</v>
+        <v>6368017</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12288,22 +12288,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128721537</v>
+        <v>128722535</v>
       </c>
       <c r="B121" t="n">
-        <v>75143</v>
+        <v>86784</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12311,21 +12311,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12335,10 +12335,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715344</v>
+        <v>715500</v>
       </c>
       <c r="R121" t="n">
-        <v>6368190</v>
+        <v>6367907</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12385,22 +12385,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128722562</v>
+        <v>128721537</v>
       </c>
       <c r="B122" t="n">
-        <v>98666</v>
+        <v>75143</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12408,21 +12408,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>6426</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12432,10 +12432,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715452</v>
+        <v>715344</v>
       </c>
       <c r="R122" t="n">
-        <v>6367610</v>
+        <v>6368190</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -12482,12 +12482,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12688,32 +12688,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721525</v>
+        <v>128721526</v>
       </c>
       <c r="B125" t="n">
-        <v>86959</v>
+        <v>58086</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003295</v>
+        <v>103015</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715141</v>
+        <v>715155</v>
       </c>
       <c r="R125" t="n">
-        <v>6367814</v>
+        <v>6367801</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12767,7 +12767,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12786,7 +12785,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128722561</v>
+        <v>128721525</v>
       </c>
       <c r="B126" t="n">
         <v>86959</v>
@@ -12821,10 +12820,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715545</v>
+        <v>715141</v>
       </c>
       <c r="R126" t="n">
-        <v>6367898</v>
+        <v>6367814</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12872,44 +12871,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128722551</v>
+        <v>128722590</v>
       </c>
       <c r="B127" t="n">
-        <v>86959</v>
+        <v>86982</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12919,10 +12918,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715313</v>
+        <v>715473</v>
       </c>
       <c r="R127" t="n">
-        <v>6368003</v>
+        <v>6367917</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12963,7 +12962,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -12982,7 +12980,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722559</v>
+        <v>128722561</v>
       </c>
       <c r="B128" t="n">
         <v>86959</v>
@@ -13017,10 +13015,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715256</v>
+        <v>715545</v>
       </c>
       <c r="R128" t="n">
-        <v>6367627</v>
+        <v>6367898</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13080,32 +13078,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128721526</v>
+        <v>128722551</v>
       </c>
       <c r="B129" t="n">
-        <v>58086</v>
+        <v>86959</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103015</v>
+        <v>6003295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13115,10 +13113,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715155</v>
+        <v>715313</v>
       </c>
       <c r="R129" t="n">
-        <v>6367801</v>
+        <v>6368003</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13159,50 +13157,51 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722590</v>
+        <v>128722559</v>
       </c>
       <c r="B130" t="n">
-        <v>86982</v>
+        <v>86959</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13212,10 +13211,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715473</v>
+        <v>715256</v>
       </c>
       <c r="R130" t="n">
-        <v>6367917</v>
+        <v>6367627</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13256,6 +13255,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128722539</v>
+        <v>128721501</v>
       </c>
       <c r="B3" t="n">
-        <v>86760</v>
+        <v>88694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>4379</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715181</v>
+        <v>715178</v>
       </c>
       <c r="R3" t="n">
-        <v>6367653</v>
+        <v>6367628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,22 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128721539</v>
+        <v>128722539</v>
       </c>
       <c r="B4" t="n">
-        <v>75143</v>
+        <v>86760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715289</v>
+        <v>715181</v>
       </c>
       <c r="R4" t="n">
-        <v>6368047</v>
+        <v>6367653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,22 +955,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128721501</v>
+        <v>128722600</v>
       </c>
       <c r="B5" t="n">
-        <v>88694</v>
+        <v>86922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4379</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715178</v>
+        <v>715327</v>
       </c>
       <c r="R5" t="n">
-        <v>6367628</v>
+        <v>6367976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,12 +1052,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128722600</v>
+        <v>128721539</v>
       </c>
       <c r="B7" t="n">
-        <v>86922</v>
+        <v>75143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715327</v>
+        <v>715289</v>
       </c>
       <c r="R7" t="n">
-        <v>6367976</v>
+        <v>6368047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,12 +1246,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B14" t="n">
-        <v>86946</v>
+        <v>105682</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R14" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B15" t="n">
-        <v>105682</v>
+        <v>86946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R15" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,19 +2030,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128721560</v>
+        <v>128721558</v>
       </c>
       <c r="B16" t="n">
         <v>86981</v>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715503</v>
+        <v>715424</v>
       </c>
       <c r="R16" t="n">
-        <v>6367589</v>
+        <v>6367651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721559</v>
+        <v>128721499</v>
       </c>
       <c r="B17" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715505</v>
+        <v>715394</v>
       </c>
       <c r="R17" t="n">
-        <v>6367598</v>
+        <v>6368208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2236,45 +2236,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721643</v>
+        <v>128722582</v>
       </c>
       <c r="B18" t="n">
-        <v>86981</v>
+        <v>92830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715270</v>
+        <v>715492</v>
       </c>
       <c r="R18" t="n">
-        <v>6367607</v>
+        <v>6367899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2315,25 +2318,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721558</v>
+        <v>128721560</v>
       </c>
       <c r="B19" t="n">
         <v>86981</v>
@@ -2368,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715424</v>
+        <v>715503</v>
       </c>
       <c r="R19" t="n">
-        <v>6367651</v>
+        <v>6367589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,48 +2434,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128722582</v>
+        <v>128721559</v>
       </c>
       <c r="B20" t="n">
-        <v>92830</v>
+        <v>86981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715492</v>
+        <v>715505</v>
       </c>
       <c r="R20" t="n">
-        <v>6367899</v>
+        <v>6367598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2493,7 +2494,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2512,51 +2513,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721578</v>
+        <v>128721643</v>
       </c>
       <c r="B21" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715215</v>
+        <v>715270</v>
       </c>
       <c r="R21" t="n">
-        <v>6367918</v>
+        <v>6367607</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,12 +2616,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128721499</v>
+        <v>128721578</v>
       </c>
       <c r="B23" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715394</v>
+        <v>715215</v>
       </c>
       <c r="R23" t="n">
-        <v>6368208</v>
+        <v>6367918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,32 +3017,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128722567</v>
+        <v>128721543</v>
       </c>
       <c r="B26" t="n">
-        <v>87004</v>
+        <v>75143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715339</v>
+        <v>715500</v>
       </c>
       <c r="R26" t="n">
-        <v>6367894</v>
+        <v>6367588</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3090,40 +3090,34 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128721543</v>
+        <v>128722602</v>
       </c>
       <c r="B27" t="n">
-        <v>75143</v>
+        <v>86922</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715500</v>
+        <v>715200</v>
       </c>
       <c r="R27" t="n">
-        <v>6367588</v>
+        <v>6367935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3180,7 +3174,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3205,44 +3199,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128722602</v>
+        <v>128722567</v>
       </c>
       <c r="B28" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715200</v>
+        <v>715339</v>
       </c>
       <c r="R28" t="n">
-        <v>6367935</v>
+        <v>6367894</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3290,12 +3284,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722577</v>
+        <v>128722564</v>
       </c>
       <c r="B33" t="n">
-        <v>86981</v>
+        <v>86946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3718,21 +3718,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715502</v>
+        <v>715387</v>
       </c>
       <c r="R33" t="n">
-        <v>6367602</v>
+        <v>6367908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3804,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721513</v>
+        <v>128722566</v>
       </c>
       <c r="B34" t="n">
-        <v>86760</v>
+        <v>91039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3762</v>
+        <v>5747</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715408</v>
+        <v>715288</v>
       </c>
       <c r="R34" t="n">
-        <v>6368189</v>
+        <v>6367866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3889,44 +3889,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722542</v>
+        <v>128722577</v>
       </c>
       <c r="B35" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715218</v>
+        <v>715502</v>
       </c>
       <c r="R35" t="n">
-        <v>6367844</v>
+        <v>6367602</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3998,32 +3998,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128722556</v>
+        <v>128721511</v>
       </c>
       <c r="B36" t="n">
-        <v>86959</v>
+        <v>91277</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4036,7 +4036,7 @@
         <v>715180</v>
       </c>
       <c r="R36" t="n">
-        <v>6368021</v>
+        <v>6367626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4077,67 +4077,63 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722517</v>
+        <v>128722608</v>
       </c>
       <c r="B37" t="n">
-        <v>86713</v>
+        <v>86922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715318</v>
+        <v>715211</v>
       </c>
       <c r="R37" t="n">
-        <v>6367974</v>
+        <v>6367929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4178,7 +4174,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4197,10 +4192,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721511</v>
+        <v>128721513</v>
       </c>
       <c r="B38" t="n">
-        <v>91277</v>
+        <v>86760</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4208,21 +4203,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4232,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715180</v>
+        <v>715408</v>
       </c>
       <c r="R38" t="n">
-        <v>6367626</v>
+        <v>6368189</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4294,32 +4289,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722566</v>
+        <v>128722542</v>
       </c>
       <c r="B39" t="n">
-        <v>91039</v>
+        <v>86760</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5747</v>
+        <v>3762</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715288</v>
+        <v>715218</v>
       </c>
       <c r="R39" t="n">
-        <v>6367866</v>
+        <v>6367844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,32 +4386,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722608</v>
+        <v>128722556</v>
       </c>
       <c r="B40" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4426,10 +4421,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715211</v>
+        <v>715180</v>
       </c>
       <c r="R40" t="n">
-        <v>6367929</v>
+        <v>6368021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4470,6 +4465,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4488,45 +4484,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722564</v>
+        <v>128722517</v>
       </c>
       <c r="B41" t="n">
-        <v>86946</v>
+        <v>86713</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3599</v>
+        <v>249278</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715387</v>
+        <v>715318</v>
       </c>
       <c r="R41" t="n">
-        <v>6367908</v>
+        <v>6367974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128722606</v>
+        <v>128721557</v>
       </c>
       <c r="B42" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715323</v>
+        <v>715213</v>
       </c>
       <c r="R42" t="n">
-        <v>6367903</v>
+        <v>6367921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4670,22 +4670,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721577</v>
+        <v>128722543</v>
       </c>
       <c r="B43" t="n">
-        <v>86922</v>
+        <v>86760</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4693,21 +4693,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715221</v>
+        <v>715253</v>
       </c>
       <c r="R43" t="n">
-        <v>6367967</v>
+        <v>6367647</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4767,19 +4767,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721653</v>
+        <v>128721577</v>
       </c>
       <c r="B44" t="n">
         <v>86922</v>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715476</v>
+        <v>715221</v>
       </c>
       <c r="R44" t="n">
-        <v>6367609</v>
+        <v>6367967</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -4864,44 +4864,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721557</v>
+        <v>128721653</v>
       </c>
       <c r="B45" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715213</v>
+        <v>715476</v>
       </c>
       <c r="R45" t="n">
-        <v>6367921</v>
+        <v>6367609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4961,44 +4961,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721497</v>
+        <v>128722606</v>
       </c>
       <c r="B46" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715243</v>
+        <v>715323</v>
       </c>
       <c r="R46" t="n">
-        <v>6367615</v>
+        <v>6367903</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5052,51 +5052,50 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128722543</v>
+        <v>128721497</v>
       </c>
       <c r="B47" t="n">
-        <v>86760</v>
+        <v>87004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5106,10 +5105,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715253</v>
+        <v>715243</v>
       </c>
       <c r="R47" t="n">
-        <v>6367647</v>
+        <v>6367615</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5150,25 +5149,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128721517</v>
+        <v>128721631</v>
       </c>
       <c r="B48" t="n">
         <v>86959</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715323</v>
+        <v>715172</v>
       </c>
       <c r="R48" t="n">
-        <v>6368092</v>
+        <v>6367927</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,19 +5254,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128721631</v>
+        <v>128721517</v>
       </c>
       <c r="B49" t="n">
         <v>86959</v>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715172</v>
+        <v>715323</v>
       </c>
       <c r="R49" t="n">
-        <v>6367927</v>
+        <v>6368092</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5352,12 +5352,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721563</v>
+        <v>128721582</v>
       </c>
       <c r="B52" t="n">
-        <v>92830</v>
+        <v>86922</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,37 +5569,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715232</v>
+        <v>715178</v>
       </c>
       <c r="R52" t="n">
-        <v>6367928</v>
+        <v>6367640</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5640,7 +5637,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5756,10 +5752,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721582</v>
+        <v>128721563</v>
       </c>
       <c r="B54" t="n">
-        <v>86922</v>
+        <v>92830</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,34 +5763,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715178</v>
+        <v>715232</v>
       </c>
       <c r="R54" t="n">
-        <v>6367640</v>
+        <v>6367928</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5835,6 +5834,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128721496</v>
+        <v>128722553</v>
       </c>
       <c r="B57" t="n">
-        <v>86902</v>
+        <v>86959</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6058,21 +6058,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715344</v>
+        <v>715261</v>
       </c>
       <c r="R57" t="n">
-        <v>6368190</v>
+        <v>6368006</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,44 +6133,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128721580</v>
+        <v>128721496</v>
       </c>
       <c r="B58" t="n">
-        <v>86922</v>
+        <v>86902</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3674</v>
+        <v>473</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715147</v>
+        <v>715344</v>
       </c>
       <c r="R58" t="n">
-        <v>6367801</v>
+        <v>6368190</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6224,6 +6224,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6339,32 +6340,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128722553</v>
+        <v>128721580</v>
       </c>
       <c r="B60" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6374,10 +6375,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715261</v>
+        <v>715147</v>
       </c>
       <c r="R60" t="n">
-        <v>6368006</v>
+        <v>6367801</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,51 +6419,50 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128721507</v>
+        <v>128721567</v>
       </c>
       <c r="B61" t="n">
-        <v>57713</v>
+        <v>96228</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715452</v>
+        <v>715422</v>
       </c>
       <c r="R61" t="n">
-        <v>6367607</v>
+        <v>6367626</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6534,32 +6534,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128722557</v>
+        <v>128722520</v>
       </c>
       <c r="B62" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715218</v>
+        <v>715450</v>
       </c>
       <c r="R62" t="n">
-        <v>6367940</v>
+        <v>6367880</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6729,32 +6729,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721567</v>
+        <v>128721507</v>
       </c>
       <c r="B64" t="n">
-        <v>96228</v>
+        <v>57713</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715422</v>
+        <v>715452</v>
       </c>
       <c r="R64" t="n">
-        <v>6367626</v>
+        <v>6367607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,32 +6826,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128722520</v>
+        <v>128722557</v>
       </c>
       <c r="B65" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715450</v>
+        <v>715218</v>
       </c>
       <c r="R65" t="n">
-        <v>6367880</v>
+        <v>6367940</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721514</v>
+        <v>128722601</v>
       </c>
       <c r="B66" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715141</v>
+        <v>715264</v>
       </c>
       <c r="R66" t="n">
-        <v>6367822</v>
+        <v>6367986</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7009,44 +7009,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721629</v>
+        <v>128721579</v>
       </c>
       <c r="B67" t="n">
-        <v>57713</v>
+        <v>86922</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715504</v>
+        <v>715191</v>
       </c>
       <c r="R67" t="n">
-        <v>6367595</v>
+        <v>6367888</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -7106,22 +7106,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721635</v>
+        <v>128721514</v>
       </c>
       <c r="B68" t="n">
-        <v>86935</v>
+        <v>86760</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1988</v>
+        <v>3762</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715194</v>
+        <v>715141</v>
       </c>
       <c r="R68" t="n">
-        <v>6367686</v>
+        <v>6367822</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7203,12 +7203,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7312,32 +7312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721579</v>
+        <v>128721629</v>
       </c>
       <c r="B70" t="n">
-        <v>86922</v>
+        <v>57713</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715191</v>
+        <v>715504</v>
       </c>
       <c r="R70" t="n">
-        <v>6367888</v>
+        <v>6367595</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -7397,22 +7397,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128722601</v>
+        <v>128721635</v>
       </c>
       <c r="B71" t="n">
-        <v>86922</v>
+        <v>86935</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715264</v>
+        <v>715194</v>
       </c>
       <c r="R71" t="n">
-        <v>6367986</v>
+        <v>6367686</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7494,12 +7494,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721523</v>
+        <v>128721522</v>
       </c>
       <c r="B73" t="n">
         <v>86959</v>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715146</v>
+        <v>715221</v>
       </c>
       <c r="R73" t="n">
-        <v>6367798</v>
+        <v>6367902</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7705,32 +7705,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128722596</v>
+        <v>128722550</v>
       </c>
       <c r="B74" t="n">
-        <v>86912</v>
+        <v>86959</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715196</v>
+        <v>715321</v>
       </c>
       <c r="R74" t="n">
-        <v>6367906</v>
+        <v>6367984</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128722550</v>
+        <v>128722596</v>
       </c>
       <c r="B75" t="n">
-        <v>86959</v>
+        <v>86912</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715321</v>
+        <v>715196</v>
       </c>
       <c r="R75" t="n">
-        <v>6367984</v>
+        <v>6367906</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7901,7 +7901,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128721522</v>
+        <v>128721523</v>
       </c>
       <c r="B76" t="n">
         <v>86959</v>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715221</v>
+        <v>715146</v>
       </c>
       <c r="R76" t="n">
-        <v>6367902</v>
+        <v>6367798</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7999,32 +7999,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128721503</v>
+        <v>128721642</v>
       </c>
       <c r="B77" t="n">
-        <v>110759</v>
+        <v>86981</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715170</v>
+        <v>715204</v>
       </c>
       <c r="R77" t="n">
-        <v>6367852</v>
+        <v>6367900</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8084,44 +8084,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128721521</v>
+        <v>128722521</v>
       </c>
       <c r="B78" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715183</v>
+        <v>715207</v>
       </c>
       <c r="R78" t="n">
-        <v>6368007</v>
+        <v>6367905</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8182,44 +8182,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721642</v>
+        <v>128721503</v>
       </c>
       <c r="B79" t="n">
-        <v>86981</v>
+        <v>110759</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715204</v>
+        <v>715170</v>
       </c>
       <c r="R79" t="n">
-        <v>6367900</v>
+        <v>6367852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8279,44 +8279,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128722521</v>
+        <v>128721521</v>
       </c>
       <c r="B80" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8326,10 +8326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715207</v>
+        <v>715183</v>
       </c>
       <c r="R80" t="n">
-        <v>6367905</v>
+        <v>6368007</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8377,12 +8377,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128721552</v>
+        <v>128722607</v>
       </c>
       <c r="B83" t="n">
-        <v>105695</v>
+        <v>86922</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8594,21 +8594,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221144</v>
+        <v>3674</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715197</v>
+        <v>715545</v>
       </c>
       <c r="R83" t="n">
-        <v>6367683</v>
+        <v>6367864</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8668,44 +8668,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128721502</v>
+        <v>128721575</v>
       </c>
       <c r="B84" t="n">
-        <v>91024</v>
+        <v>86922</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>256335</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715210</v>
+        <v>715333</v>
       </c>
       <c r="R84" t="n">
-        <v>6367925</v>
+        <v>6368090</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8759,7 +8759,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8778,32 +8777,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722547</v>
+        <v>128721581</v>
       </c>
       <c r="B85" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8813,10 +8812,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715525</v>
+        <v>715150</v>
       </c>
       <c r="R85" t="n">
-        <v>6367901</v>
+        <v>6367790</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8857,51 +8856,50 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722560</v>
+        <v>128722565</v>
       </c>
       <c r="B86" t="n">
-        <v>86959</v>
+        <v>91039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8911,10 +8909,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715549</v>
+        <v>715311</v>
       </c>
       <c r="R86" t="n">
-        <v>6367883</v>
+        <v>6367855</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8955,7 +8953,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -8974,32 +8971,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128722549</v>
+        <v>128721502</v>
       </c>
       <c r="B87" t="n">
-        <v>86959</v>
+        <v>91024</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>256335</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9009,10 +9006,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715448</v>
+        <v>715210</v>
       </c>
       <c r="R87" t="n">
-        <v>6367902</v>
+        <v>6367925</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9060,44 +9057,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722565</v>
+        <v>128721552</v>
       </c>
       <c r="B88" t="n">
-        <v>91039</v>
+        <v>105695</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5747</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9107,10 +9104,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715311</v>
+        <v>715197</v>
       </c>
       <c r="R88" t="n">
-        <v>6367855</v>
+        <v>6367683</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9157,44 +9154,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128721581</v>
+        <v>128722549</v>
       </c>
       <c r="B89" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9204,10 +9201,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715150</v>
+        <v>715448</v>
       </c>
       <c r="R89" t="n">
-        <v>6367790</v>
+        <v>6367902</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9248,50 +9245,51 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128722607</v>
+        <v>128722560</v>
       </c>
       <c r="B90" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9301,10 +9299,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715545</v>
+        <v>715549</v>
       </c>
       <c r="R90" t="n">
-        <v>6367864</v>
+        <v>6367883</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9345,6 +9343,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9363,32 +9362,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128721575</v>
+        <v>128722547</v>
       </c>
       <c r="B91" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9397,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715333</v>
+        <v>715525</v>
       </c>
       <c r="R91" t="n">
-        <v>6368090</v>
+        <v>6367901</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9442,50 +9441,51 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128722519</v>
+        <v>128722558</v>
       </c>
       <c r="B92" t="n">
-        <v>90979</v>
+        <v>86959</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>720</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715292</v>
+        <v>715177</v>
       </c>
       <c r="R92" t="n">
-        <v>6367865</v>
+        <v>6367636</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9539,6 +9539,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9557,32 +9558,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722603</v>
+        <v>128721647</v>
       </c>
       <c r="B93" t="n">
-        <v>86922</v>
+        <v>86713</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9592,10 +9593,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715233</v>
+        <v>715216</v>
       </c>
       <c r="R93" t="n">
-        <v>6367868</v>
+        <v>6367898</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,56 +9631,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128721647</v>
+        <v>128722519</v>
       </c>
       <c r="B94" t="n">
-        <v>86713</v>
+        <v>90979</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>249278</v>
+        <v>720</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9689,10 +9696,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715216</v>
+        <v>715292</v>
       </c>
       <c r="R94" t="n">
-        <v>6367898</v>
+        <v>6367865</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9727,62 +9734,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722558</v>
+        <v>128722603</v>
       </c>
       <c r="B95" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9792,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715177</v>
+        <v>715233</v>
       </c>
       <c r="R95" t="n">
-        <v>6367636</v>
+        <v>6367868</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9836,7 +9837,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9855,32 +9855,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721541</v>
+        <v>128722597</v>
       </c>
       <c r="B96" t="n">
-        <v>75143</v>
+        <v>86912</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6426</v>
+        <v>6003235</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715250</v>
+        <v>715216</v>
       </c>
       <c r="R96" t="n">
-        <v>6367931</v>
+        <v>6367914</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9934,28 +9934,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721542</v>
+        <v>128721649</v>
       </c>
       <c r="B97" t="n">
-        <v>75143</v>
+        <v>86922</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9963,21 +9964,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9988,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715519</v>
+        <v>715314</v>
       </c>
       <c r="R97" t="n">
-        <v>6367602</v>
+        <v>6368077</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10012,7 +10013,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10037,22 +10038,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721649</v>
+        <v>128721542</v>
       </c>
       <c r="B98" t="n">
-        <v>86922</v>
+        <v>75143</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10060,21 +10061,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715314</v>
+        <v>715519</v>
       </c>
       <c r="R98" t="n">
-        <v>6368077</v>
+        <v>6367602</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10109,7 +10110,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -10134,65 +10135,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721508</v>
+        <v>128721541</v>
       </c>
       <c r="B99" t="n">
-        <v>57713</v>
+        <v>75143</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715206</v>
+        <v>715250</v>
       </c>
       <c r="R99" t="n">
-        <v>6367909</v>
+        <v>6367931</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10251,45 +10244,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128722597</v>
+        <v>128721508</v>
       </c>
       <c r="B100" t="n">
-        <v>86912</v>
+        <v>57713</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003235</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715216</v>
+        <v>715206</v>
       </c>
       <c r="R100" t="n">
-        <v>6367914</v>
+        <v>6367909</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10330,19 +10331,18 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10640,32 +10640,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128721519</v>
+        <v>128722587</v>
       </c>
       <c r="B104" t="n">
-        <v>86959</v>
+        <v>86982</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715287</v>
+        <v>715464</v>
       </c>
       <c r="R104" t="n">
-        <v>6368083</v>
+        <v>6367911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10719,26 +10719,25 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722546</v>
+        <v>128721519</v>
       </c>
       <c r="B105" t="n">
         <v>86959</v>
@@ -10773,10 +10772,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715298</v>
+        <v>715287</v>
       </c>
       <c r="R105" t="n">
-        <v>6367872</v>
+        <v>6368083</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10824,44 +10823,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128722587</v>
+        <v>128722546</v>
       </c>
       <c r="B106" t="n">
-        <v>86982</v>
+        <v>86959</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10871,10 +10870,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715464</v>
+        <v>715298</v>
       </c>
       <c r="R106" t="n">
-        <v>6367911</v>
+        <v>6367872</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10915,6 +10914,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10933,32 +10933,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722599</v>
+        <v>128722522</v>
       </c>
       <c r="B107" t="n">
-        <v>86981</v>
+        <v>86760</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715214</v>
+        <v>715314</v>
       </c>
       <c r="R107" t="n">
-        <v>6367950</v>
+        <v>6367886</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11006,18 +11006,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11036,7 +11030,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128722522</v>
+        <v>128722585</v>
       </c>
       <c r="B108" t="n">
         <v>86760</v>
@@ -11071,10 +11065,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715314</v>
+        <v>715309</v>
       </c>
       <c r="R108" t="n">
-        <v>6367886</v>
+        <v>6367883</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11133,7 +11127,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128722585</v>
+        <v>128722545</v>
       </c>
       <c r="B109" t="n">
         <v>86760</v>
@@ -11168,10 +11162,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715309</v>
+        <v>715261</v>
       </c>
       <c r="R109" t="n">
-        <v>6367883</v>
+        <v>6367632</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11230,32 +11224,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128722545</v>
+        <v>128722599</v>
       </c>
       <c r="B110" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11265,10 +11259,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715261</v>
+        <v>715214</v>
       </c>
       <c r="R110" t="n">
-        <v>6367632</v>
+        <v>6367950</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11303,12 +11297,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11327,32 +11327,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128721520</v>
+        <v>128721572</v>
       </c>
       <c r="B111" t="n">
-        <v>86959</v>
+        <v>86912</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715280</v>
+        <v>715132</v>
       </c>
       <c r="R111" t="n">
-        <v>6368028</v>
+        <v>6367819</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11406,7 +11406,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11425,32 +11424,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128721572</v>
+        <v>128721520</v>
       </c>
       <c r="B112" t="n">
-        <v>86912</v>
+        <v>86959</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11460,10 +11459,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715132</v>
+        <v>715280</v>
       </c>
       <c r="R112" t="n">
-        <v>6367819</v>
+        <v>6368028</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11504,6 +11503,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11522,32 +11522,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128722562</v>
+        <v>128721500</v>
       </c>
       <c r="B113" t="n">
-        <v>98666</v>
+        <v>87004</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715452</v>
+        <v>715318</v>
       </c>
       <c r="R113" t="n">
-        <v>6367610</v>
+        <v>6368090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -11607,44 +11607,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128722548</v>
+        <v>128722523</v>
       </c>
       <c r="B114" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715513</v>
+        <v>715327</v>
       </c>
       <c r="R114" t="n">
-        <v>6367892</v>
+        <v>6367899</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11698,7 +11698,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -11717,32 +11716,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128721524</v>
+        <v>128721650</v>
       </c>
       <c r="B115" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11752,10 +11751,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715222</v>
+        <v>715161</v>
       </c>
       <c r="R115" t="n">
-        <v>6367894</v>
+        <v>6368017</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11796,51 +11795,50 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128721500</v>
+        <v>128722535</v>
       </c>
       <c r="B116" t="n">
-        <v>87004</v>
+        <v>86784</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11850,10 +11848,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715318</v>
+        <v>715500</v>
       </c>
       <c r="R116" t="n">
-        <v>6368090</v>
+        <v>6367907</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11900,19 +11898,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722523</v>
+        <v>128722541</v>
       </c>
       <c r="B117" t="n">
         <v>86760</v>
@@ -11947,10 +11945,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715327</v>
+        <v>715501</v>
       </c>
       <c r="R117" t="n">
-        <v>6367899</v>
+        <v>6367911</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12009,7 +12007,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722541</v>
+        <v>128722586</v>
       </c>
       <c r="B118" t="n">
         <v>86760</v>
@@ -12044,10 +12042,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715501</v>
+        <v>715507</v>
       </c>
       <c r="R118" t="n">
-        <v>6367911</v>
+        <v>6367904</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12106,10 +12104,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128722586</v>
+        <v>128721537</v>
       </c>
       <c r="B119" t="n">
-        <v>86760</v>
+        <v>75143</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12117,21 +12115,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12141,10 +12139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715507</v>
+        <v>715344</v>
       </c>
       <c r="R119" t="n">
-        <v>6367904</v>
+        <v>6368190</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12191,22 +12189,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128721650</v>
+        <v>128722562</v>
       </c>
       <c r="B120" t="n">
-        <v>86922</v>
+        <v>98666</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12214,21 +12212,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12238,10 +12236,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715161</v>
+        <v>715452</v>
       </c>
       <c r="R120" t="n">
-        <v>6368017</v>
+        <v>6367610</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12263,7 +12261,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12288,44 +12286,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128722535</v>
+        <v>128722548</v>
       </c>
       <c r="B121" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12335,10 +12333,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715500</v>
+        <v>715513</v>
       </c>
       <c r="R121" t="n">
-        <v>6367907</v>
+        <v>6367892</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12379,6 +12377,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12397,32 +12396,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128721537</v>
+        <v>128721524</v>
       </c>
       <c r="B122" t="n">
-        <v>75143</v>
+        <v>86959</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12432,10 +12431,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715344</v>
+        <v>715222</v>
       </c>
       <c r="R122" t="n">
-        <v>6368190</v>
+        <v>6367894</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12476,6 +12475,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12494,10 +12494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128721538</v>
+        <v>128722605</v>
       </c>
       <c r="B123" t="n">
-        <v>75143</v>
+        <v>86922</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715352</v>
+        <v>715315</v>
       </c>
       <c r="R123" t="n">
-        <v>6368147</v>
+        <v>6367838</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12579,22 +12579,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128722605</v>
+        <v>128721538</v>
       </c>
       <c r="B124" t="n">
-        <v>86922</v>
+        <v>75143</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715315</v>
+        <v>715352</v>
       </c>
       <c r="R124" t="n">
-        <v>6367838</v>
+        <v>6368147</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,44 +12676,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721526</v>
+        <v>128721525</v>
       </c>
       <c r="B125" t="n">
-        <v>58086</v>
+        <v>86959</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103015</v>
+        <v>6003295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715155</v>
+        <v>715141</v>
       </c>
       <c r="R125" t="n">
-        <v>6367801</v>
+        <v>6367814</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12767,6 +12767,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12785,7 +12786,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128721525</v>
+        <v>128722559</v>
       </c>
       <c r="B126" t="n">
         <v>86959</v>
@@ -12820,10 +12821,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715141</v>
+        <v>715256</v>
       </c>
       <c r="R126" t="n">
-        <v>6367814</v>
+        <v>6367627</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12871,44 +12872,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128722590</v>
+        <v>128722551</v>
       </c>
       <c r="B127" t="n">
-        <v>86982</v>
+        <v>86959</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12918,10 +12919,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715473</v>
+        <v>715313</v>
       </c>
       <c r="R127" t="n">
-        <v>6367917</v>
+        <v>6368003</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12962,6 +12963,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13078,32 +13080,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128722551</v>
+        <v>128721526</v>
       </c>
       <c r="B129" t="n">
-        <v>86959</v>
+        <v>58086</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003295</v>
+        <v>103015</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13113,10 +13115,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715313</v>
+        <v>715155</v>
       </c>
       <c r="R129" t="n">
-        <v>6368003</v>
+        <v>6367801</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13157,51 +13159,50 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722559</v>
+        <v>128722590</v>
       </c>
       <c r="B130" t="n">
-        <v>86959</v>
+        <v>86982</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13211,10 +13212,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715256</v>
+        <v>715473</v>
       </c>
       <c r="R130" t="n">
-        <v>6367627</v>
+        <v>6367917</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13255,7 +13256,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128722536</v>
+        <v>128721516</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
+        <v>86963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715340</v>
+        <v>715344</v>
       </c>
       <c r="R2" t="n">
-        <v>6367945</v>
+        <v>6368182</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,44 +761,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128721501</v>
+        <v>128722554</v>
       </c>
       <c r="B3" t="n">
-        <v>88694</v>
+        <v>86963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715178</v>
+        <v>715247</v>
       </c>
       <c r="R3" t="n">
-        <v>6367628</v>
+        <v>6368027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,28 +852,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722539</v>
+        <v>128722536</v>
       </c>
       <c r="B4" t="n">
-        <v>86760</v>
+        <v>91281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715181</v>
+        <v>715340</v>
       </c>
       <c r="R4" t="n">
-        <v>6367653</v>
+        <v>6367945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,6 +950,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -967,10 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128722600</v>
+        <v>128721539</v>
       </c>
       <c r="B5" t="n">
-        <v>86922</v>
+        <v>75147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +980,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1004,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715327</v>
+        <v>715289</v>
       </c>
       <c r="R5" t="n">
-        <v>6367976</v>
+        <v>6368047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,22 +1054,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128721652</v>
+        <v>128722539</v>
       </c>
       <c r="B6" t="n">
-        <v>86922</v>
+        <v>86764</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1077,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1101,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715207</v>
+        <v>715181</v>
       </c>
       <c r="R6" t="n">
-        <v>6367759</v>
+        <v>6367653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,22 +1151,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721539</v>
+        <v>128722600</v>
       </c>
       <c r="B7" t="n">
-        <v>75143</v>
+        <v>86926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1174,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1198,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715289</v>
+        <v>715327</v>
       </c>
       <c r="R7" t="n">
-        <v>6368047</v>
+        <v>6367976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,44 +1248,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128721516</v>
+        <v>128721652</v>
       </c>
       <c r="B8" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1295,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715344</v>
+        <v>715207</v>
       </c>
       <c r="R8" t="n">
-        <v>6368182</v>
+        <v>6367759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,51 +1339,50 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128722554</v>
+        <v>128721501</v>
       </c>
       <c r="B9" t="n">
-        <v>86959</v>
+        <v>88698</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715247</v>
+        <v>715178</v>
       </c>
       <c r="R9" t="n">
-        <v>6368027</v>
+        <v>6367628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,64 +1436,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128722552</v>
+        <v>128722583</v>
       </c>
       <c r="B10" t="n">
-        <v>86959</v>
+        <v>92834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715271</v>
+        <v>715227</v>
       </c>
       <c r="R10" t="n">
-        <v>6367998</v>
+        <v>6367937</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1555,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722595</v>
+        <v>128722552</v>
       </c>
       <c r="B11" t="n">
-        <v>86912</v>
+        <v>86963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1590,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715468</v>
+        <v>715271</v>
       </c>
       <c r="R11" t="n">
-        <v>6367935</v>
+        <v>6367998</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722578</v>
+        <v>128722595</v>
       </c>
       <c r="B12" t="n">
-        <v>86981</v>
+        <v>86916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>449</v>
+        <v>6003235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715461</v>
+        <v>715468</v>
       </c>
       <c r="R12" t="n">
-        <v>6367905</v>
+        <v>6367935</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1729,6 +1732,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1747,48 +1751,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722583</v>
+        <v>128722578</v>
       </c>
       <c r="B13" t="n">
-        <v>92830</v>
+        <v>86985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715227</v>
+        <v>715461</v>
       </c>
       <c r="R13" t="n">
-        <v>6367937</v>
+        <v>6367905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1829,7 +1830,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B14" t="n">
-        <v>105682</v>
+        <v>86950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R14" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B15" t="n">
-        <v>86946</v>
+        <v>105686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R15" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,22 +2030,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128721558</v>
+        <v>128721560</v>
       </c>
       <c r="B16" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715424</v>
+        <v>715503</v>
       </c>
       <c r="R16" t="n">
-        <v>6367651</v>
+        <v>6367589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721499</v>
+        <v>128721559</v>
       </c>
       <c r="B17" t="n">
-        <v>87004</v>
+        <v>86985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715394</v>
+        <v>715505</v>
       </c>
       <c r="R17" t="n">
-        <v>6368208</v>
+        <v>6367598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2236,48 +2236,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128722582</v>
+        <v>128721643</v>
       </c>
       <c r="B18" t="n">
-        <v>92830</v>
+        <v>86985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715492</v>
+        <v>715270</v>
       </c>
       <c r="R18" t="n">
-        <v>6367899</v>
+        <v>6367607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,29 +2315,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721560</v>
+        <v>128721558</v>
       </c>
       <c r="B19" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2372,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715503</v>
+        <v>715424</v>
       </c>
       <c r="R19" t="n">
-        <v>6367589</v>
+        <v>6367651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,45 +2430,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128721559</v>
+        <v>128722582</v>
       </c>
       <c r="B20" t="n">
-        <v>86981</v>
+        <v>92834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715505</v>
+        <v>715492</v>
       </c>
       <c r="R20" t="n">
-        <v>6367598</v>
+        <v>6367899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2494,7 +2493,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2513,50 +2512,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721643</v>
+        <v>128722540</v>
       </c>
       <c r="B21" t="n">
-        <v>86981</v>
+        <v>86764</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715270</v>
+        <v>715194</v>
       </c>
       <c r="R21" t="n">
-        <v>6367607</v>
+        <v>6367837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2610,50 +2610,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128722540</v>
+        <v>128721499</v>
       </c>
       <c r="B22" t="n">
-        <v>86760</v>
+        <v>87008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2663,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715194</v>
+        <v>715394</v>
       </c>
       <c r="R22" t="n">
-        <v>6367837</v>
+        <v>6368208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2707,19 +2708,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
         <v>128721578</v>
       </c>
       <c r="B23" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>128722534</v>
       </c>
       <c r="B24" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128721505</v>
+        <v>128722567</v>
       </c>
       <c r="B25" t="n">
-        <v>86806</v>
+        <v>87008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715150</v>
+        <v>715339</v>
       </c>
       <c r="R25" t="n">
-        <v>6367765</v>
+        <v>6367894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2993,34 +2993,40 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128721543</v>
+        <v>128722602</v>
       </c>
       <c r="B26" t="n">
-        <v>75143</v>
+        <v>86926</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715500</v>
+        <v>715200</v>
       </c>
       <c r="R26" t="n">
-        <v>6367588</v>
+        <v>6367935</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3077,7 +3083,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3102,44 +3108,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128722602</v>
+        <v>128721505</v>
       </c>
       <c r="B27" t="n">
-        <v>86922</v>
+        <v>86810</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715200</v>
+        <v>715150</v>
       </c>
       <c r="R27" t="n">
-        <v>6367935</v>
+        <v>6367765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,44 +3205,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128722567</v>
+        <v>128721543</v>
       </c>
       <c r="B28" t="n">
-        <v>87004</v>
+        <v>75147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715339</v>
+        <v>715500</v>
       </c>
       <c r="R28" t="n">
-        <v>6367894</v>
+        <v>6367588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3271,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3284,62 +3290,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128721628</v>
+        <v>128721540</v>
       </c>
       <c r="B29" t="n">
-        <v>87004</v>
+        <v>75147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715222</v>
+        <v>715278</v>
       </c>
       <c r="R29" t="n">
-        <v>6367915</v>
+        <v>6368028</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3393,19 +3393,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3415,7 +3414,7 @@
         <v>128722532</v>
       </c>
       <c r="B30" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3509,32 +3508,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128721540</v>
+        <v>128721628</v>
       </c>
       <c r="B31" t="n">
-        <v>75143</v>
+        <v>87008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715278</v>
+        <v>715222</v>
       </c>
       <c r="R31" t="n">
-        <v>6368028</v>
+        <v>6367915</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3588,18 +3587,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
         <v>128722518</v>
       </c>
       <c r="B32" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722564</v>
+        <v>128722566</v>
       </c>
       <c r="B33" t="n">
-        <v>86946</v>
+        <v>91043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3718,21 +3718,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715387</v>
+        <v>715288</v>
       </c>
       <c r="R33" t="n">
-        <v>6367908</v>
+        <v>6367866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3804,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722566</v>
+        <v>128722608</v>
       </c>
       <c r="B34" t="n">
-        <v>91039</v>
+        <v>86926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715288</v>
+        <v>715211</v>
       </c>
       <c r="R34" t="n">
-        <v>6367866</v>
+        <v>6367929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722577</v>
+        <v>128721513</v>
       </c>
       <c r="B35" t="n">
-        <v>86981</v>
+        <v>86764</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715502</v>
+        <v>715408</v>
       </c>
       <c r="R35" t="n">
-        <v>6367602</v>
+        <v>6368189</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3986,22 +3986,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721511</v>
+        <v>128722542</v>
       </c>
       <c r="B36" t="n">
-        <v>91277</v>
+        <v>86764</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715180</v>
+        <v>715218</v>
       </c>
       <c r="R36" t="n">
-        <v>6367626</v>
+        <v>6367844</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,44 +4083,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722608</v>
+        <v>128722556</v>
       </c>
       <c r="B37" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715211</v>
+        <v>715180</v>
       </c>
       <c r="R37" t="n">
-        <v>6367929</v>
+        <v>6368021</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4174,6 +4174,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4192,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721513</v>
+        <v>128721511</v>
       </c>
       <c r="B38" t="n">
-        <v>86760</v>
+        <v>91281</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4203,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4227,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715408</v>
+        <v>715180</v>
       </c>
       <c r="R38" t="n">
-        <v>6368189</v>
+        <v>6367626</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,32 +4290,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722542</v>
+        <v>128722564</v>
       </c>
       <c r="B39" t="n">
-        <v>86760</v>
+        <v>86950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3762</v>
+        <v>3599</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4324,10 +4325,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715218</v>
+        <v>715387</v>
       </c>
       <c r="R39" t="n">
-        <v>6367844</v>
+        <v>6367908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4386,32 +4387,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722556</v>
+        <v>128722577</v>
       </c>
       <c r="B40" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4421,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715180</v>
+        <v>715502</v>
       </c>
       <c r="R40" t="n">
-        <v>6368021</v>
+        <v>6367602</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4446,7 +4447,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4465,7 +4466,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>128722517</v>
       </c>
       <c r="B41" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>128721557</v>
       </c>
       <c r="B42" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128722543</v>
+        <v>128721497</v>
       </c>
       <c r="B43" t="n">
-        <v>86760</v>
+        <v>87008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715253</v>
+        <v>715243</v>
       </c>
       <c r="R43" t="n">
-        <v>6367647</v>
+        <v>6367615</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4761,18 +4761,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4782,7 +4783,7 @@
         <v>128721577</v>
       </c>
       <c r="B44" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,7 +4880,7 @@
         <v>128721653</v>
       </c>
       <c r="B45" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4976,7 +4977,7 @@
         <v>128722606</v>
       </c>
       <c r="B46" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5070,32 +5071,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721497</v>
+        <v>128721517</v>
       </c>
       <c r="B47" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5105,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715243</v>
+        <v>715323</v>
       </c>
       <c r="R47" t="n">
-        <v>6367615</v>
+        <v>6368092</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5171,7 +5172,7 @@
         <v>128721631</v>
       </c>
       <c r="B48" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,32 +5267,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128721517</v>
+        <v>128722543</v>
       </c>
       <c r="B49" t="n">
-        <v>86959</v>
+        <v>86764</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5301,10 +5302,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715323</v>
+        <v>715253</v>
       </c>
       <c r="R49" t="n">
-        <v>6368092</v>
+        <v>6367647</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5345,19 +5346,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5367,7 +5367,7 @@
         <v>128722580</v>
       </c>
       <c r="B50" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128722544</v>
+        <v>128722575</v>
       </c>
       <c r="B51" t="n">
-        <v>86760</v>
+        <v>105699</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3762</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715251</v>
+        <v>715498</v>
       </c>
       <c r="R51" t="n">
-        <v>6367635</v>
+        <v>6367908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721582</v>
+        <v>128721563</v>
       </c>
       <c r="B52" t="n">
-        <v>86922</v>
+        <v>92834</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,34 +5569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715178</v>
+        <v>715232</v>
       </c>
       <c r="R52" t="n">
-        <v>6367640</v>
+        <v>6367928</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5637,6 +5640,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5655,10 +5659,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128721568</v>
+        <v>128722544</v>
       </c>
       <c r="B53" t="n">
-        <v>86784</v>
+        <v>86764</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5666,21 +5670,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5690,10 +5694,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715200</v>
+        <v>715251</v>
       </c>
       <c r="R53" t="n">
-        <v>6367963</v>
+        <v>6367635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,22 +5744,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721563</v>
+        <v>128721582</v>
       </c>
       <c r="B54" t="n">
-        <v>92830</v>
+        <v>86926</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5763,37 +5767,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715232</v>
+        <v>715178</v>
       </c>
       <c r="R54" t="n">
-        <v>6367928</v>
+        <v>6367640</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5834,7 +5835,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128722575</v>
+        <v>128721568</v>
       </c>
       <c r="B55" t="n">
-        <v>105695</v>
+        <v>86788</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5864,21 +5864,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>3712</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715498</v>
+        <v>715200</v>
       </c>
       <c r="R55" t="n">
-        <v>6367908</v>
+        <v>6367963</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5938,44 +5938,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128721547</v>
+        <v>128721496</v>
       </c>
       <c r="B56" t="n">
-        <v>105682</v>
+        <v>86906</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>224098</v>
+        <v>473</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715154</v>
+        <v>715344</v>
       </c>
       <c r="R56" t="n">
-        <v>6367783</v>
+        <v>6368190</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6029,6 +6029,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6047,32 +6048,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128722553</v>
+        <v>128722604</v>
       </c>
       <c r="B57" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6082,10 +6083,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715261</v>
+        <v>715309</v>
       </c>
       <c r="R57" t="n">
-        <v>6368006</v>
+        <v>6367880</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6126,7 +6127,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6145,32 +6145,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128721496</v>
+        <v>128721580</v>
       </c>
       <c r="B58" t="n">
-        <v>86902</v>
+        <v>86926</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>473</v>
+        <v>3674</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715344</v>
+        <v>715147</v>
       </c>
       <c r="R58" t="n">
-        <v>6368190</v>
+        <v>6367801</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6224,7 +6224,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6243,10 +6242,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128722604</v>
+        <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>86922</v>
+        <v>105686</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6254,21 +6253,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>224098</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6278,10 +6277,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715309</v>
+        <v>715154</v>
       </c>
       <c r="R59" t="n">
-        <v>6367880</v>
+        <v>6367783</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6328,44 +6327,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128721580</v>
+        <v>128722553</v>
       </c>
       <c r="B60" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6375,10 +6374,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715147</v>
+        <v>715261</v>
       </c>
       <c r="R60" t="n">
-        <v>6367801</v>
+        <v>6368006</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,50 +6418,51 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128721567</v>
+        <v>128722520</v>
       </c>
       <c r="B61" t="n">
-        <v>96228</v>
+        <v>87008</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715422</v>
+        <v>715450</v>
       </c>
       <c r="R61" t="n">
-        <v>6367626</v>
+        <v>6367880</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,50 +6516,51 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128722520</v>
+        <v>128721507</v>
       </c>
       <c r="B62" t="n">
-        <v>87004</v>
+        <v>57717</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3767</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6569,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715450</v>
+        <v>715452</v>
       </c>
       <c r="R62" t="n">
-        <v>6367880</v>
+        <v>6367607</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6594,7 +6595,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -6613,51 +6614,50 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128721644</v>
+        <v>128722557</v>
       </c>
       <c r="B63" t="n">
-        <v>86981</v>
+        <v>86963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715497</v>
+        <v>715218</v>
       </c>
       <c r="R63" t="n">
-        <v>6367603</v>
+        <v>6367940</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -6711,50 +6711,51 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721507</v>
+        <v>128721567</v>
       </c>
       <c r="B64" t="n">
-        <v>57713</v>
+        <v>96232</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6764,10 +6765,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715452</v>
+        <v>715422</v>
       </c>
       <c r="R64" t="n">
-        <v>6367607</v>
+        <v>6367626</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,32 +6827,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128722557</v>
+        <v>128721644</v>
       </c>
       <c r="B65" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6861,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715218</v>
+        <v>715497</v>
       </c>
       <c r="R65" t="n">
-        <v>6367940</v>
+        <v>6367603</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6886,7 +6887,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -6905,51 +6906,50 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128722601</v>
+        <v>128721629</v>
       </c>
       <c r="B66" t="n">
-        <v>86922</v>
+        <v>57717</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715264</v>
+        <v>715504</v>
       </c>
       <c r="R66" t="n">
-        <v>6367986</v>
+        <v>6367595</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -7009,22 +7009,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721579</v>
+        <v>128721635</v>
       </c>
       <c r="B67" t="n">
-        <v>86922</v>
+        <v>86939</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715191</v>
+        <v>715194</v>
       </c>
       <c r="R67" t="n">
-        <v>6367888</v>
+        <v>6367686</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7106,22 +7106,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721514</v>
+        <v>128722601</v>
       </c>
       <c r="B68" t="n">
-        <v>86760</v>
+        <v>86926</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715141</v>
+        <v>715264</v>
       </c>
       <c r="R68" t="n">
-        <v>6367822</v>
+        <v>6367986</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7203,22 +7203,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721651</v>
+        <v>128721579</v>
       </c>
       <c r="B69" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715215</v>
+        <v>715191</v>
       </c>
       <c r="R69" t="n">
-        <v>6367933</v>
+        <v>6367888</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7300,44 +7300,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721629</v>
+        <v>128721514</v>
       </c>
       <c r="B70" t="n">
-        <v>57713</v>
+        <v>86764</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715504</v>
+        <v>715141</v>
       </c>
       <c r="R70" t="n">
-        <v>6367595</v>
+        <v>6367822</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -7397,22 +7397,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721635</v>
+        <v>128721651</v>
       </c>
       <c r="B71" t="n">
-        <v>86935</v>
+        <v>86926</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715194</v>
+        <v>715215</v>
       </c>
       <c r="R71" t="n">
-        <v>6367686</v>
+        <v>6367933</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128722516</v>
+        <v>128721523</v>
       </c>
       <c r="B72" t="n">
-        <v>86713</v>
+        <v>86963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,37 +7517,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715492</v>
+        <v>715146</v>
       </c>
       <c r="R72" t="n">
-        <v>6367910</v>
+        <v>6367798</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7595,44 +7592,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721522</v>
+        <v>128722596</v>
       </c>
       <c r="B73" t="n">
-        <v>86959</v>
+        <v>86916</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7642,10 +7639,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715221</v>
+        <v>715196</v>
       </c>
       <c r="R73" t="n">
-        <v>6367902</v>
+        <v>6367906</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7693,12 +7690,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7708,7 +7705,7 @@
         <v>128722550</v>
       </c>
       <c r="B74" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7803,32 +7800,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128722596</v>
+        <v>128721522</v>
       </c>
       <c r="B75" t="n">
-        <v>86912</v>
+        <v>86963</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7838,10 +7835,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715196</v>
+        <v>715221</v>
       </c>
       <c r="R75" t="n">
-        <v>6367906</v>
+        <v>6367902</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7889,22 +7886,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128721523</v>
+        <v>128722516</v>
       </c>
       <c r="B76" t="n">
-        <v>86959</v>
+        <v>86717</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7912,34 +7909,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715146</v>
+        <v>715492</v>
       </c>
       <c r="R76" t="n">
-        <v>6367798</v>
+        <v>6367910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7987,12 +7987,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8002,7 +8002,7 @@
         <v>128721642</v>
       </c>
       <c r="B77" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>128722521</v>
       </c>
       <c r="B78" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>128721503</v>
       </c>
       <c r="B79" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>128721521</v>
       </c>
       <c r="B80" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>128722589</v>
       </c>
       <c r="B81" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>128722581</v>
       </c>
       <c r="B82" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8583,32 +8583,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722607</v>
+        <v>128722565</v>
       </c>
       <c r="B83" t="n">
-        <v>86922</v>
+        <v>91043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715545</v>
+        <v>715311</v>
       </c>
       <c r="R83" t="n">
-        <v>6367864</v>
+        <v>6367855</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8680,32 +8680,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128721575</v>
+        <v>128722547</v>
       </c>
       <c r="B84" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715333</v>
+        <v>715525</v>
       </c>
       <c r="R84" t="n">
-        <v>6368090</v>
+        <v>6367901</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8759,50 +8759,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128721581</v>
+        <v>128722560</v>
       </c>
       <c r="B85" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8812,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715150</v>
+        <v>715549</v>
       </c>
       <c r="R85" t="n">
-        <v>6367790</v>
+        <v>6367883</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8856,50 +8857,51 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722565</v>
+        <v>128722549</v>
       </c>
       <c r="B86" t="n">
-        <v>91039</v>
+        <v>86963</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8909,10 +8911,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715311</v>
+        <v>715448</v>
       </c>
       <c r="R86" t="n">
-        <v>6367855</v>
+        <v>6367902</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8953,6 +8955,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -8974,7 +8977,7 @@
         <v>128721502</v>
       </c>
       <c r="B87" t="n">
-        <v>91024</v>
+        <v>91028</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9072,7 +9075,7 @@
         <v>128721552</v>
       </c>
       <c r="B88" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9166,32 +9169,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722549</v>
+        <v>128722607</v>
       </c>
       <c r="B89" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9201,10 +9204,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715448</v>
+        <v>715545</v>
       </c>
       <c r="R89" t="n">
-        <v>6367902</v>
+        <v>6367864</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9245,7 +9248,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9264,32 +9266,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128722560</v>
+        <v>128721575</v>
       </c>
       <c r="B90" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9299,10 +9301,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715549</v>
+        <v>715333</v>
       </c>
       <c r="R90" t="n">
-        <v>6367883</v>
+        <v>6368090</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9343,51 +9345,50 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128722547</v>
+        <v>128721581</v>
       </c>
       <c r="B91" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9397,10 +9398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715525</v>
+        <v>715150</v>
       </c>
       <c r="R91" t="n">
-        <v>6367901</v>
+        <v>6367790</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9441,51 +9442,50 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128722558</v>
+        <v>128722519</v>
       </c>
       <c r="B92" t="n">
-        <v>86959</v>
+        <v>90983</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>720</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715177</v>
+        <v>715292</v>
       </c>
       <c r="R92" t="n">
-        <v>6367636</v>
+        <v>6367865</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9539,7 +9539,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9558,32 +9557,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128721647</v>
+        <v>128722603</v>
       </c>
       <c r="B93" t="n">
-        <v>86713</v>
+        <v>86926</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9593,10 +9592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715216</v>
+        <v>715233</v>
       </c>
       <c r="R93" t="n">
-        <v>6367898</v>
+        <v>6367868</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9631,62 +9630,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722519</v>
+        <v>128722558</v>
       </c>
       <c r="B94" t="n">
-        <v>90979</v>
+        <v>86963</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>720</v>
+        <v>6003295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9696,10 +9689,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715292</v>
+        <v>715177</v>
       </c>
       <c r="R94" t="n">
-        <v>6367865</v>
+        <v>6367636</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9740,6 +9733,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9758,32 +9752,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722603</v>
+        <v>128721647</v>
       </c>
       <c r="B95" t="n">
-        <v>86922</v>
+        <v>86717</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9787,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715233</v>
+        <v>715216</v>
       </c>
       <c r="R95" t="n">
-        <v>6367868</v>
+        <v>6367898</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9831,56 +9825,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128722597</v>
+        <v>128721541</v>
       </c>
       <c r="B96" t="n">
-        <v>86912</v>
+        <v>75147</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003235</v>
+        <v>6426</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715216</v>
+        <v>715250</v>
       </c>
       <c r="R96" t="n">
-        <v>6367914</v>
+        <v>6367931</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9934,29 +9934,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721649</v>
+        <v>128721542</v>
       </c>
       <c r="B97" t="n">
-        <v>86922</v>
+        <v>75147</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9964,21 +9963,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9988,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715314</v>
+        <v>715519</v>
       </c>
       <c r="R97" t="n">
-        <v>6368077</v>
+        <v>6367602</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10013,7 +10012,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10038,22 +10037,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721542</v>
+        <v>128721649</v>
       </c>
       <c r="B98" t="n">
-        <v>75143</v>
+        <v>86926</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10061,21 +10060,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10085,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715519</v>
+        <v>715314</v>
       </c>
       <c r="R98" t="n">
-        <v>6367602</v>
+        <v>6368077</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10110,7 +10109,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -10135,57 +10134,65 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721541</v>
+        <v>128721508</v>
       </c>
       <c r="B99" t="n">
-        <v>75143</v>
+        <v>57717</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715250</v>
+        <v>715206</v>
       </c>
       <c r="R99" t="n">
-        <v>6367931</v>
+        <v>6367909</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,53 +10251,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721508</v>
+        <v>128722597</v>
       </c>
       <c r="B100" t="n">
-        <v>57713</v>
+        <v>86916</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6003235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715206</v>
+        <v>715216</v>
       </c>
       <c r="R100" t="n">
-        <v>6367909</v>
+        <v>6367914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10331,50 +10330,51 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128722598</v>
+        <v>128721519</v>
       </c>
       <c r="B101" t="n">
-        <v>86806</v>
+        <v>86963</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715487</v>
+        <v>715287</v>
       </c>
       <c r="R101" t="n">
-        <v>6367923</v>
+        <v>6368083</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10428,50 +10428,51 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722579</v>
+        <v>128722546</v>
       </c>
       <c r="B102" t="n">
-        <v>86981</v>
+        <v>86963</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10482,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715205</v>
+        <v>715298</v>
       </c>
       <c r="R102" t="n">
-        <v>6367943</v>
+        <v>6367872</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10525,6 +10526,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10543,32 +10545,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128721583</v>
+        <v>128722587</v>
       </c>
       <c r="B103" t="n">
-        <v>86922</v>
+        <v>86986</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10578,10 +10580,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715492</v>
+        <v>715464</v>
       </c>
       <c r="R103" t="n">
-        <v>6367606</v>
+        <v>6367911</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10603,7 +10605,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10628,44 +10630,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722587</v>
+        <v>128722598</v>
       </c>
       <c r="B104" t="n">
-        <v>86982</v>
+        <v>86810</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10677,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715464</v>
+        <v>715487</v>
       </c>
       <c r="R104" t="n">
-        <v>6367911</v>
+        <v>6367923</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10737,32 +10739,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128721519</v>
+        <v>128722579</v>
       </c>
       <c r="B105" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10772,10 +10774,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715287</v>
+        <v>715205</v>
       </c>
       <c r="R105" t="n">
-        <v>6368083</v>
+        <v>6367943</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10816,51 +10818,50 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128722546</v>
+        <v>128721583</v>
       </c>
       <c r="B106" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10870,10 +10871,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715298</v>
+        <v>715492</v>
       </c>
       <c r="R106" t="n">
-        <v>6367872</v>
+        <v>6367606</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10895,7 +10896,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -10914,19 +10915,18 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -10936,7 +10936,7 @@
         <v>128722522</v>
       </c>
       <c r="B107" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>128722585</v>
       </c>
       <c r="B108" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>128722545</v>
       </c>
       <c r="B109" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>128722599</v>
       </c>
       <c r="B110" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11327,32 +11327,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128721572</v>
+        <v>128721520</v>
       </c>
       <c r="B111" t="n">
-        <v>86912</v>
+        <v>86963</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715132</v>
+        <v>715280</v>
       </c>
       <c r="R111" t="n">
-        <v>6367819</v>
+        <v>6368028</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11406,6 +11406,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11424,32 +11425,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128721520</v>
+        <v>128721572</v>
       </c>
       <c r="B112" t="n">
-        <v>86959</v>
+        <v>86916</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11459,10 +11460,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715280</v>
+        <v>715132</v>
       </c>
       <c r="R112" t="n">
-        <v>6368028</v>
+        <v>6367819</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11503,7 +11504,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11522,32 +11522,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128721500</v>
+        <v>128721537</v>
       </c>
       <c r="B113" t="n">
-        <v>87004</v>
+        <v>75147</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715318</v>
+        <v>715344</v>
       </c>
       <c r="R113" t="n">
-        <v>6368090</v>
+        <v>6368190</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11619,32 +11619,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128722523</v>
+        <v>128721500</v>
       </c>
       <c r="B114" t="n">
-        <v>86760</v>
+        <v>87008</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715327</v>
+        <v>715318</v>
       </c>
       <c r="R114" t="n">
-        <v>6367899</v>
+        <v>6368090</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11704,22 +11704,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128721650</v>
+        <v>128722523</v>
       </c>
       <c r="B115" t="n">
-        <v>86922</v>
+        <v>86764</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11727,21 +11727,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11751,10 +11751,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715161</v>
+        <v>715327</v>
       </c>
       <c r="R115" t="n">
-        <v>6368017</v>
+        <v>6367899</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11801,22 +11801,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128722535</v>
+        <v>128721650</v>
       </c>
       <c r="B116" t="n">
-        <v>86784</v>
+        <v>86926</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11824,21 +11824,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11848,10 +11848,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715500</v>
+        <v>715161</v>
       </c>
       <c r="R116" t="n">
-        <v>6367907</v>
+        <v>6368017</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11898,22 +11898,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722541</v>
+        <v>128722535</v>
       </c>
       <c r="B117" t="n">
-        <v>86760</v>
+        <v>86788</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11921,21 +11921,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715501</v>
+        <v>715500</v>
       </c>
       <c r="R117" t="n">
-        <v>6367911</v>
+        <v>6367907</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12007,10 +12007,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722586</v>
+        <v>128722541</v>
       </c>
       <c r="B118" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12042,10 +12042,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715507</v>
+        <v>715501</v>
       </c>
       <c r="R118" t="n">
-        <v>6367904</v>
+        <v>6367911</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12104,10 +12104,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128721537</v>
+        <v>128722586</v>
       </c>
       <c r="B119" t="n">
-        <v>75143</v>
+        <v>86764</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12115,21 +12115,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12139,10 +12139,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715344</v>
+        <v>715507</v>
       </c>
       <c r="R119" t="n">
-        <v>6368190</v>
+        <v>6367904</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12189,12 +12189,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12204,7 +12204,7 @@
         <v>128722562</v>
       </c>
       <c r="B120" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>128722548</v>
       </c>
       <c r="B121" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>128721524</v>
       </c>
       <c r="B122" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12494,10 +12494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128722605</v>
+        <v>128721538</v>
       </c>
       <c r="B123" t="n">
-        <v>86922</v>
+        <v>75147</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715315</v>
+        <v>715352</v>
       </c>
       <c r="R123" t="n">
-        <v>6367838</v>
+        <v>6368147</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12579,22 +12579,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128721538</v>
+        <v>128722605</v>
       </c>
       <c r="B124" t="n">
-        <v>75143</v>
+        <v>86926</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715352</v>
+        <v>715315</v>
       </c>
       <c r="R124" t="n">
-        <v>6368147</v>
+        <v>6367838</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,44 +12676,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721525</v>
+        <v>128721526</v>
       </c>
       <c r="B125" t="n">
-        <v>86959</v>
+        <v>58090</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003295</v>
+        <v>103015</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715141</v>
+        <v>715155</v>
       </c>
       <c r="R125" t="n">
-        <v>6367814</v>
+        <v>6367801</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12767,7 +12767,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12786,10 +12785,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128722559</v>
+        <v>128721525</v>
       </c>
       <c r="B126" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12821,10 +12820,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715256</v>
+        <v>715141</v>
       </c>
       <c r="R126" t="n">
-        <v>6367627</v>
+        <v>6367814</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12872,22 +12871,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128722551</v>
+        <v>128722561</v>
       </c>
       <c r="B127" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12919,10 +12918,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715313</v>
+        <v>715545</v>
       </c>
       <c r="R127" t="n">
-        <v>6368003</v>
+        <v>6367898</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12982,10 +12981,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722561</v>
+        <v>128722551</v>
       </c>
       <c r="B128" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13017,10 +13016,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715545</v>
+        <v>715313</v>
       </c>
       <c r="R128" t="n">
-        <v>6367898</v>
+        <v>6368003</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13080,32 +13079,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128721526</v>
+        <v>128722559</v>
       </c>
       <c r="B129" t="n">
-        <v>58086</v>
+        <v>86963</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103015</v>
+        <v>6003295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13115,10 +13114,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715155</v>
+        <v>715256</v>
       </c>
       <c r="R129" t="n">
-        <v>6367801</v>
+        <v>6367627</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13159,18 +13158,19 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -13180,7 +13180,7 @@
         <v>128722590</v>
       </c>
       <c r="B130" t="n">
-        <v>86982</v>
+        <v>86986</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>128722530</v>
       </c>
       <c r="B131" t="n">
-        <v>86993</v>
+        <v>86997</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128721516</v>
+        <v>128722539</v>
       </c>
       <c r="B2" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715344</v>
+        <v>715181</v>
       </c>
       <c r="R2" t="n">
-        <v>6368182</v>
+        <v>6367653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,51 +754,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128722554</v>
+        <v>128722600</v>
       </c>
       <c r="B3" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715247</v>
+        <v>715327</v>
       </c>
       <c r="R3" t="n">
-        <v>6368027</v>
+        <v>6367976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -969,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128721539</v>
+        <v>128721652</v>
       </c>
       <c r="B5" t="n">
-        <v>75147</v>
+        <v>86926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -980,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1004,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715289</v>
+        <v>715207</v>
       </c>
       <c r="R5" t="n">
-        <v>6368047</v>
+        <v>6367759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,22 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128722539</v>
+        <v>128721501</v>
       </c>
       <c r="B6" t="n">
-        <v>86764</v>
+        <v>88698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1077,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>4379</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1101,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715181</v>
+        <v>715178</v>
       </c>
       <c r="R6" t="n">
-        <v>6367653</v>
+        <v>6367628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,22 +1149,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128722600</v>
+        <v>128721539</v>
       </c>
       <c r="B7" t="n">
-        <v>86926</v>
+        <v>75147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1174,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1198,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715327</v>
+        <v>715289</v>
       </c>
       <c r="R7" t="n">
-        <v>6367976</v>
+        <v>6368047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,44 +1246,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128721652</v>
+        <v>128721516</v>
       </c>
       <c r="B8" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1295,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715207</v>
+        <v>715344</v>
       </c>
       <c r="R8" t="n">
-        <v>6367759</v>
+        <v>6368182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,50 +1337,51 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128721501</v>
+        <v>128722554</v>
       </c>
       <c r="B9" t="n">
-        <v>88698</v>
+        <v>86963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715178</v>
+        <v>715247</v>
       </c>
       <c r="R9" t="n">
-        <v>6367628</v>
+        <v>6368027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,18 +1435,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1555,32 +1555,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722552</v>
+        <v>128722578</v>
       </c>
       <c r="B11" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715271</v>
+        <v>715461</v>
       </c>
       <c r="R11" t="n">
-        <v>6367998</v>
+        <v>6367905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,7 +1634,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1653,32 +1652,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722595</v>
+        <v>128722552</v>
       </c>
       <c r="B12" t="n">
-        <v>86916</v>
+        <v>86963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1687,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715468</v>
+        <v>715271</v>
       </c>
       <c r="R12" t="n">
-        <v>6367935</v>
+        <v>6367998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722578</v>
+        <v>128722595</v>
       </c>
       <c r="B13" t="n">
-        <v>86985</v>
+        <v>86916</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>449</v>
+        <v>6003235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715461</v>
+        <v>715468</v>
       </c>
       <c r="R13" t="n">
-        <v>6367905</v>
+        <v>6367935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,6 +1829,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B14" t="n">
-        <v>86950</v>
+        <v>105686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R14" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B15" t="n">
-        <v>105686</v>
+        <v>86950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R15" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,12 +2030,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128722582</v>
+        <v>128722540</v>
       </c>
       <c r="B20" t="n">
-        <v>92834</v>
+        <v>86764</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,37 +2441,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715492</v>
+        <v>715194</v>
       </c>
       <c r="R20" t="n">
-        <v>6367899</v>
+        <v>6367837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,32 +2528,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128722540</v>
+        <v>128721499</v>
       </c>
       <c r="B21" t="n">
-        <v>86764</v>
+        <v>87008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715194</v>
+        <v>715394</v>
       </c>
       <c r="R21" t="n">
-        <v>6367837</v>
+        <v>6368208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2610,51 +2607,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721499</v>
+        <v>128721578</v>
       </c>
       <c r="B22" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715394</v>
+        <v>715215</v>
       </c>
       <c r="R22" t="n">
-        <v>6368208</v>
+        <v>6367918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128721578</v>
+        <v>128722582</v>
       </c>
       <c r="B23" t="n">
-        <v>86926</v>
+        <v>92834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2737,34 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715215</v>
+        <v>715492</v>
       </c>
       <c r="R23" t="n">
-        <v>6367918</v>
+        <v>6367899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2805,18 +2804,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128722567</v>
+        <v>128721505</v>
       </c>
       <c r="B25" t="n">
-        <v>87008</v>
+        <v>86810</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715339</v>
+        <v>715150</v>
       </c>
       <c r="R25" t="n">
-        <v>6367894</v>
+        <v>6367765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2993,62 +2993,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128722602</v>
+        <v>128722567</v>
       </c>
       <c r="B26" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715200</v>
+        <v>715339</v>
       </c>
       <c r="R26" t="n">
-        <v>6367935</v>
+        <v>6367894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3096,12 +3090,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3120,32 +3120,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128721505</v>
+        <v>128722602</v>
       </c>
       <c r="B27" t="n">
-        <v>86810</v>
+        <v>86926</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715150</v>
+        <v>715200</v>
       </c>
       <c r="R27" t="n">
-        <v>6367765</v>
+        <v>6367935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3205,12 +3205,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128721540</v>
+        <v>128722532</v>
       </c>
       <c r="B29" t="n">
-        <v>75147</v>
+        <v>92443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715278</v>
+        <v>715460</v>
       </c>
       <c r="R29" t="n">
-        <v>6368028</v>
+        <v>6367601</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3399,22 +3399,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128722532</v>
+        <v>128721540</v>
       </c>
       <c r="B30" t="n">
-        <v>92443</v>
+        <v>75147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3422,21 +3422,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715460</v>
+        <v>715278</v>
       </c>
       <c r="R30" t="n">
-        <v>6367601</v>
+        <v>6368028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3496,12 +3496,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3707,32 +3707,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722566</v>
+        <v>128722608</v>
       </c>
       <c r="B33" t="n">
-        <v>91043</v>
+        <v>86926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715288</v>
+        <v>715211</v>
       </c>
       <c r="R33" t="n">
-        <v>6367866</v>
+        <v>6367929</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3804,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722608</v>
+        <v>128722564</v>
       </c>
       <c r="B34" t="n">
-        <v>86926</v>
+        <v>86950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>3599</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715211</v>
+        <v>715387</v>
       </c>
       <c r="R34" t="n">
-        <v>6367929</v>
+        <v>6367908</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128721513</v>
+        <v>128721511</v>
       </c>
       <c r="B35" t="n">
-        <v>86764</v>
+        <v>91281</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715408</v>
+        <v>715180</v>
       </c>
       <c r="R35" t="n">
-        <v>6368189</v>
+        <v>6367626</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3998,7 +3998,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128722542</v>
+        <v>128721513</v>
       </c>
       <c r="B36" t="n">
         <v>86764</v>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715218</v>
+        <v>715408</v>
       </c>
       <c r="R36" t="n">
-        <v>6367844</v>
+        <v>6368189</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,44 +4083,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722556</v>
+        <v>128722542</v>
       </c>
       <c r="B37" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715180</v>
+        <v>715218</v>
       </c>
       <c r="R37" t="n">
-        <v>6368021</v>
+        <v>6367844</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4174,7 +4174,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4193,45 +4192,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721511</v>
+        <v>128722517</v>
       </c>
       <c r="B38" t="n">
-        <v>91281</v>
+        <v>86717</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3215</v>
+        <v>249278</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715180</v>
+        <v>715318</v>
       </c>
       <c r="R38" t="n">
-        <v>6367626</v>
+        <v>6367974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4272,50 +4274,51 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722564</v>
+        <v>128722556</v>
       </c>
       <c r="B39" t="n">
-        <v>86950</v>
+        <v>86963</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3599</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4328,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715387</v>
+        <v>715180</v>
       </c>
       <c r="R39" t="n">
-        <v>6367908</v>
+        <v>6368021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4369,6 +4372,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4484,48 +4488,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722517</v>
+        <v>128722566</v>
       </c>
       <c r="B41" t="n">
-        <v>86717</v>
+        <v>91043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249278</v>
+        <v>5747</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715318</v>
+        <v>715288</v>
       </c>
       <c r="R41" t="n">
-        <v>6367974</v>
+        <v>6367866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721557</v>
+        <v>128721631</v>
       </c>
       <c r="B42" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715213</v>
+        <v>715172</v>
       </c>
       <c r="R42" t="n">
-        <v>6367921</v>
+        <v>6367927</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4664,50 +4664,51 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721497</v>
+        <v>128721517</v>
       </c>
       <c r="B43" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4717,10 +4718,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715243</v>
+        <v>715323</v>
       </c>
       <c r="R43" t="n">
-        <v>6367615</v>
+        <v>6368092</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4780,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721577</v>
+        <v>128721557</v>
       </c>
       <c r="B44" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4815,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715221</v>
+        <v>715213</v>
       </c>
       <c r="R44" t="n">
-        <v>6367967</v>
+        <v>6367921</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4877,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721653</v>
+        <v>128721497</v>
       </c>
       <c r="B45" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4912,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715476</v>
+        <v>715243</v>
       </c>
       <c r="R45" t="n">
-        <v>6367609</v>
+        <v>6367615</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4937,7 +4938,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4956,28 +4957,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128722606</v>
+        <v>128722543</v>
       </c>
       <c r="B46" t="n">
-        <v>86926</v>
+        <v>86764</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4985,21 +4987,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5009,10 +5011,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715323</v>
+        <v>715253</v>
       </c>
       <c r="R46" t="n">
-        <v>6367903</v>
+        <v>6367647</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5071,32 +5073,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721517</v>
+        <v>128721577</v>
       </c>
       <c r="B47" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5106,10 +5108,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715323</v>
+        <v>715221</v>
       </c>
       <c r="R47" t="n">
-        <v>6368092</v>
+        <v>6367967</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5150,7 +5152,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5169,32 +5170,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128721631</v>
+        <v>128721653</v>
       </c>
       <c r="B48" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5204,10 +5205,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715172</v>
+        <v>715476</v>
       </c>
       <c r="R48" t="n">
-        <v>6367927</v>
+        <v>6367609</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5229,7 +5230,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5248,7 +5249,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128722543</v>
+        <v>128722606</v>
       </c>
       <c r="B49" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5278,21 +5278,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715253</v>
+        <v>715323</v>
       </c>
       <c r="R49" t="n">
-        <v>6367647</v>
+        <v>6367903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128722575</v>
+        <v>128721563</v>
       </c>
       <c r="B51" t="n">
-        <v>105699</v>
+        <v>92834</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,34 +5472,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715498</v>
+        <v>715232</v>
       </c>
       <c r="R51" t="n">
-        <v>6367908</v>
+        <v>6367928</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5540,28 +5543,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721563</v>
+        <v>128722544</v>
       </c>
       <c r="B52" t="n">
-        <v>92834</v>
+        <v>86764</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,37 +5573,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715232</v>
+        <v>715251</v>
       </c>
       <c r="R52" t="n">
-        <v>6367928</v>
+        <v>6367635</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5640,29 +5641,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128722544</v>
+        <v>128721582</v>
       </c>
       <c r="B53" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715251</v>
+        <v>715178</v>
       </c>
       <c r="R53" t="n">
-        <v>6367635</v>
+        <v>6367640</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,22 +5744,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721582</v>
+        <v>128721568</v>
       </c>
       <c r="B54" t="n">
-        <v>86926</v>
+        <v>86788</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715178</v>
+        <v>715200</v>
       </c>
       <c r="R54" t="n">
-        <v>6367640</v>
+        <v>6367963</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128721568</v>
+        <v>128722575</v>
       </c>
       <c r="B55" t="n">
-        <v>86788</v>
+        <v>105699</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5864,21 +5864,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3712</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715200</v>
+        <v>715498</v>
       </c>
       <c r="R55" t="n">
-        <v>6367963</v>
+        <v>6367908</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5938,12 +5938,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128721547</v>
+        <v>128722553</v>
       </c>
       <c r="B59" t="n">
-        <v>105686</v>
+        <v>86963</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715154</v>
+        <v>715261</v>
       </c>
       <c r="R59" t="n">
-        <v>6367783</v>
+        <v>6368006</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6321,50 +6321,51 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128722553</v>
+        <v>128721547</v>
       </c>
       <c r="B60" t="n">
-        <v>86963</v>
+        <v>105686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6374,10 +6375,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715261</v>
+        <v>715154</v>
       </c>
       <c r="R60" t="n">
-        <v>6368006</v>
+        <v>6367783</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,29 +6419,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128722520</v>
+        <v>128721644</v>
       </c>
       <c r="B61" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6448,21 +6448,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715450</v>
+        <v>715497</v>
       </c>
       <c r="R61" t="n">
-        <v>6367880</v>
+        <v>6367603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,51 +6516,50 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128721507</v>
+        <v>128721567</v>
       </c>
       <c r="B62" t="n">
-        <v>57717</v>
+        <v>96232</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715452</v>
+        <v>715422</v>
       </c>
       <c r="R62" t="n">
-        <v>6367607</v>
+        <v>6367626</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6632,32 +6631,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128722557</v>
+        <v>128722520</v>
       </c>
       <c r="B63" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6666,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715218</v>
+        <v>715450</v>
       </c>
       <c r="R63" t="n">
-        <v>6367940</v>
+        <v>6367880</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6730,32 +6729,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721567</v>
+        <v>128721507</v>
       </c>
       <c r="B64" t="n">
-        <v>96232</v>
+        <v>57717</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6765,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715422</v>
+        <v>715452</v>
       </c>
       <c r="R64" t="n">
-        <v>6367626</v>
+        <v>6367607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6827,32 +6826,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128721644</v>
+        <v>128722557</v>
       </c>
       <c r="B65" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6862,10 +6861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715497</v>
+        <v>715218</v>
       </c>
       <c r="R65" t="n">
-        <v>6367603</v>
+        <v>6367940</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6887,7 +6886,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -6906,50 +6905,51 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721629</v>
+        <v>128722601</v>
       </c>
       <c r="B66" t="n">
-        <v>57717</v>
+        <v>86926</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715504</v>
+        <v>715264</v>
       </c>
       <c r="R66" t="n">
-        <v>6367595</v>
+        <v>6367986</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -7009,22 +7009,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721635</v>
+        <v>128721514</v>
       </c>
       <c r="B67" t="n">
-        <v>86939</v>
+        <v>86764</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1988</v>
+        <v>3762</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715194</v>
+        <v>715141</v>
       </c>
       <c r="R67" t="n">
-        <v>6367686</v>
+        <v>6367822</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7106,19 +7106,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128722601</v>
+        <v>128721651</v>
       </c>
       <c r="B68" t="n">
         <v>86926</v>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715264</v>
+        <v>715215</v>
       </c>
       <c r="R68" t="n">
-        <v>6367986</v>
+        <v>6367933</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7203,44 +7203,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721579</v>
+        <v>128721629</v>
       </c>
       <c r="B69" t="n">
-        <v>86926</v>
+        <v>57717</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715191</v>
+        <v>715504</v>
       </c>
       <c r="R69" t="n">
-        <v>6367888</v>
+        <v>6367595</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -7300,22 +7300,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721514</v>
+        <v>128721635</v>
       </c>
       <c r="B70" t="n">
-        <v>86764</v>
+        <v>86939</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,21 +7323,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715141</v>
+        <v>715194</v>
       </c>
       <c r="R70" t="n">
-        <v>6367822</v>
+        <v>6367686</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7397,19 +7397,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721651</v>
+        <v>128721579</v>
       </c>
       <c r="B71" t="n">
         <v>86926</v>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715215</v>
+        <v>715191</v>
       </c>
       <c r="R71" t="n">
-        <v>6367933</v>
+        <v>6367888</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7494,22 +7494,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128721523</v>
+        <v>128722516</v>
       </c>
       <c r="B72" t="n">
-        <v>86963</v>
+        <v>86717</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715146</v>
+        <v>715492</v>
       </c>
       <c r="R72" t="n">
-        <v>6367798</v>
+        <v>6367910</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7592,44 +7595,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128722596</v>
+        <v>128721522</v>
       </c>
       <c r="B73" t="n">
-        <v>86916</v>
+        <v>86963</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7639,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715196</v>
+        <v>715221</v>
       </c>
       <c r="R73" t="n">
-        <v>6367906</v>
+        <v>6367902</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,12 +7693,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7800,32 +7803,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128721522</v>
+        <v>128722596</v>
       </c>
       <c r="B75" t="n">
-        <v>86963</v>
+        <v>86916</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7835,10 +7838,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715221</v>
+        <v>715196</v>
       </c>
       <c r="R75" t="n">
-        <v>6367902</v>
+        <v>6367906</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7886,22 +7889,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128722516</v>
+        <v>128721523</v>
       </c>
       <c r="B76" t="n">
-        <v>86717</v>
+        <v>86963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,37 +7912,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715492</v>
+        <v>715146</v>
       </c>
       <c r="R76" t="n">
-        <v>6367910</v>
+        <v>6367798</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7987,12 +7987,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722589</v>
+        <v>128721552</v>
       </c>
       <c r="B81" t="n">
-        <v>86810</v>
+        <v>105699</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>424</v>
+        <v>221144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715223</v>
+        <v>715197</v>
       </c>
       <c r="R81" t="n">
-        <v>6367944</v>
+        <v>6367683</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8474,22 +8474,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128722581</v>
+        <v>128722589</v>
       </c>
       <c r="B82" t="n">
-        <v>86985</v>
+        <v>86810</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8497,21 +8497,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715210</v>
+        <v>715223</v>
       </c>
       <c r="R82" t="n">
-        <v>6367925</v>
+        <v>6367944</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722565</v>
+        <v>128722581</v>
       </c>
       <c r="B83" t="n">
-        <v>91043</v>
+        <v>86985</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8594,21 +8594,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5747</v>
+        <v>449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715311</v>
+        <v>715210</v>
       </c>
       <c r="R83" t="n">
-        <v>6367855</v>
+        <v>6367925</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8680,32 +8680,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722547</v>
+        <v>128722607</v>
       </c>
       <c r="B84" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715525</v>
+        <v>715545</v>
       </c>
       <c r="R84" t="n">
-        <v>6367901</v>
+        <v>6367864</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8759,7 +8759,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8778,32 +8777,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128722560</v>
+        <v>128721575</v>
       </c>
       <c r="B85" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8813,10 +8812,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715549</v>
+        <v>715333</v>
       </c>
       <c r="R85" t="n">
-        <v>6367883</v>
+        <v>6368090</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8857,51 +8856,50 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128722549</v>
+        <v>128721581</v>
       </c>
       <c r="B86" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8911,10 +8909,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715448</v>
+        <v>715150</v>
       </c>
       <c r="R86" t="n">
-        <v>6367902</v>
+        <v>6367790</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8955,29 +8953,28 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128721502</v>
+        <v>128722565</v>
       </c>
       <c r="B87" t="n">
-        <v>91028</v>
+        <v>91043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8985,21 +8982,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>256335</v>
+        <v>5747</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9009,10 +9006,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715210</v>
+        <v>715311</v>
       </c>
       <c r="R87" t="n">
-        <v>6367925</v>
+        <v>6367855</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9053,51 +9050,50 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128721552</v>
+        <v>128722549</v>
       </c>
       <c r="B88" t="n">
-        <v>105699</v>
+        <v>86963</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>6003295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9107,10 +9103,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715197</v>
+        <v>715448</v>
       </c>
       <c r="R88" t="n">
-        <v>6367683</v>
+        <v>6367902</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9151,50 +9147,51 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128722607</v>
+        <v>128721502</v>
       </c>
       <c r="B89" t="n">
-        <v>86926</v>
+        <v>91028</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3674</v>
+        <v>256335</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9204,10 +9201,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715545</v>
+        <v>715210</v>
       </c>
       <c r="R89" t="n">
-        <v>6367864</v>
+        <v>6367925</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9248,50 +9245,51 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128721575</v>
+        <v>128722560</v>
       </c>
       <c r="B90" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9301,10 +9299,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715333</v>
+        <v>715549</v>
       </c>
       <c r="R90" t="n">
-        <v>6368090</v>
+        <v>6367883</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9345,50 +9343,51 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128721581</v>
+        <v>128722547</v>
       </c>
       <c r="B91" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9397,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715150</v>
+        <v>715525</v>
       </c>
       <c r="R91" t="n">
-        <v>6367790</v>
+        <v>6367901</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9442,50 +9441,51 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128722519</v>
+        <v>128721647</v>
       </c>
       <c r="B92" t="n">
-        <v>90983</v>
+        <v>86717</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>720</v>
+        <v>249278</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715292</v>
+        <v>715216</v>
       </c>
       <c r="R92" t="n">
-        <v>6367865</v>
+        <v>6367898</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,56 +9533,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722603</v>
+        <v>128722519</v>
       </c>
       <c r="B93" t="n">
-        <v>86926</v>
+        <v>90983</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3674</v>
+        <v>720</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9592,10 +9598,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715233</v>
+        <v>715292</v>
       </c>
       <c r="R93" t="n">
-        <v>6367868</v>
+        <v>6367865</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9654,32 +9660,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722558</v>
+        <v>128722603</v>
       </c>
       <c r="B94" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9689,10 +9695,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715177</v>
+        <v>715233</v>
       </c>
       <c r="R94" t="n">
-        <v>6367636</v>
+        <v>6367868</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9733,7 +9739,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9752,10 +9757,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128721647</v>
+        <v>128722558</v>
       </c>
       <c r="B95" t="n">
-        <v>86717</v>
+        <v>86963</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9763,21 +9768,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9787,10 +9792,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715216</v>
+        <v>715177</v>
       </c>
       <c r="R95" t="n">
-        <v>6367898</v>
+        <v>6367636</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9825,11 +9830,6 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -9843,44 +9843,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721541</v>
+        <v>128722597</v>
       </c>
       <c r="B96" t="n">
-        <v>75147</v>
+        <v>86916</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6426</v>
+        <v>6003235</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715250</v>
+        <v>715216</v>
       </c>
       <c r="R96" t="n">
-        <v>6367931</v>
+        <v>6367914</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9934,28 +9934,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721542</v>
+        <v>128721649</v>
       </c>
       <c r="B97" t="n">
-        <v>75147</v>
+        <v>86926</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9963,21 +9964,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9988,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715519</v>
+        <v>715314</v>
       </c>
       <c r="R97" t="n">
-        <v>6367602</v>
+        <v>6368077</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10012,7 +10013,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10037,22 +10038,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721649</v>
+        <v>128721541</v>
       </c>
       <c r="B98" t="n">
-        <v>86926</v>
+        <v>75147</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10060,21 +10061,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715314</v>
+        <v>715250</v>
       </c>
       <c r="R98" t="n">
-        <v>6368077</v>
+        <v>6367931</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10134,65 +10135,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721508</v>
+        <v>128721542</v>
       </c>
       <c r="B99" t="n">
-        <v>57717</v>
+        <v>75147</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715206</v>
+        <v>715519</v>
       </c>
       <c r="R99" t="n">
-        <v>6367909</v>
+        <v>6367602</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10214,7 +10207,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -10251,45 +10244,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128722597</v>
+        <v>128721508</v>
       </c>
       <c r="B100" t="n">
-        <v>86916</v>
+        <v>57717</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003235</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715216</v>
+        <v>715206</v>
       </c>
       <c r="R100" t="n">
-        <v>6367914</v>
+        <v>6367909</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10330,51 +10331,50 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128721519</v>
+        <v>128722598</v>
       </c>
       <c r="B101" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715287</v>
+        <v>715487</v>
       </c>
       <c r="R101" t="n">
-        <v>6368083</v>
+        <v>6367923</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10428,51 +10428,50 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722546</v>
+        <v>128722579</v>
       </c>
       <c r="B102" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10482,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715298</v>
+        <v>715205</v>
       </c>
       <c r="R102" t="n">
-        <v>6367872</v>
+        <v>6367943</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10526,7 +10525,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10642,32 +10640,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722598</v>
+        <v>128721519</v>
       </c>
       <c r="B104" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10677,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715487</v>
+        <v>715287</v>
       </c>
       <c r="R104" t="n">
-        <v>6367923</v>
+        <v>6368083</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10721,50 +10719,51 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722579</v>
+        <v>128722546</v>
       </c>
       <c r="B105" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10774,10 +10773,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715205</v>
+        <v>715298</v>
       </c>
       <c r="R105" t="n">
-        <v>6367943</v>
+        <v>6367872</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10818,6 +10817,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10933,32 +10933,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128722522</v>
+        <v>128722599</v>
       </c>
       <c r="B107" t="n">
-        <v>86764</v>
+        <v>86985</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715314</v>
+        <v>715214</v>
       </c>
       <c r="R107" t="n">
-        <v>6367886</v>
+        <v>6367950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11006,12 +11006,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>i myrstack kollekt</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11030,7 +11036,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128722585</v>
+        <v>128722522</v>
       </c>
       <c r="B108" t="n">
         <v>86764</v>
@@ -11065,10 +11071,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715309</v>
+        <v>715314</v>
       </c>
       <c r="R108" t="n">
-        <v>6367883</v>
+        <v>6367886</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11127,7 +11133,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128722545</v>
+        <v>128722585</v>
       </c>
       <c r="B109" t="n">
         <v>86764</v>
@@ -11162,10 +11168,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715261</v>
+        <v>715309</v>
       </c>
       <c r="R109" t="n">
-        <v>6367632</v>
+        <v>6367883</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,32 +11230,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128722599</v>
+        <v>128722545</v>
       </c>
       <c r="B110" t="n">
-        <v>86985</v>
+        <v>86764</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11259,10 +11265,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715214</v>
+        <v>715261</v>
       </c>
       <c r="R110" t="n">
-        <v>6367950</v>
+        <v>6367632</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11297,18 +11303,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>i myrstack kollekt</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11327,32 +11327,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128721520</v>
+        <v>128721572</v>
       </c>
       <c r="B111" t="n">
-        <v>86963</v>
+        <v>86916</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715280</v>
+        <v>715132</v>
       </c>
       <c r="R111" t="n">
-        <v>6368028</v>
+        <v>6367819</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11406,7 +11406,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11425,32 +11424,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128721572</v>
+        <v>128721520</v>
       </c>
       <c r="B112" t="n">
-        <v>86916</v>
+        <v>86963</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003235</v>
+        <v>6003295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11460,10 +11459,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715132</v>
+        <v>715280</v>
       </c>
       <c r="R112" t="n">
-        <v>6367819</v>
+        <v>6368028</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11504,6 +11503,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11522,10 +11522,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128721537</v>
+        <v>128722562</v>
       </c>
       <c r="B113" t="n">
-        <v>75147</v>
+        <v>98670</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11533,21 +11533,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6426</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715344</v>
+        <v>715452</v>
       </c>
       <c r="R113" t="n">
-        <v>6368190</v>
+        <v>6367610</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -11607,12 +11607,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722562</v>
+        <v>128721537</v>
       </c>
       <c r="B120" t="n">
-        <v>98670</v>
+        <v>75147</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219874</v>
+        <v>6426</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715452</v>
+        <v>715344</v>
       </c>
       <c r="R120" t="n">
-        <v>6367610</v>
+        <v>6368190</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12286,12 +12286,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12494,10 +12494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128721538</v>
+        <v>128721526</v>
       </c>
       <c r="B123" t="n">
-        <v>75147</v>
+        <v>58090</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715352</v>
+        <v>715155</v>
       </c>
       <c r="R123" t="n">
-        <v>6368147</v>
+        <v>6367801</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12688,10 +12688,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721526</v>
+        <v>128721538</v>
       </c>
       <c r="B125" t="n">
-        <v>58090</v>
+        <v>75147</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12699,21 +12699,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715155</v>
+        <v>715352</v>
       </c>
       <c r="R125" t="n">
-        <v>6367801</v>
+        <v>6368147</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12785,32 +12785,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128721525</v>
+        <v>128722590</v>
       </c>
       <c r="B126" t="n">
-        <v>86963</v>
+        <v>86986</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12820,10 +12820,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715141</v>
+        <v>715473</v>
       </c>
       <c r="R126" t="n">
-        <v>6367814</v>
+        <v>6367917</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12864,26 +12864,25 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128722561</v>
+        <v>128721525</v>
       </c>
       <c r="B127" t="n">
         <v>86963</v>
@@ -12918,10 +12917,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715545</v>
+        <v>715141</v>
       </c>
       <c r="R127" t="n">
-        <v>6367898</v>
+        <v>6367814</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12969,19 +12968,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722551</v>
+        <v>128722559</v>
       </c>
       <c r="B128" t="n">
         <v>86963</v>
@@ -13016,10 +13015,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715313</v>
+        <v>715256</v>
       </c>
       <c r="R128" t="n">
-        <v>6368003</v>
+        <v>6367627</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13079,7 +13078,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128722559</v>
+        <v>128722551</v>
       </c>
       <c r="B129" t="n">
         <v>86963</v>
@@ -13114,10 +13113,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715256</v>
+        <v>715313</v>
       </c>
       <c r="R129" t="n">
-        <v>6367627</v>
+        <v>6368003</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13177,32 +13176,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722590</v>
+        <v>128722561</v>
       </c>
       <c r="B130" t="n">
-        <v>86986</v>
+        <v>86963</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13212,10 +13211,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715473</v>
+        <v>715545</v>
       </c>
       <c r="R130" t="n">
-        <v>6367917</v>
+        <v>6367898</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13256,6 +13255,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128722539</v>
+        <v>128722536</v>
       </c>
       <c r="B2" t="n">
-        <v>86764</v>
+        <v>91281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715181</v>
+        <v>715340</v>
       </c>
       <c r="R2" t="n">
-        <v>6367653</v>
+        <v>6367945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128722600</v>
+        <v>128721539</v>
       </c>
       <c r="B3" t="n">
-        <v>86926</v>
+        <v>75147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715327</v>
+        <v>715289</v>
       </c>
       <c r="R3" t="n">
-        <v>6367976</v>
+        <v>6368047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722536</v>
+        <v>128721501</v>
       </c>
       <c r="B4" t="n">
-        <v>91281</v>
+        <v>88698</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>4379</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715340</v>
+        <v>715178</v>
       </c>
       <c r="R4" t="n">
-        <v>6367945</v>
+        <v>6367628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,29 +949,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128721652</v>
+        <v>128722539</v>
       </c>
       <c r="B5" t="n">
-        <v>86926</v>
+        <v>86764</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715207</v>
+        <v>715181</v>
       </c>
       <c r="R5" t="n">
-        <v>6367759</v>
+        <v>6367653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,22 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128721501</v>
+        <v>128722600</v>
       </c>
       <c r="B6" t="n">
-        <v>88698</v>
+        <v>86926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4379</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715178</v>
+        <v>715327</v>
       </c>
       <c r="R6" t="n">
-        <v>6367628</v>
+        <v>6367976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,22 +1149,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721539</v>
+        <v>128721652</v>
       </c>
       <c r="B7" t="n">
-        <v>75147</v>
+        <v>86926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715289</v>
+        <v>715207</v>
       </c>
       <c r="R7" t="n">
-        <v>6368047</v>
+        <v>6367759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,12 +1246,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B14" t="n">
-        <v>105686</v>
+        <v>86950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R14" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B15" t="n">
-        <v>86950</v>
+        <v>105686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R15" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,57 +2030,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128721560</v>
+        <v>128722582</v>
       </c>
       <c r="B16" t="n">
-        <v>86985</v>
+        <v>92834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715503</v>
+        <v>715492</v>
       </c>
       <c r="R16" t="n">
-        <v>6367589</v>
+        <v>6367899</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2102,7 +2105,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2121,50 +2124,51 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128721559</v>
+        <v>128722534</v>
       </c>
       <c r="B17" t="n">
-        <v>86985</v>
+        <v>98614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>449</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715505</v>
+        <v>715228</v>
       </c>
       <c r="R17" t="n">
-        <v>6367598</v>
+        <v>6367909</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2199,7 +2203,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2224,19 +2228,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721643</v>
+        <v>128721560</v>
       </c>
       <c r="B18" t="n">
         <v>86985</v>
@@ -2271,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715270</v>
+        <v>715503</v>
       </c>
       <c r="R18" t="n">
-        <v>6367607</v>
+        <v>6367589</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2296,7 +2300,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2321,19 +2325,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721558</v>
+        <v>128721559</v>
       </c>
       <c r="B19" t="n">
         <v>86985</v>
@@ -2368,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715424</v>
+        <v>715505</v>
       </c>
       <c r="R19" t="n">
-        <v>6367651</v>
+        <v>6367598</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,32 +2434,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128722540</v>
+        <v>128721643</v>
       </c>
       <c r="B20" t="n">
-        <v>86764</v>
+        <v>86985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715194</v>
+        <v>715270</v>
       </c>
       <c r="R20" t="n">
-        <v>6367837</v>
+        <v>6367607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2509,29 +2513,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721499</v>
+        <v>128721558</v>
       </c>
       <c r="B21" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715394</v>
+        <v>715424</v>
       </c>
       <c r="R21" t="n">
-        <v>6368208</v>
+        <v>6367651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2588,7 +2591,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2625,10 +2628,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128721578</v>
+        <v>128722540</v>
       </c>
       <c r="B22" t="n">
-        <v>86926</v>
+        <v>86764</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2639,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715215</v>
+        <v>715194</v>
       </c>
       <c r="R22" t="n">
-        <v>6367918</v>
+        <v>6367837</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2704,66 +2707,64 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128722582</v>
+        <v>128721499</v>
       </c>
       <c r="B23" t="n">
-        <v>92834</v>
+        <v>87008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>3767</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715492</v>
+        <v>715394</v>
       </c>
       <c r="R23" t="n">
-        <v>6367899</v>
+        <v>6368208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2804,29 +2805,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128722534</v>
+        <v>128721578</v>
       </c>
       <c r="B24" t="n">
-        <v>98614</v>
+        <v>86926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>715228</v>
+        <v>715215</v>
       </c>
       <c r="R24" t="n">
-        <v>6367909</v>
+        <v>6367918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2908,44 +2908,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128721505</v>
+        <v>128721543</v>
       </c>
       <c r="B25" t="n">
-        <v>86810</v>
+        <v>75147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715150</v>
+        <v>715500</v>
       </c>
       <c r="R25" t="n">
-        <v>6367765</v>
+        <v>6367588</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128722567</v>
+        <v>128721505</v>
       </c>
       <c r="B26" t="n">
-        <v>87008</v>
+        <v>86810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,21 +3028,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715339</v>
+        <v>715150</v>
       </c>
       <c r="R26" t="n">
-        <v>6367894</v>
+        <v>6367765</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3090,62 +3090,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128722602</v>
+        <v>128722567</v>
       </c>
       <c r="B27" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715200</v>
+        <v>715339</v>
       </c>
       <c r="R27" t="n">
-        <v>6367935</v>
+        <v>6367894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3193,12 +3187,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128721543</v>
+        <v>128722602</v>
       </c>
       <c r="B28" t="n">
-        <v>75147</v>
+        <v>86926</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715500</v>
+        <v>715200</v>
       </c>
       <c r="R28" t="n">
-        <v>6367588</v>
+        <v>6367935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3302,12 +3302,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3707,45 +3707,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722608</v>
+        <v>128722517</v>
       </c>
       <c r="B33" t="n">
-        <v>86926</v>
+        <v>86717</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715211</v>
+        <v>715318</v>
       </c>
       <c r="R33" t="n">
-        <v>6367929</v>
+        <v>6367974</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3786,6 +3789,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3804,32 +3808,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128722564</v>
+        <v>128721511</v>
       </c>
       <c r="B34" t="n">
-        <v>86950</v>
+        <v>91281</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3599</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3843,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715387</v>
+        <v>715180</v>
       </c>
       <c r="R34" t="n">
-        <v>6367908</v>
+        <v>6367626</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3889,44 +3893,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128721511</v>
+        <v>128722566</v>
       </c>
       <c r="B35" t="n">
-        <v>91281</v>
+        <v>91043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>5747</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3940,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715180</v>
+        <v>715288</v>
       </c>
       <c r="R35" t="n">
-        <v>6367626</v>
+        <v>6367866</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3986,44 +3990,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721513</v>
+        <v>128722577</v>
       </c>
       <c r="B36" t="n">
-        <v>86764</v>
+        <v>86985</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4037,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715408</v>
+        <v>715502</v>
       </c>
       <c r="R36" t="n">
-        <v>6368189</v>
+        <v>6367602</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,7 +4062,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4083,22 +4087,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128722542</v>
+        <v>128722608</v>
       </c>
       <c r="B37" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4106,21 +4110,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4130,10 +4134,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715218</v>
+        <v>715211</v>
       </c>
       <c r="R37" t="n">
-        <v>6367844</v>
+        <v>6367929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,48 +4196,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128722517</v>
+        <v>128722564</v>
       </c>
       <c r="B38" t="n">
-        <v>86717</v>
+        <v>86950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>249278</v>
+        <v>3599</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715318</v>
+        <v>715387</v>
       </c>
       <c r="R38" t="n">
-        <v>6367974</v>
+        <v>6367908</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4274,7 +4275,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128722556</v>
+        <v>128721513</v>
       </c>
       <c r="B39" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715180</v>
+        <v>715408</v>
       </c>
       <c r="R39" t="n">
-        <v>6368021</v>
+        <v>6368189</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4372,51 +4372,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128722577</v>
+        <v>128722542</v>
       </c>
       <c r="B40" t="n">
-        <v>86985</v>
+        <v>86764</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4426,10 +4425,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715502</v>
+        <v>715218</v>
       </c>
       <c r="R40" t="n">
-        <v>6367602</v>
+        <v>6367844</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4451,7 +4450,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4488,32 +4487,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722566</v>
+        <v>128722556</v>
       </c>
       <c r="B41" t="n">
-        <v>91043</v>
+        <v>86963</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4523,10 +4522,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715288</v>
+        <v>715180</v>
       </c>
       <c r="R41" t="n">
-        <v>6367866</v>
+        <v>6368021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721631</v>
+        <v>128721557</v>
       </c>
       <c r="B42" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715172</v>
+        <v>715213</v>
       </c>
       <c r="R42" t="n">
-        <v>6367927</v>
+        <v>6367921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4664,51 +4664,50 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721517</v>
+        <v>128721497</v>
       </c>
       <c r="B43" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4718,10 +4717,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715323</v>
+        <v>715243</v>
       </c>
       <c r="R43" t="n">
-        <v>6368092</v>
+        <v>6367615</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4781,32 +4780,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721557</v>
+        <v>128722543</v>
       </c>
       <c r="B44" t="n">
-        <v>86985</v>
+        <v>86764</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715213</v>
+        <v>715253</v>
       </c>
       <c r="R44" t="n">
-        <v>6367921</v>
+        <v>6367647</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,44 +4865,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721497</v>
+        <v>128721577</v>
       </c>
       <c r="B45" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4912,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715243</v>
+        <v>715221</v>
       </c>
       <c r="R45" t="n">
-        <v>6367615</v>
+        <v>6367967</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4957,7 +4956,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4976,10 +4974,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128722543</v>
+        <v>128721653</v>
       </c>
       <c r="B46" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4987,21 +4985,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5011,10 +5009,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715253</v>
+        <v>715476</v>
       </c>
       <c r="R46" t="n">
-        <v>6367647</v>
+        <v>6367609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5036,7 +5034,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5061,19 +5059,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721577</v>
+        <v>128722606</v>
       </c>
       <c r="B47" t="n">
         <v>86926</v>
@@ -5108,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715221</v>
+        <v>715323</v>
       </c>
       <c r="R47" t="n">
-        <v>6367967</v>
+        <v>6367903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,44 +5156,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128721653</v>
+        <v>128721631</v>
       </c>
       <c r="B48" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5205,10 +5203,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715476</v>
+        <v>715172</v>
       </c>
       <c r="R48" t="n">
-        <v>6367609</v>
+        <v>6367927</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5230,7 +5228,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5249,6 +5247,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5267,32 +5266,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128722606</v>
+        <v>128721517</v>
       </c>
       <c r="B49" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5305,7 +5304,7 @@
         <v>715323</v>
       </c>
       <c r="R49" t="n">
-        <v>6367903</v>
+        <v>6368092</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,50 +5345,51 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722580</v>
+        <v>128722544</v>
       </c>
       <c r="B50" t="n">
-        <v>86985</v>
+        <v>86764</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715209</v>
+        <v>715251</v>
       </c>
       <c r="R50" t="n">
-        <v>6367900</v>
+        <v>6367635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128721563</v>
+        <v>128722575</v>
       </c>
       <c r="B51" t="n">
-        <v>92834</v>
+        <v>105699</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,37 +5472,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715232</v>
+        <v>715498</v>
       </c>
       <c r="R51" t="n">
-        <v>6367928</v>
+        <v>6367908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5543,29 +5540,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128722544</v>
+        <v>128721563</v>
       </c>
       <c r="B52" t="n">
-        <v>86764</v>
+        <v>92834</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5573,34 +5569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715251</v>
+        <v>715232</v>
       </c>
       <c r="R52" t="n">
-        <v>6367635</v>
+        <v>6367928</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5641,50 +5640,51 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128721582</v>
+        <v>128722580</v>
       </c>
       <c r="B53" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715178</v>
+        <v>715209</v>
       </c>
       <c r="R53" t="n">
-        <v>6367640</v>
+        <v>6367900</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,22 +5744,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128721568</v>
+        <v>128721582</v>
       </c>
       <c r="B54" t="n">
-        <v>86788</v>
+        <v>86926</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715200</v>
+        <v>715178</v>
       </c>
       <c r="R54" t="n">
-        <v>6367963</v>
+        <v>6367640</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128722575</v>
+        <v>128721568</v>
       </c>
       <c r="B55" t="n">
-        <v>105699</v>
+        <v>86788</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5864,21 +5864,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>3712</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715498</v>
+        <v>715200</v>
       </c>
       <c r="R55" t="n">
-        <v>6367908</v>
+        <v>6367963</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5938,12 +5938,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128722553</v>
+        <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>86963</v>
+        <v>105686</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715261</v>
+        <v>715154</v>
       </c>
       <c r="R59" t="n">
-        <v>6368006</v>
+        <v>6367783</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6321,51 +6321,50 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128721547</v>
+        <v>128722553</v>
       </c>
       <c r="B60" t="n">
-        <v>105686</v>
+        <v>86963</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6375,10 +6374,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715154</v>
+        <v>715261</v>
       </c>
       <c r="R60" t="n">
-        <v>6367783</v>
+        <v>6368006</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,50 +6418,51 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128721644</v>
+        <v>128722557</v>
       </c>
       <c r="B61" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715497</v>
+        <v>715218</v>
       </c>
       <c r="R61" t="n">
-        <v>6367603</v>
+        <v>6367940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,18 +6516,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6631,10 +6632,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128722520</v>
+        <v>128721644</v>
       </c>
       <c r="B63" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6642,21 +6643,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6666,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715450</v>
+        <v>715497</v>
       </c>
       <c r="R63" t="n">
-        <v>6367880</v>
+        <v>6367603</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6691,7 +6692,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -6710,51 +6711,50 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128721507</v>
+        <v>128722520</v>
       </c>
       <c r="B64" t="n">
-        <v>57717</v>
+        <v>87008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>3767</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715452</v>
+        <v>715450</v>
       </c>
       <c r="R64" t="n">
-        <v>6367607</v>
+        <v>6367880</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6808,28 +6808,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128722557</v>
+        <v>128721507</v>
       </c>
       <c r="B65" t="n">
-        <v>86963</v>
+        <v>57717</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,21 +6838,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6861,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715218</v>
+        <v>715452</v>
       </c>
       <c r="R65" t="n">
-        <v>6367940</v>
+        <v>6367607</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6886,7 +6887,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -6905,29 +6906,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128722601</v>
+        <v>128721635</v>
       </c>
       <c r="B66" t="n">
-        <v>86926</v>
+        <v>86939</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715264</v>
+        <v>715194</v>
       </c>
       <c r="R66" t="n">
-        <v>6367986</v>
+        <v>6367686</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7009,22 +7009,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128721514</v>
+        <v>128722601</v>
       </c>
       <c r="B67" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715141</v>
+        <v>715264</v>
       </c>
       <c r="R67" t="n">
-        <v>6367822</v>
+        <v>6367986</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7106,19 +7106,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721651</v>
+        <v>128721579</v>
       </c>
       <c r="B68" t="n">
         <v>86926</v>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715215</v>
+        <v>715191</v>
       </c>
       <c r="R68" t="n">
-        <v>6367933</v>
+        <v>6367888</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7203,44 +7203,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721629</v>
+        <v>128721514</v>
       </c>
       <c r="B69" t="n">
-        <v>57717</v>
+        <v>86764</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715504</v>
+        <v>715141</v>
       </c>
       <c r="R69" t="n">
-        <v>6367595</v>
+        <v>6367822</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -7300,22 +7300,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721635</v>
+        <v>128721651</v>
       </c>
       <c r="B70" t="n">
-        <v>86939</v>
+        <v>86926</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,21 +7323,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715194</v>
+        <v>715215</v>
       </c>
       <c r="R70" t="n">
-        <v>6367686</v>
+        <v>6367933</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7409,32 +7409,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721579</v>
+        <v>128721629</v>
       </c>
       <c r="B71" t="n">
-        <v>86926</v>
+        <v>57717</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715191</v>
+        <v>715504</v>
       </c>
       <c r="R71" t="n">
-        <v>6367888</v>
+        <v>6367595</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7494,12 +7494,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7999,32 +7999,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128721642</v>
+        <v>128721503</v>
       </c>
       <c r="B77" t="n">
-        <v>86985</v>
+        <v>110763</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715204</v>
+        <v>715170</v>
       </c>
       <c r="R77" t="n">
-        <v>6367900</v>
+        <v>6367852</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8084,22 +8084,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128722521</v>
+        <v>128721642</v>
       </c>
       <c r="B78" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8107,21 +8107,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715207</v>
+        <v>715204</v>
       </c>
       <c r="R78" t="n">
-        <v>6367905</v>
+        <v>6367900</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8175,51 +8175,50 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128721503</v>
+        <v>128722521</v>
       </c>
       <c r="B79" t="n">
-        <v>110763</v>
+        <v>87008</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>3767</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8229,10 +8228,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715170</v>
+        <v>715207</v>
       </c>
       <c r="R79" t="n">
-        <v>6367852</v>
+        <v>6367905</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8273,18 +8272,19 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128721552</v>
+        <v>128722565</v>
       </c>
       <c r="B81" t="n">
-        <v>105699</v>
+        <v>91043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>5747</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715197</v>
+        <v>715311</v>
       </c>
       <c r="R81" t="n">
-        <v>6367683</v>
+        <v>6367855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8474,12 +8474,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8680,32 +8680,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128722607</v>
+        <v>128722549</v>
       </c>
       <c r="B84" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715545</v>
+        <v>715448</v>
       </c>
       <c r="R84" t="n">
-        <v>6367864</v>
+        <v>6367902</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8759,6 +8759,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8777,32 +8778,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128721575</v>
+        <v>128722560</v>
       </c>
       <c r="B85" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8812,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715333</v>
+        <v>715549</v>
       </c>
       <c r="R85" t="n">
-        <v>6368090</v>
+        <v>6367883</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8856,50 +8857,51 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128721581</v>
+        <v>128722547</v>
       </c>
       <c r="B86" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8909,10 +8911,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715150</v>
+        <v>715525</v>
       </c>
       <c r="R86" t="n">
-        <v>6367790</v>
+        <v>6367901</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8953,28 +8955,29 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128722565</v>
+        <v>128721502</v>
       </c>
       <c r="B87" t="n">
-        <v>91043</v>
+        <v>91028</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8982,21 +8985,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5747</v>
+        <v>256335</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9006,10 +9009,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715311</v>
+        <v>715210</v>
       </c>
       <c r="R87" t="n">
-        <v>6367855</v>
+        <v>6367925</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9050,50 +9053,51 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128722549</v>
+        <v>128721552</v>
       </c>
       <c r="B88" t="n">
-        <v>86963</v>
+        <v>105699</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6003295</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9103,10 +9107,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715448</v>
+        <v>715197</v>
       </c>
       <c r="R88" t="n">
-        <v>6367902</v>
+        <v>6367683</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9147,51 +9151,50 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128721502</v>
+        <v>128722607</v>
       </c>
       <c r="B89" t="n">
-        <v>91028</v>
+        <v>86926</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>256335</v>
+        <v>3674</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9201,10 +9204,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715210</v>
+        <v>715545</v>
       </c>
       <c r="R89" t="n">
-        <v>6367925</v>
+        <v>6367864</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9245,51 +9248,50 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128722560</v>
+        <v>128721575</v>
       </c>
       <c r="B90" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9299,10 +9301,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715549</v>
+        <v>715333</v>
       </c>
       <c r="R90" t="n">
-        <v>6367883</v>
+        <v>6368090</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9343,51 +9345,50 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128722547</v>
+        <v>128721581</v>
       </c>
       <c r="B91" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9397,10 +9398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715525</v>
+        <v>715150</v>
       </c>
       <c r="R91" t="n">
-        <v>6367901</v>
+        <v>6367790</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9441,19 +9442,18 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9563,32 +9563,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722519</v>
+        <v>128722558</v>
       </c>
       <c r="B93" t="n">
-        <v>90983</v>
+        <v>86963</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>720</v>
+        <v>6003295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715292</v>
+        <v>715177</v>
       </c>
       <c r="R93" t="n">
-        <v>6367865</v>
+        <v>6367636</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9642,6 +9642,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9660,32 +9661,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722603</v>
+        <v>128722519</v>
       </c>
       <c r="B94" t="n">
-        <v>86926</v>
+        <v>90983</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3674</v>
+        <v>720</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9695,10 +9696,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715233</v>
+        <v>715292</v>
       </c>
       <c r="R94" t="n">
-        <v>6367868</v>
+        <v>6367865</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9757,32 +9758,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722558</v>
+        <v>128722603</v>
       </c>
       <c r="B95" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9792,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715177</v>
+        <v>715233</v>
       </c>
       <c r="R95" t="n">
-        <v>6367636</v>
+        <v>6367868</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9836,7 +9837,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9855,32 +9855,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128722597</v>
+        <v>128721542</v>
       </c>
       <c r="B96" t="n">
-        <v>86916</v>
+        <v>75147</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003235</v>
+        <v>6426</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715216</v>
+        <v>715519</v>
       </c>
       <c r="R96" t="n">
-        <v>6367914</v>
+        <v>6367602</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -9934,29 +9934,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128721649</v>
+        <v>128721541</v>
       </c>
       <c r="B97" t="n">
-        <v>86926</v>
+        <v>75147</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9964,21 +9963,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9988,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715314</v>
+        <v>715250</v>
       </c>
       <c r="R97" t="n">
-        <v>6368077</v>
+        <v>6367931</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10038,22 +10037,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721541</v>
+        <v>128721649</v>
       </c>
       <c r="B98" t="n">
-        <v>75147</v>
+        <v>86926</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10061,21 +10060,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10085,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715250</v>
+        <v>715314</v>
       </c>
       <c r="R98" t="n">
-        <v>6367931</v>
+        <v>6368077</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10135,57 +10134,65 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128721542</v>
+        <v>128721508</v>
       </c>
       <c r="B99" t="n">
-        <v>75147</v>
+        <v>57717</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715519</v>
+        <v>715206</v>
       </c>
       <c r="R99" t="n">
-        <v>6367602</v>
+        <v>6367909</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10207,7 +10214,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -10244,53 +10251,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128721508</v>
+        <v>128722597</v>
       </c>
       <c r="B100" t="n">
-        <v>57717</v>
+        <v>86916</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6003235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715206</v>
+        <v>715216</v>
       </c>
       <c r="R100" t="n">
-        <v>6367909</v>
+        <v>6367914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10331,50 +10330,51 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128722598</v>
+        <v>128721583</v>
       </c>
       <c r="B101" t="n">
-        <v>86810</v>
+        <v>86926</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715487</v>
+        <v>715492</v>
       </c>
       <c r="R101" t="n">
-        <v>6367923</v>
+        <v>6367606</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -10434,44 +10434,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128722579</v>
+        <v>128721519</v>
       </c>
       <c r="B102" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715205</v>
+        <v>715287</v>
       </c>
       <c r="R102" t="n">
-        <v>6367943</v>
+        <v>6368083</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10525,50 +10525,51 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128722587</v>
+        <v>128722546</v>
       </c>
       <c r="B103" t="n">
-        <v>86986</v>
+        <v>86963</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10578,10 +10579,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715464</v>
+        <v>715298</v>
       </c>
       <c r="R103" t="n">
-        <v>6367911</v>
+        <v>6367872</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10622,6 +10623,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10640,32 +10642,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128721519</v>
+        <v>128722598</v>
       </c>
       <c r="B104" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10675,10 +10677,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715287</v>
+        <v>715487</v>
       </c>
       <c r="R104" t="n">
-        <v>6368083</v>
+        <v>6367923</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10719,51 +10721,50 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722546</v>
+        <v>128722579</v>
       </c>
       <c r="B105" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10773,10 +10774,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715298</v>
+        <v>715205</v>
       </c>
       <c r="R105" t="n">
-        <v>6367872</v>
+        <v>6367943</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10817,7 +10818,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10836,32 +10836,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128721583</v>
+        <v>128722587</v>
       </c>
       <c r="B106" t="n">
-        <v>86926</v>
+        <v>86986</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715492</v>
+        <v>715464</v>
       </c>
       <c r="R106" t="n">
-        <v>6367606</v>
+        <v>6367911</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -10921,12 +10921,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11522,10 +11522,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128722562</v>
+        <v>128721537</v>
       </c>
       <c r="B113" t="n">
-        <v>98670</v>
+        <v>75147</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11533,21 +11533,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>6426</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715452</v>
+        <v>715344</v>
       </c>
       <c r="R113" t="n">
-        <v>6367610</v>
+        <v>6368190</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -11607,12 +11607,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128721537</v>
+        <v>128722562</v>
       </c>
       <c r="B120" t="n">
-        <v>75147</v>
+        <v>98670</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6426</v>
+        <v>219874</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715344</v>
+        <v>715452</v>
       </c>
       <c r="R120" t="n">
-        <v>6368190</v>
+        <v>6367610</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12286,12 +12286,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12494,10 +12494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128721526</v>
+        <v>128721538</v>
       </c>
       <c r="B123" t="n">
-        <v>58090</v>
+        <v>75147</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715155</v>
+        <v>715352</v>
       </c>
       <c r="R123" t="n">
-        <v>6367801</v>
+        <v>6368147</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12591,10 +12591,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128722605</v>
+        <v>128721526</v>
       </c>
       <c r="B124" t="n">
-        <v>86926</v>
+        <v>58090</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3674</v>
+        <v>103015</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715315</v>
+        <v>715155</v>
       </c>
       <c r="R124" t="n">
-        <v>6367838</v>
+        <v>6367801</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,44 +12676,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721538</v>
+        <v>128721525</v>
       </c>
       <c r="B125" t="n">
-        <v>75147</v>
+        <v>86963</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715352</v>
+        <v>715141</v>
       </c>
       <c r="R125" t="n">
-        <v>6368147</v>
+        <v>6367814</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12767,6 +12767,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12785,32 +12786,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128722590</v>
+        <v>128722559</v>
       </c>
       <c r="B126" t="n">
-        <v>86986</v>
+        <v>86963</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12820,10 +12821,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715473</v>
+        <v>715256</v>
       </c>
       <c r="R126" t="n">
-        <v>6367917</v>
+        <v>6367627</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12864,6 +12865,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -12882,7 +12884,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128721525</v>
+        <v>128722551</v>
       </c>
       <c r="B127" t="n">
         <v>86963</v>
@@ -12917,10 +12919,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715141</v>
+        <v>715313</v>
       </c>
       <c r="R127" t="n">
-        <v>6367814</v>
+        <v>6368003</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12968,19 +12970,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722559</v>
+        <v>128722561</v>
       </c>
       <c r="B128" t="n">
         <v>86963</v>
@@ -13015,10 +13017,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715256</v>
+        <v>715545</v>
       </c>
       <c r="R128" t="n">
-        <v>6367627</v>
+        <v>6367898</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13078,32 +13080,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128722551</v>
+        <v>128722605</v>
       </c>
       <c r="B129" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13113,10 +13115,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715313</v>
+        <v>715315</v>
       </c>
       <c r="R129" t="n">
-        <v>6368003</v>
+        <v>6367838</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13157,7 +13159,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13176,32 +13177,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722561</v>
+        <v>128722590</v>
       </c>
       <c r="B130" t="n">
-        <v>86963</v>
+        <v>86986</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13211,10 +13212,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715545</v>
+        <v>715473</v>
       </c>
       <c r="R130" t="n">
-        <v>6367898</v>
+        <v>6367917</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13255,7 +13256,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128722536</v>
       </c>
       <c r="B2" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128721539</v>
+        <v>128721501</v>
       </c>
       <c r="B3" t="n">
-        <v>75147</v>
+        <v>88703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>4379</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715289</v>
+        <v>715178</v>
       </c>
       <c r="R3" t="n">
-        <v>6368047</v>
+        <v>6367628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128721501</v>
+        <v>128721539</v>
       </c>
       <c r="B4" t="n">
-        <v>88698</v>
+        <v>75150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4379</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715178</v>
+        <v>715289</v>
       </c>
       <c r="R4" t="n">
-        <v>6367628</v>
+        <v>6368047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,7 +970,7 @@
         <v>128722539</v>
       </c>
       <c r="B5" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128722600</v>
       </c>
       <c r="B6" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128721652</v>
       </c>
       <c r="B7" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128721516</v>
       </c>
       <c r="B8" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128722554</v>
       </c>
       <c r="B9" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,48 +1454,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128722583</v>
+        <v>128722578</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>86990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715227</v>
+        <v>715461</v>
       </c>
       <c r="R10" t="n">
-        <v>6367937</v>
+        <v>6367905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,7 +1533,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1555,32 +1551,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128722578</v>
+        <v>128722552</v>
       </c>
       <c r="B11" t="n">
-        <v>86985</v>
+        <v>86968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715461</v>
+        <v>715271</v>
       </c>
       <c r="R11" t="n">
-        <v>6367905</v>
+        <v>6367998</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1630,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1652,32 +1649,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128722552</v>
+        <v>128722595</v>
       </c>
       <c r="B12" t="n">
-        <v>86963</v>
+        <v>86921</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>6003235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1687,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715271</v>
+        <v>715468</v>
       </c>
       <c r="R12" t="n">
-        <v>6367998</v>
+        <v>6367935</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,45 +1747,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128722595</v>
+        <v>128722583</v>
       </c>
       <c r="B13" t="n">
-        <v>86916</v>
+        <v>92839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003235</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715468</v>
+        <v>715227</v>
       </c>
       <c r="R13" t="n">
-        <v>6367935</v>
+        <v>6367937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B14" t="n">
-        <v>86950</v>
+        <v>105693</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R14" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B15" t="n">
-        <v>105686</v>
+        <v>86955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R15" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,60 +2030,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128722582</v>
+        <v>128721560</v>
       </c>
       <c r="B16" t="n">
-        <v>92834</v>
+        <v>86990</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715492</v>
+        <v>715503</v>
       </c>
       <c r="R16" t="n">
-        <v>6367899</v>
+        <v>6367589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2105,7 +2102,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2124,51 +2121,50 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128722534</v>
+        <v>128721559</v>
       </c>
       <c r="B17" t="n">
-        <v>98614</v>
+        <v>86990</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715228</v>
+        <v>715505</v>
       </c>
       <c r="R17" t="n">
-        <v>6367909</v>
+        <v>6367598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2203,7 +2199,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2228,22 +2224,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128721560</v>
+        <v>128721643</v>
       </c>
       <c r="B18" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2275,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715503</v>
+        <v>715270</v>
       </c>
       <c r="R18" t="n">
-        <v>6367589</v>
+        <v>6367607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2300,7 +2296,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2325,22 +2321,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128721559</v>
+        <v>128721558</v>
       </c>
       <c r="B19" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2372,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715505</v>
+        <v>715424</v>
       </c>
       <c r="R19" t="n">
-        <v>6367598</v>
+        <v>6367651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128721643</v>
+        <v>128722540</v>
       </c>
       <c r="B20" t="n">
-        <v>86985</v>
+        <v>86769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715270</v>
+        <v>715194</v>
       </c>
       <c r="R20" t="n">
-        <v>6367607</v>
+        <v>6367837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2513,28 +2509,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128721558</v>
+        <v>128721499</v>
       </c>
       <c r="B21" t="n">
-        <v>86985</v>
+        <v>87013</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715424</v>
+        <v>715394</v>
       </c>
       <c r="R21" t="n">
-        <v>6367651</v>
+        <v>6368208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2591,7 +2588,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2628,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128722540</v>
+        <v>128721578</v>
       </c>
       <c r="B22" t="n">
-        <v>86764</v>
+        <v>86931</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2639,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2663,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715194</v>
+        <v>715215</v>
       </c>
       <c r="R22" t="n">
-        <v>6367837</v>
+        <v>6367918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2707,51 +2704,50 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128721499</v>
+        <v>128722534</v>
       </c>
       <c r="B23" t="n">
-        <v>87008</v>
+        <v>98621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3767</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715394</v>
+        <v>715228</v>
       </c>
       <c r="R23" t="n">
-        <v>6368208</v>
+        <v>6367909</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2811,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128721578</v>
+        <v>128722582</v>
       </c>
       <c r="B24" t="n">
-        <v>86926</v>
+        <v>92839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,34 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>715215</v>
+        <v>715492</v>
       </c>
       <c r="R24" t="n">
-        <v>6367918</v>
+        <v>6367899</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2902,50 +2901,51 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128721543</v>
+        <v>128722567</v>
       </c>
       <c r="B25" t="n">
-        <v>75147</v>
+        <v>87013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715500</v>
+        <v>715339</v>
       </c>
       <c r="R25" t="n">
-        <v>6367588</v>
+        <v>6367894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -2993,56 +2993,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128721505</v>
+        <v>128722602</v>
       </c>
       <c r="B26" t="n">
-        <v>86810</v>
+        <v>86931</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715150</v>
+        <v>715200</v>
       </c>
       <c r="R26" t="n">
-        <v>6367765</v>
+        <v>6367935</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,44 +3108,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128722567</v>
+        <v>128721543</v>
       </c>
       <c r="B27" t="n">
-        <v>87008</v>
+        <v>75150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715339</v>
+        <v>715500</v>
       </c>
       <c r="R27" t="n">
-        <v>6367894</v>
+        <v>6367588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3174,7 +3180,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3187,62 +3193,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128722602</v>
+        <v>128721505</v>
       </c>
       <c r="B28" t="n">
-        <v>86926</v>
+        <v>86815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715200</v>
+        <v>715150</v>
       </c>
       <c r="R28" t="n">
-        <v>6367935</v>
+        <v>6367765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3302,44 +3302,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128722532</v>
+        <v>128721628</v>
       </c>
       <c r="B29" t="n">
-        <v>92443</v>
+        <v>87013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715460</v>
+        <v>715222</v>
       </c>
       <c r="R29" t="n">
-        <v>6367601</v>
+        <v>6367915</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3393,28 +3393,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128721540</v>
+        <v>128722532</v>
       </c>
       <c r="B30" t="n">
-        <v>75147</v>
+        <v>92448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3422,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715278</v>
+        <v>715460</v>
       </c>
       <c r="R30" t="n">
-        <v>6368028</v>
+        <v>6367601</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3471,7 +3472,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3496,44 +3497,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128721628</v>
+        <v>128721540</v>
       </c>
       <c r="B31" t="n">
-        <v>87008</v>
+        <v>75150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715222</v>
+        <v>715278</v>
       </c>
       <c r="R31" t="n">
-        <v>6367915</v>
+        <v>6368028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3587,19 +3588,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
         <v>128722518</v>
       </c>
       <c r="B32" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,48 +3707,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128722517</v>
+        <v>128721511</v>
       </c>
       <c r="B33" t="n">
-        <v>86717</v>
+        <v>91286</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>249278</v>
+        <v>3215</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715318</v>
+        <v>715180</v>
       </c>
       <c r="R33" t="n">
-        <v>6367974</v>
+        <v>6367626</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3789,51 +3786,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721511</v>
+        <v>128722566</v>
       </c>
       <c r="B34" t="n">
-        <v>91281</v>
+        <v>91048</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>5747</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3843,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715180</v>
+        <v>715288</v>
       </c>
       <c r="R34" t="n">
-        <v>6367626</v>
+        <v>6367866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,44 +3889,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128722566</v>
+        <v>128722556</v>
       </c>
       <c r="B35" t="n">
-        <v>91043</v>
+        <v>86968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3940,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715288</v>
+        <v>715180</v>
       </c>
       <c r="R35" t="n">
-        <v>6367866</v>
+        <v>6368021</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3984,6 +3980,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4005,7 +4002,7 @@
         <v>128722577</v>
       </c>
       <c r="B36" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4102,7 +4099,7 @@
         <v>128722608</v>
       </c>
       <c r="B37" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4199,7 +4196,7 @@
         <v>128722564</v>
       </c>
       <c r="B38" t="n">
-        <v>86950</v>
+        <v>86955</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4296,7 +4293,7 @@
         <v>128721513</v>
       </c>
       <c r="B39" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4393,7 +4390,7 @@
         <v>128722542</v>
       </c>
       <c r="B40" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4487,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128722556</v>
+        <v>128722517</v>
       </c>
       <c r="B41" t="n">
-        <v>86963</v>
+        <v>86722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,34 +4495,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715180</v>
+        <v>715318</v>
       </c>
       <c r="R41" t="n">
-        <v>6368021</v>
+        <v>6367974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>128721557</v>
       </c>
       <c r="B42" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>128721497</v>
       </c>
       <c r="B43" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>128722543</v>
       </c>
       <c r="B44" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>128721577</v>
       </c>
       <c r="B45" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>128721653</v>
       </c>
       <c r="B46" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>128722606</v>
       </c>
       <c r="B47" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128721631</v>
       </c>
       <c r="B48" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>128721517</v>
       </c>
       <c r="B49" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5364,32 +5364,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128722544</v>
+        <v>128722580</v>
       </c>
       <c r="B50" t="n">
-        <v>86764</v>
+        <v>86990</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715251</v>
+        <v>715209</v>
       </c>
       <c r="R50" t="n">
-        <v>6367635</v>
+        <v>6367900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128722575</v>
+        <v>128721563</v>
       </c>
       <c r="B51" t="n">
-        <v>105699</v>
+        <v>92839</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5472,34 +5472,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715498</v>
+        <v>715232</v>
       </c>
       <c r="R51" t="n">
-        <v>6367908</v>
+        <v>6367928</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5540,28 +5543,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128721563</v>
+        <v>128722575</v>
       </c>
       <c r="B52" t="n">
-        <v>92834</v>
+        <v>105706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5569,37 +5573,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715232</v>
+        <v>715498</v>
       </c>
       <c r="R52" t="n">
-        <v>6367928</v>
+        <v>6367908</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5640,51 +5641,50 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128722580</v>
+        <v>128722544</v>
       </c>
       <c r="B53" t="n">
-        <v>86985</v>
+        <v>86769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715209</v>
+        <v>715251</v>
       </c>
       <c r="R53" t="n">
-        <v>6367900</v>
+        <v>6367635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5759,7 +5759,7 @@
         <v>128721582</v>
       </c>
       <c r="B54" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>128721568</v>
       </c>
       <c r="B55" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>128721496</v>
       </c>
       <c r="B56" t="n">
-        <v>86906</v>
+        <v>86911</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>128722604</v>
       </c>
       <c r="B57" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>128721580</v>
       </c>
       <c r="B58" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>128721547</v>
       </c>
       <c r="B59" t="n">
-        <v>105686</v>
+        <v>105693</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>128722553</v>
       </c>
       <c r="B60" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6437,32 +6437,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128722557</v>
+        <v>128721644</v>
       </c>
       <c r="B61" t="n">
-        <v>86963</v>
+        <v>86990</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715218</v>
+        <v>715497</v>
       </c>
       <c r="R61" t="n">
-        <v>6367940</v>
+        <v>6367603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,19 +6516,18 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6538,7 +6537,7 @@
         <v>128721567</v>
       </c>
       <c r="B62" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6632,32 +6631,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128721644</v>
+        <v>128722557</v>
       </c>
       <c r="B63" t="n">
-        <v>86985</v>
+        <v>86968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6667,10 +6666,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715497</v>
+        <v>715218</v>
       </c>
       <c r="R63" t="n">
-        <v>6367603</v>
+        <v>6367940</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6692,7 +6691,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -6711,18 +6710,19 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
         <v>128722520</v>
       </c>
       <c r="B64" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>128721507</v>
       </c>
       <c r="B65" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6924,32 +6924,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128721635</v>
+        <v>128721629</v>
       </c>
       <c r="B66" t="n">
-        <v>86939</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1988</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715194</v>
+        <v>715504</v>
       </c>
       <c r="R66" t="n">
-        <v>6367686</v>
+        <v>6367595</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -7021,45 +7021,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128722601</v>
+        <v>128722516</v>
       </c>
       <c r="B67" t="n">
-        <v>86926</v>
+        <v>86722</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715264</v>
+        <v>715492</v>
       </c>
       <c r="R67" t="n">
-        <v>6367986</v>
+        <v>6367910</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7100,6 +7103,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7118,32 +7122,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128721579</v>
+        <v>128721522</v>
       </c>
       <c r="B68" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7157,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715191</v>
+        <v>715221</v>
       </c>
       <c r="R68" t="n">
-        <v>6367888</v>
+        <v>6367902</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7197,6 +7201,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7215,32 +7220,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128721514</v>
+        <v>128722550</v>
       </c>
       <c r="B69" t="n">
-        <v>86764</v>
+        <v>86968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7255,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715141</v>
+        <v>715321</v>
       </c>
       <c r="R69" t="n">
-        <v>6367822</v>
+        <v>6367984</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7294,50 +7299,51 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128721651</v>
+        <v>128722596</v>
       </c>
       <c r="B70" t="n">
-        <v>86926</v>
+        <v>86921</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>6003235</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bananspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius nanceiensis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7353,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715215</v>
+        <v>715196</v>
       </c>
       <c r="R70" t="n">
-        <v>6367933</v>
+        <v>6367906</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7391,28 +7397,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128721629</v>
+        <v>128721523</v>
       </c>
       <c r="B71" t="n">
-        <v>57717</v>
+        <v>86968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715504</v>
+        <v>715146</v>
       </c>
       <c r="R71" t="n">
-        <v>6367595</v>
+        <v>6367798</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7469,7 +7476,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -7488,66 +7495,64 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128722516</v>
+        <v>128721635</v>
       </c>
       <c r="B72" t="n">
-        <v>86717</v>
+        <v>86944</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715492</v>
+        <v>715194</v>
       </c>
       <c r="R72" t="n">
-        <v>6367910</v>
+        <v>6367686</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7588,51 +7593,50 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128721522</v>
+        <v>128722601</v>
       </c>
       <c r="B73" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7642,10 +7646,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715221</v>
+        <v>715264</v>
       </c>
       <c r="R73" t="n">
-        <v>6367902</v>
+        <v>6367986</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7686,51 +7690,50 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128722550</v>
+        <v>128721579</v>
       </c>
       <c r="B74" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7740,10 +7743,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715321</v>
+        <v>715191</v>
       </c>
       <c r="R74" t="n">
-        <v>6367984</v>
+        <v>6367888</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7784,51 +7787,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128722596</v>
+        <v>128721514</v>
       </c>
       <c r="B75" t="n">
-        <v>86916</v>
+        <v>86769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003235</v>
+        <v>3762</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bananspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius nanceiensis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7838,10 +7840,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715196</v>
+        <v>715141</v>
       </c>
       <c r="R75" t="n">
-        <v>6367906</v>
+        <v>6367822</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7882,51 +7884,50 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128721523</v>
+        <v>128721651</v>
       </c>
       <c r="B76" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7936,10 +7937,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715146</v>
+        <v>715215</v>
       </c>
       <c r="R76" t="n">
-        <v>6367798</v>
+        <v>6367933</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7980,19 +7981,18 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8002,7 +8002,7 @@
         <v>128721503</v>
       </c>
       <c r="B77" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>128721642</v>
       </c>
       <c r="B78" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128722521</v>
       </c>
       <c r="B79" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>128721521</v>
       </c>
       <c r="B80" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128722565</v>
+        <v>128721575</v>
       </c>
       <c r="B81" t="n">
-        <v>91043</v>
+        <v>86931</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715311</v>
+        <v>715333</v>
       </c>
       <c r="R81" t="n">
-        <v>6367855</v>
+        <v>6368090</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8474,44 +8474,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128722589</v>
+        <v>128721581</v>
       </c>
       <c r="B82" t="n">
-        <v>86810</v>
+        <v>86931</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715223</v>
+        <v>715150</v>
       </c>
       <c r="R82" t="n">
-        <v>6367944</v>
+        <v>6367790</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8571,44 +8571,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128722581</v>
+        <v>128721552</v>
       </c>
       <c r="B83" t="n">
-        <v>86985</v>
+        <v>105706</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>449</v>
+        <v>221144</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715210</v>
+        <v>715197</v>
       </c>
       <c r="R83" t="n">
-        <v>6367925</v>
+        <v>6367683</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8668,12 +8668,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8683,7 +8683,7 @@
         <v>128722549</v>
       </c>
       <c r="B84" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>128722560</v>
       </c>
       <c r="B85" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>128722547</v>
       </c>
       <c r="B86" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8974,10 +8974,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128721502</v>
+        <v>128722589</v>
       </c>
       <c r="B87" t="n">
-        <v>91028</v>
+        <v>86815</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8985,21 +8985,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>256335</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715210</v>
+        <v>715223</v>
       </c>
       <c r="R87" t="n">
-        <v>6367925</v>
+        <v>6367944</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9053,51 +9053,50 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128721552</v>
+        <v>128722581</v>
       </c>
       <c r="B88" t="n">
-        <v>105699</v>
+        <v>86990</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9107,10 +9106,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715197</v>
+        <v>715210</v>
       </c>
       <c r="R88" t="n">
-        <v>6367683</v>
+        <v>6367925</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9157,12 +9156,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9172,7 +9171,7 @@
         <v>128722607</v>
       </c>
       <c r="B89" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9266,32 +9265,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128721575</v>
+        <v>128722565</v>
       </c>
       <c r="B90" t="n">
-        <v>86926</v>
+        <v>91048</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9301,10 +9300,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715333</v>
+        <v>715311</v>
       </c>
       <c r="R90" t="n">
-        <v>6368090</v>
+        <v>6367855</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9351,44 +9350,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128721581</v>
+        <v>128721502</v>
       </c>
       <c r="B91" t="n">
-        <v>86926</v>
+        <v>91033</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3674</v>
+        <v>256335</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9398,10 +9397,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715150</v>
+        <v>715210</v>
       </c>
       <c r="R91" t="n">
-        <v>6367790</v>
+        <v>6367925</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9442,6 +9441,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9460,32 +9460,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128721647</v>
+        <v>128722519</v>
       </c>
       <c r="B92" t="n">
-        <v>86717</v>
+        <v>90988</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>249278</v>
+        <v>720</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715216</v>
+        <v>715292</v>
       </c>
       <c r="R92" t="n">
-        <v>6367898</v>
+        <v>6367865</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,62 +9533,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Det fanns små skott av asp i närheten.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128722558</v>
+        <v>128722603</v>
       </c>
       <c r="B93" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9598,10 +9592,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715177</v>
+        <v>715233</v>
       </c>
       <c r="R93" t="n">
-        <v>6367636</v>
+        <v>6367868</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9642,7 +9636,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9661,32 +9654,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128722519</v>
+        <v>128721647</v>
       </c>
       <c r="B94" t="n">
-        <v>90983</v>
+        <v>86722</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>720</v>
+        <v>249278</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9696,10 +9689,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715292</v>
+        <v>715216</v>
       </c>
       <c r="R94" t="n">
-        <v>6367865</v>
+        <v>6367898</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9734,56 +9727,62 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Det fanns små skott av asp i närheten.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128722603</v>
+        <v>128722558</v>
       </c>
       <c r="B95" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9792,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715233</v>
+        <v>715177</v>
       </c>
       <c r="R95" t="n">
-        <v>6367868</v>
+        <v>6367636</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9837,6 +9836,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128721542</v>
+        <v>128721649</v>
       </c>
       <c r="B96" t="n">
-        <v>75147</v>
+        <v>86931</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9866,21 +9866,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715519</v>
+        <v>715314</v>
       </c>
       <c r="R96" t="n">
-        <v>6367602</v>
+        <v>6368077</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -9940,12 +9940,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -9955,7 +9955,7 @@
         <v>128721541</v>
       </c>
       <c r="B97" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10049,10 +10049,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128721649</v>
+        <v>128721542</v>
       </c>
       <c r="B98" t="n">
-        <v>86926</v>
+        <v>75150</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10060,21 +10060,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715314</v>
+        <v>715519</v>
       </c>
       <c r="R98" t="n">
-        <v>6368077</v>
+        <v>6367602</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -10134,12 +10134,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10149,7 +10149,7 @@
         <v>128721508</v>
       </c>
       <c r="B99" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>128722597</v>
       </c>
       <c r="B100" t="n">
-        <v>86916</v>
+        <v>86921</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10349,32 +10349,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128721583</v>
+        <v>128722598</v>
       </c>
       <c r="B101" t="n">
-        <v>86926</v>
+        <v>86815</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715492</v>
+        <v>715487</v>
       </c>
       <c r="R101" t="n">
-        <v>6367606</v>
+        <v>6367923</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -10434,44 +10434,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128721519</v>
+        <v>128722579</v>
       </c>
       <c r="B102" t="n">
-        <v>86963</v>
+        <v>86990</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715287</v>
+        <v>715205</v>
       </c>
       <c r="R102" t="n">
-        <v>6368083</v>
+        <v>6367943</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10525,51 +10525,50 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128722546</v>
+        <v>128721583</v>
       </c>
       <c r="B103" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10579,10 +10578,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715298</v>
+        <v>715492</v>
       </c>
       <c r="R103" t="n">
-        <v>6367872</v>
+        <v>6367606</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10604,7 +10603,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -10623,51 +10622,50 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128722598</v>
+        <v>128722587</v>
       </c>
       <c r="B104" t="n">
-        <v>86810</v>
+        <v>86991</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10677,10 +10675,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715487</v>
+        <v>715464</v>
       </c>
       <c r="R104" t="n">
-        <v>6367923</v>
+        <v>6367911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10739,32 +10737,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128722579</v>
+        <v>128721519</v>
       </c>
       <c r="B105" t="n">
-        <v>86985</v>
+        <v>86968</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10774,10 +10772,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715205</v>
+        <v>715287</v>
       </c>
       <c r="R105" t="n">
-        <v>6367943</v>
+        <v>6368083</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10818,50 +10816,51 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128722587</v>
+        <v>128722546</v>
       </c>
       <c r="B106" t="n">
-        <v>86986</v>
+        <v>86968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10871,10 +10870,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715464</v>
+        <v>715298</v>
       </c>
       <c r="R106" t="n">
-        <v>6367911</v>
+        <v>6367872</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10915,6 +10914,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>128722599</v>
       </c>
       <c r="B107" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>128722522</v>
       </c>
       <c r="B108" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>128722585</v>
       </c>
       <c r="B109" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>128722545</v>
       </c>
       <c r="B110" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>128721572</v>
       </c>
       <c r="B111" t="n">
-        <v>86916</v>
+        <v>86921</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>128721520</v>
       </c>
       <c r="B112" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11522,32 +11522,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128721537</v>
+        <v>128722548</v>
       </c>
       <c r="B113" t="n">
-        <v>75147</v>
+        <v>86968</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715344</v>
+        <v>715513</v>
       </c>
       <c r="R113" t="n">
-        <v>6368190</v>
+        <v>6367892</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11601,50 +11601,51 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128721500</v>
+        <v>128721524</v>
       </c>
       <c r="B114" t="n">
-        <v>87008</v>
+        <v>86968</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11654,10 +11655,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715318</v>
+        <v>715222</v>
       </c>
       <c r="R114" t="n">
-        <v>6368090</v>
+        <v>6367894</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11698,6 +11699,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -11716,32 +11718,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128722523</v>
+        <v>128721500</v>
       </c>
       <c r="B115" t="n">
-        <v>86764</v>
+        <v>87013</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11751,10 +11753,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715327</v>
+        <v>715318</v>
       </c>
       <c r="R115" t="n">
-        <v>6367899</v>
+        <v>6368090</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11801,22 +11803,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128721650</v>
+        <v>128722523</v>
       </c>
       <c r="B116" t="n">
-        <v>86926</v>
+        <v>86769</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11824,21 +11826,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11848,10 +11850,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715161</v>
+        <v>715327</v>
       </c>
       <c r="R116" t="n">
-        <v>6368017</v>
+        <v>6367899</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11898,22 +11900,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128722535</v>
+        <v>128721650</v>
       </c>
       <c r="B117" t="n">
-        <v>86788</v>
+        <v>86931</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11921,21 +11923,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11945,10 +11947,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715500</v>
+        <v>715161</v>
       </c>
       <c r="R117" t="n">
-        <v>6367907</v>
+        <v>6368017</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11995,22 +11997,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128722541</v>
+        <v>128722535</v>
       </c>
       <c r="B118" t="n">
-        <v>86764</v>
+        <v>86793</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12018,21 +12020,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12042,10 +12044,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715501</v>
+        <v>715500</v>
       </c>
       <c r="R118" t="n">
-        <v>6367911</v>
+        <v>6367907</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12104,10 +12106,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128722586</v>
+        <v>128722541</v>
       </c>
       <c r="B119" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12139,10 +12141,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715507</v>
+        <v>715501</v>
       </c>
       <c r="R119" t="n">
-        <v>6367904</v>
+        <v>6367911</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12201,10 +12203,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128722562</v>
+        <v>128722586</v>
       </c>
       <c r="B120" t="n">
-        <v>98670</v>
+        <v>86769</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12212,21 +12214,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219874</v>
+        <v>3762</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12236,10 +12238,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715452</v>
+        <v>715507</v>
       </c>
       <c r="R120" t="n">
-        <v>6367610</v>
+        <v>6367904</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12261,7 +12263,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -12298,32 +12300,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128722548</v>
+        <v>128722562</v>
       </c>
       <c r="B121" t="n">
-        <v>86963</v>
+        <v>98677</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12333,10 +12335,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715513</v>
+        <v>715452</v>
       </c>
       <c r="R121" t="n">
-        <v>6367892</v>
+        <v>6367610</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12358,7 +12360,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -12377,7 +12379,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12396,32 +12397,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128721524</v>
+        <v>128721537</v>
       </c>
       <c r="B122" t="n">
-        <v>86963</v>
+        <v>75150</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12431,10 +12432,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715222</v>
+        <v>715344</v>
       </c>
       <c r="R122" t="n">
-        <v>6367894</v>
+        <v>6368190</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12475,7 +12476,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12494,10 +12494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128721538</v>
+        <v>128721526</v>
       </c>
       <c r="B123" t="n">
-        <v>75147</v>
+        <v>58093</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715352</v>
+        <v>715155</v>
       </c>
       <c r="R123" t="n">
-        <v>6368147</v>
+        <v>6367801</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12591,32 +12591,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128721526</v>
+        <v>128722590</v>
       </c>
       <c r="B124" t="n">
-        <v>58090</v>
+        <v>86991</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103015</v>
+        <v>248947</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12626,10 +12626,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715155</v>
+        <v>715473</v>
       </c>
       <c r="R124" t="n">
-        <v>6367801</v>
+        <v>6367917</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12676,44 +12676,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128721525</v>
+        <v>128722605</v>
       </c>
       <c r="B125" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715141</v>
+        <v>715315</v>
       </c>
       <c r="R125" t="n">
-        <v>6367814</v>
+        <v>6367838</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12767,51 +12767,50 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128722559</v>
+        <v>128721538</v>
       </c>
       <c r="B126" t="n">
-        <v>86963</v>
+        <v>75150</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12821,10 +12820,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715256</v>
+        <v>715352</v>
       </c>
       <c r="R126" t="n">
-        <v>6367627</v>
+        <v>6368147</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12865,29 +12864,28 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128722551</v>
+        <v>128721525</v>
       </c>
       <c r="B127" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12919,10 +12917,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715313</v>
+        <v>715141</v>
       </c>
       <c r="R127" t="n">
-        <v>6368003</v>
+        <v>6367814</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12970,22 +12968,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128722561</v>
+        <v>128722559</v>
       </c>
       <c r="B128" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13017,10 +13015,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715545</v>
+        <v>715256</v>
       </c>
       <c r="R128" t="n">
-        <v>6367898</v>
+        <v>6367627</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13080,32 +13078,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128722605</v>
+        <v>128722551</v>
       </c>
       <c r="B129" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13115,10 +13113,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>715315</v>
+        <v>715313</v>
       </c>
       <c r="R129" t="n">
-        <v>6367838</v>
+        <v>6368003</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13159,6 +13157,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13177,32 +13176,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128722590</v>
+        <v>128722561</v>
       </c>
       <c r="B130" t="n">
-        <v>86986</v>
+        <v>86968</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13212,10 +13211,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>715473</v>
+        <v>715545</v>
       </c>
       <c r="R130" t="n">
-        <v>6367917</v>
+        <v>6367898</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13256,6 +13255,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>128722530</v>
       </c>
       <c r="B131" t="n">
-        <v>86997</v>
+        <v>87002</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>128746575</v>
       </c>
       <c r="B132" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 15075-2025 artfynd.xlsx
+++ b/artfynd/A 15075-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128721539</v>
+        <v>128722539</v>
       </c>
       <c r="B2" t="n">
-        <v>75155</v>
+        <v>86776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715289</v>
+        <v>715181</v>
       </c>
       <c r="R2" t="n">
-        <v>6368047</v>
+        <v>6367653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128721501</v>
+        <v>128722600</v>
       </c>
       <c r="B3" t="n">
-        <v>88710</v>
+        <v>86938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4379</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715178</v>
+        <v>715327</v>
       </c>
       <c r="R3" t="n">
-        <v>6367628</v>
+        <v>6367976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128722539</v>
+        <v>128722536</v>
       </c>
       <c r="B4" t="n">
-        <v>86776</v>
+        <v>91293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715181</v>
+        <v>715340</v>
       </c>
       <c r="R4" t="n">
-        <v>6367653</v>
+        <v>6367945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,7 +967,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128722600</v>
+        <v>128721652</v>
       </c>
       <c r="B5" t="n">
         <v>86938</v>
@@ -1001,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715327</v>
+        <v>715207</v>
       </c>
       <c r="R5" t="n">
-        <v>6367976</v>
+        <v>6367759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128722536</v>
+        <v>128721539</v>
       </c>
       <c r="B6" t="n">
-        <v>91293</v>
+        <v>75155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715340</v>
+        <v>715289</v>
       </c>
       <c r="R6" t="n">
-        <v>6367945</v>
+        <v>6368047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,29 +1143,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128721652</v>
+        <v>128721501</v>
       </c>
       <c r="B7" t="n">
-        <v>86938</v>
+        <v>88710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>4379</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715207</v>
+        <v>715178</v>
       </c>
       <c r="R7" t="n">
-        <v>6367759</v>
+        <v>6367628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,12 +1246,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128722563</v>
+        <v>128721548</v>
       </c>
       <c r="B14" t="n">
-        <v>86962</v>
+        <v>105701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3599</v>
+        <v>224098</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715437</v>
+        <v>715290</v>
       </c>
       <c r="R14" t="n">
-        <v>6367894</v>
+        <v>6367601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,44 +1933,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128721548</v>
+        <v>128722563</v>
       </c>
       <c r="B15" t="n">
-        <v>105701</v>
+        <v>86962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224098</v>
+        <v>3599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715290</v>
+        <v>715437</v>
       </c>
       <c r="R15" t="n">
-        <v>6367601</v>
+        <v>6367894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,12 +2030,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128722567</v>
+        <v>128721505</v>
       </c>
       <c r="B25" t="n">
-        <v>87020</v>
+        <v>86822</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715339</v>
+        <v>715150</v>
       </c>
       <c r="R25" t="n">
-        <v>6367894</v>
+        <v>6367765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2993,62 +2993,56 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128722602</v>
+        <v>128722567</v>
       </c>
       <c r="B26" t="n">
-        <v>86938</v>
+        <v>87020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715200</v>
+        <v>715339</v>
       </c>
       <c r="R26" t="n">
-        <v>6367935</v>
+        <v>6367894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3096,12 +3090,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128721543</v>
+        <v>128722602</v>
       </c>
       <c r="B27" t="n">
-        <v>75155</v>
+        <v>86938</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715500</v>
+        <v>715200</v>
       </c>
       <c r="R27" t="n">
-        <v>6367588</v>
+        <v>6367935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3205,44 +3205,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128721505</v>
+        <v>128721543</v>
       </c>
       <c r="B28" t="n">
-        <v>86822</v>
+        <v>75155</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>424</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715150</v>
+        <v>715500</v>
       </c>
       <c r="R28" t="n">
-        <v>6367765</v>
+        <v>6367588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4585,10 +4585,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721557</v>
+        <v>128721497</v>
       </c>
       <c r="B42" t="n">
-        <v>86997</v>
+        <v>87020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4596,21 +4596,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715213</v>
+        <v>715243</v>
       </c>
       <c r="R42" t="n">
-        <v>6367921</v>
+        <v>6367615</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4664,6 +4664,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4682,32 +4683,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721497</v>
+        <v>128722543</v>
       </c>
       <c r="B43" t="n">
-        <v>87020</v>
+        <v>86776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4717,10 +4718,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715243</v>
+        <v>715253</v>
       </c>
       <c r="R43" t="n">
-        <v>6367615</v>
+        <v>6367647</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4761,29 +4762,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128722543</v>
+        <v>128721577</v>
       </c>
       <c r="B44" t="n">
-        <v>86776</v>
+        <v>86938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715253</v>
+        <v>715221</v>
       </c>
       <c r="R44" t="n">
-        <v>6367647</v>
+        <v>6367967</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4865,19 +4865,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721577</v>
+        <v>128721653</v>
       </c>
       <c r="B45" t="n">
         <v>86938</v>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715221</v>
+        <v>715476</v>
       </c>
       <c r="R45" t="n">
-        <v>6367967</v>
+        <v>6367609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Buttle</t>
+          <t>Ala</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4962,19 +4962,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721653</v>
+        <v>128722606</v>
       </c>
       <c r="B46" t="n">
         <v>86938</v>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715476</v>
+        <v>715323</v>
       </c>
       <c r="R46" t="n">
-        <v>6367609</v>
+        <v>6367903</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5059,44 +5059,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128722606</v>
+        <v>128721557</v>
       </c>
       <c r="B47" t="n">
-        <v>86938</v>
+        <v>86997</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715323</v>
+        <v>715213</v>
       </c>
       <c r="R47" t="n">
-        <v>6367903</v>
+        <v>6367921</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,12 +5156,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128721644</v>
+        <v>128722520</v>
       </c>
       <c r="B61" t="n">
-        <v>86997</v>
+        <v>87020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6448,21 +6448,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715497</v>
+        <v>715450</v>
       </c>
       <c r="R61" t="n">
-        <v>6367603</v>
+        <v>6367880</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6516,50 +6516,51 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128721567</v>
+        <v>128722557</v>
       </c>
       <c r="B62" t="n">
-        <v>96247</v>
+        <v>86975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2180</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6569,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715422</v>
+        <v>715218</v>
       </c>
       <c r="R62" t="n">
-        <v>6367626</v>
+        <v>6367940</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6594,7 +6595,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Ala</t>
+          <t>Buttle</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -6613,28 +6614,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+         